--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC48257C-515C-49A4-ADCC-108F7A6BB811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6234B3-4C8B-40E1-92EB-A9658AB8A675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo &amp; Mov." sheetId="12" r:id="rId1"/>
-    <sheet name="Receitas - Mapa" sheetId="8" state="hidden" r:id="rId2"/>
-    <sheet name="Despesas - Mapa" sheetId="1" state="hidden" r:id="rId3"/>
-    <sheet name="Gráfico - Anual" sheetId="13" r:id="rId4"/>
+    <sheet name="Receita Líquida" sheetId="8" state="hidden" r:id="rId2"/>
+    <sheet name="Despesas Gerais" sheetId="1" state="hidden" r:id="rId3"/>
+    <sheet name="Gráfico Anual" sheetId="13" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Ativos">'Saldo &amp; Mov.'!$B$6:$B$8</definedName>
-    <definedName name="Categorias">'Despesas - Mapa'!$C$7:$C$15</definedName>
-    <definedName name="Dash">'Gráfico - Anual'!$A$1:$P$26</definedName>
-    <definedName name="Despesas">'Despesas - Mapa'!$C$7:$C$15</definedName>
-    <definedName name="Investimentos">'Receitas - Mapa'!$A$16:$A$17</definedName>
-    <definedName name="Perdas">'Receitas - Mapa'!$A$9:$A$12</definedName>
-    <definedName name="Receitas">'Receitas - Mapa'!$A$4:$A$6</definedName>
-    <definedName name="Transferir">'Saldo &amp; Mov.'!$B$6:$B$8</definedName>
-    <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="2" hidden="1">'Despesas - Mapa'!$6:$6,'Despesas - Mapa'!#REF!</definedName>
+    <definedName name="Ativos">'Saldo &amp; Mov.'!$B$9:$B$11</definedName>
+    <definedName name="Categorias">'Despesas Gerais'!$C$7:$C$15</definedName>
+    <definedName name="Dash">'Gráfico Anual'!$A$1:$P$26</definedName>
+    <definedName name="Despesas">'Despesas Gerais'!$C$7:$C$15</definedName>
+    <definedName name="Investimentos">'Receita Líquida'!$A$9:$A$11</definedName>
+    <definedName name="Perdas">'Receita Líquida'!$A$6:$A$8</definedName>
+    <definedName name="Receita_Líquida">'Receita Líquida'!$A$3:$A$11</definedName>
+    <definedName name="Receitas">'Receita Líquida'!$A$3:$A$5</definedName>
+    <definedName name="Transferir">'Saldo &amp; Mov.'!$B$9:$B$11</definedName>
+    <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="2" hidden="1">'Despesas Gerais'!$6:$6,'Despesas Gerais'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
   <si>
     <t>Mês</t>
   </si>
@@ -114,9 +115,6 @@
   </si>
   <si>
     <t>Rolê</t>
-  </si>
-  <si>
-    <t>Outros</t>
   </si>
   <si>
     <t>Descrição</t>
@@ -200,22 +198,13 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Dízimo</t>
-  </si>
-  <si>
     <t>Receitas</t>
-  </si>
-  <si>
-    <t>Perdas</t>
   </si>
   <si>
     <t>Vendas</t>
   </si>
   <si>
     <t>Inss</t>
-  </si>
-  <si>
-    <t>T. Trans.</t>
   </si>
   <si>
     <t>Alocação</t>
@@ -251,7 +240,16 @@
     <t>Diferença</t>
   </si>
   <si>
-    <t>Outubro</t>
+    <t>Inv. Outros</t>
+  </si>
+  <si>
+    <t>Receitas Outros</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>Dízimo</t>
   </si>
 </sst>
 </file>
@@ -576,7 +574,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -586,7 +584,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -652,7 +649,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -721,9 +717,6 @@
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -814,10 +807,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2551,7 +2550,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Gráfico - Anual'!$C$2</c:f>
+              <c:f>'Gráfico Anual'!$C$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2609,7 +2608,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Gráfico - Anual'!$A$3:$A$14</c:f>
+              <c:f>'Gráfico Anual'!$A$3:$A$14</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2653,12 +2652,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Gráfico - Anual'!$C$3:$C$14</c:f>
+              <c:f>'Gráfico Anual'!$C$3:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2685,7 +2684,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>150</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -2707,7 +2706,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Gráfico - Anual'!$F$2</c:f>
+              <c:f>'Gráfico Anual'!$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2820,7 +2819,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Gráfico - Anual'!$A$3:$A$14</c:f>
+              <c:f>'Gráfico Anual'!$A$3:$A$14</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2864,12 +2863,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Gráfico - Anual'!$F$3:$F$14</c:f>
+              <c:f>'Gráfico Anual'!$F$3:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2896,7 +2895,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>100</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -2933,7 +2932,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Gráfico - Anual'!$D$2</c:f>
+              <c:f>'Gráfico Anual'!$D$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2962,7 +2961,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Gráfico - Anual'!$A$3:$A$14</c:f>
+              <c:f>'Gráfico Anual'!$A$3:$A$14</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -3006,7 +3005,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Gráfico - Anual'!$D$3:$D$14</c:f>
+              <c:f>'Gráfico Anual'!$D$3:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3385,11 +3384,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Gráfico - Anual'!$K$2:$K$10</c15:sqref>
+                    <c15:sqref>'Gráfico Anual'!$K$2:$K$10</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('Gráfico - Anual'!$K$3:$K$7,'Gráfico - Anual'!$K$10)</c:f>
+              <c:f>('Gráfico Anual'!$K$3:$K$7,'Gráfico Anual'!$K$10)</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -3418,11 +3417,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Gráfico - Anual'!$L$2:$L$10</c15:sqref>
+                    <c15:sqref>'Gráfico Anual'!$L$2:$L$10</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('Gráfico - Anual'!$L$3:$L$7,'Gráfico - Anual'!$L$10)</c:f>
+              <c:f>('Gráfico Anual'!$L$3:$L$7,'Gráfico Anual'!$L$10)</c:f>
               <c:numCache>
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3702,11 +3701,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Gráfico - Anual'!$N$2:$N$11</c15:sqref>
+                    <c15:sqref>'Gráfico Anual'!$N$2:$N$11</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Gráfico - Anual'!$N$3:$N$10</c:f>
+              <c:f>'Gráfico Anual'!$N$3:$N$10</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3741,11 +3740,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Gráfico - Anual'!$O$2:$O$11</c15:sqref>
+                    <c15:sqref>'Gráfico Anual'!$O$2:$O$11</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>'Gráfico - Anual'!$O$3:$O$10</c:f>
+              <c:f>'Gráfico Anual'!$O$3:$O$10</c:f>
               <c:numCache>
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="8"/>
@@ -6850,3452 +6849,3468 @@
   <sheetPr codeName="Planilha1">
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:I555"/>
+  <dimension ref="A1:I556"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" style="93" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="90" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" style="91" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" style="93" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="93" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" style="94" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="92" customWidth="1"/>
-    <col min="9" max="9" width="6" style="93" customWidth="1"/>
-    <col min="10" max="10" width="10" style="93" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="93"/>
+    <col min="1" max="1" width="6" style="90" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="87" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" style="88" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" style="90" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="90" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="91" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" style="89" customWidth="1"/>
+    <col min="9" max="9" width="6" style="90" customWidth="1"/>
+    <col min="10" max="10" width="10" style="90" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="10.7" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="89" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="89" t="s">
-        <v>59</v>
+      <c r="B2" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="98" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="56">
-        <f>SUM(F4:F14)</f>
+      <c r="E3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="90"/>
+    </row>
+    <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="54">
+        <f>IF(C3="Despesas",HLOOKUP(C2,'Despesas Gerais'!C2:AK17,16,FALSE),IF(C3="Receita Líquida",HLOOKUP(C2,'Receita Líquida'!B2:M13,12,FALSE)))</f>
         <v>100</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="93"/>
-    </row>
-    <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="56">
-        <f>VLOOKUP(C2,'Gráfico - Anual'!A3:I14,9,FALSE)</f>
-        <v>50</v>
-      </c>
       <c r="E4" s="5" t="str" cm="1">
-        <f t="array" ref="E4:E12">Categorias</f>
+        <f t="array" ref="E4:E12">IF(C3="Despesas",Categorias,IF(C3="Receita Líquida",Receita_Líquida,""))</f>
         <v>Alimentação</v>
       </c>
-      <c r="F4" s="100" cm="1">
-        <f t="array" ref="F4:F12">_xlfn._xlws.FILTER('Despesas - Mapa'!D7:AK15,'Despesas - Mapa'!D2:AK2=C2)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="93"/>
+      <c r="F4" s="97" cm="1">
+        <f t="array" ref="F4:F12">IF(C3="Despesas",_xlfn._xlws.FILTER('Despesas Gerais'!D7:AK15,'Despesas Gerais'!D2:AK2=C2),IF(C3="Receita Líquida",_xlfn._xlws.FILTER('Receita Líquida'!B3:M11,'Receita Líquida'!B2:M2=C2),""))</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="90"/>
     </row>
     <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E5" s="5" t="str">
         <v>G. Resid.</v>
       </c>
-      <c r="F5" s="100">
-        <v>0</v>
-      </c>
-      <c r="H5" s="93"/>
+      <c r="F5" s="97">
+        <v>0</v>
+      </c>
+      <c r="H5" s="90"/>
     </row>
     <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="7" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B6,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B6,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B6,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+      <c r="B6" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="54">
+        <f>VLOOKUP(C2,'Gráfico Anual'!A3:I14,9,FALSE)</f>
         <v>50</v>
       </c>
       <c r="E6" s="5" t="str">
         <v>Eletron e Jogos</v>
       </c>
-      <c r="F6" s="100">
+      <c r="F6" s="97">
         <v>50</v>
       </c>
-      <c r="H6" s="93"/>
+      <c r="H6" s="90"/>
     </row>
     <row r="7" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="7" cm="1">
-        <f t="array" aca="1" ref="C7" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B7,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B7,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B7,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
-        <v>0</v>
+      <c r="B7" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="54">
+        <f>'Gráfico Anual'!I15</f>
+        <v>50</v>
       </c>
       <c r="E7" s="5" t="str">
         <v>Cursos</v>
       </c>
-      <c r="F7" s="100">
-        <v>0</v>
-      </c>
-      <c r="H7" s="93"/>
+      <c r="F7" s="97">
+        <v>0</v>
+      </c>
+      <c r="H7" s="90"/>
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="7" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B8,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B8,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B8,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
-        <v>0</v>
-      </c>
       <c r="E8" s="5" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="F8" s="100">
-        <v>0</v>
-      </c>
-      <c r="H8" s="93"/>
+      <c r="F8" s="97">
+        <v>0</v>
+      </c>
+      <c r="H8" s="90"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="7">
-        <f ca="1">SUM(C6:C8)</f>
+      <c r="B9" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="7" cm="1">
+        <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B9,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>50</v>
       </c>
       <c r="E9" s="5" t="str">
         <v>Entret e Livros</v>
       </c>
-      <c r="F9" s="100">
-        <v>0</v>
-      </c>
-      <c r="H9" s="93"/>
+      <c r="F9" s="97">
+        <v>0</v>
+      </c>
+      <c r="H9" s="90"/>
     </row>
     <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91"/>
-      <c r="B10" s="57" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="56">
-        <f ca="1">C4-C9</f>
+      <c r="A10" s="88"/>
+      <c r="B10" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="7" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B10,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
       <c r="E10" s="5" t="str">
         <v>Rolê</v>
       </c>
-      <c r="F10" s="100">
-        <v>0</v>
-      </c>
-      <c r="H10" s="93"/>
+      <c r="F10" s="97">
+        <v>0</v>
+      </c>
+      <c r="H10" s="90"/>
     </row>
     <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="91"/>
+      <c r="A11" s="88"/>
+      <c r="B11" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="7" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B11,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
+      </c>
       <c r="E11" s="5" t="str">
         <v>Roupas</v>
       </c>
-      <c r="F11" s="100">
+      <c r="F11" s="97">
         <v>50</v>
       </c>
-      <c r="H11" s="93"/>
+      <c r="H11" s="90"/>
     </row>
     <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="91"/>
-      <c r="B12" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="56">
-        <f>'Gráfico - Anual'!I15</f>
+      <c r="A12" s="88"/>
+      <c r="B12" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="7">
+        <f ca="1">SUM(C9:C11)</f>
         <v>50</v>
       </c>
       <c r="E12" s="5" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="F12" s="100">
-        <v>0</v>
-      </c>
-      <c r="H12" s="93"/>
+      <c r="F12" s="97">
+        <v>0</v>
+      </c>
+      <c r="H12" s="90"/>
     </row>
     <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="E13" s="91"/>
-      <c r="H13" s="93"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="54">
+        <f ca="1">C6-C12</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="97"/>
+      <c r="H13" s="90"/>
     </row>
     <row r="14" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="97"/>
-      <c r="B14" s="99">
+      <c r="A14" s="94"/>
+      <c r="B14" s="90"/>
+      <c r="H14" s="90"/>
+    </row>
+    <row r="15" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="96">
         <f>SUBTOTAL(2,Tabela1[Data])</f>
         <v>3</v>
       </c>
-      <c r="H14" s="93"/>
-    </row>
-    <row r="15" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="66" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="69" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="70" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="71" t="s">
+      <c r="F15" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="67" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="70">
+        <v>44927</v>
+      </c>
+      <c r="C16" s="71" t="str">
+        <f t="shared" ref="C16:C38" si="0">IF(ISBLANK(B16),"",PROPER(TEXT(B16,"MMMM")))</f>
+        <v>Janeiro</v>
+      </c>
+      <c r="D16" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="70" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="73">
-        <v>45200</v>
-      </c>
-      <c r="C16" s="74" t="str">
-        <f t="shared" ref="C16:C37" si="0">IF(ISBLANK(B16),"",PROPER(TEXT(B16,"MMMM")))</f>
-        <v>Outubro</v>
-      </c>
-      <c r="D16" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="76">
+      <c r="F16" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="73">
         <v>150</v>
       </c>
-      <c r="H16" s="77"/>
+      <c r="H16" s="74"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="73">
-        <v>45200</v>
-      </c>
-      <c r="C17" s="74" t="str">
+      <c r="B17" s="70">
+        <v>44927</v>
+      </c>
+      <c r="C17" s="71" t="str">
         <f t="shared" si="0"/>
-        <v>Outubro</v>
-      </c>
-      <c r="D17" s="74" t="s">
+        <v>Janeiro</v>
+      </c>
+      <c r="D17" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="76">
+      <c r="E17" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="73">
         <v>50</v>
       </c>
-      <c r="H17" s="77"/>
+      <c r="H17" s="74"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="73">
-        <v>45201</v>
-      </c>
-      <c r="C18" s="74" t="str">
+      <c r="B18" s="70">
+        <v>44928</v>
+      </c>
+      <c r="C18" s="71" t="str">
         <f t="shared" si="0"/>
-        <v>Outubro</v>
-      </c>
-      <c r="D18" s="74" t="s">
+        <v>Janeiro</v>
+      </c>
+      <c r="D18" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="75" t="s">
+      <c r="E18" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="88">
+      <c r="F18" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="85">
         <v>50</v>
       </c>
-      <c r="H18" s="77"/>
+      <c r="H18" s="74"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="73"/>
-      <c r="C19" s="74" t="str">
+      <c r="B19" s="70"/>
+      <c r="C19" s="71" t="str">
         <f>IF(ISBLANK(B19),"",PROPER(TEXT(B19,"MMMM")))</f>
         <v/>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="75"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="77"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C28" s="91" t="str">
-        <f>IF(ISBLANK(B28),"",PROPER(TEXT(B28,"MMMM")))</f>
-        <v/>
-      </c>
-      <c r="D28" s="91" t="str">
-        <f t="shared" ref="D28:G28" si="1">IF(ISBLANK(C28),"",PROPER(TEXT(C28,"MMMM")))</f>
-        <v/>
-      </c>
-      <c r="E28" s="91" t="str">
+      <c r="D19" s="71"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="74"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="88" t="str">
+        <f>IF(ISBLANK(B20),"",PROPER(TEXT(B20,"MMMM")))</f>
+        <v/>
+      </c>
+      <c r="G20" s="103"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C29" s="88" t="str">
+        <f>IF(ISBLANK(B29),"",PROPER(TEXT(B29,"MMMM")))</f>
+        <v/>
+      </c>
+      <c r="D29" s="88" t="str">
+        <f t="shared" ref="D29:G29" si="1">IF(ISBLANK(C29),"",PROPER(TEXT(C29,"MMMM")))</f>
+        <v/>
+      </c>
+      <c r="E29" s="88" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F28" s="91" t="str">
+      <c r="F29" s="88" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G28" s="91" t="str">
+      <c r="G29" s="88" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C37" s="91" t="str">
+      <c r="I37" s="90" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C38" s="88" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I37" s="93" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C38" s="91" t="str">
-        <f t="shared" ref="C38:C52" si="2">IF(ISBLANK(B38),"",PROPER(TEXT(B38,"MMMM")))</f>
-        <v/>
-      </c>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C39" s="91" t="str">
-        <f t="shared" ref="C39:C49" si="3">IF(ISBLANK(B39),"",PROPER(TEXT(B39,"MMMM")))</f>
+      <c r="C39" s="88" t="str">
+        <f t="shared" ref="C39:C53" si="2">IF(ISBLANK(B39),"",PROPER(TEXT(B39,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C40" s="91" t="str">
+      <c r="C40" s="88" t="str">
+        <f t="shared" ref="C40:C50" si="3">IF(ISBLANK(B40),"",PROPER(TEXT(B40,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C41" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C41" s="91" t="str">
+    <row r="42" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C42" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C42" s="91" t="str">
+    <row r="43" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C43" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C43" s="91" t="str">
+    <row r="44" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C44" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C44" s="91" t="str">
+    <row r="45" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C45" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="45" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C45" s="91" t="str">
+    <row r="46" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C46" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="46" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C46" s="91" t="str">
+    <row r="47" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C47" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C47" s="91" t="str">
+    <row r="48" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C48" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C48" s="91" t="str">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C49" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C49" s="91" t="str">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C50" s="88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C50" s="91" t="str">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C51" s="88" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C51" s="91" t="str">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C52" s="88" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C52" s="91" t="str">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C53" s="88" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G52" s="95"/>
-      <c r="H52" s="96"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="93"/>
-      <c r="C53" s="93"/>
-      <c r="D53" s="93"/>
-      <c r="E53" s="97"/>
-      <c r="F53" s="97"/>
-      <c r="G53" s="95"/>
-      <c r="H53" s="96"/>
+      <c r="G53" s="92"/>
+      <c r="H53" s="93"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="93"/>
-      <c r="C54" s="93"/>
-      <c r="D54" s="93"/>
-      <c r="E54" s="97"/>
-      <c r="F54" s="97"/>
-      <c r="G54" s="95"/>
-      <c r="H54" s="96"/>
+      <c r="B54" s="90"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="90"/>
+      <c r="E54" s="94"/>
+      <c r="F54" s="94"/>
+      <c r="G54" s="92"/>
+      <c r="H54" s="93"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="93"/>
-      <c r="C55" s="93"/>
-      <c r="D55" s="93"/>
-      <c r="E55" s="97"/>
-      <c r="F55" s="97"/>
-      <c r="G55" s="95"/>
-      <c r="H55" s="96"/>
+      <c r="B55" s="90"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="94"/>
+      <c r="F55" s="94"/>
+      <c r="G55" s="92"/>
+      <c r="H55" s="93"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="93"/>
-      <c r="C56" s="98"/>
-      <c r="D56" s="98"/>
-      <c r="E56" s="97"/>
-      <c r="F56" s="97"/>
-      <c r="G56" s="95"/>
-      <c r="H56" s="96"/>
+      <c r="B56" s="90"/>
+      <c r="C56" s="90"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="94"/>
+      <c r="F56" s="94"/>
+      <c r="G56" s="92"/>
+      <c r="H56" s="93"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B57" s="93"/>
-      <c r="C57" s="93"/>
-      <c r="D57" s="93"/>
-      <c r="G57" s="93"/>
+      <c r="B57" s="90"/>
+      <c r="C57" s="95"/>
+      <c r="D57" s="95"/>
+      <c r="E57" s="94"/>
+      <c r="F57" s="94"/>
+      <c r="G57" s="92"/>
+      <c r="H57" s="93"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B58" s="93"/>
-      <c r="C58" s="93"/>
-      <c r="D58" s="93"/>
-      <c r="G58" s="93"/>
+      <c r="B58" s="90"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="90"/>
+      <c r="G58" s="90"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="93"/>
-      <c r="C59" s="93"/>
-      <c r="D59" s="93"/>
-      <c r="G59" s="93"/>
+      <c r="B59" s="90"/>
+      <c r="C59" s="90"/>
+      <c r="D59" s="90"/>
+      <c r="G59" s="90"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="93"/>
-      <c r="C60" s="93"/>
-      <c r="D60" s="93"/>
-      <c r="G60" s="93"/>
+      <c r="B60" s="90"/>
+      <c r="C60" s="90"/>
+      <c r="D60" s="90"/>
+      <c r="G60" s="90"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="93"/>
-      <c r="C61" s="93"/>
-      <c r="D61" s="93"/>
-      <c r="G61" s="93"/>
+      <c r="B61" s="90"/>
+      <c r="C61" s="90"/>
+      <c r="D61" s="90"/>
+      <c r="G61" s="90"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="93"/>
-      <c r="C62" s="93"/>
-      <c r="D62" s="93"/>
-      <c r="G62" s="93"/>
+      <c r="B62" s="90"/>
+      <c r="C62" s="90"/>
+      <c r="D62" s="90"/>
+      <c r="G62" s="90"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="93"/>
-      <c r="C63" s="93"/>
-      <c r="D63" s="93"/>
-      <c r="G63" s="93"/>
+      <c r="B63" s="90"/>
+      <c r="C63" s="90"/>
+      <c r="D63" s="90"/>
+      <c r="G63" s="90"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C64" s="91" t="str">
-        <f t="shared" ref="C64:C122" si="4">IF(ISBLANK(B64),"",PROPER(TEXT(B64,"MMMM")))</f>
-        <v/>
-      </c>
+      <c r="B64" s="90"/>
+      <c r="C64" s="90"/>
+      <c r="D64" s="90"/>
+      <c r="G64" s="90"/>
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C65" s="91" t="str">
+      <c r="C65" s="88" t="str">
+        <f t="shared" ref="C65:C123" si="4">IF(ISBLANK(B65),"",PROPER(TEXT(B65,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C66" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C66" s="91" t="str">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C67" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C67" s="91" t="str">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C68" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C68" s="91" t="str">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C69" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C69" s="91" t="str">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C70" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C70" s="91" t="str">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C71" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C71" s="91" t="str">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C72" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C72" s="91" t="str">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C73" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C73" s="91" t="str">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C74" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C74" s="91" t="str">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C75" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C75" s="91" t="str">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C76" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C76" s="91" t="str">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C77" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C77" s="91" t="str">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C78" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C78" s="91" t="str">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C79" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C79" s="91" t="str">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C80" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C80" s="91" t="str">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C81" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C81" s="91" t="str">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C82" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C82" s="91" t="str">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C83" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C83" s="91" t="str">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C84" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C84" s="91" t="str">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C85" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C85" s="91" t="str">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C86" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C86" s="91" t="str">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C87" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C87" s="91" t="str">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C88" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C88" s="91" t="str">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C89" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C89" s="91" t="str">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C90" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C90" s="91" t="str">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C91" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C91" s="91" t="str">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C92" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C92" s="91" t="str">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C93" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C93" s="91" t="str">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C94" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C94" s="91" t="str">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C95" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C95" s="91" t="str">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C96" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C96" s="91" t="str">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C97" s="91" t="str">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C98" s="91" t="str">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C99" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C99" s="91" t="str">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C100" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C100" s="91" t="str">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C101" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C101" s="91" t="str">
+    <row r="102" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C102" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C102" s="91" t="str">
+    <row r="103" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C103" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C103" s="91" t="str">
+    <row r="104" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C104" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C104" s="91" t="str">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C105" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C105" s="91" t="str">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C106" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C106" s="91" t="str">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C107" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C107" s="91" t="str">
+    <row r="108" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C108" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C108" s="91" t="str">
+    <row r="109" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C109" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C109" s="91" t="str">
+    <row r="110" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C110" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C110" s="91" t="str">
+    <row r="111" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C111" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C111" s="91" t="str">
+    <row r="112" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C112" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C112" s="91" t="str">
+    <row r="113" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C113" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C113" s="91" t="str">
+    <row r="114" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C114" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C114" s="91" t="str">
+    <row r="115" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C115" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C115" s="91" t="str">
+    <row r="116" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C116" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C116" s="91" t="str">
+    <row r="117" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C117" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C117" s="91" t="str">
+    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C118" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C118" s="91" t="str">
+    <row r="119" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C119" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C119" s="91" t="str">
+    <row r="120" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C120" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C120" s="91" t="str">
+    <row r="121" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C121" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C121" s="91" t="str">
+    <row r="122" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C122" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C122" s="91" t="str">
+    <row r="123" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C123" s="88" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C123" s="91" t="str">
-        <f t="shared" ref="C123:C186" si="5">IF(ISBLANK(B123),"",PROPER(TEXT(B123,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
     <row r="124" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C124" s="91" t="str">
+      <c r="C124" s="88" t="str">
+        <f t="shared" ref="C124:C187" si="5">IF(ISBLANK(B124),"",PROPER(TEXT(B124,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C125" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C125" s="91" t="str">
+    <row r="126" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C126" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C126" s="91" t="str">
+    <row r="127" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C127" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C127" s="91" t="str">
+    <row r="128" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C128" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C128" s="91" t="str">
+    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C129" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C129" s="91" t="str">
+    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C130" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C130" s="91" t="str">
+    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C131" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C131" s="91" t="str">
+    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C132" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C132" s="91" t="str">
+    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C133" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C133" s="91" t="str">
+    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C134" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C134" s="91" t="str">
+    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C135" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C135" s="91" t="str">
+    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C136" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C136" s="91" t="str">
+    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C137" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C137" s="91" t="str">
+    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C138" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C138" s="91" t="str">
+    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C139" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C139" s="91" t="str">
+    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C140" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C140" s="91" t="str">
+    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C141" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C141" s="91" t="str">
+    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C142" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C142" s="91" t="str">
+    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C143" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C143" s="91" t="str">
+    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C144" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C144" s="91" t="str">
+    <row r="145" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C145" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C145" s="91" t="str">
+    <row r="146" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C146" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C146" s="91" t="str">
+    <row r="147" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C147" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C147" s="91" t="str">
+    <row r="148" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C148" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C148" s="91" t="str">
+    <row r="149" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C149" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C149" s="91" t="str">
+    <row r="150" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C150" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C150" s="91" t="str">
+    <row r="151" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C151" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C151" s="91" t="str">
+    <row r="152" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C152" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C152" s="91" t="str">
+    <row r="153" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C153" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C153" s="91" t="str">
+    <row r="154" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C154" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C154" s="91" t="str">
+    <row r="155" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C155" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C155" s="91" t="str">
+    <row r="156" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C156" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C156" s="91" t="str">
+    <row r="157" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C157" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C157" s="91" t="str">
+    <row r="158" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C158" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C158" s="91" t="str">
+    <row r="159" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C159" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C159" s="91" t="str">
+    <row r="160" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C160" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C160" s="91" t="str">
+    <row r="161" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C161" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C161" s="91" t="str">
+    <row r="162" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C162" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C162" s="91" t="str">
+    <row r="163" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C163" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C163" s="91" t="str">
+    <row r="164" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C164" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C164" s="91" t="str">
+    <row r="165" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C165" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C165" s="91" t="str">
+    <row r="166" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C166" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C166" s="91" t="str">
+    <row r="167" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C167" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C167" s="91" t="str">
+    <row r="168" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C168" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C168" s="91" t="str">
+    <row r="169" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C169" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C169" s="91" t="str">
+    <row r="170" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C170" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C170" s="91" t="str">
+    <row r="171" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C171" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="171" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C171" s="91" t="str">
+    <row r="172" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C172" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="172" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C172" s="91" t="str">
+    <row r="173" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C173" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="173" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C173" s="91" t="str">
+    <row r="174" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C174" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="174" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C174" s="91" t="str">
+    <row r="175" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C175" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="175" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C175" s="91" t="str">
+    <row r="176" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C176" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="176" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C176" s="91" t="str">
+    <row r="177" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C177" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C177" s="91" t="str">
+    <row r="178" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C178" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C178" s="91" t="str">
+    <row r="179" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C179" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C179" s="91" t="str">
+    <row r="180" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C180" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C180" s="91" t="str">
+    <row r="181" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C181" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C181" s="91" t="str">
+    <row r="182" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C182" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C182" s="91" t="str">
+    <row r="183" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C183" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C183" s="91" t="str">
+    <row r="184" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C184" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C184" s="91" t="str">
+    <row r="185" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C185" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C185" s="91" t="str">
+    <row r="186" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C186" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C186" s="91" t="str">
+    <row r="187" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C187" s="88" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C187" s="91" t="str">
-        <f t="shared" ref="C187:C250" si="6">IF(ISBLANK(B187),"",PROPER(TEXT(B187,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
     <row r="188" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C188" s="91" t="str">
+      <c r="C188" s="88" t="str">
+        <f t="shared" ref="C188:C251" si="6">IF(ISBLANK(B188),"",PROPER(TEXT(B188,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C189" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C189" s="91" t="str">
+    <row r="190" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C190" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="190" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C190" s="91" t="str">
+    <row r="191" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C191" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="191" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C191" s="91" t="str">
+    <row r="192" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C192" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="192" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C192" s="91" t="str">
+    <row r="193" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C193" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C193" s="91" t="str">
+    <row r="194" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C194" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C194" s="91" t="str">
+    <row r="195" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C195" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C195" s="91" t="str">
+    <row r="196" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C196" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C196" s="91" t="str">
+    <row r="197" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C197" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C197" s="91" t="str">
+    <row r="198" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C198" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C198" s="91" t="str">
+    <row r="199" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C199" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C199" s="91" t="str">
+    <row r="200" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C200" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C200" s="91" t="str">
+    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C201" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C201" s="91" t="str">
+    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C202" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C202" s="91" t="str">
+    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C203" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C203" s="91" t="str">
+    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C204" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C204" s="91" t="str">
+    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C205" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C205" s="91" t="str">
+    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C206" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C206" s="91" t="str">
+    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C207" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C207" s="91" t="str">
+    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C208" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C208" s="91" t="str">
+    <row r="209" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C209" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C209" s="91" t="str">
+    <row r="210" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C210" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C210" s="91" t="str">
+    <row r="211" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C211" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C211" s="91" t="str">
+    <row r="212" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C212" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C212" s="91" t="str">
+    <row r="213" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C213" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C213" s="91" t="str">
+    <row r="214" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C214" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C214" s="91" t="str">
+    <row r="215" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C215" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C215" s="91" t="str">
+    <row r="216" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C216" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C216" s="91" t="str">
+    <row r="217" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C217" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C217" s="91" t="str">
+    <row r="218" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C218" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C218" s="91" t="str">
+    <row r="219" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C219" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C219" s="91" t="str">
+    <row r="220" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C220" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C220" s="91" t="str">
+    <row r="221" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C221" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C221" s="91" t="str">
+    <row r="222" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C222" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C222" s="91" t="str">
+    <row r="223" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C223" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C223" s="91" t="str">
+    <row r="224" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C224" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C224" s="91" t="str">
+    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C225" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C225" s="91" t="str">
+    <row r="226" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C226" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C226" s="91" t="str">
+    <row r="227" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C227" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C227" s="91" t="str">
+    <row r="228" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C228" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C228" s="91" t="str">
+    <row r="229" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C229" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C229" s="91" t="str">
+    <row r="230" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C230" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C230" s="91" t="str">
+    <row r="231" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C231" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C231" s="91" t="str">
+    <row r="232" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C232" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C232" s="91" t="str">
+    <row r="233" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C233" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C233" s="91" t="str">
+    <row r="234" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C234" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C234" s="91" t="str">
+    <row r="235" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C235" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C235" s="91" t="str">
+    <row r="236" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C236" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C236" s="91" t="str">
+    <row r="237" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C237" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C237" s="91" t="str">
+    <row r="238" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C238" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C238" s="91" t="str">
+    <row r="239" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C239" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C239" s="91" t="str">
+    <row r="240" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C240" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C240" s="91" t="str">
+    <row r="241" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C241" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C241" s="91" t="str">
+    <row r="242" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C242" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C242" s="91" t="str">
+    <row r="243" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C243" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C243" s="91" t="str">
+    <row r="244" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C244" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C244" s="91" t="str">
+    <row r="245" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C245" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C245" s="91" t="str">
+    <row r="246" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C246" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C246" s="91" t="str">
+    <row r="247" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C247" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C247" s="91" t="str">
+    <row r="248" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C248" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="248" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C248" s="91" t="str">
+    <row r="249" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C249" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C249" s="91" t="str">
+    <row r="250" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C250" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C250" s="91" t="str">
+    <row r="251" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C251" s="88" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C251" s="91" t="str">
-        <f t="shared" ref="C251:C314" si="7">IF(ISBLANK(B251),"",PROPER(TEXT(B251,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
     <row r="252" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C252" s="91" t="str">
+      <c r="C252" s="88" t="str">
+        <f t="shared" ref="C252:C315" si="7">IF(ISBLANK(B252),"",PROPER(TEXT(B252,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C253" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C253" s="91" t="str">
+    <row r="254" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C254" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C254" s="91" t="str">
+    <row r="255" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C255" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C255" s="91" t="str">
+    <row r="256" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C256" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C256" s="91" t="str">
+    <row r="257" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C257" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C257" s="91" t="str">
+    <row r="258" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C258" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C258" s="91" t="str">
+    <row r="259" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C259" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C259" s="91" t="str">
+    <row r="260" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C260" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C260" s="91" t="str">
+    <row r="261" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C261" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C261" s="91" t="str">
+    <row r="262" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C262" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C262" s="91" t="str">
+    <row r="263" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C263" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="263" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C263" s="91" t="str">
+    <row r="264" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C264" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C264" s="91" t="str">
+    <row r="265" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C265" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C265" s="91" t="str">
+    <row r="266" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C266" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C266" s="91" t="str">
+    <row r="267" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C267" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C267" s="91" t="str">
+    <row r="268" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C268" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C268" s="91" t="str">
+    <row r="269" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C269" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C269" s="91" t="str">
+    <row r="270" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C270" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C270" s="91" t="str">
+    <row r="271" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C271" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C271" s="91" t="str">
+    <row r="272" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C272" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C272" s="91" t="str">
+    <row r="273" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C273" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="273" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C273" s="91" t="str">
+    <row r="274" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C274" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="274" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C274" s="91" t="str">
+    <row r="275" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C275" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="275" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C275" s="91" t="str">
+    <row r="276" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C276" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="276" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C276" s="91" t="str">
+    <row r="277" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C277" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="277" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C277" s="91" t="str">
+    <row r="278" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C278" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="278" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C278" s="91" t="str">
+    <row r="279" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C279" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="279" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C279" s="91" t="str">
+    <row r="280" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C280" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="280" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C280" s="91" t="str">
+    <row r="281" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C281" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="281" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C281" s="91" t="str">
+    <row r="282" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C282" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="282" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C282" s="91" t="str">
+    <row r="283" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C283" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="283" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C283" s="91" t="str">
+    <row r="284" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C284" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="284" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C284" s="91" t="str">
+    <row r="285" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C285" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="285" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C285" s="91" t="str">
+    <row r="286" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C286" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="286" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C286" s="91" t="str">
+    <row r="287" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C287" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="287" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C287" s="91" t="str">
+    <row r="288" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C288" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="288" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C288" s="91" t="str">
+    <row r="289" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C289" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="289" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C289" s="91" t="str">
+    <row r="290" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C290" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="290" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C290" s="91" t="str">
+    <row r="291" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C291" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="291" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C291" s="91" t="str">
+    <row r="292" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C292" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="292" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C292" s="91" t="str">
+    <row r="293" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C293" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="293" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C293" s="91" t="str">
+    <row r="294" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C294" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="294" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C294" s="91" t="str">
+    <row r="295" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C295" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="295" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C295" s="91" t="str">
+    <row r="296" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C296" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="296" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C296" s="91" t="str">
+    <row r="297" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C297" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="297" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C297" s="91" t="str">
+    <row r="298" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C298" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="298" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C298" s="91" t="str">
+    <row r="299" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C299" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="299" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C299" s="91" t="str">
+    <row r="300" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C300" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="300" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C300" s="91" t="str">
+    <row r="301" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C301" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="301" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C301" s="91" t="str">
+    <row r="302" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C302" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="302" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C302" s="91" t="str">
+    <row r="303" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C303" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="303" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C303" s="91" t="str">
+    <row r="304" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C304" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="304" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C304" s="91" t="str">
+    <row r="305" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C305" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="305" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C305" s="91" t="str">
+    <row r="306" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C306" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="306" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C306" s="91" t="str">
+    <row r="307" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C307" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="307" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C307" s="91" t="str">
+    <row r="308" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C308" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" s="91" t="str">
+    <row r="309" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C309" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="309" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C309" s="91" t="str">
+    <row r="310" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C310" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="310" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C310" s="91" t="str">
+    <row r="311" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C311" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="311" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C311" s="91" t="str">
+    <row r="312" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C312" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="312" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C312" s="91" t="str">
+    <row r="313" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C313" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="313" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C313" s="91" t="str">
+    <row r="314" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C314" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="314" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C314" s="91" t="str">
+    <row r="315" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C315" s="88" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="315" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C315" s="91" t="str">
-        <f t="shared" ref="C315:C378" si="8">IF(ISBLANK(B315),"",PROPER(TEXT(B315,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C316" s="91" t="str">
+      <c r="C316" s="88" t="str">
+        <f t="shared" ref="C316:C379" si="8">IF(ISBLANK(B316),"",PROPER(TEXT(B316,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C317" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="317" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C317" s="91" t="str">
+    <row r="318" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C318" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="318" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C318" s="91" t="str">
+    <row r="319" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C319" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="319" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C319" s="91" t="str">
+    <row r="320" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C320" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="320" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C320" s="91" t="str">
+    <row r="321" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C321" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="321" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C321" s="91" t="str">
+    <row r="322" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C322" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="322" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C322" s="91" t="str">
+    <row r="323" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C323" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="323" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C323" s="91" t="str">
+    <row r="324" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C324" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="324" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C324" s="91" t="str">
+    <row r="325" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C325" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="325" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C325" s="91" t="str">
+    <row r="326" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C326" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="326" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C326" s="91" t="str">
+    <row r="327" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C327" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="327" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C327" s="91" t="str">
+    <row r="328" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C328" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="328" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C328" s="91" t="str">
+    <row r="329" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C329" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="329" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C329" s="91" t="str">
+    <row r="330" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C330" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="330" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C330" s="91" t="str">
+    <row r="331" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C331" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="331" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C331" s="91" t="str">
+    <row r="332" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C332" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="332" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C332" s="91" t="str">
+    <row r="333" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C333" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="333" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C333" s="91" t="str">
+    <row r="334" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C334" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="334" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C334" s="91" t="str">
+    <row r="335" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C335" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="335" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C335" s="91" t="str">
+    <row r="336" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C336" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="336" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C336" s="91" t="str">
+    <row r="337" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C337" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="337" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C337" s="91" t="str">
+    <row r="338" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C338" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="338" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C338" s="91" t="str">
+    <row r="339" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C339" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="339" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C339" s="91" t="str">
+    <row r="340" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C340" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="340" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C340" s="91" t="str">
+    <row r="341" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C341" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="341" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C341" s="91" t="str">
+    <row r="342" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C342" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="342" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C342" s="91" t="str">
+    <row r="343" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C343" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="343" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C343" s="91" t="str">
+    <row r="344" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C344" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="344" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C344" s="91" t="str">
+    <row r="345" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C345" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="345" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C345" s="91" t="str">
+    <row r="346" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C346" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="346" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C346" s="91" t="str">
+    <row r="347" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C347" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="347" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C347" s="91" t="str">
+    <row r="348" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C348" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="348" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C348" s="91" t="str">
+    <row r="349" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C349" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="349" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C349" s="91" t="str">
+    <row r="350" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C350" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="350" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C350" s="91" t="str">
+    <row r="351" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C351" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="351" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C351" s="91" t="str">
+    <row r="352" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C352" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="352" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C352" s="91" t="str">
+    <row r="353" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C353" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="353" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C353" s="91" t="str">
+    <row r="354" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C354" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="354" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C354" s="91" t="str">
+    <row r="355" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C355" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="355" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C355" s="91" t="str">
+    <row r="356" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C356" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="356" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C356" s="91" t="str">
+    <row r="357" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C357" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="357" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C357" s="91" t="str">
+    <row r="358" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C358" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="358" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C358" s="91" t="str">
+    <row r="359" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C359" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="359" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C359" s="91" t="str">
+    <row r="360" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C360" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="360" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C360" s="91" t="str">
+    <row r="361" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C361" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="361" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C361" s="91" t="str">
+    <row r="362" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C362" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="362" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C362" s="91" t="str">
+    <row r="363" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C363" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="363" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C363" s="91" t="str">
+    <row r="364" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C364" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="364" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C364" s="91" t="str">
+    <row r="365" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C365" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="365" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C365" s="91" t="str">
+    <row r="366" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C366" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="366" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C366" s="91" t="str">
+    <row r="367" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C367" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="367" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C367" s="91" t="str">
+    <row r="368" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C368" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="368" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C368" s="91" t="str">
+    <row r="369" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C369" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="369" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C369" s="91" t="str">
+    <row r="370" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C370" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="370" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C370" s="91" t="str">
+    <row r="371" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C371" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="371" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C371" s="91" t="str">
+    <row r="372" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C372" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="372" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C372" s="91" t="str">
+    <row r="373" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C373" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="373" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C373" s="91" t="str">
+    <row r="374" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C374" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="374" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C374" s="91" t="str">
+    <row r="375" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C375" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="375" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C375" s="91" t="str">
+    <row r="376" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C376" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C376" s="91" t="str">
+    <row r="377" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C377" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="377" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C377" s="91" t="str">
+    <row r="378" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C378" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="378" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C378" s="91" t="str">
+    <row r="379" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C379" s="88" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="379" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C379" s="91" t="str">
-        <f t="shared" ref="C379:C442" si="9">IF(ISBLANK(B379),"",PROPER(TEXT(B379,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C380" s="91" t="str">
+      <c r="C380" s="88" t="str">
+        <f t="shared" ref="C380:C443" si="9">IF(ISBLANK(B380),"",PROPER(TEXT(B380,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C381" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="381" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C381" s="91" t="str">
+    <row r="382" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C382" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="382" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C382" s="91" t="str">
+    <row r="383" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C383" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="383" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C383" s="91" t="str">
+    <row r="384" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C384" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="384" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C384" s="91" t="str">
+    <row r="385" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C385" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="385" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C385" s="91" t="str">
+    <row r="386" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C386" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="386" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C386" s="91" t="str">
+    <row r="387" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C387" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="387" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C387" s="91" t="str">
+    <row r="388" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C388" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="388" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C388" s="91" t="str">
+    <row r="389" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C389" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="389" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C389" s="91" t="str">
+    <row r="390" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C390" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="91" t="str">
+    <row r="391" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C391" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="391" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C391" s="91" t="str">
+    <row r="392" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C392" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="392" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C392" s="91" t="str">
+    <row r="393" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C393" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="393" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C393" s="91" t="str">
+    <row r="394" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C394" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="394" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C394" s="91" t="str">
+    <row r="395" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C395" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="395" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C395" s="91" t="str">
+    <row r="396" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C396" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="396" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C396" s="91" t="str">
+    <row r="397" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C397" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="397" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C397" s="91" t="str">
+    <row r="398" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C398" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="398" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C398" s="91" t="str">
+    <row r="399" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C399" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="399" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C399" s="91" t="str">
+    <row r="400" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C400" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="400" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C400" s="91" t="str">
+    <row r="401" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C401" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="401" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C401" s="91" t="str">
+    <row r="402" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C402" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="402" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C402" s="91" t="str">
+    <row r="403" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C403" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="403" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C403" s="91" t="str">
+    <row r="404" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C404" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="404" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C404" s="91" t="str">
+    <row r="405" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C405" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="405" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C405" s="91" t="str">
+    <row r="406" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C406" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="406" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C406" s="91" t="str">
+    <row r="407" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C407" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="407" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C407" s="91" t="str">
+    <row r="408" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C408" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="408" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C408" s="91" t="str">
+    <row r="409" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C409" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="409" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C409" s="91" t="str">
+    <row r="410" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C410" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="410" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C410" s="91" t="str">
+    <row r="411" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C411" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="411" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C411" s="91" t="str">
+    <row r="412" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C412" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="412" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C412" s="91" t="str">
+    <row r="413" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C413" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="413" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C413" s="91" t="str">
+    <row r="414" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C414" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="414" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C414" s="91" t="str">
+    <row r="415" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C415" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="415" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C415" s="91" t="str">
+    <row r="416" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C416" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="416" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C416" s="91" t="str">
+    <row r="417" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C417" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="91" t="str">
+    <row r="418" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C418" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="418" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C418" s="91" t="str">
+    <row r="419" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C419" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="419" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C419" s="91" t="str">
+    <row r="420" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C420" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="91" t="str">
+    <row r="421" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C421" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="421" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C421" s="91" t="str">
+    <row r="422" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C422" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="422" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C422" s="91" t="str">
+    <row r="423" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C423" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="423" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C423" s="91" t="str">
+    <row r="424" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C424" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="424" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C424" s="91" t="str">
+    <row r="425" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C425" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="425" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C425" s="91" t="str">
+    <row r="426" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C426" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="426" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C426" s="91" t="str">
+    <row r="427" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C427" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="427" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C427" s="91" t="str">
+    <row r="428" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C428" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="428" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C428" s="91" t="str">
+    <row r="429" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C429" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="429" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C429" s="91" t="str">
+    <row r="430" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C430" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="430" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C430" s="91" t="str">
+    <row r="431" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C431" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="431" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C431" s="91" t="str">
+    <row r="432" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C432" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="432" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C432" s="91" t="str">
+    <row r="433" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C433" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="91" t="str">
+    <row r="434" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C434" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="434" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C434" s="91" t="str">
+    <row r="435" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C435" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="435" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C435" s="91" t="str">
+    <row r="436" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C436" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="91" t="str">
+    <row r="437" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C437" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="437" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C437" s="91" t="str">
+    <row r="438" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C438" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="438" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C438" s="91" t="str">
+    <row r="439" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C439" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="439" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C439" s="91" t="str">
+    <row r="440" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C440" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="440" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C440" s="91" t="str">
+    <row r="441" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C441" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="441" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C441" s="91" t="str">
+    <row r="442" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C442" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="442" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C442" s="91" t="str">
+    <row r="443" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C443" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="443" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C443" s="91" t="str">
-        <f t="shared" ref="C443:C506" si="10">IF(ISBLANK(B443),"",PROPER(TEXT(B443,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C444" s="91" t="str">
+      <c r="C444" s="88" t="str">
+        <f t="shared" ref="C444:C507" si="10">IF(ISBLANK(B444),"",PROPER(TEXT(B444,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C445" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="445" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C445" s="91" t="str">
+    <row r="446" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C446" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="446" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C446" s="91" t="str">
+    <row r="447" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C447" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="447" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C447" s="91" t="str">
+    <row r="448" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C448" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="448" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C448" s="91" t="str">
+    <row r="449" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C449" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="449" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C449" s="91" t="str">
+    <row r="450" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C450" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="450" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C450" s="91" t="str">
+    <row r="451" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C451" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="451" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C451" s="91" t="str">
+    <row r="452" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C452" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="452" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C452" s="91" t="str">
+    <row r="453" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C453" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="453" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C453" s="91" t="str">
+    <row r="454" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C454" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="454" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C454" s="91" t="str">
+    <row r="455" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C455" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="455" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C455" s="91" t="str">
+    <row r="456" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C456" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="456" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C456" s="91" t="str">
+    <row r="457" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C457" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="457" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C457" s="91" t="str">
+    <row r="458" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C458" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="458" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C458" s="91" t="str">
+    <row r="459" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C459" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="459" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C459" s="91" t="str">
+    <row r="460" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C460" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="460" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C460" s="91" t="str">
+    <row r="461" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C461" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="461" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C461" s="91" t="str">
+    <row r="462" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C462" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="462" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C462" s="91" t="str">
+    <row r="463" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C463" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="463" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C463" s="91" t="str">
+    <row r="464" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C464" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="464" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C464" s="91" t="str">
+    <row r="465" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C465" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" s="91" t="str">
+    <row r="466" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C466" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="466" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C466" s="91" t="str">
+    <row r="467" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C467" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="467" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C467" s="91" t="str">
+    <row r="468" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C468" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="468" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C468" s="91" t="str">
+    <row r="469" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C469" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="469" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C469" s="91" t="str">
+    <row r="470" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C470" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="470" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C470" s="91" t="str">
+    <row r="471" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C471" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="471" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C471" s="91" t="str">
+    <row r="472" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C472" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="472" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C472" s="91" t="str">
+    <row r="473" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C473" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="473" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C473" s="91" t="str">
+    <row r="474" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C474" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" s="91" t="str">
+    <row r="475" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C475" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" s="91" t="str">
+    <row r="476" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C476" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" s="91" t="str">
+    <row r="477" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C477" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="477" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C477" s="91" t="str">
+    <row r="478" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C478" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="478" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C478" s="91" t="str">
+    <row r="479" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C479" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="479" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C479" s="91" t="str">
+    <row r="480" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C480" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="480" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C480" s="91" t="str">
+    <row r="481" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C481" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="481" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C481" s="91" t="str">
+    <row r="482" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C482" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="482" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C482" s="91" t="str">
+    <row r="483" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C483" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="483" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C483" s="91" t="str">
+    <row r="484" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C484" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="484" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C484" s="91" t="str">
+    <row r="485" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C485" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="485" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C485" s="91" t="str">
+    <row r="486" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C486" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="486" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C486" s="91" t="str">
+    <row r="487" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C487" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="91" t="str">
+    <row r="488" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C488" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" s="91" t="str">
+    <row r="489" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C489" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" s="91" t="str">
+    <row r="490" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C490" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="490" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C490" s="91" t="str">
+    <row r="491" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C491" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="491" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C491" s="91" t="str">
+    <row r="492" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C492" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="492" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C492" s="91" t="str">
+    <row r="493" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C493" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="493" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C493" s="91" t="str">
+    <row r="494" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C494" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="494" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C494" s="91" t="str">
+    <row r="495" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C495" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="495" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C495" s="91" t="str">
+    <row r="496" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C496" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="496" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C496" s="91" t="str">
+    <row r="497" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C497" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="497" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C497" s="91" t="str">
+    <row r="498" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C498" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="91" t="str">
+    <row r="499" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C499" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" s="91" t="str">
+    <row r="500" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C500" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" s="91" t="str">
+    <row r="501" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C501" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="91" t="str">
+    <row r="502" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C502" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="502" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C502" s="91" t="str">
+    <row r="503" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C503" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="503" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C503" s="91" t="str">
+    <row r="504" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C504" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="504" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C504" s="91" t="str">
+    <row r="505" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C505" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="505" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C505" s="91" t="str">
+    <row r="506" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C506" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="506" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C506" s="91" t="str">
+    <row r="507" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C507" s="88" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="507" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C507" s="91" t="str">
-        <f t="shared" ref="C507:C555" si="11">IF(ISBLANK(B507),"",PROPER(TEXT(B507,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C508" s="91" t="str">
+      <c r="C508" s="88" t="str">
+        <f t="shared" ref="C508:C556" si="11">IF(ISBLANK(B508),"",PROPER(TEXT(B508,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="509" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C509" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="509" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C509" s="91" t="str">
+    <row r="510" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C510" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="510" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C510" s="91" t="str">
+    <row r="511" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C511" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="511" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C511" s="91" t="str">
+    <row r="512" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C512" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="512" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C512" s="91" t="str">
+    <row r="513" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C513" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="513" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C513" s="91" t="str">
+    <row r="514" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C514" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" s="91" t="str">
+    <row r="515" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C515" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" s="91" t="str">
+    <row r="516" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C516" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" s="91" t="str">
+    <row r="517" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C517" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="517" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C517" s="91" t="str">
+    <row r="518" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C518" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="518" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C518" s="91" t="str">
+    <row r="519" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C519" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="519" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C519" s="91" t="str">
+    <row r="520" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C520" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="520" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C520" s="91" t="str">
+    <row r="521" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C521" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="521" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C521" s="91" t="str">
+    <row r="522" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C522" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" s="91" t="str">
+    <row r="523" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C523" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" s="91" t="str">
+    <row r="524" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C524" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" s="91" t="str">
+    <row r="525" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C525" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="525" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C525" s="91" t="str">
+    <row r="526" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C526" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="526" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C526" s="91" t="str">
+    <row r="527" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C527" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="527" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C527" s="91" t="str">
+    <row r="528" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C528" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="528" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C528" s="91" t="str">
+    <row r="529" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C529" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="529" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C529" s="91" t="str">
+    <row r="530" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C530" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" s="91" t="str">
+    <row r="531" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C531" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" s="91" t="str">
+    <row r="532" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C532" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" s="91" t="str">
+    <row r="533" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C533" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="533" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C533" s="91" t="str">
+    <row r="534" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C534" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="534" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C534" s="91" t="str">
+    <row r="535" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C535" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="535" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C535" s="91" t="str">
+    <row r="536" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C536" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="536" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C536" s="91" t="str">
+    <row r="537" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C537" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="537" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C537" s="91" t="str">
+    <row r="538" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C538" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="538" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C538" s="91" t="str">
+    <row r="539" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C539" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="539" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C539" s="91" t="str">
+    <row r="540" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C540" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="540" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C540" s="91" t="str">
+    <row r="541" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C541" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="541" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C541" s="91" t="str">
+    <row r="542" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C542" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="542" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C542" s="91" t="str">
+    <row r="543" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C543" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="543" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C543" s="91" t="str">
+    <row r="544" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C544" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="544" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C544" s="91" t="str">
+    <row r="545" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C545" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="545" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C545" s="91" t="str">
+    <row r="546" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C546" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="546" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C546" s="91" t="str">
+    <row r="547" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C547" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="547" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C547" s="91" t="str">
+    <row r="548" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C548" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="548" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C548" s="91" t="str">
+    <row r="549" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C549" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="549" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C549" s="91" t="str">
+    <row r="550" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C550" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="550" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C550" s="91" t="str">
+    <row r="551" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C551" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="551" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C551" s="91" t="str">
+    <row r="552" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C552" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="552" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C552" s="91" t="str">
+    <row r="553" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C553" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="553" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C553" s="91" t="str">
+    <row r="554" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C554" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="554" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C554" s="91" t="str">
+    <row r="555" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C555" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="555" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C555" s="91" t="str">
+    <row r="556" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C556" s="88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
-  <conditionalFormatting sqref="C10">
+  <conditionalFormatting sqref="C13">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -10303,14 +10318,17 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16:E27" xr:uid="{E4F2BDDC-1223-4DFF-8087-7B85DF038B73}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
+      <formula1>"Despesas, Receita Líquida"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16:E28" xr:uid="{E4F2BDDC-1223-4DFF-8087-7B85DF038B73}">
       <formula1>INDIRECT(D16)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D16:D27" xr:uid="{4E564D7B-00FF-4101-8D9D-5EA4D9B1919A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D16:D28" xr:uid="{4E564D7B-00FF-4101-8D9D-5EA4D9B1919A}">
       <formula1>"Receitas, Perdas, Investimentos, Despesas, Transferir"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16:F27" xr:uid="{0D51CC9B-6F94-4F85-BAFC-26C786BB30BC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16:F28" xr:uid="{0D51CC9B-6F94-4F85-BAFC-26C786BB30BC}">
       <formula1>Ativos</formula1>
     </dataValidation>
   </dataValidations>
@@ -10325,7 +10343,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9270E47-B020-4CBF-A3A9-E523B28C14E7}">
           <x14:formula1>
-            <xm:f>'Receitas - Mapa'!$B$2:$M$2</xm:f>
+            <xm:f>'Receita Líquida'!$B$2:$M$2</xm:f>
           </x14:formula1>
           <xm:sqref>C2</xm:sqref>
         </x14:dataValidation>
@@ -10340,10 +10358,10 @@
   <sheetPr codeName="Planilha2">
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A2:M19"/>
+  <dimension ref="A2:M15"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
     <col min="2" max="13" width="15" style="1" customWidth="1"/>
     <col min="14" max="14" width="5.7109375" style="1" customWidth="1"/>
     <col min="15" max="15" width="4.28515625" style="1" customWidth="1"/>
@@ -10351,63 +10369,111 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="11" t="str">
+      <c r="B2" s="10" t="str">
         <f>PROPER(TEXT("01/01","MMMM"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="C2" s="11" t="str">
+      <c r="C2" s="10" t="str">
         <f>PROPER(TEXT("01/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="10" t="str">
         <f>PROPER(TEXT("01/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="E2" s="11" t="str">
+      <c r="E2" s="10" t="str">
         <f>PROPER(TEXT("01/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="F2" s="11" t="str">
+      <c r="F2" s="10" t="str">
         <f>PROPER(TEXT("01/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="G2" s="11" t="str">
+      <c r="G2" s="10" t="str">
         <f>PROPER(TEXT("01/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="H2" s="11" t="str">
+      <c r="H2" s="10" t="str">
         <f>PROPER(TEXT("01/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="I2" s="11" t="str">
+      <c r="I2" s="10" t="str">
         <f>PROPER(TEXT("01/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="J2" s="11" t="str">
+      <c r="J2" s="10" t="str">
         <f>PROPER(TEXT("01/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="K2" s="11" t="str">
+      <c r="K2" s="10" t="str">
         <f>PROPER(TEXT("01/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="L2" s="11" t="str">
+      <c r="L2" s="10" t="str">
         <f>PROPER(TEXT("01/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="M2" s="11" t="str">
+      <c r="M2" s="10" t="str">
         <f>PROPER(TEXT("01/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
-        <v>43</v>
+    <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A3)</f>
+        <v>150</v>
+      </c>
+      <c r="C3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="33">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>32</v>
+      <c r="A4" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="B4" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A4)</f>
@@ -10433,7 +10499,7 @@
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="33">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
@@ -10447,7 +10513,7 @@
       </c>
       <c r="K4" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A4)</f>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L4" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A4)</f>
@@ -10458,9 +10524,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>45</v>
+    <row r="5" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="B5" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A5)</f>
@@ -10486,7 +10552,7 @@
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="33">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
@@ -10511,9 +10577,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>14</v>
+    <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="B6" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A6)</f>
@@ -10539,7 +10605,7 @@
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="33">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
@@ -10564,41 +10630,115 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+    <row r="7" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="33">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A7)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="65" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
+      <c r="A8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A8)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>46</v>
+      <c r="A9" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="B9" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A9)</f>
@@ -10624,7 +10764,7 @@
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
@@ -10649,9 +10789,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>47</v>
+    <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="B10" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A10)</f>
@@ -10677,7 +10817,7 @@
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="33">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
@@ -10702,9 +10842,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>54</v>
+    <row r="11" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="B11" s="7">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A11)</f>
@@ -10755,315 +10895,109 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="34">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A12)</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="13" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="72">
-        <f>IF((SUM(B4:B6)-SUM(B9:B11)) &gt; 10, ((SUM(B4:B6)-SUM(B9:B11))*0.1), (0))-B12</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="72">
-        <f t="shared" ref="C13:L13" si="0">IF((SUM(C4:C6)-SUM(C9:C11)) &gt; 10, ((SUM(C4:C6)-SUM(C9:C11))*0.1), (0))-C12</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="72">
+      <c r="A13" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="7">
+        <f>ROUND(SUM(B3:B5)-SUM(B6:B11),2)</f>
+        <v>150</v>
+      </c>
+      <c r="C13" s="7">
+        <f t="shared" ref="C13:M13" si="0">ROUND(SUM(C3:C5)-SUM(C6:C11),2)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E13" s="72">
+      <c r="E13" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13" s="72">
+      <c r="F13" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="72">
+      <c r="G13" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="72">
+      <c r="H13" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="72">
+      <c r="I13" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="72">
+      <c r="K13" s="7">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="69">
+        <f>ROUND(IF((SUM(B3:B5)-SUM(B6:B7)) &gt; 10, ((SUM(B3:B5)-SUM(B6:B7))*0.1), (0))-B8,2)</f>
         <v>15</v>
       </c>
-      <c r="L13" s="72">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="72">
-        <f>IF((SUM(M4:M6)-SUM(M9:M11)) &gt; 10, ((SUM(M4:M6)-SUM(M9:M11))*0.1), (0))-M12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-    </row>
-    <row r="15" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="65" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-    </row>
-    <row r="16" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="34">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="7">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-    </row>
-    <row r="19" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="7">
-        <f>ROUND(SUM(B4:B6)-SUM(B16:B17)-SUM(B9:B12),2)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="7">
-        <f t="shared" ref="C19:L19" si="1">ROUND(SUM(C4:C6)-SUM(C16:C17)-SUM(C9:C12),2)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="C15" s="69">
+        <f t="shared" ref="C15:M15" si="1">ROUND(IF((SUM(C3:C5)-SUM(C6:C7)) &gt; 10, ((SUM(C3:C5)-SUM(C6:C7))*0.1), (0))-C8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E15" s="69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F15" s="69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G15" s="69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H15" s="69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I15" s="69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J15" s="69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K15" s="69">
         <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-      <c r="L19" s="7">
+        <v>0</v>
+      </c>
+      <c r="L15" s="69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M19" s="7">
-        <f>ROUND(SUM(M4:M6)-SUM(M16:M17)-SUM(M9:M12),2)</f>
+      <c r="M15" s="69">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -11079,14 +11013,14 @@
   <sheetPr codeName="Planilha3">
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A2:AK17"/>
+  <dimension ref="A2:AL17"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="5" customWidth="1"/>
     <col min="2" max="2" width="6.5703125" style="5" customWidth="1"/>
     <col min="3" max="4" width="15.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="6.5703125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" style="36" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="34" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="6.42578125" style="5" customWidth="1"/>
     <col min="9" max="10" width="15.7109375" style="5" customWidth="1"/>
@@ -11114,1354 +11048,1353 @@
     <col min="42" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:37" s="55" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="78" t="str">
+    <row r="2" spans="1:37" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="75" t="str">
         <f>PROPER(TEXT("01/01","MMMM"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="62" t="str">
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="60" t="str">
         <f>PROPER(TEXT("1/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="79" t="str">
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="76" t="str">
         <f>PROPER(TEXT("1/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="62" t="str">
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="60" t="str">
         <f>PROPER(TEXT("1/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="79" t="str">
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="76" t="str">
         <f>PROPER(TEXT("1/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="62" t="str">
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="60" t="str">
         <f>PROPER(TEXT("1/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="79" t="str">
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="76" t="str">
         <f>PROPER(TEXT("1/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="62" t="str">
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="60" t="str">
         <f>PROPER(TEXT("1/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="79" t="str">
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="76" t="str">
         <f>PROPER(TEXT("1/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="62" t="str">
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="60" t="str">
         <f>PROPER(TEXT("1/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="79" t="str">
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="76" t="str">
         <f>PROPER(TEXT("1/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="AI2" s="53"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="62" t="str">
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="60" t="str">
         <f>PROPER(TEXT("1/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
-    <row r="3" spans="1:37" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
+    <row r="3" spans="1:37" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="36"/>
       <c r="D3" s="4">
-        <f>'Receitas - Mapa'!B19</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="38"/>
+        <f>'Receita Líquida'!B13</f>
+        <v>150</v>
+      </c>
+      <c r="F3" s="36"/>
       <c r="G3" s="4">
-        <f>'Receitas - Mapa'!C19</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="38"/>
+        <f>'Receita Líquida'!C13</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="36"/>
       <c r="J3" s="4">
-        <f>'Receitas - Mapa'!D19</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="38"/>
+        <f>'Receita Líquida'!D13</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="36"/>
       <c r="M3" s="4">
-        <f>'Receitas - Mapa'!E19</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="38"/>
+        <f>'Receita Líquida'!E13</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="36"/>
       <c r="P3" s="4">
-        <f>'Receitas - Mapa'!F19</f>
-        <v>0</v>
-      </c>
-      <c r="R3" s="38"/>
+        <f>'Receita Líquida'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="36"/>
       <c r="S3" s="4">
-        <f>'Receitas - Mapa'!G19</f>
-        <v>0</v>
-      </c>
-      <c r="U3" s="38"/>
+        <f>'Receita Líquida'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="36"/>
       <c r="V3" s="4">
-        <f>'Receitas - Mapa'!H19</f>
-        <v>0</v>
-      </c>
-      <c r="X3" s="38"/>
+        <f>'Receita Líquida'!H13</f>
+        <v>0</v>
+      </c>
+      <c r="X3" s="36"/>
       <c r="Y3" s="4">
-        <f>'Receitas - Mapa'!I19</f>
-        <v>0</v>
-      </c>
-      <c r="AA3" s="38"/>
+        <f>'Receita Líquida'!I13</f>
+        <v>0</v>
+      </c>
+      <c r="AA3" s="36"/>
       <c r="AB3" s="4">
-        <f>'Receitas - Mapa'!J19</f>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="38"/>
+        <f>'Receita Líquida'!J13</f>
+        <v>0</v>
+      </c>
+      <c r="AD3" s="36"/>
       <c r="AE3" s="4">
-        <f>'Receitas - Mapa'!K19</f>
-        <v>150</v>
-      </c>
-      <c r="AG3" s="38"/>
+        <f>'Receita Líquida'!K13</f>
+        <v>0</v>
+      </c>
+      <c r="AG3" s="36"/>
       <c r="AH3" s="4">
-        <f>'Receitas - Mapa'!L19</f>
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="38"/>
+        <f>'Receita Líquida'!L13</f>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="36"/>
       <c r="AK3" s="4">
-        <f>'Receitas - Mapa'!M19</f>
+        <f>'Receita Líquida'!M13</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="D4" s="51">
+      <c r="B4" s="37"/>
+      <c r="D4" s="49">
         <f>D3-(SUM(D7:D15))</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="40"/>
+        <v>50</v>
+      </c>
+      <c r="E4" s="38"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="51">
+      <c r="G4" s="49">
         <f>G3-(SUM(G7:G15))+D4</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="40"/>
-      <c r="J4" s="51">
+        <v>50</v>
+      </c>
+      <c r="H4" s="38"/>
+      <c r="J4" s="49">
         <f>J3-(SUM(J7:J15))+G4</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="40"/>
-      <c r="M4" s="51">
+        <v>50</v>
+      </c>
+      <c r="K4" s="38"/>
+      <c r="M4" s="49">
         <f>M3-(SUM(M7:M15))+J4</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="40"/>
-      <c r="P4" s="51">
+        <v>50</v>
+      </c>
+      <c r="N4" s="38"/>
+      <c r="P4" s="49">
         <f>P3-(SUM(P7:P15))+M4</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="40"/>
-      <c r="S4" s="51">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="38"/>
+      <c r="S4" s="49">
         <f>S3-(SUM(S7:S15))+P4</f>
-        <v>0</v>
-      </c>
-      <c r="T4" s="40"/>
-      <c r="V4" s="51">
+        <v>50</v>
+      </c>
+      <c r="T4" s="38"/>
+      <c r="V4" s="49">
         <f>V3-(SUM(V7:V15))+S4</f>
-        <v>0</v>
-      </c>
-      <c r="W4" s="40"/>
-      <c r="Y4" s="51">
+        <v>50</v>
+      </c>
+      <c r="W4" s="38"/>
+      <c r="Y4" s="49">
         <f>Y3-(SUM(Y7:Y15))+V4</f>
-        <v>0</v>
-      </c>
-      <c r="Z4" s="40"/>
-      <c r="AB4" s="51">
+        <v>50</v>
+      </c>
+      <c r="Z4" s="38"/>
+      <c r="AB4" s="49">
         <f>AB3-(SUM(AB7:AB15))+Y4</f>
-        <v>0</v>
-      </c>
-      <c r="AC4" s="40"/>
-      <c r="AE4" s="51">
+        <v>50</v>
+      </c>
+      <c r="AC4" s="38"/>
+      <c r="AE4" s="49">
         <f>AE3-(SUM(AE7:AE15))+AB4</f>
         <v>50</v>
       </c>
-      <c r="AF4" s="40"/>
-      <c r="AH4" s="51">
+      <c r="AF4" s="38"/>
+      <c r="AH4" s="49">
         <f>AH3-(SUM(AH7:AH15))+AE4</f>
         <v>50</v>
       </c>
-      <c r="AI4" s="40"/>
-      <c r="AK4" s="51">
+      <c r="AI4" s="38"/>
+      <c r="AK4" s="49">
         <f>AK3-SUM(AK7:AK15)+AH4</f>
         <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-      <c r="S5" s="39"/>
-      <c r="T5" s="39"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="39"/>
-      <c r="W5" s="39"/>
-      <c r="X5" s="39"/>
-      <c r="Y5" s="39"/>
-      <c r="Z5" s="39"/>
-      <c r="AA5" s="39"/>
-      <c r="AB5" s="39"/>
-      <c r="AC5" s="39"/>
-      <c r="AD5" s="39"/>
-      <c r="AE5" s="39"/>
-      <c r="AF5" s="39"/>
-      <c r="AG5" s="39"/>
-      <c r="AH5" s="39"/>
-      <c r="AI5" s="39"/>
-      <c r="AJ5" s="39"/>
-      <c r="AK5" s="39"/>
+      <c r="A5" s="39"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="37"/>
+      <c r="V5" s="37"/>
+      <c r="W5" s="37"/>
+      <c r="X5" s="37"/>
+      <c r="Y5" s="37"/>
+      <c r="Z5" s="37"/>
+      <c r="AA5" s="37"/>
+      <c r="AB5" s="37"/>
+      <c r="AC5" s="37"/>
+      <c r="AD5" s="37"/>
+      <c r="AE5" s="37"/>
+      <c r="AF5" s="37"/>
+      <c r="AG5" s="37"/>
+      <c r="AH5" s="37"/>
+      <c r="AI5" s="37"/>
+      <c r="AJ5" s="37"/>
+      <c r="AK5" s="37"/>
     </row>
     <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="39"/>
-      <c r="L6" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="39"/>
-      <c r="O6" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="P6" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="S6" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="T6" s="39"/>
-      <c r="U6" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="V6" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="W6" s="39"/>
-      <c r="X6" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y6" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z6" s="39"/>
-      <c r="AA6" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB6" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE6" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF6" s="39"/>
-      <c r="AG6" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH6" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI6" s="39"/>
-      <c r="AJ6" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK6" s="49" t="s">
-        <v>31</v>
+      <c r="B6" s="40"/>
+      <c r="C6" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="37"/>
+      <c r="F6" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="37"/>
+      <c r="I6" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="37"/>
+      <c r="L6" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="37"/>
+      <c r="O6" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="T6" s="37"/>
+      <c r="U6" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="V6" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="W6" s="37"/>
+      <c r="X6" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y6" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z6" s="37"/>
+      <c r="AA6" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB6" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC6" s="37"/>
+      <c r="AD6" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE6" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF6" s="37"/>
+      <c r="AG6" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH6" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI6" s="37"/>
+      <c r="AJ6" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK6" s="47" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="103"/>
-      <c r="B7" s="42"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C7)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!C7)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="34"/>
       <c r="F7" s="6" t="str" cm="1">
         <f t="array" ref="F7:F15">Categorias</f>
         <v>Alimentação</v>
       </c>
-      <c r="G7" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!G$2,Tabela1[Categoria],'Despesas - Mapa'!F7)</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="36"/>
+      <c r="G7" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!F7)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="34"/>
       <c r="I7" s="2" t="str" cm="1">
         <f t="array" ref="I7:I15">Categorias</f>
         <v>Alimentação</v>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!J$2,Tabela1[Categoria],'Despesas - Mapa'!I7)</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!I7)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="34"/>
       <c r="L7" s="6" t="str" cm="1">
         <f t="array" ref="L7:L15">Categorias</f>
         <v>Alimentação</v>
       </c>
-      <c r="M7" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!M$2,Tabela1[Categoria],'Despesas - Mapa'!L7)</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="36"/>
+      <c r="M7" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!L7)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="34"/>
       <c r="O7" s="2" t="str" cm="1">
         <f t="array" ref="O7:O15">Categorias</f>
         <v>Alimentação</v>
       </c>
       <c r="P7" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!P$2,Tabela1[Categoria],'Despesas - Mapa'!O7)</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!P$2,Tabela1[Categoria],'Despesas Gerais'!O7)</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="34"/>
       <c r="R7" s="6" t="str" cm="1">
         <f t="array" ref="R7:R15">Categorias</f>
         <v>Alimentação</v>
       </c>
-      <c r="S7" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!S$2,Tabela1[Categoria],'Despesas - Mapa'!R7)</f>
-        <v>0</v>
-      </c>
-      <c r="T7" s="36"/>
+      <c r="S7" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!S$2,Tabela1[Categoria],'Despesas Gerais'!R7)</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="34"/>
       <c r="U7" s="2" t="str" cm="1">
         <f t="array" ref="U7:U15">Categorias</f>
         <v>Alimentação</v>
       </c>
       <c r="V7" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!V$2,Tabela1[Categoria],'Despesas - Mapa'!U7)</f>
-        <v>0</v>
-      </c>
-      <c r="W7" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!V$2,Tabela1[Categoria],'Despesas Gerais'!U7)</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="34"/>
       <c r="X7" s="6" t="str" cm="1">
         <f t="array" ref="X7:X15">Categorias</f>
         <v>Alimentação</v>
       </c>
-      <c r="Y7" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!Y$2,Tabela1[Categoria],'Despesas - Mapa'!X7)</f>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="36"/>
+      <c r="Y7" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!Y$2,Tabela1[Categoria],'Despesas Gerais'!X7)</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="34"/>
       <c r="AA7" s="2" t="str" cm="1">
         <f t="array" ref="AA7:AA15">Categorias</f>
         <v>Alimentação</v>
       </c>
       <c r="AB7" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AB$2,Tabela1[Categoria],'Despesas - Mapa'!AA7)</f>
-        <v>0</v>
-      </c>
-      <c r="AC7" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AB$2,Tabela1[Categoria],'Despesas Gerais'!AA7)</f>
+        <v>0</v>
+      </c>
+      <c r="AC7" s="34"/>
       <c r="AD7" s="6" t="str" cm="1">
         <f t="array" ref="AD7:AD15">Categorias</f>
         <v>Alimentação</v>
       </c>
-      <c r="AE7" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AE$2,Tabela1[Categoria],'Despesas - Mapa'!AD7)</f>
-        <v>0</v>
-      </c>
-      <c r="AF7" s="36"/>
+      <c r="AE7" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AE$2,Tabela1[Categoria],'Despesas Gerais'!AD7)</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="34"/>
       <c r="AG7" s="2" t="str" cm="1">
         <f t="array" ref="AG7:AG15">Categorias</f>
         <v>Alimentação</v>
       </c>
       <c r="AH7" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AH$2,Tabela1[Categoria],'Despesas - Mapa'!AG7)</f>
-        <v>0</v>
-      </c>
-      <c r="AI7" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AH$2,Tabela1[Categoria],'Despesas Gerais'!AG7)</f>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="34"/>
       <c r="AJ7" s="6" t="str" cm="1">
         <f t="array" ref="AJ7:AJ15">Categorias</f>
         <v>Alimentação</v>
       </c>
-      <c r="AK7" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AK$2,Tabela1[Categoria],'Despesas - Mapa'!AJ7)</f>
+      <c r="AK7" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AK$2,Tabela1[Categoria],'Despesas Gerais'!AJ7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="103"/>
-      <c r="B8" s="42"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C8)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!C8)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="34"/>
       <c r="F8" s="6" t="str">
         <v>G. Resid.</v>
       </c>
-      <c r="G8" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!G$2,Tabela1[Categoria],'Despesas - Mapa'!F8)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="36"/>
+      <c r="G8" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!F8)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="34"/>
       <c r="I8" s="2" t="str">
         <v>G. Resid.</v>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!J$2,Tabela1[Categoria],'Despesas - Mapa'!I8)</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!I8)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="34"/>
       <c r="L8" s="6" t="str">
         <v>G. Resid.</v>
       </c>
-      <c r="M8" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!M$2,Tabela1[Categoria],'Despesas - Mapa'!L8)</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="36"/>
+      <c r="M8" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!L8)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="34"/>
       <c r="O8" s="2" t="str">
         <v>G. Resid.</v>
       </c>
       <c r="P8" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!P$2,Tabela1[Categoria],'Despesas - Mapa'!O8)</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!P$2,Tabela1[Categoria],'Despesas Gerais'!O8)</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="34"/>
       <c r="R8" s="6" t="str">
         <v>G. Resid.</v>
       </c>
-      <c r="S8" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!S$2,Tabela1[Categoria],'Despesas - Mapa'!R8)</f>
-        <v>0</v>
-      </c>
-      <c r="T8" s="36"/>
+      <c r="S8" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!S$2,Tabela1[Categoria],'Despesas Gerais'!R8)</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="34"/>
       <c r="U8" s="2" t="str">
         <v>G. Resid.</v>
       </c>
       <c r="V8" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!V$2,Tabela1[Categoria],'Despesas - Mapa'!U8)</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!V$2,Tabela1[Categoria],'Despesas Gerais'!U8)</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="34"/>
       <c r="X8" s="6" t="str">
         <v>G. Resid.</v>
       </c>
-      <c r="Y8" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!Y$2,Tabela1[Categoria],'Despesas - Mapa'!X8)</f>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="36"/>
+      <c r="Y8" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!Y$2,Tabela1[Categoria],'Despesas Gerais'!X8)</f>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="34"/>
       <c r="AA8" s="2" t="str">
         <v>G. Resid.</v>
       </c>
       <c r="AB8" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AB$2,Tabela1[Categoria],'Despesas - Mapa'!AA8)</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AB$2,Tabela1[Categoria],'Despesas Gerais'!AA8)</f>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="34"/>
       <c r="AD8" s="6" t="str">
         <v>G. Resid.</v>
       </c>
-      <c r="AE8" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AE$2,Tabela1[Categoria],'Despesas - Mapa'!AD8)</f>
-        <v>0</v>
-      </c>
-      <c r="AF8" s="36"/>
+      <c r="AE8" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AE$2,Tabela1[Categoria],'Despesas Gerais'!AD8)</f>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="34"/>
       <c r="AG8" s="2" t="str">
         <v>G. Resid.</v>
       </c>
       <c r="AH8" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AH$2,Tabela1[Categoria],'Despesas - Mapa'!AG8)</f>
-        <v>0</v>
-      </c>
-      <c r="AI8" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AH$2,Tabela1[Categoria],'Despesas Gerais'!AG8)</f>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="34"/>
       <c r="AJ8" s="6" t="str">
         <v>G. Resid.</v>
       </c>
-      <c r="AK8" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AK$2,Tabela1[Categoria],'Despesas - Mapa'!AJ8)</f>
+      <c r="AK8" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AK$2,Tabela1[Categoria],'Despesas Gerais'!AJ8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="103"/>
-      <c r="B9" s="42"/>
+      <c r="A9" s="104"/>
+      <c r="B9" s="40"/>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C9)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!C9)</f>
+        <v>50</v>
+      </c>
+      <c r="E9" s="34"/>
       <c r="F9" s="6" t="str">
         <v>Eletron e Jogos</v>
       </c>
-      <c r="G9" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!G$2,Tabela1[Categoria],'Despesas - Mapa'!F9)</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="36"/>
+      <c r="G9" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!F9)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="34"/>
       <c r="I9" s="2" t="str">
         <v>Eletron e Jogos</v>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!J$2,Tabela1[Categoria],'Despesas - Mapa'!I9)</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!I9)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="34"/>
       <c r="L9" s="6" t="str">
         <v>Eletron e Jogos</v>
       </c>
-      <c r="M9" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!M$2,Tabela1[Categoria],'Despesas - Mapa'!L9)</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="36"/>
+      <c r="M9" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!L9)</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="34"/>
       <c r="O9" s="2" t="str">
         <v>Eletron e Jogos</v>
       </c>
       <c r="P9" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!P$2,Tabela1[Categoria],'Despesas - Mapa'!O9)</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!P$2,Tabela1[Categoria],'Despesas Gerais'!O9)</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="34"/>
       <c r="R9" s="6" t="str">
         <v>Eletron e Jogos</v>
       </c>
-      <c r="S9" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!S$2,Tabela1[Categoria],'Despesas - Mapa'!R9)</f>
-        <v>0</v>
-      </c>
-      <c r="T9" s="36"/>
+      <c r="S9" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!S$2,Tabela1[Categoria],'Despesas Gerais'!R9)</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="34"/>
       <c r="U9" s="2" t="str">
         <v>Eletron e Jogos</v>
       </c>
       <c r="V9" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!V$2,Tabela1[Categoria],'Despesas - Mapa'!U9)</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!V$2,Tabela1[Categoria],'Despesas Gerais'!U9)</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="34"/>
       <c r="X9" s="6" t="str">
         <v>Eletron e Jogos</v>
       </c>
-      <c r="Y9" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!Y$2,Tabela1[Categoria],'Despesas - Mapa'!X9)</f>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="36"/>
+      <c r="Y9" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!Y$2,Tabela1[Categoria],'Despesas Gerais'!X9)</f>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="34"/>
       <c r="AA9" s="2" t="str">
         <v>Eletron e Jogos</v>
       </c>
       <c r="AB9" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AB$2,Tabela1[Categoria],'Despesas - Mapa'!AA9)</f>
-        <v>0</v>
-      </c>
-      <c r="AC9" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AB$2,Tabela1[Categoria],'Despesas Gerais'!AA9)</f>
+        <v>0</v>
+      </c>
+      <c r="AC9" s="34"/>
       <c r="AD9" s="6" t="str">
         <v>Eletron e Jogos</v>
       </c>
-      <c r="AE9" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AE$2,Tabela1[Categoria],'Despesas - Mapa'!AD9)</f>
-        <v>50</v>
-      </c>
-      <c r="AF9" s="36"/>
+      <c r="AE9" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AE$2,Tabela1[Categoria],'Despesas Gerais'!AD9)</f>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="34"/>
       <c r="AG9" s="2" t="str">
         <v>Eletron e Jogos</v>
       </c>
       <c r="AH9" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AH$2,Tabela1[Categoria],'Despesas - Mapa'!AG9)</f>
-        <v>0</v>
-      </c>
-      <c r="AI9" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AH$2,Tabela1[Categoria],'Despesas Gerais'!AG9)</f>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="34"/>
       <c r="AJ9" s="6" t="str">
         <v>Eletron e Jogos</v>
       </c>
-      <c r="AK9" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AK$2,Tabela1[Categoria],'Despesas - Mapa'!AJ9)</f>
+      <c r="AK9" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AK$2,Tabela1[Categoria],'Despesas Gerais'!AJ9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="103"/>
-      <c r="B10" s="42"/>
+      <c r="A10" s="104"/>
+      <c r="B10" s="40"/>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C10)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!C10)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="34"/>
       <c r="F10" s="6" t="str">
         <v>Cursos</v>
       </c>
-      <c r="G10" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!G$2,Tabela1[Categoria],'Despesas - Mapa'!F10)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="36"/>
+      <c r="G10" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!F10)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="34"/>
       <c r="I10" s="2" t="str">
         <v>Cursos</v>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!J$2,Tabela1[Categoria],'Despesas - Mapa'!I10)</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!I10)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="34"/>
       <c r="L10" s="6" t="str">
         <v>Cursos</v>
       </c>
-      <c r="M10" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!M$2,Tabela1[Categoria],'Despesas - Mapa'!L10)</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="36"/>
+      <c r="M10" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!L10)</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="34"/>
       <c r="O10" s="2" t="str">
         <v>Cursos</v>
       </c>
       <c r="P10" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!P$2,Tabela1[Categoria],'Despesas - Mapa'!O10)</f>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!P$2,Tabela1[Categoria],'Despesas Gerais'!O10)</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="34"/>
       <c r="R10" s="6" t="str">
         <v>Cursos</v>
       </c>
-      <c r="S10" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!S$2,Tabela1[Categoria],'Despesas - Mapa'!R10)</f>
-        <v>0</v>
-      </c>
-      <c r="T10" s="36"/>
+      <c r="S10" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!S$2,Tabela1[Categoria],'Despesas Gerais'!R10)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="34"/>
       <c r="U10" s="2" t="str">
         <v>Cursos</v>
       </c>
       <c r="V10" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!V$2,Tabela1[Categoria],'Despesas - Mapa'!U10)</f>
-        <v>0</v>
-      </c>
-      <c r="W10" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!V$2,Tabela1[Categoria],'Despesas Gerais'!U10)</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="34"/>
       <c r="X10" s="6" t="str">
         <v>Cursos</v>
       </c>
-      <c r="Y10" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!Y$2,Tabela1[Categoria],'Despesas - Mapa'!X10)</f>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="36"/>
+      <c r="Y10" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!Y$2,Tabela1[Categoria],'Despesas Gerais'!X10)</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="34"/>
       <c r="AA10" s="2" t="str">
         <v>Cursos</v>
       </c>
       <c r="AB10" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AB$2,Tabela1[Categoria],'Despesas - Mapa'!AA10)</f>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AB$2,Tabela1[Categoria],'Despesas Gerais'!AA10)</f>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="34"/>
       <c r="AD10" s="6" t="str">
         <v>Cursos</v>
       </c>
-      <c r="AE10" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AE$2,Tabela1[Categoria],'Despesas - Mapa'!AD10)</f>
-        <v>0</v>
-      </c>
-      <c r="AF10" s="36"/>
+      <c r="AE10" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AE$2,Tabela1[Categoria],'Despesas Gerais'!AD10)</f>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="34"/>
       <c r="AG10" s="2" t="str">
         <v>Cursos</v>
       </c>
       <c r="AH10" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AH$2,Tabela1[Categoria],'Despesas - Mapa'!AG10)</f>
-        <v>0</v>
-      </c>
-      <c r="AI10" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AH$2,Tabela1[Categoria],'Despesas Gerais'!AG10)</f>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="34"/>
       <c r="AJ10" s="6" t="str">
         <v>Cursos</v>
       </c>
-      <c r="AK10" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AK$2,Tabela1[Categoria],'Despesas - Mapa'!AJ10)</f>
+      <c r="AK10" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AK$2,Tabela1[Categoria],'Despesas Gerais'!AJ10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="103"/>
-      <c r="B11" s="42"/>
+      <c r="A11" s="104"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C11)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!C11)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="34"/>
       <c r="F11" s="6" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="G11" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!G$2,Tabela1[Categoria],'Despesas - Mapa'!F11)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="36"/>
+      <c r="G11" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!F11)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="34"/>
       <c r="I11" s="2" t="str">
         <v>Farm. e Saúde.</v>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!J$2,Tabela1[Categoria],'Despesas - Mapa'!I11)</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!I11)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="34"/>
       <c r="L11" s="6" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="M11" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!M$2,Tabela1[Categoria],'Despesas - Mapa'!L11)</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="36"/>
+      <c r="M11" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!L11)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="34"/>
       <c r="O11" s="2" t="str">
         <v>Farm. e Saúde.</v>
       </c>
       <c r="P11" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!P$2,Tabela1[Categoria],'Despesas - Mapa'!O11)</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!P$2,Tabela1[Categoria],'Despesas Gerais'!O11)</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="34"/>
       <c r="R11" s="6" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="S11" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!S$2,Tabela1[Categoria],'Despesas - Mapa'!R11)</f>
-        <v>0</v>
-      </c>
-      <c r="T11" s="36"/>
+      <c r="S11" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!S$2,Tabela1[Categoria],'Despesas Gerais'!R11)</f>
+        <v>0</v>
+      </c>
+      <c r="T11" s="34"/>
       <c r="U11" s="2" t="str">
         <v>Farm. e Saúde.</v>
       </c>
       <c r="V11" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!V$2,Tabela1[Categoria],'Despesas - Mapa'!U11)</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!V$2,Tabela1[Categoria],'Despesas Gerais'!U11)</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="34"/>
       <c r="X11" s="6" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="Y11" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!Y$2,Tabela1[Categoria],'Despesas - Mapa'!X11)</f>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="36"/>
+      <c r="Y11" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!Y$2,Tabela1[Categoria],'Despesas Gerais'!X11)</f>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="34"/>
       <c r="AA11" s="2" t="str">
         <v>Farm. e Saúde.</v>
       </c>
       <c r="AB11" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AB$2,Tabela1[Categoria],'Despesas - Mapa'!AA11)</f>
-        <v>0</v>
-      </c>
-      <c r="AC11" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AB$2,Tabela1[Categoria],'Despesas Gerais'!AA11)</f>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="34"/>
       <c r="AD11" s="6" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="AE11" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AE$2,Tabela1[Categoria],'Despesas - Mapa'!AD11)</f>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="36"/>
+      <c r="AE11" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AE$2,Tabela1[Categoria],'Despesas Gerais'!AD11)</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="34"/>
       <c r="AG11" s="2" t="str">
         <v>Farm. e Saúde.</v>
       </c>
       <c r="AH11" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AH$2,Tabela1[Categoria],'Despesas - Mapa'!AG11)</f>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AH$2,Tabela1[Categoria],'Despesas Gerais'!AG11)</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="34"/>
       <c r="AJ11" s="6" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="AK11" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AK$2,Tabela1[Categoria],'Despesas - Mapa'!AJ11)</f>
+      <c r="AK11" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AK$2,Tabela1[Categoria],'Despesas Gerais'!AJ11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="103"/>
-      <c r="B12" s="42"/>
+      <c r="A12" s="104"/>
+      <c r="B12" s="40"/>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C12)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!C12)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="34"/>
       <c r="F12" s="6" t="str">
         <v>Entret e Livros</v>
       </c>
-      <c r="G12" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!G$2,Tabela1[Categoria],'Despesas - Mapa'!F12)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="36"/>
+      <c r="G12" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!F12)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="34"/>
       <c r="I12" s="2" t="str">
         <v>Entret e Livros</v>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!J$2,Tabela1[Categoria],'Despesas - Mapa'!I12)</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!I12)</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="34"/>
       <c r="L12" s="6" t="str">
         <v>Entret e Livros</v>
       </c>
-      <c r="M12" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!M$2,Tabela1[Categoria],'Despesas - Mapa'!L12)</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="36"/>
+      <c r="M12" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!L12)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="34"/>
       <c r="O12" s="2" t="str">
         <v>Entret e Livros</v>
       </c>
       <c r="P12" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!P$2,Tabela1[Categoria],'Despesas - Mapa'!O12)</f>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!P$2,Tabela1[Categoria],'Despesas Gerais'!O12)</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="34"/>
       <c r="R12" s="6" t="str">
         <v>Entret e Livros</v>
       </c>
-      <c r="S12" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!S$2,Tabela1[Categoria],'Despesas - Mapa'!R12)</f>
-        <v>0</v>
-      </c>
-      <c r="T12" s="36"/>
+      <c r="S12" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!S$2,Tabela1[Categoria],'Despesas Gerais'!R12)</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="34"/>
       <c r="U12" s="2" t="str">
         <v>Entret e Livros</v>
       </c>
       <c r="V12" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!V$2,Tabela1[Categoria],'Despesas - Mapa'!U12)</f>
-        <v>0</v>
-      </c>
-      <c r="W12" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!V$2,Tabela1[Categoria],'Despesas Gerais'!U12)</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="34"/>
       <c r="X12" s="6" t="str">
         <v>Entret e Livros</v>
       </c>
-      <c r="Y12" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!Y$2,Tabela1[Categoria],'Despesas - Mapa'!X12)</f>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="36"/>
+      <c r="Y12" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!Y$2,Tabela1[Categoria],'Despesas Gerais'!X12)</f>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="34"/>
       <c r="AA12" s="2" t="str">
         <v>Entret e Livros</v>
       </c>
       <c r="AB12" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AB$2,Tabela1[Categoria],'Despesas - Mapa'!AA12)</f>
-        <v>0</v>
-      </c>
-      <c r="AC12" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AB$2,Tabela1[Categoria],'Despesas Gerais'!AA12)</f>
+        <v>0</v>
+      </c>
+      <c r="AC12" s="34"/>
       <c r="AD12" s="6" t="str">
         <v>Entret e Livros</v>
       </c>
-      <c r="AE12" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AE$2,Tabela1[Categoria],'Despesas - Mapa'!AD12)</f>
-        <v>0</v>
-      </c>
-      <c r="AF12" s="36"/>
+      <c r="AE12" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AE$2,Tabela1[Categoria],'Despesas Gerais'!AD12)</f>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="34"/>
       <c r="AG12" s="2" t="str">
         <v>Entret e Livros</v>
       </c>
       <c r="AH12" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AH$2,Tabela1[Categoria],'Despesas - Mapa'!AG12)</f>
-        <v>0</v>
-      </c>
-      <c r="AI12" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AH$2,Tabela1[Categoria],'Despesas Gerais'!AG12)</f>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="34"/>
       <c r="AJ12" s="6" t="str">
         <v>Entret e Livros</v>
       </c>
-      <c r="AK12" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AK$2,Tabela1[Categoria],'Despesas - Mapa'!AJ12)</f>
+      <c r="AK12" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AK$2,Tabela1[Categoria],'Despesas Gerais'!AJ12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="103"/>
-      <c r="B13" s="42"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C13)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!C13)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="34"/>
       <c r="F13" s="6" t="str">
         <v>Rolê</v>
       </c>
-      <c r="G13" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!G$2,Tabela1[Categoria],'Despesas - Mapa'!F13)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="36"/>
+      <c r="G13" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!F13)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="34"/>
       <c r="I13" s="2" t="str">
         <v>Rolê</v>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!J$2,Tabela1[Categoria],'Despesas - Mapa'!I13)</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!I13)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="34"/>
       <c r="L13" s="6" t="str">
         <v>Rolê</v>
       </c>
-      <c r="M13" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!M$2,Tabela1[Categoria],'Despesas - Mapa'!L13)</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="36"/>
+      <c r="M13" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!L13)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="34"/>
       <c r="O13" s="2" t="str">
         <v>Rolê</v>
       </c>
       <c r="P13" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!P$2,Tabela1[Categoria],'Despesas - Mapa'!O13)</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!P$2,Tabela1[Categoria],'Despesas Gerais'!O13)</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="34"/>
       <c r="R13" s="6" t="str">
         <v>Rolê</v>
       </c>
-      <c r="S13" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!S$2,Tabela1[Categoria],'Despesas - Mapa'!R13)</f>
-        <v>0</v>
-      </c>
-      <c r="T13" s="36"/>
+      <c r="S13" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!S$2,Tabela1[Categoria],'Despesas Gerais'!R13)</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="34"/>
       <c r="U13" s="2" t="str">
         <v>Rolê</v>
       </c>
       <c r="V13" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!V$2,Tabela1[Categoria],'Despesas - Mapa'!U13)</f>
-        <v>0</v>
-      </c>
-      <c r="W13" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!V$2,Tabela1[Categoria],'Despesas Gerais'!U13)</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="34"/>
       <c r="X13" s="6" t="str">
         <v>Rolê</v>
       </c>
-      <c r="Y13" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!Y$2,Tabela1[Categoria],'Despesas - Mapa'!X13)</f>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="36"/>
+      <c r="Y13" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!Y$2,Tabela1[Categoria],'Despesas Gerais'!X13)</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="34"/>
       <c r="AA13" s="2" t="str">
         <v>Rolê</v>
       </c>
       <c r="AB13" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AB$2,Tabela1[Categoria],'Despesas - Mapa'!AA13)</f>
-        <v>0</v>
-      </c>
-      <c r="AC13" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AB$2,Tabela1[Categoria],'Despesas Gerais'!AA13)</f>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="34"/>
       <c r="AD13" s="6" t="str">
         <v>Rolê</v>
       </c>
-      <c r="AE13" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AE$2,Tabela1[Categoria],'Despesas - Mapa'!AD13)</f>
-        <v>0</v>
-      </c>
-      <c r="AF13" s="36"/>
+      <c r="AE13" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AE$2,Tabela1[Categoria],'Despesas Gerais'!AD13)</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="34"/>
       <c r="AG13" s="2" t="str">
         <v>Rolê</v>
       </c>
       <c r="AH13" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AH$2,Tabela1[Categoria],'Despesas - Mapa'!AG13)</f>
-        <v>0</v>
-      </c>
-      <c r="AI13" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AH$2,Tabela1[Categoria],'Despesas Gerais'!AG13)</f>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="34"/>
       <c r="AJ13" s="6" t="str">
         <v>Rolê</v>
       </c>
-      <c r="AK13" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AK$2,Tabela1[Categoria],'Despesas - Mapa'!AJ13)</f>
+      <c r="AK13" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AK$2,Tabela1[Categoria],'Despesas Gerais'!AJ13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="103"/>
-      <c r="B14" s="42"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C14)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!C14)</f>
+        <v>50</v>
+      </c>
+      <c r="E14" s="34"/>
       <c r="F14" s="6" t="str">
         <v>Roupas</v>
       </c>
-      <c r="G14" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!G$2,Tabela1[Categoria],'Despesas - Mapa'!F14)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="36"/>
+      <c r="G14" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!F14)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="34"/>
       <c r="I14" s="2" t="str">
         <v>Roupas</v>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!J$2,Tabela1[Categoria],'Despesas - Mapa'!I14)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!I14)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="34"/>
       <c r="L14" s="6" t="str">
         <v>Roupas</v>
       </c>
-      <c r="M14" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!M$2,Tabela1[Categoria],'Despesas - Mapa'!L14)</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="36"/>
+      <c r="M14" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!L14)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="34"/>
       <c r="O14" s="2" t="str">
         <v>Roupas</v>
       </c>
       <c r="P14" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!P$2,Tabela1[Categoria],'Despesas - Mapa'!O14)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!P$2,Tabela1[Categoria],'Despesas Gerais'!O14)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="34"/>
       <c r="R14" s="6" t="str">
         <v>Roupas</v>
       </c>
-      <c r="S14" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!S$2,Tabela1[Categoria],'Despesas - Mapa'!R14)</f>
-        <v>0</v>
-      </c>
-      <c r="T14" s="36"/>
+      <c r="S14" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!S$2,Tabela1[Categoria],'Despesas Gerais'!R14)</f>
+        <v>0</v>
+      </c>
+      <c r="T14" s="34"/>
       <c r="U14" s="2" t="str">
         <v>Roupas</v>
       </c>
       <c r="V14" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!V$2,Tabela1[Categoria],'Despesas - Mapa'!U14)</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!V$2,Tabela1[Categoria],'Despesas Gerais'!U14)</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="34"/>
       <c r="X14" s="6" t="str">
         <v>Roupas</v>
       </c>
-      <c r="Y14" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!Y$2,Tabela1[Categoria],'Despesas - Mapa'!X14)</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="36"/>
+      <c r="Y14" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!Y$2,Tabela1[Categoria],'Despesas Gerais'!X14)</f>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="34"/>
       <c r="AA14" s="2" t="str">
         <v>Roupas</v>
       </c>
       <c r="AB14" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AB$2,Tabela1[Categoria],'Despesas - Mapa'!AA14)</f>
-        <v>0</v>
-      </c>
-      <c r="AC14" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AB$2,Tabela1[Categoria],'Despesas Gerais'!AA14)</f>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="34"/>
       <c r="AD14" s="6" t="str">
         <v>Roupas</v>
       </c>
-      <c r="AE14" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AE$2,Tabela1[Categoria],'Despesas - Mapa'!AD14)</f>
-        <v>50</v>
-      </c>
-      <c r="AF14" s="36"/>
+      <c r="AE14" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AE$2,Tabela1[Categoria],'Despesas Gerais'!AD14)</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="34"/>
       <c r="AG14" s="2" t="str">
         <v>Roupas</v>
       </c>
       <c r="AH14" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AH$2,Tabela1[Categoria],'Despesas - Mapa'!AG14)</f>
-        <v>0</v>
-      </c>
-      <c r="AI14" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AH$2,Tabela1[Categoria],'Despesas Gerais'!AG14)</f>
+        <v>0</v>
+      </c>
+      <c r="AI14" s="34"/>
       <c r="AJ14" s="6" t="str">
         <v>Roupas</v>
       </c>
-      <c r="AK14" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AK$2,Tabela1[Categoria],'Despesas - Mapa'!AJ14)</f>
+      <c r="AK14" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AK$2,Tabela1[Categoria],'Despesas Gerais'!AJ14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:37" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="66"/>
-      <c r="B15" s="43"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!D$2,Tabela1[Categoria],'Despesas - Mapa'!C15)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!C15)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="34"/>
       <c r="F15" s="6" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="G15" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!G$2,Tabela1[Categoria],'Despesas - Mapa'!F15)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="36"/>
+      <c r="G15" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!F15)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="34"/>
       <c r="I15" s="2" t="str">
         <v>G. Gerais</v>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!J$2,Tabela1[Categoria],'Despesas - Mapa'!I15)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!I15)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="34"/>
       <c r="L15" s="6" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="M15" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!M$2,Tabela1[Categoria],'Despesas - Mapa'!L15)</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="36"/>
+      <c r="M15" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!L15)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="34"/>
       <c r="O15" s="2" t="str">
         <v>G. Gerais</v>
       </c>
       <c r="P15" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!P$2,Tabela1[Categoria],'Despesas - Mapa'!O15)</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!P$2,Tabela1[Categoria],'Despesas Gerais'!O15)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="34"/>
       <c r="R15" s="6" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="S15" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!S$2,Tabela1[Categoria],'Despesas - Mapa'!R15)</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="36"/>
+      <c r="S15" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!S$2,Tabela1[Categoria],'Despesas Gerais'!R15)</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="34"/>
       <c r="U15" s="2" t="str">
         <v>G. Gerais</v>
       </c>
       <c r="V15" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!V$2,Tabela1[Categoria],'Despesas - Mapa'!U15)</f>
-        <v>0</v>
-      </c>
-      <c r="W15" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!V$2,Tabela1[Categoria],'Despesas Gerais'!U15)</f>
+        <v>0</v>
+      </c>
+      <c r="W15" s="34"/>
       <c r="X15" s="6" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="Y15" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!Y$2,Tabela1[Categoria],'Despesas - Mapa'!X15)</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="36"/>
+      <c r="Y15" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!Y$2,Tabela1[Categoria],'Despesas Gerais'!X15)</f>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="34"/>
       <c r="AA15" s="2" t="str">
         <v>G. Gerais</v>
       </c>
       <c r="AB15" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AB$2,Tabela1[Categoria],'Despesas - Mapa'!AA15)</f>
-        <v>0</v>
-      </c>
-      <c r="AC15" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AB$2,Tabela1[Categoria],'Despesas Gerais'!AA15)</f>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="34"/>
       <c r="AD15" s="6" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="AE15" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AE$2,Tabela1[Categoria],'Despesas - Mapa'!AD15)</f>
-        <v>0</v>
-      </c>
-      <c r="AF15" s="36"/>
+      <c r="AE15" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AE$2,Tabela1[Categoria],'Despesas Gerais'!AD15)</f>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="34"/>
       <c r="AG15" s="2" t="str">
         <v>G. Gerais</v>
       </c>
       <c r="AH15" s="4">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AH$2,Tabela1[Categoria],'Despesas - Mapa'!AG15)</f>
-        <v>0</v>
-      </c>
-      <c r="AI15" s="36"/>
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AH$2,Tabela1[Categoria],'Despesas Gerais'!AG15)</f>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="34"/>
       <c r="AJ15" s="6" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="AK15" s="63">
-        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas - Mapa'!AK$2,Tabela1[Categoria],'Despesas - Mapa'!AJ15)</f>
+      <c r="AK15" s="61">
+        <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!AK$2,Tabela1[Categoria],'Despesas Gerais'!AJ15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="59"/>
-      <c r="B16" s="43"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="61"/>
-      <c r="N16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="61"/>
-      <c r="T16" s="36"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="60"/>
-      <c r="Y16" s="61"/>
-      <c r="Z16" s="36"/>
-      <c r="AB16" s="36"/>
-      <c r="AC16" s="36"/>
-      <c r="AD16" s="60"/>
-      <c r="AE16" s="61"/>
-      <c r="AF16" s="36"/>
-      <c r="AH16" s="58"/>
-      <c r="AI16" s="36"/>
-      <c r="AJ16" s="60"/>
-      <c r="AK16" s="61"/>
-    </row>
-    <row r="17" spans="1:37" s="36" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="67" t="s">
+      <c r="A16" s="57"/>
+      <c r="B16" s="41"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="59"/>
+      <c r="N16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="59"/>
+      <c r="T16" s="34"/>
+      <c r="V16" s="34"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="58"/>
+      <c r="Y16" s="59"/>
+      <c r="Z16" s="34"/>
+      <c r="AB16" s="34"/>
+      <c r="AC16" s="34"/>
+      <c r="AD16" s="58"/>
+      <c r="AE16" s="59"/>
+      <c r="AF16" s="34"/>
+      <c r="AH16" s="56"/>
+      <c r="AI16" s="34"/>
+      <c r="AJ16" s="58"/>
+      <c r="AK16" s="59"/>
+    </row>
+    <row r="17" spans="1:38" s="34" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="101">
+      <c r="B17" s="42"/>
+      <c r="D17" s="99">
         <f>SUM(D7:D15)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="101"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="102">
+        <v>100</v>
+      </c>
+      <c r="E17" s="43"/>
+      <c r="G17" s="101">
         <f>SUM(G7:G15)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="102"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="101">
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="99">
         <f>SUM(J7:J15)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="101"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="102">
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="101">
         <f>SUM(M7:M15)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="102"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="101">
+      <c r="N17" s="100"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="99">
         <f>SUM(P7:P15)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="101"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="102">
+      <c r="Q17" s="100"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="101">
         <f>SUM(S7:S15)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="102"/>
-      <c r="T17" s="45"/>
-      <c r="U17" s="101">
+      <c r="T17" s="100"/>
+      <c r="U17" s="100"/>
+      <c r="V17" s="99">
         <f>SUM(V7:V15)</f>
         <v>0</v>
       </c>
-      <c r="V17" s="101"/>
-      <c r="W17" s="45"/>
-      <c r="X17" s="102">
+      <c r="W17" s="100"/>
+      <c r="X17" s="100"/>
+      <c r="Y17" s="101">
         <f>SUM(Y7:Y15)</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="102"/>
-      <c r="Z17" s="45"/>
-      <c r="AA17" s="101">
+      <c r="Z17" s="100"/>
+      <c r="AA17" s="100"/>
+      <c r="AB17" s="99">
         <f>SUM(AB7:AB15)</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="101"/>
-      <c r="AC17" s="45"/>
-      <c r="AD17" s="102">
+      <c r="AC17" s="100"/>
+      <c r="AD17" s="100"/>
+      <c r="AE17" s="101">
         <f>SUM(AE7:AE15)</f>
-        <v>100</v>
-      </c>
-      <c r="AE17" s="102"/>
-      <c r="AF17" s="45"/>
-      <c r="AG17" s="101">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="100"/>
+      <c r="AG17" s="100"/>
+      <c r="AH17" s="99">
         <f>SUM(AH7:AH15)</f>
         <v>0</v>
       </c>
-      <c r="AH17" s="101"/>
-      <c r="AI17" s="45"/>
-      <c r="AJ17" s="102">
+      <c r="AI17" s="100"/>
+      <c r="AJ17" s="100"/>
+      <c r="AK17" s="101">
         <f>SUM(AK7:AK15)</f>
         <v>0</v>
       </c>
-      <c r="AK17" s="102"/>
+      <c r="AL17" s="100"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D13:D15">
@@ -12475,20 +12408,8 @@
       <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="13">
+  <mergeCells count="1">
     <mergeCell ref="A6:A14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="AG17:AH17"/>
-    <mergeCell ref="AJ17:AK17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AD17:AE17"/>
   </mergeCells>
   <conditionalFormatting sqref="A4">
     <cfRule type="iconSet" priority="1">
@@ -12543,684 +12464,684 @@
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="22" t="s">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="12" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>55</v>
+      <c r="G2" s="12"/>
+      <c r="H2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="104" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="105"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="104" t="s">
+      <c r="K2" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="106"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="105"/>
-      <c r="P2" s="81"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="78"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="str">
+      <c r="A3" s="13" t="str">
         <f>PROPER(TEXT("01/01","MMMM"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="23">
-        <f>'Receitas - Mapa'!B19</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="24">
-        <f>SUM('Receitas - Mapa'!B16:B17)</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="29">
-        <f>SUM('Despesas - Mapa'!C17:C17)</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="23">
+      <c r="B3" s="12"/>
+      <c r="C3" s="22">
+        <f>'Receita Líquida'!B13</f>
+        <v>150</v>
+      </c>
+      <c r="D3" s="23">
+        <f>SUM('Receita Líquida'!B9:B10)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="14"/>
+      <c r="F3" s="28">
+        <f>SUM('Despesas Gerais'!D17:D17)</f>
+        <v>100</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="22">
         <f>I3</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="26">
-        <f>'Despesas - Mapa'!D4</f>
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="I3" s="25">
+        <f>'Despesas Gerais'!D4</f>
+        <v>50</v>
       </c>
       <c r="J3" s="8"/>
-      <c r="K3" s="83" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="24">
-        <f>SUM('Receitas - Mapa'!B4:M6)</f>
+      <c r="K3" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="23">
+        <f>SUM('Receita Líquida'!B3:M5)</f>
         <v>150</v>
       </c>
-      <c r="M3" s="15"/>
-      <c r="N3" s="85" t="str">
-        <f>'Despesas - Mapa'!C7</f>
+      <c r="M3" s="14"/>
+      <c r="N3" s="82" t="str">
+        <f>'Despesas Gerais'!C7</f>
         <v>Alimentação</v>
       </c>
-      <c r="O3" s="86">
-        <f>SUM('Despesas - Mapa'!D7,'Despesas - Mapa'!G7,'Despesas - Mapa'!J7,'Despesas - Mapa'!M7,'Despesas - Mapa'!P7,'Despesas - Mapa'!S7,'Despesas - Mapa'!V7,'Despesas - Mapa'!Y7,'Despesas - Mapa'!AB7,'Despesas - Mapa'!AE7,'Despesas - Mapa'!AH7,'Despesas - Mapa'!AK7)</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="81"/>
+      <c r="O3" s="83">
+        <f>SUM('Despesas Gerais'!D7,'Despesas Gerais'!G7,'Despesas Gerais'!J7,'Despesas Gerais'!M7,'Despesas Gerais'!P7,'Despesas Gerais'!S7,'Despesas Gerais'!V7,'Despesas Gerais'!Y7,'Despesas Gerais'!AB7,'Despesas Gerais'!AE7,'Despesas Gerais'!AH7,'Despesas Gerais'!AK7)</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="78"/>
     </row>
     <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="str">
+      <c r="A4" s="13" t="str">
         <f>PROPER(TEXT("01/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="23">
-        <f>'Receitas - Mapa'!C19</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="24">
-        <f>SUM('Receitas - Mapa'!C16:C17)</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="29">
-        <f>SUM('Despesas - Mapa'!F17:G17)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="23">
+      <c r="B4" s="12"/>
+      <c r="C4" s="22">
+        <f>'Receita Líquida'!C13</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="23">
+        <f>SUM('Receita Líquida'!C9:C10)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="28">
+        <f>SUM('Despesas Gerais'!G17:H17)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="22">
         <f t="shared" ref="H4:H14" si="0">I4-I3</f>
         <v>0</v>
       </c>
-      <c r="I4" s="26">
-        <f>'Despesas - Mapa'!G4</f>
-        <v>0</v>
+      <c r="I4" s="25">
+        <f>'Despesas Gerais'!G4</f>
+        <v>50</v>
       </c>
       <c r="J4" s="8"/>
-      <c r="K4" s="83" t="s">
+      <c r="K4" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="24">
-        <f>SUM('Receitas - Mapa'!B9:M12)</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="85" t="str">
-        <f>'Despesas - Mapa'!C8</f>
+      <c r="L4" s="23">
+        <f>SUM('Receita Líquida'!B6:M8)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="14"/>
+      <c r="N4" s="82" t="str">
+        <f>'Despesas Gerais'!C8</f>
         <v>G. Resid.</v>
       </c>
-      <c r="O4" s="86">
-        <f>SUM('Despesas - Mapa'!D8,'Despesas - Mapa'!G8,'Despesas - Mapa'!J8,'Despesas - Mapa'!M8,'Despesas - Mapa'!P8,'Despesas - Mapa'!S8,'Despesas - Mapa'!V8,'Despesas - Mapa'!Y8,'Despesas - Mapa'!AB8,'Despesas - Mapa'!AE8,'Despesas - Mapa'!AH8,'Despesas - Mapa'!AK8)</f>
-        <v>0</v>
-      </c>
-      <c r="P4" s="81"/>
+      <c r="O4" s="83">
+        <f>SUM('Despesas Gerais'!D8,'Despesas Gerais'!G8,'Despesas Gerais'!J8,'Despesas Gerais'!M8,'Despesas Gerais'!P8,'Despesas Gerais'!S8,'Despesas Gerais'!V8,'Despesas Gerais'!Y8,'Despesas Gerais'!AB8,'Despesas Gerais'!AE8,'Despesas Gerais'!AH8,'Despesas Gerais'!AK8)</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="78"/>
     </row>
     <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="str">
+      <c r="A5" s="13" t="str">
         <f>PROPER(TEXT("01/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="23">
-        <f>'Receitas - Mapa'!D19</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="24">
-        <f>SUM('Receitas - Mapa'!D16:D17)</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="29">
-        <f>SUM('Despesas - Mapa'!I17:J17)</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="23">
+      <c r="B5" s="12"/>
+      <c r="C5" s="22">
+        <f>'Receita Líquida'!D13</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="23">
+        <f>SUM('Receita Líquida'!D9:D10)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="28">
+        <f>SUM('Despesas Gerais'!J17:K17)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="26">
-        <f>'Despesas - Mapa'!J4</f>
-        <v>0</v>
+      <c r="I5" s="25">
+        <f>'Despesas Gerais'!J4</f>
+        <v>50</v>
       </c>
       <c r="J5" s="8"/>
-      <c r="K5" s="83" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="24">
-        <f>SUM('Receitas - Mapa'!B4:M6)-SUM('Receitas - Mapa'!B15:M17)-SUM('Receitas - Mapa'!B9:M12)</f>
+      <c r="K5" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="23">
+        <f>SUM('Receita Líquida'!B3:M5)-SUM('Receita Líquida'!B9:M10)-SUM('Receita Líquida'!B6:M8)</f>
         <v>150</v>
       </c>
-      <c r="M5" s="15"/>
-      <c r="N5" s="85" t="str">
-        <f>'Despesas - Mapa'!C9</f>
+      <c r="M5" s="14"/>
+      <c r="N5" s="82" t="str">
+        <f>'Despesas Gerais'!C9</f>
         <v>Eletron e Jogos</v>
       </c>
-      <c r="O5" s="86">
-        <f>SUM('Despesas - Mapa'!D9,'Despesas - Mapa'!G9,'Despesas - Mapa'!J9,'Despesas - Mapa'!M9,'Despesas - Mapa'!P9,'Despesas - Mapa'!S9,'Despesas - Mapa'!V9,'Despesas - Mapa'!Y9,'Despesas - Mapa'!AB9,'Despesas - Mapa'!AE9,'Despesas - Mapa'!AH9,'Despesas - Mapa'!AK9)</f>
+      <c r="O5" s="83">
+        <f>SUM('Despesas Gerais'!D9,'Despesas Gerais'!G9,'Despesas Gerais'!J9,'Despesas Gerais'!M9,'Despesas Gerais'!P9,'Despesas Gerais'!S9,'Despesas Gerais'!V9,'Despesas Gerais'!Y9,'Despesas Gerais'!AB9,'Despesas Gerais'!AE9,'Despesas Gerais'!AH9,'Despesas Gerais'!AK9)</f>
         <v>50</v>
       </c>
-      <c r="P5" s="81"/>
+      <c r="P5" s="78"/>
     </row>
     <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="str">
+      <c r="A6" s="13" t="str">
         <f>PROPER(TEXT("01/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="23">
-        <f>'Receitas - Mapa'!E19</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="24">
-        <f>SUM('Receitas - Mapa'!E16:E17)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="29">
-        <f>SUM('Despesas - Mapa'!L17:M17)</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="23">
+      <c r="B6" s="12"/>
+      <c r="C6" s="22">
+        <f>'Receita Líquida'!E13</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="23">
+        <f>SUM('Receita Líquida'!E9:E10)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="28">
+        <f>SUM('Despesas Gerais'!M17:N17)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="26">
-        <f>'Despesas - Mapa'!M4</f>
-        <v>0</v>
+      <c r="I6" s="25">
+        <f>'Despesas Gerais'!M4</f>
+        <v>50</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="83" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="24">
-        <f>SUM('Despesas - Mapa'!D7:D14,'Despesas - Mapa'!G7:G14,'Despesas - Mapa'!J7:J14,'Despesas - Mapa'!M7:M14,'Despesas - Mapa'!P7:P14,'Despesas - Mapa'!S7:S14,'Despesas - Mapa'!V7:V14,'Despesas - Mapa'!Y7:Y14,'Despesas - Mapa'!AB7:AB14,'Despesas - Mapa'!AE7:AE14,'Despesas - Mapa'!AH7:AH14,'Despesas - Mapa'!AK7:AK14)</f>
+      <c r="K6" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="23">
+        <f>SUM('Despesas Gerais'!D7:D14,'Despesas Gerais'!G7:G14,'Despesas Gerais'!J7:J14,'Despesas Gerais'!M7:M14,'Despesas Gerais'!P7:P14,'Despesas Gerais'!S7:S14,'Despesas Gerais'!V7:V14,'Despesas Gerais'!Y7:Y14,'Despesas Gerais'!AB7:AB14,'Despesas Gerais'!AE7:AE14,'Despesas Gerais'!AH7:AH14,'Despesas Gerais'!AK7:AK14)</f>
         <v>100</v>
       </c>
-      <c r="M6" s="15"/>
-      <c r="N6" s="85" t="str">
-        <f>'Despesas - Mapa'!C10</f>
+      <c r="M6" s="14"/>
+      <c r="N6" s="82" t="str">
+        <f>'Despesas Gerais'!C10</f>
         <v>Cursos</v>
       </c>
-      <c r="O6" s="86">
-        <f>SUM('Despesas - Mapa'!D10,'Despesas - Mapa'!G10,'Despesas - Mapa'!J10,'Despesas - Mapa'!M10,'Despesas - Mapa'!P10,'Despesas - Mapa'!S10,'Despesas - Mapa'!V10,'Despesas - Mapa'!Y10,'Despesas - Mapa'!AB10,'Despesas - Mapa'!AE10,'Despesas - Mapa'!AH10,'Despesas - Mapa'!AK10)</f>
-        <v>0</v>
-      </c>
-      <c r="P6" s="81"/>
+      <c r="O6" s="83">
+        <f>SUM('Despesas Gerais'!D10,'Despesas Gerais'!G10,'Despesas Gerais'!J10,'Despesas Gerais'!M10,'Despesas Gerais'!P10,'Despesas Gerais'!S10,'Despesas Gerais'!V10,'Despesas Gerais'!Y10,'Despesas Gerais'!AB10,'Despesas Gerais'!AE10,'Despesas Gerais'!AH10,'Despesas Gerais'!AK10)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="78"/>
     </row>
     <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="str">
+      <c r="A7" s="13" t="str">
         <f>PROPER(TEXT("01/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="23">
-        <f>'Receitas - Mapa'!F19</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="24">
-        <f>SUM('Receitas - Mapa'!F16:F17)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="29">
-        <f>SUM('Despesas - Mapa'!O17:P17)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="23">
+      <c r="B7" s="12"/>
+      <c r="C7" s="22">
+        <f>'Receita Líquida'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="23">
+        <f>SUM('Receita Líquida'!F9:F10)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="28">
+        <f>SUM('Despesas Gerais'!P17:Q17)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="26">
-        <f>'Despesas - Mapa'!P4</f>
-        <v>0</v>
+      <c r="I7" s="25">
+        <f>'Despesas Gerais'!P4</f>
+        <v>50</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="83" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="24">
-        <f>SUM('Despesas - Mapa'!D15:D15,'Despesas - Mapa'!G15:G15,'Despesas - Mapa'!J15:J15,'Despesas - Mapa'!M15:M15,'Despesas - Mapa'!P15:P15,'Despesas - Mapa'!S15:S15,'Despesas - Mapa'!V15:V15,'Despesas - Mapa'!Y15:Y15,'Despesas - Mapa'!AB15:AB15,'Despesas - Mapa'!AE15:AE15,'Despesas - Mapa'!AH15:AH15,'Despesas - Mapa'!AK15:AK15)</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="15"/>
-      <c r="N7" s="85" t="str">
-        <f>'Despesas - Mapa'!C11</f>
+      <c r="K7" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="23">
+        <f>SUM('Despesas Gerais'!D15:D15,'Despesas Gerais'!G15:G15,'Despesas Gerais'!J15:J15,'Despesas Gerais'!M15:M15,'Despesas Gerais'!P15:P15,'Despesas Gerais'!S15:S15,'Despesas Gerais'!V15:V15,'Despesas Gerais'!Y15:Y15,'Despesas Gerais'!AB15:AB15,'Despesas Gerais'!AE15:AE15,'Despesas Gerais'!AH15:AH15,'Despesas Gerais'!AK15:AK15)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="14"/>
+      <c r="N7" s="82" t="str">
+        <f>'Despesas Gerais'!C11</f>
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="O7" s="86">
-        <f>SUM('Despesas - Mapa'!D11,'Despesas - Mapa'!G11,'Despesas - Mapa'!J11,'Despesas - Mapa'!M11,'Despesas - Mapa'!P11,'Despesas - Mapa'!S11,'Despesas - Mapa'!V11,'Despesas - Mapa'!Y11,'Despesas - Mapa'!AB11,'Despesas - Mapa'!AE11,'Despesas - Mapa'!AH11,'Despesas - Mapa'!AK11)</f>
-        <v>0</v>
-      </c>
-      <c r="P7" s="81"/>
+      <c r="O7" s="83">
+        <f>SUM('Despesas Gerais'!D11,'Despesas Gerais'!G11,'Despesas Gerais'!J11,'Despesas Gerais'!M11,'Despesas Gerais'!P11,'Despesas Gerais'!S11,'Despesas Gerais'!V11,'Despesas Gerais'!Y11,'Despesas Gerais'!AB11,'Despesas Gerais'!AE11,'Despesas Gerais'!AH11,'Despesas Gerais'!AK11)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="78"/>
     </row>
     <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="str">
+      <c r="A8" s="13" t="str">
         <f>PROPER(TEXT("01/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="23">
-        <f>'Receitas - Mapa'!G19</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="24">
-        <f>SUM('Receitas - Mapa'!G16:G17)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="29">
-        <f>SUM('Despesas - Mapa'!R17:S17)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="23">
+      <c r="B8" s="12"/>
+      <c r="C8" s="22">
+        <f>'Receita Líquida'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="23">
+        <f>SUM('Receita Líquida'!G9:G10)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="28">
+        <f>SUM('Despesas Gerais'!S17:T17)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="15"/>
+      <c r="H8" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="26">
-        <f>'Despesas - Mapa'!S4</f>
-        <v>0</v>
+      <c r="I8" s="25">
+        <f>'Despesas Gerais'!S4</f>
+        <v>50</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="83" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="24">
+      <c r="K8" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="23">
         <f>SUM(L6:L7)</f>
         <v>100</v>
       </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="85" t="str">
-        <f>'Despesas - Mapa'!C12</f>
+      <c r="M8" s="14"/>
+      <c r="N8" s="82" t="str">
+        <f>'Despesas Gerais'!C12</f>
         <v>Entret e Livros</v>
       </c>
-      <c r="O8" s="86">
-        <f>SUM('Despesas - Mapa'!D12,'Despesas - Mapa'!G12,'Despesas - Mapa'!J12,'Despesas - Mapa'!M12,'Despesas - Mapa'!P12,'Despesas - Mapa'!S12,'Despesas - Mapa'!V12,'Despesas - Mapa'!Y12,'Despesas - Mapa'!AB12,'Despesas - Mapa'!AE12,'Despesas - Mapa'!AH12,'Despesas - Mapa'!AK12)</f>
-        <v>0</v>
-      </c>
-      <c r="P8" s="81"/>
+      <c r="O8" s="83">
+        <f>SUM('Despesas Gerais'!D12,'Despesas Gerais'!G12,'Despesas Gerais'!J12,'Despesas Gerais'!M12,'Despesas Gerais'!P12,'Despesas Gerais'!S12,'Despesas Gerais'!V12,'Despesas Gerais'!Y12,'Despesas Gerais'!AB12,'Despesas Gerais'!AE12,'Despesas Gerais'!AH12,'Despesas Gerais'!AK12)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="78"/>
     </row>
     <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="str">
+      <c r="A9" s="13" t="str">
         <f>PROPER(TEXT("01/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="23">
-        <f>'Receitas - Mapa'!H19</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="24">
-        <f>SUM('Receitas - Mapa'!H16:H17)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="29">
-        <f>SUM('Despesas - Mapa'!U17:V17)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="23">
+      <c r="B9" s="12"/>
+      <c r="C9" s="22">
+        <f>'Receita Líquida'!H13</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <f>SUM('Receita Líquida'!H9:H10)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="28">
+        <f>SUM('Despesas Gerais'!V17:W17)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="15"/>
+      <c r="H9" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="26">
-        <f>'Despesas - Mapa'!V4</f>
-        <v>0</v>
+      <c r="I9" s="25">
+        <f>'Despesas Gerais'!V4</f>
+        <v>50</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="83" t="s">
+      <c r="K9" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="26">
-        <f>'Despesas - Mapa'!AK4</f>
+      <c r="L9" s="25">
+        <f>'Despesas Gerais'!AK4</f>
         <v>50</v>
       </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="85" t="str">
-        <f>'Despesas - Mapa'!C13</f>
+      <c r="M9" s="15"/>
+      <c r="N9" s="82" t="str">
+        <f>'Despesas Gerais'!C13</f>
         <v>Rolê</v>
       </c>
-      <c r="O9" s="86">
-        <f>SUM('Despesas - Mapa'!D13,'Despesas - Mapa'!G13,'Despesas - Mapa'!J13,'Despesas - Mapa'!M13,'Despesas - Mapa'!P13,'Despesas - Mapa'!S13,'Despesas - Mapa'!V13,'Despesas - Mapa'!Y13,'Despesas - Mapa'!AB13,'Despesas - Mapa'!AE13,'Despesas - Mapa'!AH13,'Despesas - Mapa'!AK13)</f>
-        <v>0</v>
-      </c>
-      <c r="P9" s="81"/>
+      <c r="O9" s="83">
+        <f>SUM('Despesas Gerais'!D13,'Despesas Gerais'!G13,'Despesas Gerais'!J13,'Despesas Gerais'!M13,'Despesas Gerais'!P13,'Despesas Gerais'!S13,'Despesas Gerais'!V13,'Despesas Gerais'!Y13,'Despesas Gerais'!AB13,'Despesas Gerais'!AE13,'Despesas Gerais'!AH13,'Despesas Gerais'!AK13)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="78"/>
     </row>
     <row r="10" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="str">
+      <c r="A10" s="13" t="str">
         <f>PROPER(TEXT("01/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="23">
-        <f>'Receitas - Mapa'!I19</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="24">
-        <f>SUM('Receitas - Mapa'!I16:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="29">
-        <f>SUM('Despesas - Mapa'!X17:Y17)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="23">
+      <c r="B10" s="12"/>
+      <c r="C10" s="22">
+        <f>'Receita Líquida'!I13</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <f>SUM('Receita Líquida'!I9:I10)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="28">
+        <f>SUM('Despesas Gerais'!Y17:Z17)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="26">
-        <f>'Despesas - Mapa'!Y4</f>
-        <v>0</v>
+      <c r="I10" s="25">
+        <f>'Despesas Gerais'!Y4</f>
+        <v>50</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="84" t="s">
+      <c r="K10" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="28">
-        <f>'Gráfico - Anual'!D15</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="16"/>
-      <c r="N10" s="85" t="str">
-        <f>'Despesas - Mapa'!C14</f>
+      <c r="L10" s="27">
+        <f>'Gráfico Anual'!D15</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="82" t="str">
+        <f>'Despesas Gerais'!C14</f>
         <v>Roupas</v>
       </c>
-      <c r="O10" s="86">
-        <f>SUM('Despesas - Mapa'!D14,'Despesas - Mapa'!G14,'Despesas - Mapa'!J14,'Despesas - Mapa'!M14,'Despesas - Mapa'!P14,'Despesas - Mapa'!S14,'Despesas - Mapa'!V14,'Despesas - Mapa'!Y14,'Despesas - Mapa'!AB14,'Despesas - Mapa'!AE14,'Despesas - Mapa'!AH14,'Despesas - Mapa'!AK14)</f>
+      <c r="O10" s="83">
+        <f>SUM('Despesas Gerais'!D14,'Despesas Gerais'!G14,'Despesas Gerais'!J14,'Despesas Gerais'!M14,'Despesas Gerais'!P14,'Despesas Gerais'!S14,'Despesas Gerais'!V14,'Despesas Gerais'!Y14,'Despesas Gerais'!AB14,'Despesas Gerais'!AE14,'Despesas Gerais'!AH14,'Despesas Gerais'!AK14)</f>
         <v>50</v>
       </c>
-      <c r="P10" s="81"/>
+      <c r="P10" s="78"/>
     </row>
     <row r="11" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="str">
+      <c r="A11" s="13" t="str">
         <f>PROPER(TEXT("01/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="23">
-        <f>'Receitas - Mapa'!J19</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="24">
-        <f>SUM('Receitas - Mapa'!J16:J17)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="29">
-        <f>SUM('Despesas - Mapa'!AA17:AB17)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="23">
+      <c r="B11" s="12"/>
+      <c r="C11" s="22">
+        <f>'Receita Líquida'!J13</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="23">
+        <f>SUM('Receita Líquida'!J9:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="28">
+        <f>SUM('Despesas Gerais'!AB17:AC17)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="15"/>
+      <c r="H11" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="26">
-        <f>'Despesas - Mapa'!AB4</f>
-        <v>0</v>
+      <c r="I11" s="25">
+        <f>'Despesas Gerais'!AB4</f>
+        <v>50</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="84" t="s">
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="O11" s="87">
+      <c r="O11" s="84">
         <f>SUM(O3:O10)</f>
         <v>100</v>
       </c>
-      <c r="P11" s="81"/>
+      <c r="P11" s="78"/>
     </row>
     <row r="12" spans="1:16" ht="15.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="str">
+      <c r="A12" s="13" t="str">
         <f>PROPER(TEXT("01/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="23">
-        <f>'Receitas - Mapa'!K19</f>
-        <v>150</v>
-      </c>
-      <c r="D12" s="24">
-        <f>SUM('Receitas - Mapa'!K16:K17)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="29">
-        <f>SUM('Despesas - Mapa'!AD17:AE17)</f>
-        <v>100</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="23">
+      <c r="B12" s="12"/>
+      <c r="C12" s="22">
+        <f>'Receita Líquida'!K13</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <f>SUM('Receita Líquida'!K9:K10)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="28">
+        <f>SUM('Despesas Gerais'!AE17:AF17)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="22">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="25">
+        <f>'Despesas Gerais'!AE4</f>
         <v>50</v>
       </c>
-      <c r="I12" s="26">
-        <f>'Despesas - Mapa'!AE4</f>
-        <v>50</v>
-      </c>
       <c r="J12" s="8"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="82"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="78"/>
+      <c r="P12" s="79"/>
     </row>
     <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="str">
+      <c r="A13" s="13" t="str">
         <f>PROPER(TEXT("01/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="23">
-        <f>'Receitas - Mapa'!L19</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="24">
-        <f>SUM('Receitas - Mapa'!L16:L17)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="29">
-        <f>SUM('Despesas - Mapa'!AG17:AH17)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="23">
+      <c r="B13" s="12"/>
+      <c r="C13" s="22">
+        <f>'Receita Líquida'!L13</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="23">
+        <f>SUM('Receita Líquida'!L9:L10)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="28">
+        <f>SUM('Despesas Gerais'!AH17:AI17)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="26">
-        <f>'Despesas - Mapa'!AH4</f>
+      <c r="I13" s="25">
+        <f>'Despesas Gerais'!AH4</f>
         <v>50</v>
       </c>
       <c r="J13" s="8"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="82"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="78"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="79"/>
     </row>
     <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="str">
+      <c r="A14" s="13" t="str">
         <f>PROPER(TEXT("01/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="23">
-        <f>'Receitas - Mapa'!M19</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="24">
-        <f>SUM('Receitas - Mapa'!M16:M17)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="29">
-        <f>SUM('Despesas - Mapa'!AJ17:AK17)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="23">
+      <c r="B14" s="12"/>
+      <c r="C14" s="22">
+        <f>'Receita Líquida'!M13</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="23">
+        <f>SUM('Receita Líquida'!M9:M10)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="28">
+        <f>SUM('Despesas Gerais'!AK17:AL17)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="26">
-        <f>'Despesas - Mapa'!AK4</f>
+      <c r="I14" s="25">
+        <f>'Despesas Gerais'!AK4</f>
         <v>50</v>
       </c>
       <c r="J14" s="8"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="81"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="81"/>
-      <c r="P14" s="81"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
     </row>
     <row r="15" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="25">
+      <c r="B15" s="12"/>
+      <c r="C15" s="24">
         <f>SUM(C3:C14)</f>
         <v>150</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <f>SUM(D3:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="29">
+      <c r="E15" s="14"/>
+      <c r="F15" s="28">
         <f>SUM(F3:F14)</f>
         <v>100</v>
       </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="33" t="s">
+      <c r="G15" s="15"/>
+      <c r="H15" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="28">
-        <f>'Gráfico - Anual'!L9</f>
+      <c r="I15" s="27">
+        <f>'Gráfico Anual'!L9</f>
         <v>50</v>
       </c>
       <c r="J15" s="8"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="81"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="78"/>
+      <c r="M15" s="78"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="78"/>
     </row>
     <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="25">
+      <c r="B16" s="12"/>
+      <c r="C16" s="24">
         <f>AVERAGE(C3:C14)</f>
         <v>12.5</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <f>AVERAGE(D3:D14)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="30">
+      <c r="E16" s="14"/>
+      <c r="F16" s="29">
         <f>AVERAGE(F3:F14)</f>
         <v>8.3333333333333339</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="18"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="17"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="78"/>
+      <c r="P16" s="78"/>
     </row>
     <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="23">
+      <c r="A17" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="22">
         <f>SUM(C3:C8)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="26">
+        <v>150</v>
+      </c>
+      <c r="D17" s="25">
         <f>SUM(D3:D8)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="31">
+      <c r="E17" s="15"/>
+      <c r="F17" s="30">
         <f>SUM(F3:F8)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="15"/>
+        <v>100</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="14"/>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="81"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
     </row>
     <row r="18" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="27">
+      <c r="A18" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="26">
         <f>SUM($C$9:$C$14)</f>
-        <v>150</v>
-      </c>
-      <c r="D18" s="28">
+        <v>0</v>
+      </c>
+      <c r="D18" s="27">
         <f>SUM($D$9:$D$14)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="32">
+      <c r="E18" s="15"/>
+      <c r="F18" s="31">
         <f>SUM($F$9:$F$14)</f>
-        <v>100</v>
-      </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="81"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="78"/>
+      <c r="M18" s="78"/>
+      <c r="N18" s="78"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="78"/>
     </row>
     <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
@@ -13233,48 +13154,48 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="81"/>
-      <c r="O19" s="81"/>
-      <c r="P19" s="81"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="81"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="81"/>
-      <c r="N20" s="81"/>
-      <c r="O20" s="81"/>
-      <c r="P20" s="81"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="78"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="78"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="81"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="81"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="78"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="78"/>
     </row>
     <row r="26" spans="1:16" ht="14.3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:16" ht="8.5500000000000007" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9078F453-80BE-4B7F-9592-4A64061745B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E07224-326A-40D9-BFFE-D3D8E83367D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Saldo &amp; Mov." sheetId="12" r:id="rId1"/>
     <sheet name="Receita Líquida" sheetId="8" state="hidden" r:id="rId2"/>
     <sheet name="Despesas Gerais" sheetId="1" state="hidden" r:id="rId3"/>
-    <sheet name="Gráfico Categoria" sheetId="14" state="hidden" r:id="rId4"/>
+    <sheet name="Gráfico Categorias" sheetId="14" r:id="rId4"/>
     <sheet name="Gráfico Anual" sheetId="13" r:id="rId5"/>
   </sheets>
   <definedNames>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
   <si>
     <t>Mês</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Transferir</t>
+  </si>
+  <si>
+    <t>Receita_Líquida</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1152,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1809,7 +1812,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2830,9 +2833,19 @@
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14178717146972417"/>
+          <c:y val="0"/>
+          <c:w val="0.85821282853027581"/>
+          <c:h val="1"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -2840,7 +2853,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Gráfico Categoria'!$F$3</c:f>
+              <c:f>'Gráfico Categorias'!$C$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2850,50 +2863,37 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:gradFill rotWithShape="1">
+            <a:gradFill flip="none" rotWithShape="1">
               <a:gsLst>
                 <a:gs pos="0">
+                  <a:schemeClr val="accent1"/>
+                </a:gs>
+                <a:gs pos="75000">
                   <a:schemeClr val="accent1">
-                    <a:shade val="51000"/>
-                    <a:satMod val="130000"/>
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
                   </a:schemeClr>
                 </a:gs>
-                <a:gs pos="80000">
+                <a:gs pos="51000">
                   <a:schemeClr val="accent1">
-                    <a:shade val="93000"/>
-                    <a:satMod val="130000"/>
+                    <a:alpha val="75000"/>
                   </a:schemeClr>
                 </a:gs>
                 <a:gs pos="100000">
                   <a:schemeClr val="accent1">
-                    <a:shade val="94000"/>
-                    <a:satMod val="135000"/>
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                    <a:alpha val="15000"/>
                   </a:schemeClr>
                 </a:gs>
               </a:gsLst>
-              <a:lin ang="16200000" scaled="0"/>
+              <a:lin ang="10800000" scaled="1"/>
+              <a:tileRect/>
             </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="35000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-            <a:scene3d>
-              <a:camera prst="orthographicFront">
-                <a:rot lat="0" lon="0" rev="0"/>
-              </a:camera>
-              <a:lightRig rig="threePt" dir="t">
-                <a:rot lat="0" lon="0" rev="1200000"/>
-              </a:lightRig>
-            </a:scene3d>
-            <a:sp3d>
-              <a:bevelT w="63500" h="25400"/>
-            </a:sp3d>
+            <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -2911,10 +2911,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -2939,9 +2940,9 @@
                   <c:spPr>
                     <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="95000"/>
-                          <a:alpha val="54000"/>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
                     </a:ln>
@@ -2953,7 +2954,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Gráfico Categoria'!$E$4:$E$15</c:f>
+              <c:f>'Gráfico Categorias'!$B$6:$B$17</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2997,12 +2998,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Gráfico Categoria'!$F$4:$F$15</c:f>
+              <c:f>'Gráfico Categorias'!$C$6:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3054,32 +3055,34 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="-24"/>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-58"/>
         <c:axId val="128784240"/>
         <c:axId val="1981972528"/>
       </c:barChart>
       <c:catAx>
         <c:axId val="128784240"/>
         <c:scaling>
-          <c:orientation val="minMax"/>
+          <c:orientation val="maxMin"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -3090,8 +3093,9 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -3115,16 +3119,27 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
-        <c:axPos val="l"/>
+        <c:axPos val="t"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="99000">
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="15000"/>
+                      <a:lumOff val="85000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -3139,7 +3154,12 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -3158,28 +3178,17 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -3202,6 +3211,399 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14519363859177192"/>
+          <c:y val="0"/>
+          <c:w val="0.85480636140822808"/>
+          <c:h val="1"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Gráfico Categorias'!$J$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Valor </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill flip="none" rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1"/>
+                </a:gs>
+                <a:gs pos="75000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="51000">
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="75000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                    <a:alpha val="15000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="10800000" scaled="1"/>
+              <a:tileRect/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Gráfico Categorias'!$I$6:$I$17</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Janeiro</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Fevereiro</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Março</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Abril</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Maio</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Junho</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Julho</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Agosto</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Setembro</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Outubro</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Novembro</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dezembro</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Gráfico Categorias'!$J$6:$J$17</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-417E-409B-8C34-E661A1256AF5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-58"/>
+        <c:axId val="313549504"/>
+        <c:axId val="307726576"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="313549504"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="307726576"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="307726576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="99000">
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="15000"/>
+                      <a:lumOff val="85000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="313549504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -3953,7 +4355,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -4270,7 +4672,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -4431,7 +4833,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4446,7 +4848,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -4803,6 +5205,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="210">
   <cs:axisTitle>
@@ -5401,78 +5843,75 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="223">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -5482,14 +5921,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="bg1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
       </a:solidFill>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -5499,35 +5938,93 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="10800000" scaled="1"/>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="10800000" scaled="1"/>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="34925" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -5539,17 +6036,39 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="46000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="0"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -5560,10 +6079,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -5579,16 +6098,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -5600,7 +6120,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -5611,9 +6131,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -5624,17 +6144,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -5643,13 +6162,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -5661,7 +6181,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -5669,16 +6189,27 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="99000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
@@ -5688,16 +6219,28 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
-          </a:schemeClr>
-        </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -5706,17 +6249,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -5725,14 +6267,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -5743,26 +6285,27 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -5770,19 +6313,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -5792,14 +6338,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -5811,19 +6357,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="50" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -5832,10 +6371,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -5847,8 +6386,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -5858,7 +6398,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -5866,9 +6406,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -5879,8 +6419,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -5890,13 +6431,608 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="223">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="bg1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="10800000" scaled="1"/>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="10800000" scaled="1"/>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="46000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="0"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="99000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="50" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="328">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6409,7 +7545,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="210">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7006,7 +8142,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="210">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7650,16 +8786,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2343</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>4198</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4658</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>189574</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>335901</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>59789</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>578697</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>37465</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7679,6 +8815,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7528</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>3662</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>366548</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>43939</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F7FA5FC-900E-AB25-6602-3A4F3C31FD65}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8117,7 +9289,7 @@
   <sheetPr codeName="Planilha1">
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:I672"/>
+  <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" style="50" customWidth="1"/>
@@ -8161,7 +9333,7 @@
       </c>
       <c r="F3" s="57" cm="1">
         <f t="array" ref="F3:F14">IF(C3="Despesas",_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,'Despesas Gerais'!B2:M2=C2),IF(C3="Receita Líquida",_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,'Receita Líquida'!B2:M2=C2),""))</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H3" s="50"/>
     </row>
@@ -8170,7 +9342,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="27">
-        <f>IF(C3="Despesas",HLOOKUP(C2,'Despesas Gerais'!B2:M20,19,FALSE),IF(C3="Receita Líquida",HLOOKUP(C2,'Receita Líquida'!B2:M16,15,FALSE),IF(C3="Item",SUM(F3:F14),"")))</f>
+        <f>IF(C3="Despesas",HLOOKUP(C2,'Despesas Gerais'!B2:M20,19,FALSE),IF(C3="Receita Líquida",HLOOKUP(C2,'Receita Líquida'!B2:M16,15,FALSE),""))</f>
         <v>50</v>
       </c>
       <c r="D4" s="35"/>
@@ -8231,7 +9403,7 @@
         <v>Entret e Livros</v>
       </c>
       <c r="F8" s="57">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H8" s="50"/>
     </row>
@@ -8368,7 +9540,7 @@
         <v>44927</v>
       </c>
       <c r="C17" s="35" t="str">
-        <f t="shared" ref="C17:C19" si="0">IF(ISBLANK(B17),"",PROPER(TEXT(B17,"MMMM")))</f>
+        <f t="shared" ref="C17:C20" si="0">IF(ISBLANK(B17),"",PROPER(TEXT(B17,"MMMM")))</f>
         <v>Janeiro</v>
       </c>
       <c r="D17" s="35" t="s">
@@ -8387,7 +9559,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="34">
-        <v>44927</v>
+        <v>44928</v>
       </c>
       <c r="C18" s="35" t="str">
         <f t="shared" si="0"/>
@@ -8397,7 +9569,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" s="36" t="s">
         <v>33</v>
@@ -8409,7 +9581,7 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="34">
-        <v>44928</v>
+        <v>44929</v>
       </c>
       <c r="C19" s="35" t="str">
         <f t="shared" si="0"/>
@@ -8432,7 +9604,7 @@
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="34"/>
       <c r="C20" s="35" t="str">
-        <f>IF(ISBLANK(B20),"",PROPER(TEXT(B20,"MMMM")))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="D20" s="35"/>
@@ -8441,8 +9613,11 @@
       <c r="G20" s="37"/>
       <c r="H20" s="38"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G24" s="52"/>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G23" s="52"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G25" s="52"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G26" s="52"/>
@@ -8452,3174 +9627,3186 @@
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G28" s="52"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G29" s="52"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I38" s="50" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C135" s="48" t="str">
-        <f>IF(ISBLANK(B135),"",PROPER(TEXT(B135,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C136" s="48" t="str">
-        <f>IF(ISBLANK(B136),"",PROPER(TEXT(B136,"MMMM")))</f>
-        <v/>
-      </c>
-      <c r="G136" s="58"/>
-    </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C145" s="48" t="str">
-        <f>IF(ISBLANK(B145),"",PROPER(TEXT(B145,"MMMM")))</f>
-        <v/>
-      </c>
-      <c r="D145" s="48" t="str">
-        <f t="shared" ref="D145:G145" si="1">IF(ISBLANK(C145),"",PROPER(TEXT(C145,"MMMM")))</f>
-        <v/>
-      </c>
-      <c r="E145" s="48" t="str">
+    <row r="137" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G137" s="52"/>
+    </row>
+    <row r="139" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G139" s="52"/>
+    </row>
+    <row r="140" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G140" s="52"/>
+    </row>
+    <row r="141" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G141" s="52"/>
+    </row>
+    <row r="142" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G142" s="52"/>
+    </row>
+    <row r="248" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C248" s="48" t="str">
+        <f>IF(ISBLANK(B248),"",PROPER(TEXT(B248,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C249" s="48" t="str">
+        <f>IF(ISBLANK(B249),"",PROPER(TEXT(B249,"MMMM")))</f>
+        <v/>
+      </c>
+      <c r="G249" s="58"/>
+    </row>
+    <row r="258" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C258" s="48" t="str">
+        <f>IF(ISBLANK(B258),"",PROPER(TEXT(B258,"MMMM")))</f>
+        <v/>
+      </c>
+      <c r="D258" s="48" t="str">
+        <f t="shared" ref="D258:G258" si="1">IF(ISBLANK(C258),"",PROPER(TEXT(C258,"MMMM")))</f>
+        <v/>
+      </c>
+      <c r="E258" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F145" s="48" t="str">
+      <c r="F258" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G145" s="48" t="str">
+      <c r="G258" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C154" s="48" t="str">
-        <f t="shared" ref="C154" si="2">IF(ISBLANK(B154),"",PROPER(TEXT(B154,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C155" s="48" t="str">
-        <f t="shared" ref="C155:C169" si="3">IF(ISBLANK(B155),"",PROPER(TEXT(B155,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C156" s="48" t="str">
-        <f t="shared" ref="C156:C166" si="4">IF(ISBLANK(B156),"",PROPER(TEXT(B156,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C157" s="48" t="str">
+    <row r="267" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C267" s="48" t="str">
+        <f t="shared" ref="C267" si="2">IF(ISBLANK(B267),"",PROPER(TEXT(B267,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C268" s="48" t="str">
+        <f t="shared" ref="C268:C282" si="3">IF(ISBLANK(B268),"",PROPER(TEXT(B268,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C269" s="48" t="str">
+        <f t="shared" ref="C269:C279" si="4">IF(ISBLANK(B269),"",PROPER(TEXT(B269,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C270" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="158" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C158" s="48" t="str">
+    <row r="271" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C271" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="159" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C159" s="48" t="str">
+    <row r="272" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C272" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="160" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C160" s="48" t="str">
+    <row r="273" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C273" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C161" s="48" t="str">
+    <row r="274" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C274" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C162" s="48" t="str">
+    <row r="275" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C275" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C163" s="48" t="str">
+    <row r="276" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C276" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C164" s="48" t="str">
+    <row r="277" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C277" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C165" s="48" t="str">
+    <row r="278" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C278" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C166" s="48" t="str">
+    <row r="279" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C279" s="48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C167" s="48" t="str">
+    <row r="280" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C280" s="48" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C168" s="48" t="str">
+    <row r="281" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C281" s="48" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C169" s="48" t="str">
+    <row r="282" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C282" s="48" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G169" s="52"/>
-      <c r="H169" s="53"/>
-    </row>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B170" s="50"/>
-      <c r="C170" s="50"/>
-      <c r="D170" s="50"/>
-      <c r="E170" s="54"/>
-      <c r="F170" s="54"/>
-      <c r="G170" s="52"/>
-      <c r="H170" s="53"/>
-    </row>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B171" s="50"/>
-      <c r="C171" s="50"/>
-      <c r="D171" s="50"/>
-      <c r="E171" s="54"/>
-      <c r="F171" s="54"/>
-      <c r="G171" s="52"/>
-      <c r="H171" s="53"/>
-    </row>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B172" s="50"/>
-      <c r="C172" s="50"/>
-      <c r="D172" s="50"/>
-      <c r="E172" s="54"/>
-      <c r="F172" s="54"/>
-      <c r="G172" s="52"/>
-      <c r="H172" s="53"/>
-    </row>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B173" s="50"/>
-      <c r="C173" s="55"/>
-      <c r="D173" s="55"/>
-      <c r="E173" s="54"/>
-      <c r="F173" s="54"/>
-      <c r="G173" s="52"/>
-      <c r="H173" s="53"/>
-    </row>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B174" s="50"/>
-      <c r="C174" s="50"/>
-      <c r="D174" s="50"/>
-      <c r="G174" s="50"/>
-    </row>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B175" s="50"/>
-      <c r="C175" s="50"/>
-      <c r="D175" s="50"/>
-      <c r="G175" s="50"/>
-    </row>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B176" s="50"/>
-      <c r="C176" s="50"/>
-      <c r="D176" s="50"/>
-      <c r="G176" s="50"/>
-    </row>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B177" s="50"/>
-      <c r="C177" s="50"/>
-      <c r="D177" s="50"/>
-      <c r="G177" s="50"/>
-    </row>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B178" s="50"/>
-      <c r="C178" s="50"/>
-      <c r="D178" s="50"/>
-      <c r="G178" s="50"/>
-    </row>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B179" s="50"/>
-      <c r="C179" s="50"/>
-      <c r="D179" s="50"/>
-      <c r="G179" s="50"/>
-    </row>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B180" s="50"/>
-      <c r="C180" s="50"/>
-      <c r="D180" s="50"/>
-      <c r="G180" s="50"/>
-    </row>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C181" s="48" t="str">
-        <f t="shared" ref="C181:C239" si="5">IF(ISBLANK(B181),"",PROPER(TEXT(B181,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C182" s="48" t="str">
+      <c r="G282" s="52"/>
+      <c r="H282" s="53"/>
+    </row>
+    <row r="283" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B283" s="50"/>
+      <c r="C283" s="50"/>
+      <c r="D283" s="50"/>
+      <c r="E283" s="54"/>
+      <c r="F283" s="54"/>
+      <c r="G283" s="52"/>
+      <c r="H283" s="53"/>
+    </row>
+    <row r="284" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B284" s="50"/>
+      <c r="C284" s="50"/>
+      <c r="D284" s="50"/>
+      <c r="E284" s="54"/>
+      <c r="F284" s="54"/>
+      <c r="G284" s="52"/>
+      <c r="H284" s="53"/>
+    </row>
+    <row r="285" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B285" s="50"/>
+      <c r="C285" s="50"/>
+      <c r="D285" s="50"/>
+      <c r="E285" s="54"/>
+      <c r="F285" s="54"/>
+      <c r="G285" s="52"/>
+      <c r="H285" s="53"/>
+    </row>
+    <row r="286" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B286" s="50"/>
+      <c r="C286" s="55"/>
+      <c r="D286" s="55"/>
+      <c r="E286" s="54"/>
+      <c r="F286" s="54"/>
+      <c r="G286" s="52"/>
+      <c r="H286" s="53"/>
+    </row>
+    <row r="287" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B287" s="50"/>
+      <c r="C287" s="50"/>
+      <c r="D287" s="50"/>
+      <c r="G287" s="50"/>
+    </row>
+    <row r="288" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B288" s="50"/>
+      <c r="C288" s="50"/>
+      <c r="D288" s="50"/>
+      <c r="G288" s="50"/>
+    </row>
+    <row r="289" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B289" s="50"/>
+      <c r="C289" s="50"/>
+      <c r="D289" s="50"/>
+      <c r="G289" s="50"/>
+    </row>
+    <row r="290" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B290" s="50"/>
+      <c r="C290" s="50"/>
+      <c r="D290" s="50"/>
+      <c r="G290" s="50"/>
+    </row>
+    <row r="291" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B291" s="50"/>
+      <c r="C291" s="50"/>
+      <c r="D291" s="50"/>
+      <c r="G291" s="50"/>
+    </row>
+    <row r="292" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B292" s="50"/>
+      <c r="C292" s="50"/>
+      <c r="D292" s="50"/>
+      <c r="G292" s="50"/>
+    </row>
+    <row r="293" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B293" s="50"/>
+      <c r="C293" s="50"/>
+      <c r="D293" s="50"/>
+      <c r="G293" s="50"/>
+    </row>
+    <row r="294" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C294" s="48" t="str">
+        <f t="shared" ref="C294:C352" si="5">IF(ISBLANK(B294),"",PROPER(TEXT(B294,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C295" s="48" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C183" s="48" t="str">
+    <row r="296" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C296" s="48" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="184" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C184" s="48" t="str">
+    <row r="297" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C297" s="48" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="185" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C185" s="48" t="str">
+    <row r="298" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C298" s="48" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C186" s="48" t="str">
+    <row r="299" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C299" s="48" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C187" s="48" t="str">
+    <row r="300" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C300" s="48" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C188" s="48" t="str">
+    <row r="301" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C301" s="48" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C189" s="48" t="str">
+    <row r="302" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C302" s="48" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C190" s="48" t="str">
+    <row r="303" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C303" s="48" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C191" s="48" t="str">
+    <row r="304" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C304" s="48" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C192" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C193" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C194" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C195" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C196" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C197" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C198" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C199" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C200" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C201" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C202" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C203" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C204" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C205" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C206" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C207" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C208" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C209" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C210" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C211" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C212" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C213" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C214" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C215" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C216" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C217" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C218" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C219" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C220" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C221" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C222" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C223" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C224" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C225" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C226" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C227" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C228" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C229" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C230" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C231" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C232" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C233" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C234" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C235" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C236" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C237" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C238" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C239" s="48" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C240" s="48" t="str">
-        <f t="shared" ref="C240:C303" si="6">IF(ISBLANK(B240),"",PROPER(TEXT(B240,"MMMM")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C241" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C242" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C243" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C244" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C245" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C246" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C247" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C248" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C249" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C250" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C251" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C252" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C253" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C254" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C255" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C256" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C257" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C258" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C259" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C260" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C261" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C262" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C263" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C264" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C265" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C266" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C267" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C268" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C269" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C270" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C271" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C272" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C273" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C274" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C275" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C276" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C277" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C278" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C279" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C280" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C281" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C282" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C283" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C284" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C285" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C286" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C287" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C288" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C289" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C290" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C291" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C292" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C293" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C294" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C295" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C296" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C297" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C298" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C299" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C300" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C301" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C302" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C303" s="48" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C304" s="48" t="str">
-        <f t="shared" ref="C304:C367" si="7">IF(ISBLANK(B304),"",PROPER(TEXT(B304,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C305" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C306" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C307" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C308" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C309" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C310" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C311" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C312" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C313" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C314" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C315" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C316" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C317" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C318" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C319" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C320" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C321" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C322" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C323" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C324" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C325" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C326" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C327" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C328" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C329" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C330" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C331" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C332" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C333" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C334" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C335" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C336" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C337" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C338" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C339" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C340" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C341" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C342" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C343" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C344" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C345" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C346" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C347" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C348" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C349" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C350" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C351" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C352" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C353" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C353:C416" si="6">IF(ISBLANK(B353),"",PROPER(TEXT(B353,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C354" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C355" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C356" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C357" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C358" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C359" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C360" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C361" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C362" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C363" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C364" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C365" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C366" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C367" s="48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C368" s="48" t="str">
-        <f t="shared" ref="C368:C431" si="8">IF(ISBLANK(B368),"",PROPER(TEXT(B368,"MMMM")))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C369" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C370" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C371" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C372" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C373" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C374" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C375" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C376" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C377" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C378" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C379" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C380" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C381" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C382" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C383" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C384" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C385" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C386" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C387" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C388" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C389" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C390" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C391" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C392" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C393" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C394" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C395" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C396" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C397" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C398" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C399" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C400" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C401" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C402" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C403" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C404" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C405" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C406" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C407" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C408" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C409" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C410" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C411" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C412" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C413" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C414" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C415" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C416" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C417" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C417:C480" si="7">IF(ISBLANK(B417),"",PROPER(TEXT(B417,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C418" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C419" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C420" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C421" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C422" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C423" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C424" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C425" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C426" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C427" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C428" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C429" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C430" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C431" s="48" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C432" s="48" t="str">
-        <f t="shared" ref="C432:C495" si="9">IF(ISBLANK(B432),"",PROPER(TEXT(B432,"MMMM")))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C433" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C434" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C435" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C436" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C437" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C438" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C439" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C440" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C441" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C442" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C443" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C444" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C445" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C446" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C447" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C448" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C449" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C450" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C451" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C452" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C453" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C454" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C455" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C456" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C457" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C458" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C459" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C460" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C461" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C462" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C463" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C464" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C465" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C466" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C467" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C468" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C469" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C470" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C471" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C472" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C473" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C474" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C475" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C476" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C477" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C478" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C479" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C480" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C481" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="C481:C544" si="8">IF(ISBLANK(B481),"",PROPER(TEXT(B481,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="482" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C482" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C483" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C484" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C485" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C486" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C487" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C488" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C489" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C490" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C491" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C492" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C493" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C494" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C495" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C496" s="48" t="str">
-        <f t="shared" ref="C496:C559" si="10">IF(ISBLANK(B496),"",PROPER(TEXT(B496,"MMMM")))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C497" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C498" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C499" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C500" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C501" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C502" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C503" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C504" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C505" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C506" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C507" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C508" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C509" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C510" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C511" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C512" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C513" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C514" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C515" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C516" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C517" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C518" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C519" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C520" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C521" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C522" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C523" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C524" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C525" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C526" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C527" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C528" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C529" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C530" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C531" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C532" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C533" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C534" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C535" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C536" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C537" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C538" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C539" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C540" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C541" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C542" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C543" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C544" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C545" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="C545:C608" si="9">IF(ISBLANK(B545),"",PROPER(TEXT(B545,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="546" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C546" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C547" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C548" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C549" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C550" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C551" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C552" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C553" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C554" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C555" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C556" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C557" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C558" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C559" s="48" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C560" s="48" t="str">
-        <f t="shared" ref="C560:C623" si="11">IF(ISBLANK(B560),"",PROPER(TEXT(B560,"MMMM")))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C561" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C562" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C563" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C564" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C565" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C566" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C567" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C568" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C569" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C570" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C571" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C572" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C573" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C574" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C575" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C576" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C577" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C578" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C579" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C580" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C581" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C582" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C583" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C584" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C585" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C586" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C587" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C588" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C589" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C590" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C591" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C592" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C593" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C594" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C595" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C596" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C597" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C598" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C599" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C600" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C601" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C602" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C603" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C604" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C605" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C606" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C607" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C608" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C609" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="C609:C672" si="10">IF(ISBLANK(B609),"",PROPER(TEXT(B609,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="610" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C610" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C611" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C612" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C613" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C614" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C615" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C616" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C617" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C618" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C619" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C620" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C621" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C622" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C623" s="48" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C624" s="48" t="str">
-        <f t="shared" ref="C624:C672" si="12">IF(ISBLANK(B624),"",PROPER(TEXT(B624,"MMMM")))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C625" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C626" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C627" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C628" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C629" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C630" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C631" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C632" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C633" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C634" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C635" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C636" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C637" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C638" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C639" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C640" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C641" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C642" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C643" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C644" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C645" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C646" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C647" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C648" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C649" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C650" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C651" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C652" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C653" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C654" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C655" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C656" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C657" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C658" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C659" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C660" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C661" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C662" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C663" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C664" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C665" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C666" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C667" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C668" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C669" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C670" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C671" s="48" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C672" s="48" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="673" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C673" s="48" t="str">
+        <f t="shared" ref="C673:C736" si="11">IF(ISBLANK(B673),"",PROPER(TEXT(B673,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="674" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C674" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="675" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C675" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="676" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C676" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="677" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C677" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="678" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C678" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="679" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C679" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="680" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C680" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="681" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C681" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="682" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C682" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="683" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C683" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="684" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C684" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="685" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C685" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="686" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C686" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="687" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C687" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="688" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C688" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="689" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C689" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="690" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C690" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="691" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C691" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="692" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C692" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="693" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C693" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="694" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C694" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="695" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C695" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="696" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C696" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="697" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C697" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="698" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C698" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="699" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C699" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="700" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C700" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="701" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C701" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="702" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C702" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="703" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C703" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="704" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C704" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="705" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C705" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="706" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C706" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="707" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C707" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="708" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C708" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="709" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C709" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="710" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C710" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="711" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C711" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="712" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C712" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="713" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C713" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="714" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C714" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="715" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C715" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="716" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C716" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="717" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C717" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="718" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C718" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="719" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C719" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="720" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C720" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="721" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C721" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="722" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C722" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="723" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C723" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="724" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C724" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="725" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C725" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="726" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C726" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="727" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C727" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="728" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C728" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="729" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C729" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="730" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C730" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="731" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C731" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="732" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C732" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="733" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C733" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="734" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C734" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="735" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C735" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="736" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C736" s="48" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="737" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C737" s="48" t="str">
+        <f t="shared" ref="C737:C785" si="12">IF(ISBLANK(B737),"",PROPER(TEXT(B737,"MMMM")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="738" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C738" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="739" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C739" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="740" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C740" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="741" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C741" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="742" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C742" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="743" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C743" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="744" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C744" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="745" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C745" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="746" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C746" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="747" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C747" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="748" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C748" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="749" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C749" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="750" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C750" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="751" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C751" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="752" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C752" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="753" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C753" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="754" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C754" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="755" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C755" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="756" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C756" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="757" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C757" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="758" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C758" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="759" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C759" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="760" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C760" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="761" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C761" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="762" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C762" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="763" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C763" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="764" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C764" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="765" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C765" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="766" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C766" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="767" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C767" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="768" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C768" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="769" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C769" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="770" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C770" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="771" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C771" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="772" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C772" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="773" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C773" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="774" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C774" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="775" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C775" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="776" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C776" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="777" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C777" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="778" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C778" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="779" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C779" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="780" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C780" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="781" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C781" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="782" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C782" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="783" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C783" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="784" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C784" s="48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="785" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C785" s="48" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
@@ -11638,13 +12825,13 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
       <formula1>"Despesas, Receita Líquida"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17:E144" xr:uid="{E4F2BDDC-1223-4DFF-8087-7B85DF038B73}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17:E257" xr:uid="{E4F2BDDC-1223-4DFF-8087-7B85DF038B73}">
       <formula1>INDIRECT(D17)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D144" xr:uid="{4E564D7B-00FF-4101-8D9D-5EA4D9B1919A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D257" xr:uid="{4E564D7B-00FF-4101-8D9D-5EA4D9B1919A}">
       <formula1>"Receitas, Perdas, Investimentos, Despesas, Transferir"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F144" xr:uid="{0D51CC9B-6F94-4F85-BAFC-26C786BB30BC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F257" xr:uid="{0D51CC9B-6F94-4F85-BAFC-26C786BB30BC}">
       <formula1>Ativos</formula1>
     </dataValidation>
   </dataValidations>
@@ -12425,15 +13612,15 @@
     </row>
     <row r="18" spans="1:13" ht="18.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="59" t="str">
-        <f>A12</f>
-        <v>Perdas Outros</v>
+        <f>A10</f>
+        <v>Taxa</v>
       </c>
       <c r="B18" s="3">
-        <f t="shared" ref="B18:M18" si="1">ROUND(IF((SUM(B3:B9)-SUM(B10:B11,B13)) &gt; 10, ((SUM(B3:B9)-SUM(B10:B11,B13))*0.1), (0))-B12,2)</f>
+        <f>ROUND(IF((SUM(B3:B7) - SUM(B8:B9,B11:B12)) &gt; 10, (SUM(B3:B7) - SUM(B8:B9,B11:B12))*0.1, )-B10,2)</f>
         <v>15</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C18:M18" si="1">ROUND(IF((SUM(C3:C7) - SUM(C8:C9,C11:C12)) &gt; 10, (SUM(C3:C7) - SUM(C8:C9,C11:C12))*0.1, )-C10,2)</f>
         <v>0</v>
       </c>
       <c r="D18" s="3">
@@ -12473,7 +13660,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="3">
-        <f t="shared" si="1"/>
+        <f>ROUND(IF((SUM(M3:M7) - SUM(M8:M9,M11:M12)) &gt; 10, (SUM(M3:M7) - SUM(M8:M9,M11:M12))*0.1, )-M10,2)</f>
         <v>0</v>
       </c>
     </row>
@@ -12720,7 +13907,7 @@
       </c>
       <c r="B7" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
@@ -12985,7 +14172,7 @@
       </c>
       <c r="B12" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C12" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
@@ -13455,138 +14642,234 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6BFD9AA-7466-45C1-AB6A-4AD451301F03}">
-  <dimension ref="B2:F15"/>
+  <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" style="4" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.42578125" style="4" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="13" width="9.140625" style="4"/>
+    <col min="6" max="6" width="16.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="4" customWidth="1"/>
+    <col min="9" max="10" width="17.140625" style="4" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="4"/>
     <col min="14" max="14" width="7.140625" style="4" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="J2" s="46" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="78" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="79">
-        <f>SUM(_xlfn.ANCHORARRAY(F4))</f>
-        <v>50</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="s">
+        <f>SUM(C6:C17)</f>
+        <v>150</v>
+      </c>
+      <c r="I3" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="79">
+        <f>SUM(J6:J17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E4" s="4" t="str" cm="1">
-        <f t="array" ref="E4:E15">TRANSPOSE(Meses)</f>
+      <c r="I5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="77" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="str" cm="1">
+        <f t="array" ref="B6:B17">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="F4" s="77" cm="1">
-        <f t="array" ref="F4:F15">IF(B2="Despesas",TRANSPOSE(_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,Categorias='Gráfico Categoria'!C2)),IF(B2="Receita_Líquida",TRANSPOSE(_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,Receita_Líquida='Gráfico Categoria'!C2)),""))</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E5" s="4" t="str">
+      <c r="C6" s="77" cm="1">
+        <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,Receita_Líquida='Gráfico Categorias'!C2))</f>
+        <v>150</v>
+      </c>
+      <c r="I6" s="4" t="str" cm="1">
+        <f t="array" ref="I6:I17">TRANSPOSE(Meses)</f>
+        <v>Janeiro</v>
+      </c>
+      <c r="J6" s="77" cm="1">
+        <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,Categorias='Gráfico Categorias'!J2))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="F5" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E6" s="4" t="str">
+      <c r="C7" s="77">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="str">
+        <v>Fevereiro</v>
+      </c>
+      <c r="J7" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="str">
         <v>Março</v>
       </c>
-      <c r="F6" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E7" s="4" t="str">
+      <c r="C8" s="77">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="str">
+        <v>Março</v>
+      </c>
+      <c r="J8" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="str">
         <v>Abril</v>
       </c>
-      <c r="F7" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E8" s="4" t="str">
+      <c r="C9" s="77">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="str">
+        <v>Abril</v>
+      </c>
+      <c r="J9" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="str">
         <v>Maio</v>
       </c>
-      <c r="F8" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E9" s="4" t="str">
+      <c r="C10" s="77">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="str">
+        <v>Maio</v>
+      </c>
+      <c r="J10" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="str">
         <v>Junho</v>
       </c>
-      <c r="F9" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E10" s="4" t="str">
+      <c r="C11" s="77">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="str">
+        <v>Junho</v>
+      </c>
+      <c r="J11" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="str">
         <v>Julho</v>
       </c>
-      <c r="F10" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E11" s="4" t="str">
+      <c r="C12" s="77">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="str">
+        <v>Julho</v>
+      </c>
+      <c r="J12" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="str">
         <v>Agosto</v>
       </c>
-      <c r="F11" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E12" s="4" t="str">
+      <c r="C13" s="77">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="str">
+        <v>Agosto</v>
+      </c>
+      <c r="J13" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="str">
         <v>Setembro</v>
       </c>
-      <c r="F12" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E13" s="4" t="str">
+      <c r="C14" s="77">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="str">
+        <v>Setembro</v>
+      </c>
+      <c r="J14" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="str">
         <v>Outubro</v>
       </c>
-      <c r="F13" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E14" s="4" t="str">
+      <c r="C15" s="77">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="str">
+        <v>Outubro</v>
+      </c>
+      <c r="J15" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="str">
         <v>Novembro</v>
       </c>
-      <c r="F14" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E15" s="4" t="str">
+      <c r="C16" s="77">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="str">
+        <v>Novembro</v>
+      </c>
+      <c r="J16" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="F15" s="77">
+      <c r="C17" s="77">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="str">
+        <v>Dezembro</v>
+      </c>
+      <c r="J17" s="77">
         <v>0</v>
       </c>
     </row>
@@ -13595,8 +14878,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{F3C6D088-7A2D-43B3-A954-374141D733A9}">
       <formula1>INDIRECT($B$2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{C672E275-C985-431E-B4B0-CE130F067F5D}">
-      <formula1>"Despesas, Receita_Líquida"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2" xr:uid="{25F76189-A24E-400D-B956-F7969AA2CC14}">
+      <formula1>INDIRECT($I$2)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -13711,7 +14994,7 @@
       </c>
       <c r="O3" s="45">
         <f>SUM('Despesas Gerais'!B7:M7)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P3" s="40"/>
     </row>
@@ -13941,7 +15224,7 @@
       </c>
       <c r="O8" s="45">
         <f>SUM('Despesas Gerais'!B12:M12)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P8" s="40"/>
     </row>

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E07224-326A-40D9-BFFE-D3D8E83367D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81DDB3F-1709-48A3-AE82-C669DDD0DBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo &amp; Mov." sheetId="12" r:id="rId1"/>
-    <sheet name="Receita Líquida" sheetId="8" state="hidden" r:id="rId2"/>
-    <sheet name="Despesas Gerais" sheetId="1" state="hidden" r:id="rId3"/>
+    <sheet name="Receita Líquida" sheetId="8" r:id="rId2"/>
+    <sheet name="Despesas Gerais" sheetId="1" r:id="rId3"/>
     <sheet name="Gráfico Categorias" sheetId="14" r:id="rId4"/>
     <sheet name="Gráfico Anual" sheetId="13" r:id="rId5"/>
   </sheets>
@@ -117,9 +117,6 @@
     <t>Saldo Anual</t>
   </si>
   <si>
-    <t>Rolê</t>
-  </si>
-  <si>
     <t>Descrição</t>
   </si>
   <si>
@@ -144,13 +141,7 @@
     <t>Farm. e Saúde.</t>
   </si>
   <si>
-    <t>Cursos</t>
-  </si>
-  <si>
     <t>Alimentação</t>
-  </si>
-  <si>
-    <t>Entret e Livros</t>
   </si>
   <si>
     <t>Desp. Total</t>
@@ -252,13 +243,7 @@
     <t>G. Residencial</t>
   </si>
   <si>
-    <t>Jogos</t>
-  </si>
-  <si>
     <t>Eletrônicos</t>
-  </si>
-  <si>
-    <t>Carro - Gas</t>
   </si>
   <si>
     <t>Condomínio</t>
@@ -274,6 +259,21 @@
   </si>
   <si>
     <t>Receita_Líquida</t>
+  </si>
+  <si>
+    <t>Jogos/ Livros</t>
+  </si>
+  <si>
+    <t>Rolê/ Entret.</t>
+  </si>
+  <si>
+    <t>Carro</t>
+  </si>
+  <si>
+    <t>Gasolina</t>
+  </si>
+  <si>
+    <t>Curso</t>
   </si>
 </sst>
 </file>
@@ -343,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -366,6 +366,24 @@
       <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +561,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -695,9 +713,6 @@
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -707,12 +722,6 @@
     <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -738,6 +747,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1172,7 +1200,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Carro - Gas</c:v>
+                  <c:v>Carro</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1436,7 +1464,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Cursos</c:v>
+                  <c:v>Curso</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1700,7 +1728,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Entret e Livros</c:v>
+                  <c:v>Farm. e Saúde.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1812,7 +1840,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1832,7 +1860,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Farm. e Saúde.</c:v>
+                  <c:v>G. Residencial</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1969,7 +1997,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>G. Residencial</c:v>
+                  <c:v>Gasolina</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2086,7 +2114,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2106,7 +2134,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Jogos</c:v>
+                  <c:v>Jogos/ Livros</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2243,7 +2271,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Rolê</c:v>
+                  <c:v>Rolê/ Entret.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3155,10 +3183,7 @@
       </c:valAx>
       <c:spPr>
         <a:solidFill>
-          <a:schemeClr val="accent3">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
+          <a:schemeClr val="bg1"/>
         </a:solidFill>
         <a:ln>
           <a:noFill/>
@@ -3548,10 +3573,7 @@
       </c:valAx>
       <c:spPr>
         <a:solidFill>
-          <a:schemeClr val="accent3">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
         <a:ln>
           <a:noFill/>
@@ -4794,31 +4816,31 @@
                   <c:v>Alimentação</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Carro - Gas</c:v>
+                  <c:v>Carro</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Condomínio</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Cursos</c:v>
+                  <c:v>Curso</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Eletrônicos</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Entret e Livros</c:v>
+                  <c:v>Farm. e Saúde.</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Farm. e Saúde.</c:v>
+                  <c:v>G. Residencial</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>G. Residencial</c:v>
+                  <c:v>Gasolina</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Jogos</c:v>
+                  <c:v>Jogos/ Livros</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Rolê</c:v>
+                  <c:v>Rolê/ Entret.</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Roupas</c:v>
@@ -4848,13 +4870,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -8745,14 +8767,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>2</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>36214</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2254313</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>33532</xdr:rowOff>
+      <xdr:rowOff>24479</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9292,42 +9314,40 @@
   <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" style="50" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="47" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="48" customWidth="1"/>
-    <col min="4" max="4" width="15" style="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" style="50" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="50" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" style="51" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="50" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="47" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" style="48" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="50" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="51" customWidth="1"/>
     <col min="8" max="8" width="35.7109375" style="49" customWidth="1"/>
-    <col min="9" max="9" width="6" style="50" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="50" customWidth="1"/>
     <col min="10" max="10" width="10" style="50" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="1:9" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F2" s="57" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73" t="s">
-        <v>36</v>
+      <c r="B3" s="70" t="s">
+        <v>33</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="71" t="str" cm="1">
+      <c r="E3" s="68" t="str" cm="1">
         <f t="array" ref="E3:E14">IF(C3="Despesas",Categorias,IF(C3="Receita Líquida",Receita_Líquida,""))</f>
         <v>Alimentação</v>
       </c>
@@ -9346,8 +9366,8 @@
         <v>50</v>
       </c>
       <c r="D4" s="35"/>
-      <c r="E4" s="71" t="str">
-        <v>Carro - Gas</v>
+      <c r="E4" s="68" t="str">
+        <v>Carro</v>
       </c>
       <c r="F4" s="57">
         <v>0</v>
@@ -9357,7 +9377,7 @@
     <row r="5" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="50"/>
       <c r="C5" s="50"/>
-      <c r="E5" s="71" t="str">
+      <c r="E5" s="68" t="str">
         <v>Condomínio</v>
       </c>
       <c r="F5" s="57">
@@ -9373,8 +9393,8 @@
         <f>VLOOKUP(C2,'Gráfico Anual'!A3:I14,9,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="E6" s="71" t="str">
-        <v>Cursos</v>
+      <c r="E6" s="68" t="str">
+        <v>Curso</v>
       </c>
       <c r="F6" s="57">
         <v>0</v>
@@ -9383,13 +9403,13 @@
     </row>
     <row r="7" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C7" s="27">
         <f>'Gráfico Anual'!I15</f>
         <v>100</v>
       </c>
-      <c r="E7" s="71" t="str">
+      <c r="E7" s="68" t="str">
         <v>Eletrônicos</v>
       </c>
       <c r="F7" s="57">
@@ -9399,24 +9419,24 @@
       <c r="I7" s="36"/>
     </row>
     <row r="8" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="71" t="str">
-        <v>Entret e Livros</v>
+      <c r="E8" s="68" t="str">
+        <v>Farm. e Saúde.</v>
       </c>
       <c r="F8" s="57">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H8" s="50"/>
     </row>
     <row r="9" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B9,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>75</v>
       </c>
-      <c r="E9" s="71" t="str">
-        <v>Farm. e Saúde.</v>
+      <c r="E9" s="68" t="str">
+        <v>G. Residencial</v>
       </c>
       <c r="F9" s="57">
         <v>0</v>
@@ -9426,31 +9446,31 @@
     <row r="10" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
       <c r="B10" s="28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B10,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="71" t="str">
-        <v>G. Residencial</v>
+      <c r="E10" s="68" t="str">
+        <v>Gasolina</v>
       </c>
       <c r="F10" s="57">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H10" s="50"/>
     </row>
     <row r="11" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="48"/>
       <c r="B11" s="28" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B11,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>25</v>
       </c>
-      <c r="E11" s="71" t="str">
-        <v>Jogos</v>
+      <c r="E11" s="68" t="str">
+        <v>Jogos/ Livros</v>
       </c>
       <c r="F11" s="57">
         <v>0</v>
@@ -9460,14 +9480,14 @@
     <row r="12" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48"/>
       <c r="B12" s="28" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C12" s="3">
         <f ca="1">SUM(C9:C11)</f>
         <v>100</v>
       </c>
-      <c r="E12" s="71" t="str">
-        <v>Rolê</v>
+      <c r="E12" s="68" t="str">
+        <v>Rolê/ Entret.</v>
       </c>
       <c r="F12" s="57">
         <v>0</v>
@@ -9477,13 +9497,13 @@
     <row r="13" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="48"/>
       <c r="B13" s="28" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C13" s="27">
-        <f ca="1">C6-C12</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="71" t="str">
+        <f ca="1">ROUND(C6-C12,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="68" t="str">
         <v>Roupas</v>
       </c>
       <c r="F13" s="57">
@@ -9495,15 +9515,15 @@
       <c r="A14" s="48"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="E14" s="71" t="str">
+      <c r="E14" s="68" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="F14" s="72">
+      <c r="F14" s="69">
         <v>0</v>
       </c>
       <c r="H14" s="50"/>
     </row>
-    <row r="15" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="54"/>
       <c r="B15" s="50"/>
       <c r="H15" s="50"/>
@@ -9514,25 +9534,25 @@
         <v>3</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>0</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F16" s="32" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -9544,13 +9564,13 @@
         <v>Janeiro</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G17" s="37">
         <v>150</v>
@@ -9559,7 +9579,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="34">
-        <v>44928</v>
+        <v>44927</v>
       </c>
       <c r="C18" s="35" t="str">
         <f t="shared" si="0"/>
@@ -9569,10 +9589,10 @@
         <v>1</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G18" s="37">
         <v>50</v>
@@ -9581,20 +9601,20 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="34">
-        <v>44929</v>
+        <v>44927</v>
       </c>
       <c r="C19" s="35" t="str">
         <f t="shared" si="0"/>
         <v>Janeiro</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G19" s="37">
         <v>25</v>
@@ -9630,7 +9650,7 @@
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I38" s="50" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.3">
@@ -12821,7 +12841,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations disablePrompts="1" count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
       <formula1>"Despesas, Receita Líquida"</formula1>
     </dataValidation>
@@ -12843,7 +12863,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9270E47-B020-4CBF-A3A9-E523B28C14E7}">
           <x14:formula1>
             <xm:f>'Receita Líquida'!$B$2:$M$2</xm:f>
@@ -12872,58 +12892,58 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="62" t="str">
+      <c r="B2" s="61" t="str">
         <f>PROPER(TEXT("01/01","MMMM"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="C2" s="62" t="str">
+      <c r="C2" s="61" t="str">
         <f>PROPER(TEXT("01/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="D2" s="62" t="str">
+      <c r="D2" s="61" t="str">
         <f>PROPER(TEXT("01/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="E2" s="62" t="str">
+      <c r="E2" s="61" t="str">
         <f>PROPER(TEXT("01/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="F2" s="62" t="str">
+      <c r="F2" s="61" t="str">
         <f>PROPER(TEXT("01/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="G2" s="62" t="str">
+      <c r="G2" s="61" t="str">
         <f>PROPER(TEXT("01/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="H2" s="62" t="str">
+      <c r="H2" s="61" t="str">
         <f>PROPER(TEXT("01/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="I2" s="62" t="str">
+      <c r="I2" s="61" t="str">
         <f>PROPER(TEXT("01/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="J2" s="62" t="str">
+      <c r="J2" s="61" t="str">
         <f>PROPER(TEXT("01/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="K2" s="62" t="str">
+      <c r="K2" s="61" t="str">
         <f>PROPER(TEXT("01/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="L2" s="62" t="str">
+      <c r="L2" s="61" t="str">
         <f>PROPER(TEXT("01/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="M2" s="62" t="str">
+      <c r="M2" s="61" t="str">
         <f>PROPER(TEXT("01/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="59" t="s">
-        <v>29</v>
+      <c r="A3" s="79" t="s">
+        <v>26</v>
       </c>
       <c r="B3" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A3)</f>
@@ -12975,8 +12995,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="59" t="s">
-        <v>39</v>
+      <c r="A4" s="79" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A4)</f>
@@ -13028,8 +13048,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
-        <v>53</v>
+      <c r="A5" s="79" t="s">
+        <v>50</v>
       </c>
       <c r="B5" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A5)</f>
@@ -13081,8 +13101,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="59" t="s">
-        <v>52</v>
+      <c r="A6" s="79" t="s">
+        <v>49</v>
       </c>
       <c r="B6" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A6)</f>
@@ -13134,8 +13154,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="59" t="s">
-        <v>49</v>
+      <c r="A7" s="79" t="s">
+        <v>46</v>
       </c>
       <c r="B7" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A7)</f>
@@ -13187,8 +13207,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="59" t="s">
-        <v>40</v>
+      <c r="A8" s="80" t="s">
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A8)</f>
@@ -13240,8 +13260,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="59" t="s">
-        <v>51</v>
+      <c r="A9" s="80" t="s">
+        <v>48</v>
       </c>
       <c r="B9" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A9)</f>
@@ -13293,8 +13313,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="59" t="s">
-        <v>62</v>
+      <c r="A10" s="80" t="s">
+        <v>57</v>
       </c>
       <c r="B10" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A10)</f>
@@ -13346,8 +13366,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="59" t="s">
-        <v>54</v>
+      <c r="A11" s="80" t="s">
+        <v>51</v>
       </c>
       <c r="B11" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A11)</f>
@@ -13399,8 +13419,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="59" t="s">
-        <v>44</v>
+      <c r="A12" s="80" t="s">
+        <v>41</v>
       </c>
       <c r="B12" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A12)</f>
@@ -13452,8 +13472,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
-        <v>55</v>
+      <c r="A13" s="81" t="s">
+        <v>52</v>
       </c>
       <c r="B13" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A13)</f>
@@ -13505,8 +13525,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="59" t="s">
-        <v>56</v>
+      <c r="A14" s="81" t="s">
+        <v>53</v>
       </c>
       <c r="B14" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A14)</f>
@@ -13620,7 +13640,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" ref="C18:M18" si="1">ROUND(IF((SUM(C3:C7) - SUM(C8:C9,C11:C12)) &gt; 10, (SUM(C3:C7) - SUM(C8:C9,C11:C12))*0.1, )-C10,2)</f>
+        <f t="shared" ref="C18:L18" si="1">ROUND(IF((SUM(C3:C7) - SUM(C8:C9,C11:C12)) &gt; 10, (SUM(C3:C7) - SUM(C8:C9,C11:C12))*0.1, )-C10,2)</f>
         <v>0</v>
       </c>
       <c r="D18" s="3">
@@ -13679,69 +13699,69 @@
   <dimension ref="A2:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="66" customWidth="1"/>
-    <col min="2" max="4" width="17.7109375" style="66" customWidth="1"/>
-    <col min="5" max="10" width="17.85546875" style="66" customWidth="1"/>
-    <col min="11" max="13" width="17.7109375" style="66" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="66" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="66" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.5703125" style="66" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="66"/>
+    <col min="1" max="1" width="15.7109375" style="65" customWidth="1"/>
+    <col min="2" max="4" width="17.7109375" style="65" customWidth="1"/>
+    <col min="5" max="10" width="17.85546875" style="65" customWidth="1"/>
+    <col min="11" max="13" width="17.7109375" style="65" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="65" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="65" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.5703125" style="65" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="65"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="63" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="66"/>
-      <c r="B2" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="62" t="str">
+    <row r="2" spans="1:13" s="62" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="65"/>
+      <c r="B2" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="61" t="str">
         <f>PROPER(TEXT("1/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="D2" s="62" t="str">
+      <c r="D2" s="61" t="str">
         <f>PROPER(TEXT("1/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="E2" s="62" t="str">
+      <c r="E2" s="61" t="str">
         <f>PROPER(TEXT("1/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="F2" s="62" t="str">
+      <c r="F2" s="61" t="str">
         <f>PROPER(TEXT("1/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="G2" s="62" t="str">
+      <c r="G2" s="61" t="str">
         <f>PROPER(TEXT("1/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="H2" s="62" t="str">
+      <c r="H2" s="61" t="str">
         <f>PROPER(TEXT("1/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="I2" s="62" t="str">
+      <c r="I2" s="61" t="str">
         <f>PROPER(TEXT("1/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="J2" s="62" t="str">
+      <c r="J2" s="61" t="str">
         <f>PROPER(TEXT("1/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="K2" s="62" t="str">
+      <c r="K2" s="61" t="str">
         <f>PROPER(TEXT("1/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="L2" s="62" t="str">
+      <c r="L2" s="61" t="str">
         <f>PROPER(TEXT("1/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="M2" s="62" t="str">
+      <c r="M2" s="61" t="str">
         <f>PROPER(TEXT("1/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="64" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="61" t="s">
-        <v>16</v>
+    <row r="3" spans="1:13" s="63" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="83" t="s">
+        <v>15</v>
       </c>
       <c r="B3" s="3">
         <f>'Receita Líquida'!B16</f>
@@ -13793,54 +13813,54 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="65">
+      <c r="B4" s="64">
         <f>B3-(SUM(B7:B18))</f>
         <v>100</v>
       </c>
-      <c r="C4" s="65">
+      <c r="C4" s="64">
         <f t="shared" ref="C4:L4" si="0">C3-(SUM(C7:C18))+B4</f>
         <v>100</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="64">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="E4" s="65">
+      <c r="E4" s="64">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F4" s="65">
+      <c r="F4" s="64">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="64">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="H4" s="65">
+      <c r="H4" s="64">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="I4" s="65">
+      <c r="I4" s="64">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="J4" s="65">
+      <c r="J4" s="64">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K4" s="65">
+      <c r="K4" s="64">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="L4" s="65">
+      <c r="L4" s="64">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="M4" s="65">
+      <c r="M4" s="64">
         <f>M3-SUM(M7:M18)+L4</f>
         <v>100</v>
       </c>
@@ -13861,49 +13881,49 @@
       <c r="M5" s="50"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="68" t="s">
-        <v>28</v>
+      <c r="A6" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="85" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28" t="s">
-        <v>23</v>
+      <c r="A7" s="82" t="s">
+        <v>21</v>
       </c>
       <c r="B7" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
@@ -13955,8 +13975,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
-        <v>60</v>
+      <c r="A8" s="82" t="s">
+        <v>63</v>
       </c>
       <c r="B8" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
@@ -14008,8 +14028,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28" t="s">
-        <v>61</v>
+      <c r="A9" s="82" t="s">
+        <v>56</v>
       </c>
       <c r="B9" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
@@ -14061,8 +14081,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="28" t="s">
-        <v>22</v>
+      <c r="A10" s="82" t="s">
+        <v>65</v>
       </c>
       <c r="B10" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
@@ -14114,8 +14134,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28" t="s">
-        <v>59</v>
+      <c r="A11" s="82" t="s">
+        <v>55</v>
       </c>
       <c r="B11" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
@@ -14167,12 +14187,12 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28" t="s">
-        <v>24</v>
+      <c r="A12" s="82" t="s">
+        <v>20</v>
       </c>
       <c r="B12" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C12" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
@@ -14220,8 +14240,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
-        <v>21</v>
+      <c r="A13" s="82" t="s">
+        <v>54</v>
       </c>
       <c r="B13" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
@@ -14273,12 +14293,12 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28" t="s">
-        <v>57</v>
+      <c r="A14" s="82" t="s">
+        <v>64</v>
       </c>
       <c r="B14" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
@@ -14326,8 +14346,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="28" t="s">
-        <v>58</v>
+      <c r="A15" s="82" t="s">
+        <v>61</v>
       </c>
       <c r="B15" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
@@ -14379,8 +14399,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28" t="s">
-        <v>13</v>
+      <c r="A16" s="82" t="s">
+        <v>62</v>
       </c>
       <c r="B16" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
@@ -14432,7 +14452,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="82" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="3">
@@ -14485,8 +14505,8 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="17.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
-        <v>37</v>
+      <c r="A18" s="82" t="s">
+        <v>34</v>
       </c>
       <c r="B18" s="3">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
@@ -14538,72 +14558,72 @@
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
-    </row>
-    <row r="20" spans="1:14" s="64" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="62" t="s">
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+    </row>
+    <row r="20" spans="1:14" s="63" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="69">
+      <c r="B20" s="66">
         <f t="shared" ref="B20:M20" si="1">SUM(B7:B18)</f>
         <v>50</v>
       </c>
-      <c r="C20" s="69">
+      <c r="C20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D20" s="69">
+      <c r="D20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E20" s="69">
+      <c r="E20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F20" s="69">
+      <c r="F20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="69">
+      <c r="G20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="69">
+      <c r="H20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="69">
+      <c r="I20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="69">
+      <c r="J20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="69">
+      <c r="K20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="69">
+      <c r="L20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="69">
+      <c r="M20" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="70"/>
+      <c r="N20" s="67"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:A17">
@@ -14659,30 +14679,30 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="46" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I2" s="46" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="79">
+      <c r="C3" s="76">
         <f>SUM(C6:C17)</f>
         <v>150</v>
       </c>
-      <c r="I3" s="78" t="s">
+      <c r="I3" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="79">
+      <c r="J3" s="76">
         <f>SUM(J6:J17)</f>
         <v>0</v>
       </c>
@@ -14692,13 +14712,13 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="77" t="s">
-        <v>28</v>
+      <c r="J5" s="74" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -14706,7 +14726,7 @@
         <f t="array" ref="B6:B17">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="C6" s="77" cm="1">
+      <c r="C6" s="74" cm="1">
         <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,Receita_Líquida='Gráfico Categorias'!C2))</f>
         <v>150</v>
       </c>
@@ -14714,7 +14734,7 @@
         <f t="array" ref="I6:I17">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="J6" s="77" cm="1">
+      <c r="J6" s="74" cm="1">
         <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,Categorias='Gráfico Categorias'!J2))</f>
         <v>0</v>
       </c>
@@ -14723,13 +14743,13 @@
       <c r="B7" s="4" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="C7" s="77">
+      <c r="C7" s="74">
         <v>0</v>
       </c>
       <c r="I7" s="4" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14737,13 +14757,13 @@
       <c r="B8" s="4" t="str">
         <v>Março</v>
       </c>
-      <c r="C8" s="77">
+      <c r="C8" s="74">
         <v>0</v>
       </c>
       <c r="I8" s="4" t="str">
         <v>Março</v>
       </c>
-      <c r="J8" s="77">
+      <c r="J8" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14751,13 +14771,13 @@
       <c r="B9" s="4" t="str">
         <v>Abril</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="74">
         <v>0</v>
       </c>
       <c r="I9" s="4" t="str">
         <v>Abril</v>
       </c>
-      <c r="J9" s="77">
+      <c r="J9" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14765,13 +14785,13 @@
       <c r="B10" s="4" t="str">
         <v>Maio</v>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="74">
         <v>0</v>
       </c>
       <c r="I10" s="4" t="str">
         <v>Maio</v>
       </c>
-      <c r="J10" s="77">
+      <c r="J10" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14779,13 +14799,13 @@
       <c r="B11" s="4" t="str">
         <v>Junho</v>
       </c>
-      <c r="C11" s="77">
+      <c r="C11" s="74">
         <v>0</v>
       </c>
       <c r="I11" s="4" t="str">
         <v>Junho</v>
       </c>
-      <c r="J11" s="77">
+      <c r="J11" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14793,13 +14813,13 @@
       <c r="B12" s="4" t="str">
         <v>Julho</v>
       </c>
-      <c r="C12" s="77">
+      <c r="C12" s="74">
         <v>0</v>
       </c>
       <c r="I12" s="4" t="str">
         <v>Julho</v>
       </c>
-      <c r="J12" s="77">
+      <c r="J12" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14807,13 +14827,13 @@
       <c r="B13" s="4" t="str">
         <v>Agosto</v>
       </c>
-      <c r="C13" s="77">
+      <c r="C13" s="74">
         <v>0</v>
       </c>
       <c r="I13" s="4" t="str">
         <v>Agosto</v>
       </c>
-      <c r="J13" s="77">
+      <c r="J13" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14821,13 +14841,13 @@
       <c r="B14" s="4" t="str">
         <v>Setembro</v>
       </c>
-      <c r="C14" s="77">
+      <c r="C14" s="74">
         <v>0</v>
       </c>
       <c r="I14" s="4" t="str">
         <v>Setembro</v>
       </c>
-      <c r="J14" s="77">
+      <c r="J14" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14835,13 +14855,13 @@
       <c r="B15" s="4" t="str">
         <v>Outubro</v>
       </c>
-      <c r="C15" s="77">
+      <c r="C15" s="74">
         <v>0</v>
       </c>
       <c r="I15" s="4" t="str">
         <v>Outubro</v>
       </c>
-      <c r="J15" s="77">
+      <c r="J15" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14849,13 +14869,13 @@
       <c r="B16" s="4" t="str">
         <v>Novembro</v>
       </c>
-      <c r="C16" s="77">
+      <c r="C16" s="74">
         <v>0</v>
       </c>
       <c r="I16" s="4" t="str">
         <v>Novembro</v>
       </c>
-      <c r="J16" s="77">
+      <c r="J16" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14863,13 +14883,13 @@
       <c r="B17" s="4" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="C17" s="77">
+      <c r="C17" s="74">
         <v>0</v>
       </c>
       <c r="I17" s="4" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="J17" s="77">
+      <c r="J17" s="74">
         <v>0</v>
       </c>
     </row>
@@ -14923,7 +14943,7 @@
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>3</v>
@@ -14934,21 +14954,21 @@
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J2" s="4"/>
-      <c r="K2" s="80" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="81"/>
+      <c r="K2" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="78"/>
       <c r="M2" s="39"/>
-      <c r="N2" s="80" t="s">
+      <c r="N2" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="81"/>
+      <c r="O2" s="78"/>
       <c r="P2" s="40"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
@@ -14981,7 +15001,7 @@
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L3" s="17">
         <f>SUM('Receita Líquida'!B3:M7)</f>
@@ -15036,7 +15056,7 @@
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="44" t="str">
-        <v>Carro - Gas</v>
+        <v>Carro</v>
       </c>
       <c r="O4" s="45">
         <f>SUM('Despesas Gerais'!B8:M8)</f>
@@ -15074,7 +15094,7 @@
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L5" s="17">
         <f>SUM('Receita Líquida'!B16:M16)</f>
@@ -15120,7 +15140,7 @@
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="42" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L6" s="17">
         <f>SUM('Despesas Gerais'!B7:B17,'Despesas Gerais'!C7:C17,'Despesas Gerais'!D7:D17,'Despesas Gerais'!E7:E17,'Despesas Gerais'!F7:F17,'Despesas Gerais'!G7:G17,'Despesas Gerais'!H7:H17,'Despesas Gerais'!I7:I17,'Despesas Gerais'!J7:J17,'Despesas Gerais'!K7:K17,'Despesas Gerais'!L7:L17,'Despesas Gerais'!M7:M17)</f>
@@ -15128,7 +15148,7 @@
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="44" t="str">
-        <v>Cursos</v>
+        <v>Curso</v>
       </c>
       <c r="O6" s="45">
         <f>SUM('Despesas Gerais'!B10:M10)</f>
@@ -15166,7 +15186,7 @@
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L7" s="17">
         <f>SUM('Despesas Gerais'!B18:B18,'Despesas Gerais'!C18:C18,'Despesas Gerais'!D18:D18,'Despesas Gerais'!E18:E18,'Despesas Gerais'!F18:F18,'Despesas Gerais'!G18:G18,'Despesas Gerais'!H18:H18,'Despesas Gerais'!I18:I18,'Despesas Gerais'!J18:J18,'Despesas Gerais'!K18:K18,'Despesas Gerais'!L18:L18,'Despesas Gerais'!M18:M18)</f>
@@ -15212,7 +15232,7 @@
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="42" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L8" s="17">
         <f>SUM(L6:L7)</f>
@@ -15220,11 +15240,11 @@
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="44" t="str">
-        <v>Entret e Livros</v>
+        <v>Farm. e Saúde.</v>
       </c>
       <c r="O8" s="45">
         <f>SUM('Despesas Gerais'!B12:M12)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P8" s="40"/>
     </row>
@@ -15266,7 +15286,7 @@
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="44" t="str">
-        <v>Farm. e Saúde.</v>
+        <v>G. Residencial</v>
       </c>
       <c r="O9" s="45">
         <f>SUM('Despesas Gerais'!B13:M13)</f>
@@ -15312,11 +15332,11 @@
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="44" t="str">
-        <v>G. Residencial</v>
+        <v>Gasolina</v>
       </c>
       <c r="O10" s="45">
         <f>SUM('Despesas Gerais'!B14:M14)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P10" s="40"/>
     </row>
@@ -15353,7 +15373,7 @@
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="42" t="str">
-        <v>Jogos</v>
+        <v>Jogos/ Livros</v>
       </c>
       <c r="O11" s="45">
         <f>SUM('Despesas Gerais'!B15:M15)</f>
@@ -15393,8 +15413,8 @@
       <c r="K12" s="40"/>
       <c r="L12" s="41"/>
       <c r="M12" s="41"/>
-      <c r="N12" s="74" t="str">
-        <v>Rolê</v>
+      <c r="N12" s="71" t="str">
+        <v>Rolê/ Entret.</v>
       </c>
       <c r="O12" s="45">
         <f>SUM('Despesas Gerais'!B16:M16)</f>
@@ -15434,7 +15454,7 @@
       <c r="K13" s="40"/>
       <c r="L13" s="41"/>
       <c r="M13" s="41"/>
-      <c r="N13" s="74" t="str">
+      <c r="N13" s="71" t="str">
         <v>Roupas</v>
       </c>
       <c r="O13" s="45">
@@ -15475,10 +15495,10 @@
       <c r="K14" s="40"/>
       <c r="L14" s="40"/>
       <c r="M14" s="40"/>
-      <c r="N14" s="75" t="str">
+      <c r="N14" s="72" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="O14" s="76">
+      <c r="O14" s="73">
         <f>SUM('Despesas Gerais'!B18:M18)</f>
         <v>0</v>
       </c>
@@ -15549,7 +15569,7 @@
     </row>
     <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="16">
@@ -15578,7 +15598,7 @@
     </row>
     <row r="18" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="20">

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81DDB3F-1709-48A3-AE82-C669DDD0DBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C98EDD8-B05E-4212-A645-DEE9F8878BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,6 +383,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -561,10 +567,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -675,36 +680,7 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -724,12 +700,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -741,12 +711,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -766,6 +730,51 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="8" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8768,13 +8777,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>2</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>36214</xdr:rowOff>
+      <xdr:rowOff>28669</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2254313</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>24479</xdr:rowOff>
+      <xdr:rowOff>16934</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9314,3519 +9323,3517 @@
   <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="50" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="47" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" style="48" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" style="50" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="51" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="49" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="50" customWidth="1"/>
-    <col min="10" max="10" width="10" style="50" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="50"/>
+    <col min="1" max="1" width="13.5703125" style="70" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="71" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" style="72" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="70" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="75" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" style="74" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="70" customWidth="1"/>
+    <col min="10" max="10" width="10" style="70" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="70"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="46" t="s">
+    <row r="1" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="83" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="70" t="s">
+    <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="68" t="str" cm="1">
+      <c r="E3" s="81" t="str" cm="1">
         <f t="array" ref="E3:E14">IF(C3="Despesas",Categorias,IF(C3="Receita Líquida",Receita_Líquida,""))</f>
         <v>Alimentação</v>
       </c>
-      <c r="F3" s="57" cm="1">
+      <c r="F3" s="83" cm="1">
         <f t="array" ref="F3:F14">IF(C3="Despesas",_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,'Despesas Gerais'!B2:M2=C2),IF(C3="Receita Líquida",_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,'Receita Líquida'!B2:M2=C2),""))</f>
         <v>0</v>
       </c>
-      <c r="H3" s="50"/>
-    </row>
-    <row r="4" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="28" t="s">
+      <c r="H3" s="70"/>
+    </row>
+    <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <f>IF(C3="Despesas",HLOOKUP(C2,'Despesas Gerais'!B2:M20,19,FALSE),IF(C3="Receita Líquida",HLOOKUP(C2,'Receita Líquida'!B2:M16,15,FALSE),""))</f>
         <v>50</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="68" t="str">
+      <c r="E4" s="81" t="str">
         <v>Carro</v>
       </c>
-      <c r="F4" s="57">
-        <v>0</v>
-      </c>
-      <c r="H4" s="50"/>
-    </row>
-    <row r="5" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="E5" s="68" t="str">
+      <c r="F4" s="83">
+        <v>0</v>
+      </c>
+      <c r="H4" s="70"/>
+    </row>
+    <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="E5" s="81" t="str">
         <v>Condomínio</v>
       </c>
-      <c r="F5" s="57">
-        <v>0</v>
-      </c>
-      <c r="H5" s="50"/>
-    </row>
-    <row r="6" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="28" t="s">
+      <c r="F5" s="83">
+        <v>0</v>
+      </c>
+      <c r="H5" s="70"/>
+    </row>
+    <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <f>VLOOKUP(C2,'Gráfico Anual'!A3:I14,9,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="E6" s="68" t="str">
+      <c r="E6" s="81" t="str">
         <v>Curso</v>
       </c>
-      <c r="F6" s="57">
-        <v>0</v>
-      </c>
-      <c r="H6" s="50"/>
-    </row>
-    <row r="7" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="28" t="s">
+      <c r="F6" s="83">
+        <v>0</v>
+      </c>
+      <c r="H6" s="70"/>
+    </row>
+    <row r="7" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <f>'Gráfico Anual'!I15</f>
         <v>100</v>
       </c>
-      <c r="E7" s="68" t="str">
+      <c r="E7" s="81" t="str">
         <v>Eletrônicos</v>
       </c>
-      <c r="F7" s="57">
-        <v>0</v>
-      </c>
-      <c r="H7" s="50"/>
-      <c r="I7" s="36"/>
-    </row>
-    <row r="8" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="68" t="str">
+      <c r="F7" s="83">
+        <v>0</v>
+      </c>
+      <c r="H7" s="70"/>
+    </row>
+    <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="81" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="F8" s="57">
-        <v>0</v>
-      </c>
-      <c r="H8" s="50"/>
-    </row>
-    <row r="9" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="28" t="s">
+      <c r="F8" s="83">
+        <v>0</v>
+      </c>
+      <c r="H8" s="70"/>
+    </row>
+    <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="3" cm="1">
+      <c r="C9" s="2" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B9,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>75</v>
       </c>
-      <c r="E9" s="68" t="str">
+      <c r="E9" s="81" t="str">
         <v>G. Residencial</v>
       </c>
-      <c r="F9" s="57">
-        <v>0</v>
-      </c>
-      <c r="H9" s="50"/>
-    </row>
-    <row r="10" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48"/>
-      <c r="B10" s="28" t="s">
+      <c r="F9" s="83">
+        <v>0</v>
+      </c>
+      <c r="H9" s="70"/>
+    </row>
+    <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="72"/>
+      <c r="B10" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="3" cm="1">
+      <c r="C10" s="2" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B10,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="68" t="str">
+      <c r="E10" s="81" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="F10" s="57">
+      <c r="F10" s="83">
         <v>50</v>
       </c>
-      <c r="H10" s="50"/>
-    </row>
-    <row r="11" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48"/>
-      <c r="B11" s="28" t="s">
+      <c r="H10" s="70"/>
+    </row>
+    <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="72"/>
+      <c r="B11" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="3" cm="1">
+      <c r="C11" s="2" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B11,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>25</v>
       </c>
-      <c r="E11" s="68" t="str">
+      <c r="E11" s="81" t="str">
         <v>Jogos/ Livros</v>
       </c>
-      <c r="F11" s="57">
-        <v>0</v>
-      </c>
-      <c r="H11" s="50"/>
-    </row>
-    <row r="12" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
-      <c r="B12" s="28" t="s">
+      <c r="F11" s="83">
+        <v>0</v>
+      </c>
+      <c r="H11" s="70"/>
+    </row>
+    <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="72"/>
+      <c r="B12" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f ca="1">SUM(C9:C11)</f>
         <v>100</v>
       </c>
-      <c r="E12" s="68" t="str">
+      <c r="E12" s="81" t="str">
         <v>Rolê/ Entret.</v>
       </c>
-      <c r="F12" s="57">
-        <v>0</v>
-      </c>
-      <c r="H12" s="50"/>
-    </row>
-    <row r="13" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
-      <c r="B13" s="28" t="s">
+      <c r="F12" s="83">
+        <v>0</v>
+      </c>
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="72"/>
+      <c r="B13" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <f ca="1">ROUND(C6-C12,2)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="68" t="str">
+      <c r="E13" s="81" t="str">
         <v>Roupas</v>
       </c>
-      <c r="F13" s="57">
-        <v>0</v>
-      </c>
-      <c r="H13" s="50"/>
-    </row>
-    <row r="14" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="E14" s="68" t="str">
+      <c r="F13" s="83">
+        <v>0</v>
+      </c>
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="72"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="E14" s="81" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="F14" s="69">
-        <v>0</v>
-      </c>
-      <c r="H14" s="50"/>
-    </row>
-    <row r="15" spans="1:9" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54"/>
-      <c r="B15" s="50"/>
-      <c r="H15" s="50"/>
-    </row>
-    <row r="16" spans="1:9" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="56">
+      <c r="F14" s="82">
+        <v>0</v>
+      </c>
+      <c r="H14" s="70"/>
+    </row>
+    <row r="15" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="78"/>
+      <c r="B15" s="70"/>
+      <c r="H15" s="70"/>
+    </row>
+    <row r="16" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="80">
         <f>SUBTOTAL(2,Tabela1[Data])</f>
         <v>3</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="31" t="s">
+      <c r="C16" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="31" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="34">
+      <c r="B17" s="33">
         <v>44927</v>
       </c>
-      <c r="C17" s="35" t="str">
+      <c r="C17" s="34" t="str">
         <f t="shared" ref="C17:C20" si="0">IF(ISBLANK(B17),"",PROPER(TEXT(B17,"MMMM")))</f>
         <v>Janeiro</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="36">
         <v>150</v>
       </c>
-      <c r="H17" s="38"/>
+      <c r="H17" s="37"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="34">
+      <c r="B18" s="33">
         <v>44927</v>
       </c>
-      <c r="C18" s="35" t="str">
+      <c r="C18" s="34" t="str">
         <f t="shared" si="0"/>
         <v>Janeiro</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="36">
         <v>50</v>
       </c>
-      <c r="H18" s="38"/>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="34">
+      <c r="B19" s="33">
         <v>44927</v>
       </c>
-      <c r="C19" s="35" t="str">
+      <c r="C19" s="34" t="str">
         <f t="shared" si="0"/>
         <v>Janeiro</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="36">
         <v>25</v>
       </c>
-      <c r="H19" s="38"/>
+      <c r="H19" s="37"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="34"/>
-      <c r="C20" s="35" t="str">
+      <c r="B20" s="33"/>
+      <c r="C20" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="38"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G23" s="52"/>
+      <c r="G23" s="73"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G25" s="52"/>
+      <c r="G25" s="73"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G26" s="52"/>
+      <c r="G26" s="73"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G27" s="52"/>
+      <c r="G27" s="73"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G28" s="52"/>
+      <c r="G28" s="73"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I38" s="50" t="s">
+      <c r="I38" s="70" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G137" s="52"/>
+      <c r="G137" s="73"/>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G139" s="52"/>
+      <c r="G139" s="73"/>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G140" s="52"/>
+      <c r="G140" s="73"/>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G141" s="52"/>
+      <c r="G141" s="73"/>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G142" s="52"/>
+      <c r="G142" s="73"/>
     </row>
     <row r="248" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C248" s="48" t="str">
+      <c r="C248" s="72" t="str">
         <f>IF(ISBLANK(B248),"",PROPER(TEXT(B248,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="249" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C249" s="48" t="str">
+      <c r="C249" s="72" t="str">
         <f>IF(ISBLANK(B249),"",PROPER(TEXT(B249,"MMMM")))</f>
         <v/>
       </c>
-      <c r="G249" s="58"/>
+      <c r="G249" s="76"/>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C258" s="48" t="str">
+      <c r="C258" s="72" t="str">
         <f>IF(ISBLANK(B258),"",PROPER(TEXT(B258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="D258" s="48" t="str">
+      <c r="D258" s="72" t="str">
         <f t="shared" ref="D258:G258" si="1">IF(ISBLANK(C258),"",PROPER(TEXT(C258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="E258" s="48" t="str">
+      <c r="E258" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F258" s="48" t="str">
+      <c r="F258" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G258" s="48" t="str">
+      <c r="G258" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C267" s="48" t="str">
+      <c r="C267" s="72" t="str">
         <f t="shared" ref="C267" si="2">IF(ISBLANK(B267),"",PROPER(TEXT(B267,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C268" s="48" t="str">
+      <c r="C268" s="72" t="str">
         <f t="shared" ref="C268:C282" si="3">IF(ISBLANK(B268),"",PROPER(TEXT(B268,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C269" s="48" t="str">
+      <c r="C269" s="72" t="str">
         <f t="shared" ref="C269:C279" si="4">IF(ISBLANK(B269),"",PROPER(TEXT(B269,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C270" s="48" t="str">
+      <c r="C270" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C271" s="48" t="str">
+      <c r="C271" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C272" s="48" t="str">
+      <c r="C272" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C273" s="48" t="str">
+      <c r="C273" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C274" s="48" t="str">
+      <c r="C274" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C275" s="48" t="str">
+      <c r="C275" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C276" s="48" t="str">
+      <c r="C276" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C277" s="48" t="str">
+      <c r="C277" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C278" s="48" t="str">
+      <c r="C278" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C279" s="48" t="str">
+      <c r="C279" s="72" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C280" s="48" t="str">
+      <c r="C280" s="72" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C281" s="48" t="str">
+      <c r="C281" s="72" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C282" s="48" t="str">
+      <c r="C282" s="72" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G282" s="52"/>
-      <c r="H282" s="53"/>
+      <c r="G282" s="73"/>
+      <c r="H282" s="77"/>
     </row>
     <row r="283" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B283" s="50"/>
-      <c r="C283" s="50"/>
-      <c r="D283" s="50"/>
-      <c r="E283" s="54"/>
-      <c r="F283" s="54"/>
-      <c r="G283" s="52"/>
-      <c r="H283" s="53"/>
+      <c r="B283" s="70"/>
+      <c r="C283" s="70"/>
+      <c r="D283" s="70"/>
+      <c r="E283" s="78"/>
+      <c r="F283" s="78"/>
+      <c r="G283" s="73"/>
+      <c r="H283" s="77"/>
     </row>
     <row r="284" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B284" s="50"/>
-      <c r="C284" s="50"/>
-      <c r="D284" s="50"/>
-      <c r="E284" s="54"/>
-      <c r="F284" s="54"/>
-      <c r="G284" s="52"/>
-      <c r="H284" s="53"/>
+      <c r="B284" s="70"/>
+      <c r="C284" s="70"/>
+      <c r="D284" s="70"/>
+      <c r="E284" s="78"/>
+      <c r="F284" s="78"/>
+      <c r="G284" s="73"/>
+      <c r="H284" s="77"/>
     </row>
     <row r="285" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B285" s="50"/>
-      <c r="C285" s="50"/>
-      <c r="D285" s="50"/>
-      <c r="E285" s="54"/>
-      <c r="F285" s="54"/>
-      <c r="G285" s="52"/>
-      <c r="H285" s="53"/>
+      <c r="B285" s="70"/>
+      <c r="C285" s="70"/>
+      <c r="D285" s="70"/>
+      <c r="E285" s="78"/>
+      <c r="F285" s="78"/>
+      <c r="G285" s="73"/>
+      <c r="H285" s="77"/>
     </row>
     <row r="286" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B286" s="50"/>
-      <c r="C286" s="55"/>
-      <c r="D286" s="55"/>
-      <c r="E286" s="54"/>
-      <c r="F286" s="54"/>
-      <c r="G286" s="52"/>
-      <c r="H286" s="53"/>
+      <c r="B286" s="70"/>
+      <c r="C286" s="79"/>
+      <c r="D286" s="79"/>
+      <c r="E286" s="78"/>
+      <c r="F286" s="78"/>
+      <c r="G286" s="73"/>
+      <c r="H286" s="77"/>
     </row>
     <row r="287" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B287" s="50"/>
-      <c r="C287" s="50"/>
-      <c r="D287" s="50"/>
-      <c r="G287" s="50"/>
+      <c r="B287" s="70"/>
+      <c r="C287" s="70"/>
+      <c r="D287" s="70"/>
+      <c r="G287" s="70"/>
     </row>
     <row r="288" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B288" s="50"/>
-      <c r="C288" s="50"/>
-      <c r="D288" s="50"/>
-      <c r="G288" s="50"/>
+      <c r="B288" s="70"/>
+      <c r="C288" s="70"/>
+      <c r="D288" s="70"/>
+      <c r="G288" s="70"/>
     </row>
     <row r="289" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B289" s="50"/>
-      <c r="C289" s="50"/>
-      <c r="D289" s="50"/>
-      <c r="G289" s="50"/>
+      <c r="B289" s="70"/>
+      <c r="C289" s="70"/>
+      <c r="D289" s="70"/>
+      <c r="G289" s="70"/>
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B290" s="50"/>
-      <c r="C290" s="50"/>
-      <c r="D290" s="50"/>
-      <c r="G290" s="50"/>
+      <c r="B290" s="70"/>
+      <c r="C290" s="70"/>
+      <c r="D290" s="70"/>
+      <c r="G290" s="70"/>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B291" s="50"/>
-      <c r="C291" s="50"/>
-      <c r="D291" s="50"/>
-      <c r="G291" s="50"/>
+      <c r="B291" s="70"/>
+      <c r="C291" s="70"/>
+      <c r="D291" s="70"/>
+      <c r="G291" s="70"/>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B292" s="50"/>
-      <c r="C292" s="50"/>
-      <c r="D292" s="50"/>
-      <c r="G292" s="50"/>
+      <c r="B292" s="70"/>
+      <c r="C292" s="70"/>
+      <c r="D292" s="70"/>
+      <c r="G292" s="70"/>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B293" s="50"/>
-      <c r="C293" s="50"/>
-      <c r="D293" s="50"/>
-      <c r="G293" s="50"/>
+      <c r="B293" s="70"/>
+      <c r="C293" s="70"/>
+      <c r="D293" s="70"/>
+      <c r="G293" s="70"/>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C294" s="48" t="str">
+      <c r="C294" s="72" t="str">
         <f t="shared" ref="C294:C352" si="5">IF(ISBLANK(B294),"",PROPER(TEXT(B294,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C295" s="48" t="str">
+      <c r="C295" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C296" s="48" t="str">
+      <c r="C296" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C297" s="48" t="str">
+      <c r="C297" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C298" s="48" t="str">
+      <c r="C298" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C299" s="48" t="str">
+      <c r="C299" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C300" s="48" t="str">
+      <c r="C300" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C301" s="48" t="str">
+      <c r="C301" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C302" s="48" t="str">
+      <c r="C302" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C303" s="48" t="str">
+      <c r="C303" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C304" s="48" t="str">
+      <c r="C304" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C305" s="48" t="str">
+      <c r="C305" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C306" s="48" t="str">
+      <c r="C306" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C307" s="48" t="str">
+      <c r="C307" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" s="48" t="str">
+      <c r="C308" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C309" s="48" t="str">
+      <c r="C309" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C310" s="48" t="str">
+      <c r="C310" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C311" s="48" t="str">
+      <c r="C311" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C312" s="48" t="str">
+      <c r="C312" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C313" s="48" t="str">
+      <c r="C313" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C314" s="48" t="str">
+      <c r="C314" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C315" s="48" t="str">
+      <c r="C315" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C316" s="48" t="str">
+      <c r="C316" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C317" s="48" t="str">
+      <c r="C317" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C318" s="48" t="str">
+      <c r="C318" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C319" s="48" t="str">
+      <c r="C319" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C320" s="48" t="str">
+      <c r="C320" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C321" s="48" t="str">
+      <c r="C321" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C322" s="48" t="str">
+      <c r="C322" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C323" s="48" t="str">
+      <c r="C323" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C324" s="48" t="str">
+      <c r="C324" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C325" s="48" t="str">
+      <c r="C325" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C326" s="48" t="str">
+      <c r="C326" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C327" s="48" t="str">
+      <c r="C327" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C328" s="48" t="str">
+      <c r="C328" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C329" s="48" t="str">
+      <c r="C329" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C330" s="48" t="str">
+      <c r="C330" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C331" s="48" t="str">
+      <c r="C331" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C332" s="48" t="str">
+      <c r="C332" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C333" s="48" t="str">
+      <c r="C333" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C334" s="48" t="str">
+      <c r="C334" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C335" s="48" t="str">
+      <c r="C335" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C336" s="48" t="str">
+      <c r="C336" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C337" s="48" t="str">
+      <c r="C337" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C338" s="48" t="str">
+      <c r="C338" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C339" s="48" t="str">
+      <c r="C339" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C340" s="48" t="str">
+      <c r="C340" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C341" s="48" t="str">
+      <c r="C341" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C342" s="48" t="str">
+      <c r="C342" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C343" s="48" t="str">
+      <c r="C343" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C344" s="48" t="str">
+      <c r="C344" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C345" s="48" t="str">
+      <c r="C345" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C346" s="48" t="str">
+      <c r="C346" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C347" s="48" t="str">
+      <c r="C347" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C348" s="48" t="str">
+      <c r="C348" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C349" s="48" t="str">
+      <c r="C349" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C350" s="48" t="str">
+      <c r="C350" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C351" s="48" t="str">
+      <c r="C351" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C352" s="48" t="str">
+      <c r="C352" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C353" s="48" t="str">
+      <c r="C353" s="72" t="str">
         <f t="shared" ref="C353:C416" si="6">IF(ISBLANK(B353),"",PROPER(TEXT(B353,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C354" s="48" t="str">
+      <c r="C354" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C355" s="48" t="str">
+      <c r="C355" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C356" s="48" t="str">
+      <c r="C356" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C357" s="48" t="str">
+      <c r="C357" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C358" s="48" t="str">
+      <c r="C358" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C359" s="48" t="str">
+      <c r="C359" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C360" s="48" t="str">
+      <c r="C360" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C361" s="48" t="str">
+      <c r="C361" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C362" s="48" t="str">
+      <c r="C362" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C363" s="48" t="str">
+      <c r="C363" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C364" s="48" t="str">
+      <c r="C364" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C365" s="48" t="str">
+      <c r="C365" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C366" s="48" t="str">
+      <c r="C366" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C367" s="48" t="str">
+      <c r="C367" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C368" s="48" t="str">
+      <c r="C368" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C369" s="48" t="str">
+      <c r="C369" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C370" s="48" t="str">
+      <c r="C370" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C371" s="48" t="str">
+      <c r="C371" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C372" s="48" t="str">
+      <c r="C372" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C373" s="48" t="str">
+      <c r="C373" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C374" s="48" t="str">
+      <c r="C374" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C375" s="48" t="str">
+      <c r="C375" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C376" s="48" t="str">
+      <c r="C376" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C377" s="48" t="str">
+      <c r="C377" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C378" s="48" t="str">
+      <c r="C378" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C379" s="48" t="str">
+      <c r="C379" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C380" s="48" t="str">
+      <c r="C380" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C381" s="48" t="str">
+      <c r="C381" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C382" s="48" t="str">
+      <c r="C382" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C383" s="48" t="str">
+      <c r="C383" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C384" s="48" t="str">
+      <c r="C384" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C385" s="48" t="str">
+      <c r="C385" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C386" s="48" t="str">
+      <c r="C386" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C387" s="48" t="str">
+      <c r="C387" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C388" s="48" t="str">
+      <c r="C388" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C389" s="48" t="str">
+      <c r="C389" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="48" t="str">
+      <c r="C390" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C391" s="48" t="str">
+      <c r="C391" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C392" s="48" t="str">
+      <c r="C392" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C393" s="48" t="str">
+      <c r="C393" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C394" s="48" t="str">
+      <c r="C394" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C395" s="48" t="str">
+      <c r="C395" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C396" s="48" t="str">
+      <c r="C396" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C397" s="48" t="str">
+      <c r="C397" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C398" s="48" t="str">
+      <c r="C398" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C399" s="48" t="str">
+      <c r="C399" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C400" s="48" t="str">
+      <c r="C400" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C401" s="48" t="str">
+      <c r="C401" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C402" s="48" t="str">
+      <c r="C402" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C403" s="48" t="str">
+      <c r="C403" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C404" s="48" t="str">
+      <c r="C404" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C405" s="48" t="str">
+      <c r="C405" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C406" s="48" t="str">
+      <c r="C406" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C407" s="48" t="str">
+      <c r="C407" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C408" s="48" t="str">
+      <c r="C408" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C409" s="48" t="str">
+      <c r="C409" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C410" s="48" t="str">
+      <c r="C410" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C411" s="48" t="str">
+      <c r="C411" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C412" s="48" t="str">
+      <c r="C412" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C413" s="48" t="str">
+      <c r="C413" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C414" s="48" t="str">
+      <c r="C414" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C415" s="48" t="str">
+      <c r="C415" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C416" s="48" t="str">
+      <c r="C416" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="48" t="str">
+      <c r="C417" s="72" t="str">
         <f t="shared" ref="C417:C480" si="7">IF(ISBLANK(B417),"",PROPER(TEXT(B417,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C418" s="48" t="str">
+      <c r="C418" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C419" s="48" t="str">
+      <c r="C419" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="48" t="str">
+      <c r="C420" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C421" s="48" t="str">
+      <c r="C421" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C422" s="48" t="str">
+      <c r="C422" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C423" s="48" t="str">
+      <c r="C423" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C424" s="48" t="str">
+      <c r="C424" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C425" s="48" t="str">
+      <c r="C425" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C426" s="48" t="str">
+      <c r="C426" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C427" s="48" t="str">
+      <c r="C427" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C428" s="48" t="str">
+      <c r="C428" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C429" s="48" t="str">
+      <c r="C429" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C430" s="48" t="str">
+      <c r="C430" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C431" s="48" t="str">
+      <c r="C431" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C432" s="48" t="str">
+      <c r="C432" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="48" t="str">
+      <c r="C433" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C434" s="48" t="str">
+      <c r="C434" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C435" s="48" t="str">
+      <c r="C435" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="48" t="str">
+      <c r="C436" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C437" s="48" t="str">
+      <c r="C437" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C438" s="48" t="str">
+      <c r="C438" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C439" s="48" t="str">
+      <c r="C439" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C440" s="48" t="str">
+      <c r="C440" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C441" s="48" t="str">
+      <c r="C441" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C442" s="48" t="str">
+      <c r="C442" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C443" s="48" t="str">
+      <c r="C443" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C444" s="48" t="str">
+      <c r="C444" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C445" s="48" t="str">
+      <c r="C445" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C446" s="48" t="str">
+      <c r="C446" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C447" s="48" t="str">
+      <c r="C447" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C448" s="48" t="str">
+      <c r="C448" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C449" s="48" t="str">
+      <c r="C449" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C450" s="48" t="str">
+      <c r="C450" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C451" s="48" t="str">
+      <c r="C451" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C452" s="48" t="str">
+      <c r="C452" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C453" s="48" t="str">
+      <c r="C453" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C454" s="48" t="str">
+      <c r="C454" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C455" s="48" t="str">
+      <c r="C455" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C456" s="48" t="str">
+      <c r="C456" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C457" s="48" t="str">
+      <c r="C457" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C458" s="48" t="str">
+      <c r="C458" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C459" s="48" t="str">
+      <c r="C459" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C460" s="48" t="str">
+      <c r="C460" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C461" s="48" t="str">
+      <c r="C461" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C462" s="48" t="str">
+      <c r="C462" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C463" s="48" t="str">
+      <c r="C463" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C464" s="48" t="str">
+      <c r="C464" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" s="48" t="str">
+      <c r="C465" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C466" s="48" t="str">
+      <c r="C466" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C467" s="48" t="str">
+      <c r="C467" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C468" s="48" t="str">
+      <c r="C468" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C469" s="48" t="str">
+      <c r="C469" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C470" s="48" t="str">
+      <c r="C470" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C471" s="48" t="str">
+      <c r="C471" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C472" s="48" t="str">
+      <c r="C472" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C473" s="48" t="str">
+      <c r="C473" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" s="48" t="str">
+      <c r="C474" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" s="48" t="str">
+      <c r="C475" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" s="48" t="str">
+      <c r="C476" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C477" s="48" t="str">
+      <c r="C477" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C478" s="48" t="str">
+      <c r="C478" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C479" s="48" t="str">
+      <c r="C479" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C480" s="48" t="str">
+      <c r="C480" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C481" s="48" t="str">
+      <c r="C481" s="72" t="str">
         <f t="shared" ref="C481:C544" si="8">IF(ISBLANK(B481),"",PROPER(TEXT(B481,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="482" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C482" s="48" t="str">
+      <c r="C482" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C483" s="48" t="str">
+      <c r="C483" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C484" s="48" t="str">
+      <c r="C484" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C485" s="48" t="str">
+      <c r="C485" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C486" s="48" t="str">
+      <c r="C486" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="48" t="str">
+      <c r="C487" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" s="48" t="str">
+      <c r="C488" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" s="48" t="str">
+      <c r="C489" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C490" s="48" t="str">
+      <c r="C490" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C491" s="48" t="str">
+      <c r="C491" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C492" s="48" t="str">
+      <c r="C492" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C493" s="48" t="str">
+      <c r="C493" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C494" s="48" t="str">
+      <c r="C494" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C495" s="48" t="str">
+      <c r="C495" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C496" s="48" t="str">
+      <c r="C496" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C497" s="48" t="str">
+      <c r="C497" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="48" t="str">
+      <c r="C498" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" s="48" t="str">
+      <c r="C499" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" s="48" t="str">
+      <c r="C500" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="48" t="str">
+      <c r="C501" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C502" s="48" t="str">
+      <c r="C502" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C503" s="48" t="str">
+      <c r="C503" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C504" s="48" t="str">
+      <c r="C504" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C505" s="48" t="str">
+      <c r="C505" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C506" s="48" t="str">
+      <c r="C506" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C507" s="48" t="str">
+      <c r="C507" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C508" s="48" t="str">
+      <c r="C508" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C509" s="48" t="str">
+      <c r="C509" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C510" s="48" t="str">
+      <c r="C510" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C511" s="48" t="str">
+      <c r="C511" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C512" s="48" t="str">
+      <c r="C512" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C513" s="48" t="str">
+      <c r="C513" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" s="48" t="str">
+      <c r="C514" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" s="48" t="str">
+      <c r="C515" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" s="48" t="str">
+      <c r="C516" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C517" s="48" t="str">
+      <c r="C517" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C518" s="48" t="str">
+      <c r="C518" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C519" s="48" t="str">
+      <c r="C519" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C520" s="48" t="str">
+      <c r="C520" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C521" s="48" t="str">
+      <c r="C521" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" s="48" t="str">
+      <c r="C522" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" s="48" t="str">
+      <c r="C523" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" s="48" t="str">
+      <c r="C524" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C525" s="48" t="str">
+      <c r="C525" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C526" s="48" t="str">
+      <c r="C526" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C527" s="48" t="str">
+      <c r="C527" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C528" s="48" t="str">
+      <c r="C528" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C529" s="48" t="str">
+      <c r="C529" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" s="48" t="str">
+      <c r="C530" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" s="48" t="str">
+      <c r="C531" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" s="48" t="str">
+      <c r="C532" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C533" s="48" t="str">
+      <c r="C533" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C534" s="48" t="str">
+      <c r="C534" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C535" s="48" t="str">
+      <c r="C535" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C536" s="48" t="str">
+      <c r="C536" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C537" s="48" t="str">
+      <c r="C537" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C538" s="48" t="str">
+      <c r="C538" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C539" s="48" t="str">
+      <c r="C539" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C540" s="48" t="str">
+      <c r="C540" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C541" s="48" t="str">
+      <c r="C541" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C542" s="48" t="str">
+      <c r="C542" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C543" s="48" t="str">
+      <c r="C543" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C544" s="48" t="str">
+      <c r="C544" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C545" s="48" t="str">
+      <c r="C545" s="72" t="str">
         <f t="shared" ref="C545:C608" si="9">IF(ISBLANK(B545),"",PROPER(TEXT(B545,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="546" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C546" s="48" t="str">
+      <c r="C546" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C547" s="48" t="str">
+      <c r="C547" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C548" s="48" t="str">
+      <c r="C548" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C549" s="48" t="str">
+      <c r="C549" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C550" s="48" t="str">
+      <c r="C550" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C551" s="48" t="str">
+      <c r="C551" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C552" s="48" t="str">
+      <c r="C552" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C553" s="48" t="str">
+      <c r="C553" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C554" s="48" t="str">
+      <c r="C554" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C555" s="48" t="str">
+      <c r="C555" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C556" s="48" t="str">
+      <c r="C556" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C557" s="48" t="str">
+      <c r="C557" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C558" s="48" t="str">
+      <c r="C558" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C559" s="48" t="str">
+      <c r="C559" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C560" s="48" t="str">
+      <c r="C560" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C561" s="48" t="str">
+      <c r="C561" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C562" s="48" t="str">
+      <c r="C562" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C563" s="48" t="str">
+      <c r="C563" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C564" s="48" t="str">
+      <c r="C564" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C565" s="48" t="str">
+      <c r="C565" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C566" s="48" t="str">
+      <c r="C566" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C567" s="48" t="str">
+      <c r="C567" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C568" s="48" t="str">
+      <c r="C568" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C569" s="48" t="str">
+      <c r="C569" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C570" s="48" t="str">
+      <c r="C570" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C571" s="48" t="str">
+      <c r="C571" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C572" s="48" t="str">
+      <c r="C572" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C573" s="48" t="str">
+      <c r="C573" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C574" s="48" t="str">
+      <c r="C574" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C575" s="48" t="str">
+      <c r="C575" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C576" s="48" t="str">
+      <c r="C576" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C577" s="48" t="str">
+      <c r="C577" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C578" s="48" t="str">
+      <c r="C578" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C579" s="48" t="str">
+      <c r="C579" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C580" s="48" t="str">
+      <c r="C580" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C581" s="48" t="str">
+      <c r="C581" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C582" s="48" t="str">
+      <c r="C582" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C583" s="48" t="str">
+      <c r="C583" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C584" s="48" t="str">
+      <c r="C584" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C585" s="48" t="str">
+      <c r="C585" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C586" s="48" t="str">
+      <c r="C586" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C587" s="48" t="str">
+      <c r="C587" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C588" s="48" t="str">
+      <c r="C588" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C589" s="48" t="str">
+      <c r="C589" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C590" s="48" t="str">
+      <c r="C590" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C591" s="48" t="str">
+      <c r="C591" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C592" s="48" t="str">
+      <c r="C592" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C593" s="48" t="str">
+      <c r="C593" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C594" s="48" t="str">
+      <c r="C594" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C595" s="48" t="str">
+      <c r="C595" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C596" s="48" t="str">
+      <c r="C596" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C597" s="48" t="str">
+      <c r="C597" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C598" s="48" t="str">
+      <c r="C598" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C599" s="48" t="str">
+      <c r="C599" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C600" s="48" t="str">
+      <c r="C600" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C601" s="48" t="str">
+      <c r="C601" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C602" s="48" t="str">
+      <c r="C602" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C603" s="48" t="str">
+      <c r="C603" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C604" s="48" t="str">
+      <c r="C604" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C605" s="48" t="str">
+      <c r="C605" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C606" s="48" t="str">
+      <c r="C606" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C607" s="48" t="str">
+      <c r="C607" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C608" s="48" t="str">
+      <c r="C608" s="72" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C609" s="48" t="str">
+      <c r="C609" s="72" t="str">
         <f t="shared" ref="C609:C672" si="10">IF(ISBLANK(B609),"",PROPER(TEXT(B609,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="610" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C610" s="48" t="str">
+      <c r="C610" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C611" s="48" t="str">
+      <c r="C611" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C612" s="48" t="str">
+      <c r="C612" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C613" s="48" t="str">
+      <c r="C613" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C614" s="48" t="str">
+      <c r="C614" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C615" s="48" t="str">
+      <c r="C615" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C616" s="48" t="str">
+      <c r="C616" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C617" s="48" t="str">
+      <c r="C617" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C618" s="48" t="str">
+      <c r="C618" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C619" s="48" t="str">
+      <c r="C619" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C620" s="48" t="str">
+      <c r="C620" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C621" s="48" t="str">
+      <c r="C621" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C622" s="48" t="str">
+      <c r="C622" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C623" s="48" t="str">
+      <c r="C623" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C624" s="48" t="str">
+      <c r="C624" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C625" s="48" t="str">
+      <c r="C625" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C626" s="48" t="str">
+      <c r="C626" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C627" s="48" t="str">
+      <c r="C627" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C628" s="48" t="str">
+      <c r="C628" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C629" s="48" t="str">
+      <c r="C629" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C630" s="48" t="str">
+      <c r="C630" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C631" s="48" t="str">
+      <c r="C631" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C632" s="48" t="str">
+      <c r="C632" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C633" s="48" t="str">
+      <c r="C633" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C634" s="48" t="str">
+      <c r="C634" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C635" s="48" t="str">
+      <c r="C635" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C636" s="48" t="str">
+      <c r="C636" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C637" s="48" t="str">
+      <c r="C637" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C638" s="48" t="str">
+      <c r="C638" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C639" s="48" t="str">
+      <c r="C639" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C640" s="48" t="str">
+      <c r="C640" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C641" s="48" t="str">
+      <c r="C641" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C642" s="48" t="str">
+      <c r="C642" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C643" s="48" t="str">
+      <c r="C643" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C644" s="48" t="str">
+      <c r="C644" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C645" s="48" t="str">
+      <c r="C645" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C646" s="48" t="str">
+      <c r="C646" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C647" s="48" t="str">
+      <c r="C647" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C648" s="48" t="str">
+      <c r="C648" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C649" s="48" t="str">
+      <c r="C649" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C650" s="48" t="str">
+      <c r="C650" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C651" s="48" t="str">
+      <c r="C651" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C652" s="48" t="str">
+      <c r="C652" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C653" s="48" t="str">
+      <c r="C653" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C654" s="48" t="str">
+      <c r="C654" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C655" s="48" t="str">
+      <c r="C655" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C656" s="48" t="str">
+      <c r="C656" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C657" s="48" t="str">
+      <c r="C657" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C658" s="48" t="str">
+      <c r="C658" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C659" s="48" t="str">
+      <c r="C659" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C660" s="48" t="str">
+      <c r="C660" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C661" s="48" t="str">
+      <c r="C661" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C662" s="48" t="str">
+      <c r="C662" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C663" s="48" t="str">
+      <c r="C663" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C664" s="48" t="str">
+      <c r="C664" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C665" s="48" t="str">
+      <c r="C665" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C666" s="48" t="str">
+      <c r="C666" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C667" s="48" t="str">
+      <c r="C667" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C668" s="48" t="str">
+      <c r="C668" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C669" s="48" t="str">
+      <c r="C669" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C670" s="48" t="str">
+      <c r="C670" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C671" s="48" t="str">
+      <c r="C671" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C672" s="48" t="str">
+      <c r="C672" s="72" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C673" s="48" t="str">
+      <c r="C673" s="72" t="str">
         <f t="shared" ref="C673:C736" si="11">IF(ISBLANK(B673),"",PROPER(TEXT(B673,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="674" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C674" s="48" t="str">
+      <c r="C674" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C675" s="48" t="str">
+      <c r="C675" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C676" s="48" t="str">
+      <c r="C676" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C677" s="48" t="str">
+      <c r="C677" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C678" s="48" t="str">
+      <c r="C678" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C679" s="48" t="str">
+      <c r="C679" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C680" s="48" t="str">
+      <c r="C680" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C681" s="48" t="str">
+      <c r="C681" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C682" s="48" t="str">
+      <c r="C682" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C683" s="48" t="str">
+      <c r="C683" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C684" s="48" t="str">
+      <c r="C684" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C685" s="48" t="str">
+      <c r="C685" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="686" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C686" s="48" t="str">
+      <c r="C686" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="687" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C687" s="48" t="str">
+      <c r="C687" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="688" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C688" s="48" t="str">
+      <c r="C688" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="689" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C689" s="48" t="str">
+      <c r="C689" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="690" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C690" s="48" t="str">
+      <c r="C690" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="691" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C691" s="48" t="str">
+      <c r="C691" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="692" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C692" s="48" t="str">
+      <c r="C692" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="693" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C693" s="48" t="str">
+      <c r="C693" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="694" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C694" s="48" t="str">
+      <c r="C694" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="695" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C695" s="48" t="str">
+      <c r="C695" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="696" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C696" s="48" t="str">
+      <c r="C696" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="697" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C697" s="48" t="str">
+      <c r="C697" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="698" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C698" s="48" t="str">
+      <c r="C698" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="699" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C699" s="48" t="str">
+      <c r="C699" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="700" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C700" s="48" t="str">
+      <c r="C700" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="701" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C701" s="48" t="str">
+      <c r="C701" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="702" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C702" s="48" t="str">
+      <c r="C702" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="703" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C703" s="48" t="str">
+      <c r="C703" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="704" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C704" s="48" t="str">
+      <c r="C704" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="705" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C705" s="48" t="str">
+      <c r="C705" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="706" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C706" s="48" t="str">
+      <c r="C706" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="707" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C707" s="48" t="str">
+      <c r="C707" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="708" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C708" s="48" t="str">
+      <c r="C708" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="709" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C709" s="48" t="str">
+      <c r="C709" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="710" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C710" s="48" t="str">
+      <c r="C710" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="711" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C711" s="48" t="str">
+      <c r="C711" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="712" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C712" s="48" t="str">
+      <c r="C712" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="713" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C713" s="48" t="str">
+      <c r="C713" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="714" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C714" s="48" t="str">
+      <c r="C714" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="715" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C715" s="48" t="str">
+      <c r="C715" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="716" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C716" s="48" t="str">
+      <c r="C716" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="717" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C717" s="48" t="str">
+      <c r="C717" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="718" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C718" s="48" t="str">
+      <c r="C718" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="719" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C719" s="48" t="str">
+      <c r="C719" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="720" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C720" s="48" t="str">
+      <c r="C720" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="721" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C721" s="48" t="str">
+      <c r="C721" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="722" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C722" s="48" t="str">
+      <c r="C722" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="723" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C723" s="48" t="str">
+      <c r="C723" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="724" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C724" s="48" t="str">
+      <c r="C724" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="725" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C725" s="48" t="str">
+      <c r="C725" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="726" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C726" s="48" t="str">
+      <c r="C726" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="727" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C727" s="48" t="str">
+      <c r="C727" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="728" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C728" s="48" t="str">
+      <c r="C728" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="729" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C729" s="48" t="str">
+      <c r="C729" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="730" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C730" s="48" t="str">
+      <c r="C730" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="731" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C731" s="48" t="str">
+      <c r="C731" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="732" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C732" s="48" t="str">
+      <c r="C732" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="733" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C733" s="48" t="str">
+      <c r="C733" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="734" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C734" s="48" t="str">
+      <c r="C734" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="735" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C735" s="48" t="str">
+      <c r="C735" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="736" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C736" s="48" t="str">
+      <c r="C736" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="737" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C737" s="48" t="str">
+      <c r="C737" s="72" t="str">
         <f t="shared" ref="C737:C785" si="12">IF(ISBLANK(B737),"",PROPER(TEXT(B737,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="738" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C738" s="48" t="str">
+      <c r="C738" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="739" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C739" s="48" t="str">
+      <c r="C739" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="740" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C740" s="48" t="str">
+      <c r="C740" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="741" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C741" s="48" t="str">
+      <c r="C741" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="742" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C742" s="48" t="str">
+      <c r="C742" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="743" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C743" s="48" t="str">
+      <c r="C743" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="744" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C744" s="48" t="str">
+      <c r="C744" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="745" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C745" s="48" t="str">
+      <c r="C745" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="746" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C746" s="48" t="str">
+      <c r="C746" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="747" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C747" s="48" t="str">
+      <c r="C747" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="748" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C748" s="48" t="str">
+      <c r="C748" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="749" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C749" s="48" t="str">
+      <c r="C749" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="750" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C750" s="48" t="str">
+      <c r="C750" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="751" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C751" s="48" t="str">
+      <c r="C751" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="752" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C752" s="48" t="str">
+      <c r="C752" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="753" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C753" s="48" t="str">
+      <c r="C753" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="754" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C754" s="48" t="str">
+      <c r="C754" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="755" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C755" s="48" t="str">
+      <c r="C755" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="756" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C756" s="48" t="str">
+      <c r="C756" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="757" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C757" s="48" t="str">
+      <c r="C757" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="758" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C758" s="48" t="str">
+      <c r="C758" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="759" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C759" s="48" t="str">
+      <c r="C759" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="760" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C760" s="48" t="str">
+      <c r="C760" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="761" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C761" s="48" t="str">
+      <c r="C761" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="762" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C762" s="48" t="str">
+      <c r="C762" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="763" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C763" s="48" t="str">
+      <c r="C763" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="764" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C764" s="48" t="str">
+      <c r="C764" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="765" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C765" s="48" t="str">
+      <c r="C765" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="766" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C766" s="48" t="str">
+      <c r="C766" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="767" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C767" s="48" t="str">
+      <c r="C767" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="768" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C768" s="48" t="str">
+      <c r="C768" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="769" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C769" s="48" t="str">
+      <c r="C769" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="770" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C770" s="48" t="str">
+      <c r="C770" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="771" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C771" s="48" t="str">
+      <c r="C771" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="772" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C772" s="48" t="str">
+      <c r="C772" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="773" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C773" s="48" t="str">
+      <c r="C773" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="774" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C774" s="48" t="str">
+      <c r="C774" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="775" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C775" s="48" t="str">
+      <c r="C775" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="776" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C776" s="48" t="str">
+      <c r="C776" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="777" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C777" s="48" t="str">
+      <c r="C777" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="778" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C778" s="48" t="str">
+      <c r="C778" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="779" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C779" s="48" t="str">
+      <c r="C779" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="780" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C780" s="48" t="str">
+      <c r="C780" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="781" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C781" s="48" t="str">
+      <c r="C781" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="782" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C782" s="48" t="str">
+      <c r="C782" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="783" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C783" s="48" t="str">
+      <c r="C783" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="784" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C784" s="48" t="str">
+      <c r="C784" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C785" s="48" t="str">
+      <c r="C785" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
@@ -12884,802 +12891,802 @@
   <dimension ref="A2:M18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" style="4" customWidth="1"/>
-    <col min="2" max="13" width="15" style="4" customWidth="1"/>
-    <col min="14" max="14" width="5.7109375" style="4" customWidth="1"/>
-    <col min="15" max="15" width="4.28515625" style="4" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="17.85546875" style="3" customWidth="1"/>
+    <col min="2" max="13" width="15" style="3" customWidth="1"/>
+    <col min="14" max="14" width="5.7109375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="4.28515625" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="61" t="str">
+      <c r="B2" s="49" t="str">
         <f>PROPER(TEXT("01/01","MMMM"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="C2" s="61" t="str">
+      <c r="C2" s="49" t="str">
         <f>PROPER(TEXT("01/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="D2" s="61" t="str">
+      <c r="D2" s="49" t="str">
         <f>PROPER(TEXT("01/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="E2" s="61" t="str">
+      <c r="E2" s="49" t="str">
         <f>PROPER(TEXT("01/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="F2" s="61" t="str">
+      <c r="F2" s="49" t="str">
         <f>PROPER(TEXT("01/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="G2" s="61" t="str">
+      <c r="G2" s="49" t="str">
         <f>PROPER(TEXT("01/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="H2" s="61" t="str">
+      <c r="H2" s="49" t="str">
         <f>PROPER(TEXT("01/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="I2" s="61" t="str">
+      <c r="I2" s="49" t="str">
         <f>PROPER(TEXT("01/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="J2" s="61" t="str">
+      <c r="J2" s="49" t="str">
         <f>PROPER(TEXT("01/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="K2" s="61" t="str">
+      <c r="K2" s="49" t="str">
         <f>PROPER(TEXT("01/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="L2" s="61" t="str">
+      <c r="L2" s="49" t="str">
         <f>PROPER(TEXT("01/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="M2" s="61" t="str">
+      <c r="M2" s="49" t="str">
         <f>PROPER(TEXT("01/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A3)</f>
         <v>150</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="79" t="s">
+      <c r="A7" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="80" t="s">
+      <c r="A10" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="80" t="s">
+      <c r="A12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <f>ROUND(SUM(B3:B7)-SUM(B8:B14),2)</f>
         <v>150</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f t="shared" ref="C16:M16" si="0">ROUND(SUM(C3:C7)-SUM(C8:C14),2)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="18.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="59" t="str">
+      <c r="A18" s="47" t="str">
         <f>A10</f>
         <v>Taxa</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f>ROUND(IF((SUM(B3:B7) - SUM(B8:B9,B11:B12)) &gt; 10, (SUM(B3:B7) - SUM(B8:B9,B11:B12))*0.1, )-B10,2)</f>
         <v>15</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f t="shared" ref="C18:L18" si="1">ROUND(IF((SUM(C3:C7) - SUM(C8:C9,C11:C12)) &gt; 10, (SUM(C3:C7) - SUM(C8:C9,C11:C12))*0.1, )-C10,2)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="2">
         <f>ROUND(IF((SUM(M3:M7) - SUM(M8:M9,M11:M12)) &gt; 10, (SUM(M3:M7) - SUM(M8:M9,M11:M12))*0.1, )-M10,2)</f>
         <v>0</v>
       </c>
@@ -13699,931 +13706,931 @@
   <dimension ref="A2:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="65" customWidth="1"/>
-    <col min="2" max="4" width="17.7109375" style="65" customWidth="1"/>
-    <col min="5" max="10" width="17.85546875" style="65" customWidth="1"/>
-    <col min="11" max="13" width="17.7109375" style="65" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="65" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="65" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.5703125" style="65" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="65"/>
+    <col min="1" max="1" width="15.7109375" style="53" customWidth="1"/>
+    <col min="2" max="4" width="17.7109375" style="53" customWidth="1"/>
+    <col min="5" max="10" width="17.85546875" style="53" customWidth="1"/>
+    <col min="11" max="13" width="17.7109375" style="53" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="53"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="62" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="65"/>
-      <c r="B2" s="61" t="s">
+    <row r="2" spans="1:13" s="50" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="53"/>
+      <c r="B2" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="61" t="str">
+      <c r="C2" s="49" t="str">
         <f>PROPER(TEXT("1/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="D2" s="61" t="str">
+      <c r="D2" s="49" t="str">
         <f>PROPER(TEXT("1/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="E2" s="61" t="str">
+      <c r="E2" s="49" t="str">
         <f>PROPER(TEXT("1/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="F2" s="61" t="str">
+      <c r="F2" s="49" t="str">
         <f>PROPER(TEXT("1/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="G2" s="61" t="str">
+      <c r="G2" s="49" t="str">
         <f>PROPER(TEXT("1/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="H2" s="61" t="str">
+      <c r="H2" s="49" t="str">
         <f>PROPER(TEXT("1/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="I2" s="61" t="str">
+      <c r="I2" s="49" t="str">
         <f>PROPER(TEXT("1/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="J2" s="61" t="str">
+      <c r="J2" s="49" t="str">
         <f>PROPER(TEXT("1/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="K2" s="61" t="str">
+      <c r="K2" s="49" t="str">
         <f>PROPER(TEXT("1/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="L2" s="61" t="str">
+      <c r="L2" s="49" t="str">
         <f>PROPER(TEXT("1/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="M2" s="61" t="str">
+      <c r="M2" s="49" t="str">
         <f>PROPER(TEXT("1/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="63" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="83" t="s">
+    <row r="3" spans="1:13" s="51" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f>'Receita Líquida'!B16</f>
         <v>150</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>'Receita Líquida'!C16</f>
         <v>0</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>'Receita Líquida'!D16</f>
         <v>0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f>'Receita Líquida'!E16</f>
         <v>0</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f>'Receita Líquida'!F16</f>
         <v>0</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <f>'Receita Líquida'!G16</f>
         <v>0</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <f>'Receita Líquida'!H16</f>
         <v>0</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <f>'Receita Líquida'!I16</f>
         <v>0</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <f>'Receita Líquida'!J16</f>
         <v>0</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <f>'Receita Líquida'!K16</f>
         <v>0</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <f>'Receita Líquida'!L16</f>
         <v>0</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <f>'Receita Líquida'!M16</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="64">
+      <c r="B4" s="52">
         <f>B3-(SUM(B7:B18))</f>
         <v>100</v>
       </c>
-      <c r="C4" s="64">
+      <c r="C4" s="52">
         <f t="shared" ref="C4:L4" si="0">C3-(SUM(C7:C18))+B4</f>
         <v>100</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="52">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="E4" s="64">
+      <c r="E4" s="52">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F4" s="64">
+      <c r="F4" s="52">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="G4" s="64">
+      <c r="G4" s="52">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="H4" s="64">
+      <c r="H4" s="52">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="I4" s="64">
+      <c r="I4" s="52">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="52">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K4" s="64">
+      <c r="K4" s="52">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="L4" s="64">
+      <c r="L4" s="52">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="M4" s="64">
+      <c r="M4" s="52">
         <f>M3-SUM(M7:M18)+L4</f>
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="50"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="85" t="s">
+      <c r="C6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="85" t="s">
+      <c r="E6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="85" t="s">
+      <c r="F6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="85" t="s">
+      <c r="G6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="85" t="s">
+      <c r="H6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="85" t="s">
+      <c r="I6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="85" t="s">
+      <c r="J6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="85" t="s">
+      <c r="K6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="85" t="s">
+      <c r="L6" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="85" t="s">
+      <c r="M6" s="69" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="82" t="s">
+      <c r="A10" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="82" t="s">
+      <c r="A11" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>50</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="82" t="s">
+      <c r="A15" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="82" t="s">
+      <c r="A16" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="82" t="s">
+      <c r="A17" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="17.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="82" t="s">
+      <c r="A18" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-    </row>
-    <row r="20" spans="1:14" s="63" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="61" t="s">
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="51"/>
+    </row>
+    <row r="20" spans="1:14" s="51" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="66">
+      <c r="B20" s="54">
         <f t="shared" ref="B20:M20" si="1">SUM(B7:B18)</f>
         <v>50</v>
       </c>
-      <c r="C20" s="66">
+      <c r="C20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D20" s="66">
+      <c r="D20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="66">
+      <c r="H20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="66">
+      <c r="I20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="66">
+      <c r="J20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="66">
+      <c r="K20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="66">
+      <c r="L20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="66">
+      <c r="M20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="67"/>
+      <c r="N20" s="55"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:A17">
@@ -14665,231 +14672,231 @@
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="4" customWidth="1"/>
-    <col min="2" max="3" width="17.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="4" customWidth="1"/>
-    <col min="9" max="10" width="17.140625" style="4" customWidth="1"/>
-    <col min="11" max="13" width="9.140625" style="4"/>
-    <col min="14" max="14" width="7.140625" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="8.5703125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="3" customWidth="1"/>
+    <col min="9" max="10" width="17.140625" style="3" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="3"/>
+    <col min="14" max="14" width="7.140625" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="46" t="s">
+      <c r="I2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="46" t="s">
+      <c r="J2" s="45" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="76">
+      <c r="C3" s="62">
         <f>SUM(C6:C17)</f>
         <v>150</v>
       </c>
-      <c r="I3" s="75" t="s">
+      <c r="I3" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="76">
+      <c r="J3" s="62">
         <f>SUM(J6:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5" s="74" t="s">
+      <c r="I5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="60" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="4" t="str" cm="1">
+      <c r="B6" s="3" t="str" cm="1">
         <f t="array" ref="B6:B17">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="C6" s="74" cm="1">
+      <c r="C6" s="60" cm="1">
         <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,Receita_Líquida='Gráfico Categorias'!C2))</f>
         <v>150</v>
       </c>
-      <c r="I6" s="4" t="str" cm="1">
+      <c r="I6" s="3" t="str" cm="1">
         <f t="array" ref="I6:I17">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="J6" s="74" cm="1">
+      <c r="J6" s="60" cm="1">
         <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,Categorias='Gráfico Categorias'!J2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="str">
+      <c r="B7" s="3" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="C7" s="74">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4" t="str">
+      <c r="C7" s="60">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="str">
+      <c r="B8" s="3" t="str">
         <v>Março</v>
       </c>
-      <c r="C8" s="74">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4" t="str">
+      <c r="C8" s="60">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="str">
         <v>Março</v>
       </c>
-      <c r="J8" s="74">
+      <c r="J8" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="str">
+      <c r="B9" s="3" t="str">
         <v>Abril</v>
       </c>
-      <c r="C9" s="74">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="str">
+      <c r="C9" s="60">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="str">
         <v>Abril</v>
       </c>
-      <c r="J9" s="74">
+      <c r="J9" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="4" t="str">
+      <c r="B10" s="3" t="str">
         <v>Maio</v>
       </c>
-      <c r="C10" s="74">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="str">
+      <c r="C10" s="60">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="str">
         <v>Maio</v>
       </c>
-      <c r="J10" s="74">
+      <c r="J10" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="4" t="str">
+      <c r="B11" s="3" t="str">
         <v>Junho</v>
       </c>
-      <c r="C11" s="74">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="str">
+      <c r="C11" s="60">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="str">
         <v>Junho</v>
       </c>
-      <c r="J11" s="74">
+      <c r="J11" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="str">
+      <c r="B12" s="3" t="str">
         <v>Julho</v>
       </c>
-      <c r="C12" s="74">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="str">
+      <c r="C12" s="60">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="str">
         <v>Julho</v>
       </c>
-      <c r="J12" s="74">
+      <c r="J12" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="4" t="str">
+      <c r="B13" s="3" t="str">
         <v>Agosto</v>
       </c>
-      <c r="C13" s="74">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="str">
+      <c r="C13" s="60">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="str">
         <v>Agosto</v>
       </c>
-      <c r="J13" s="74">
+      <c r="J13" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="str">
+      <c r="B14" s="3" t="str">
         <v>Setembro</v>
       </c>
-      <c r="C14" s="74">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="str">
+      <c r="C14" s="60">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="str">
         <v>Setembro</v>
       </c>
-      <c r="J14" s="74">
+      <c r="J14" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="4" t="str">
+      <c r="B15" s="3" t="str">
         <v>Outubro</v>
       </c>
-      <c r="C15" s="74">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4" t="str">
+      <c r="C15" s="60">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="str">
         <v>Outubro</v>
       </c>
-      <c r="J15" s="74">
+      <c r="J15" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="str">
+      <c r="B16" s="3" t="str">
         <v>Novembro</v>
       </c>
-      <c r="C16" s="74">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4" t="str">
+      <c r="C16" s="60">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="str">
         <v>Novembro</v>
       </c>
-      <c r="J16" s="74">
+      <c r="J16" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="str">
+      <c r="B17" s="3" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="C17" s="74">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="str">
+      <c r="C17" s="60">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="J17" s="74">
+      <c r="J17" s="60">
         <v>0</v>
       </c>
     </row>
@@ -14938,746 +14945,746 @@
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="14" t="s">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="12" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="77" t="s">
+      <c r="J2" s="3"/>
+      <c r="K2" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="78"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="77" t="s">
+      <c r="L2" s="86"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="78"/>
-      <c r="P2" s="40"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="39"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="str">
+      <c r="A3" s="6" t="str">
         <f>PROPER(TEXT("01/01","MMMM"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="16">
+      <c r="B3" s="5"/>
+      <c r="C3" s="15">
         <f>'Receita Líquida'!B16</f>
         <v>150</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <f>SUM('Receita Líquida'!B$13:B$14)</f>
         <v>0</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="22">
+      <c r="E3" s="7"/>
+      <c r="F3" s="21">
         <f>SUM('Despesas Gerais'!B20:B20)</f>
         <v>50</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="16">
+      <c r="G3" s="8"/>
+      <c r="H3" s="15">
         <f>I3</f>
         <v>100</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="18">
         <f>'Despesas Gerais'!B4</f>
         <v>100</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="42" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="16">
         <f>SUM('Receita Líquida'!B3:M7)</f>
         <v>150</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="44" t="str" cm="1">
+      <c r="M3" s="7"/>
+      <c r="N3" s="43" t="str" cm="1">
         <f t="array" ref="N3:N14">Categorias</f>
         <v>Alimentação</v>
       </c>
-      <c r="O3" s="45">
+      <c r="O3" s="44">
         <f>SUM('Despesas Gerais'!B7:M7)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="40"/>
+      <c r="P3" s="39"/>
     </row>
     <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="str">
+      <c r="A4" s="6" t="str">
         <f>PROPER(TEXT("01/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="16">
+      <c r="B4" s="5"/>
+      <c r="C4" s="15">
         <f>'Receita Líquida'!C16</f>
         <v>0</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <f>SUM('Receita Líquida'!C$13:C$14)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="22">
+      <c r="E4" s="7"/>
+      <c r="F4" s="21">
         <f>SUM('Despesas Gerais'!C20:C20)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="16">
+      <c r="G4" s="8"/>
+      <c r="H4" s="15">
         <f t="shared" ref="H4:H14" si="0">I4-I3</f>
         <v>0</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="18">
         <f>'Despesas Gerais'!C4</f>
         <v>100</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="42" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="16">
         <f>SUM('Receita Líquida'!B8:M12)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="44" t="str">
+      <c r="M4" s="7"/>
+      <c r="N4" s="43" t="str">
         <v>Carro</v>
       </c>
-      <c r="O4" s="45">
+      <c r="O4" s="44">
         <f>SUM('Despesas Gerais'!B8:M8)</f>
         <v>0</v>
       </c>
-      <c r="P4" s="40"/>
+      <c r="P4" s="39"/>
     </row>
     <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="6" t="str">
         <f>PROPER(TEXT("01/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="16">
+      <c r="B5" s="5"/>
+      <c r="C5" s="15">
         <f>'Receita Líquida'!D16</f>
         <v>0</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <f>SUM('Receita Líquida'!D$13:D$14)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="22">
+      <c r="E5" s="7"/>
+      <c r="F5" s="21">
         <f>SUM('Despesas Gerais'!D20:D20)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="16">
+      <c r="G5" s="8"/>
+      <c r="H5" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="18">
         <f>'Despesas Gerais'!D4</f>
         <v>100</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="42" t="s">
+      <c r="J5" s="3"/>
+      <c r="K5" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="16">
         <f>SUM('Receita Líquida'!B16:M16)</f>
         <v>150</v>
       </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="44" t="str">
+      <c r="M5" s="7"/>
+      <c r="N5" s="43" t="str">
         <v>Condomínio</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="44">
         <f>SUM('Despesas Gerais'!B9:M9)</f>
         <v>0</v>
       </c>
-      <c r="P5" s="40"/>
+      <c r="P5" s="39"/>
     </row>
     <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="str">
+      <c r="A6" s="6" t="str">
         <f>PROPER(TEXT("01/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="16">
+      <c r="B6" s="5"/>
+      <c r="C6" s="15">
         <f>'Receita Líquida'!E16</f>
         <v>0</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <f>SUM('Receita Líquida'!E$13:E$14)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="22">
+      <c r="E6" s="7"/>
+      <c r="F6" s="21">
         <f>SUM('Despesas Gerais'!E20:E20)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="16">
+      <c r="G6" s="8"/>
+      <c r="H6" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="18">
         <f>'Despesas Gerais'!E4</f>
         <v>100</v>
       </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="42" t="s">
+      <c r="J6" s="3"/>
+      <c r="K6" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="16">
         <f>SUM('Despesas Gerais'!B7:B17,'Despesas Gerais'!C7:C17,'Despesas Gerais'!D7:D17,'Despesas Gerais'!E7:E17,'Despesas Gerais'!F7:F17,'Despesas Gerais'!G7:G17,'Despesas Gerais'!H7:H17,'Despesas Gerais'!I7:I17,'Despesas Gerais'!J7:J17,'Despesas Gerais'!K7:K17,'Despesas Gerais'!L7:L17,'Despesas Gerais'!M7:M17)</f>
         <v>50</v>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="44" t="str">
+      <c r="M6" s="7"/>
+      <c r="N6" s="43" t="str">
         <v>Curso</v>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="44">
         <f>SUM('Despesas Gerais'!B10:M10)</f>
         <v>0</v>
       </c>
-      <c r="P6" s="40"/>
+      <c r="P6" s="39"/>
     </row>
     <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="6" t="str">
         <f>PROPER(TEXT("01/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="16">
+      <c r="B7" s="5"/>
+      <c r="C7" s="15">
         <f>'Receita Líquida'!F16</f>
         <v>0</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <f>SUM('Receita Líquida'!F$13:F$14)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="22">
+      <c r="E7" s="7"/>
+      <c r="F7" s="21">
         <f>SUM('Despesas Gerais'!F20:F20)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="16">
+      <c r="G7" s="8"/>
+      <c r="H7" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="18">
         <f>'Despesas Gerais'!F4</f>
         <v>100</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="42" t="s">
+      <c r="J7" s="3"/>
+      <c r="K7" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="16">
         <f>SUM('Despesas Gerais'!B18:B18,'Despesas Gerais'!C18:C18,'Despesas Gerais'!D18:D18,'Despesas Gerais'!E18:E18,'Despesas Gerais'!F18:F18,'Despesas Gerais'!G18:G18,'Despesas Gerais'!H18:H18,'Despesas Gerais'!I18:I18,'Despesas Gerais'!J18:J18,'Despesas Gerais'!K18:K18,'Despesas Gerais'!L18:L18,'Despesas Gerais'!M18:M18)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="44" t="str">
+      <c r="M7" s="7"/>
+      <c r="N7" s="43" t="str">
         <v>Eletrônicos</v>
       </c>
-      <c r="O7" s="45">
+      <c r="O7" s="44">
         <f>SUM('Despesas Gerais'!B11:M11)</f>
         <v>0</v>
       </c>
-      <c r="P7" s="40"/>
+      <c r="P7" s="39"/>
     </row>
     <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="6" t="str">
         <f>PROPER(TEXT("01/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="16">
+      <c r="B8" s="5"/>
+      <c r="C8" s="15">
         <f>'Receita Líquida'!G16</f>
         <v>0</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <f>SUM('Receita Líquida'!G$13:G$14)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="22">
+      <c r="E8" s="7"/>
+      <c r="F8" s="21">
         <f>SUM('Despesas Gerais'!G20:G20)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="16">
+      <c r="G8" s="8"/>
+      <c r="H8" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="18">
         <f>'Despesas Gerais'!G4</f>
         <v>100</v>
       </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="42" t="s">
+      <c r="J8" s="3"/>
+      <c r="K8" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="16">
         <f>SUM(L6:L7)</f>
         <v>50</v>
       </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="44" t="str">
+      <c r="M8" s="7"/>
+      <c r="N8" s="43" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="O8" s="45">
+      <c r="O8" s="44">
         <f>SUM('Despesas Gerais'!B12:M12)</f>
         <v>0</v>
       </c>
-      <c r="P8" s="40"/>
+      <c r="P8" s="39"/>
     </row>
     <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="str">
+      <c r="A9" s="6" t="str">
         <f>PROPER(TEXT("01/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="16">
+      <c r="B9" s="5"/>
+      <c r="C9" s="15">
         <f>'Receita Líquida'!H16</f>
         <v>0</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <f>SUM('Receita Líquida'!H$13:H$14)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="22">
+      <c r="E9" s="7"/>
+      <c r="F9" s="21">
         <f>SUM('Despesas Gerais'!H20:H20)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="16">
+      <c r="G9" s="8"/>
+      <c r="H9" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="18">
         <f>'Despesas Gerais'!H4</f>
         <v>100</v>
       </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="42" t="s">
+      <c r="J9" s="3"/>
+      <c r="K9" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="18">
         <f>'Despesas Gerais'!M4</f>
         <v>100</v>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="44" t="str">
+      <c r="M9" s="8"/>
+      <c r="N9" s="43" t="str">
         <v>G. Residencial</v>
       </c>
-      <c r="O9" s="45">
+      <c r="O9" s="44">
         <f>SUM('Despesas Gerais'!B13:M13)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="40"/>
+      <c r="P9" s="39"/>
     </row>
     <row r="10" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="str">
+      <c r="A10" s="6" t="str">
         <f>PROPER(TEXT("01/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="16">
+      <c r="B10" s="5"/>
+      <c r="C10" s="15">
         <f>'Receita Líquida'!I16</f>
         <v>0</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <f>SUM('Receita Líquida'!I$13:I$14)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="22">
+      <c r="E10" s="7"/>
+      <c r="F10" s="21">
         <f>SUM('Despesas Gerais'!I20:I20)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="16">
+      <c r="G10" s="8"/>
+      <c r="H10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="18">
         <f>'Despesas Gerais'!I4</f>
         <v>100</v>
       </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="43" t="s">
+      <c r="J10" s="3"/>
+      <c r="K10" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="20">
         <f>'Gráfico Anual'!D15</f>
         <v>0</v>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="44" t="str">
+      <c r="M10" s="8"/>
+      <c r="N10" s="43" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="O10" s="45">
+      <c r="O10" s="44">
         <f>SUM('Despesas Gerais'!B14:M14)</f>
         <v>50</v>
       </c>
-      <c r="P10" s="40"/>
+      <c r="P10" s="39"/>
     </row>
     <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="str">
+      <c r="A11" s="6" t="str">
         <f>PROPER(TEXT("01/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="16">
+      <c r="B11" s="5"/>
+      <c r="C11" s="15">
         <f>'Receita Líquida'!J16</f>
         <v>0</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="16">
         <f>SUM('Receita Líquida'!J$13:J$14)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="22">
+      <c r="E11" s="7"/>
+      <c r="F11" s="21">
         <f>SUM('Despesas Gerais'!J20:J20)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="16">
+      <c r="G11" s="8"/>
+      <c r="H11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="18">
         <f>'Despesas Gerais'!J4</f>
         <v>100</v>
       </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="42" t="str">
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="41" t="str">
         <v>Jogos/ Livros</v>
       </c>
-      <c r="O11" s="45">
+      <c r="O11" s="44">
         <f>SUM('Despesas Gerais'!B15:M15)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="40"/>
+      <c r="P11" s="39"/>
     </row>
     <row r="12" spans="1:16" ht="15.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="str">
+      <c r="A12" s="6" t="str">
         <f>PROPER(TEXT("01/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="16">
+      <c r="B12" s="5"/>
+      <c r="C12" s="15">
         <f>'Receita Líquida'!K16</f>
         <v>0</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <f>SUM('Receita Líquida'!K$13:K$14)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="22">
+      <c r="E12" s="7"/>
+      <c r="F12" s="21">
         <f>SUM('Despesas Gerais'!K20:K20)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="16">
+      <c r="G12" s="8"/>
+      <c r="H12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="18">
         <f>'Despesas Gerais'!K4</f>
         <v>100</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="71" t="str">
+      <c r="J12" s="3"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="57" t="str">
         <v>Rolê/ Entret.</v>
       </c>
-      <c r="O12" s="45">
+      <c r="O12" s="44">
         <f>SUM('Despesas Gerais'!B16:M16)</f>
         <v>0</v>
       </c>
-      <c r="P12" s="41"/>
+      <c r="P12" s="40"/>
     </row>
     <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="str">
+      <c r="A13" s="6" t="str">
         <f>PROPER(TEXT("01/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="16">
+      <c r="B13" s="5"/>
+      <c r="C13" s="15">
         <f>'Receita Líquida'!L16</f>
         <v>0</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="16">
         <f>SUM('Receita Líquida'!L$13:L$14)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="22">
+      <c r="E13" s="7"/>
+      <c r="F13" s="21">
         <f>SUM('Despesas Gerais'!L20:L20)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="16">
+      <c r="G13" s="8"/>
+      <c r="H13" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="18">
         <f>'Despesas Gerais'!L4</f>
         <v>100</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="71" t="str">
+      <c r="J13" s="3"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="57" t="str">
         <v>Roupas</v>
       </c>
-      <c r="O13" s="45">
+      <c r="O13" s="44">
         <f>SUM('Despesas Gerais'!B17:M17)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="41"/>
+      <c r="P13" s="40"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="str">
+      <c r="A14" s="6" t="str">
         <f>PROPER(TEXT("01/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="16">
+      <c r="B14" s="5"/>
+      <c r="C14" s="15">
         <f>'Receita Líquida'!M16</f>
         <v>0</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="16">
         <f>SUM('Receita Líquida'!M$13:M$14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="22">
+      <c r="E14" s="7"/>
+      <c r="F14" s="21">
         <f>SUM('Despesas Gerais'!M20:N20)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="16">
+      <c r="G14" s="8"/>
+      <c r="H14" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="18">
         <f>'Despesas Gerais'!M4</f>
         <v>100</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="72" t="str">
+      <c r="J14" s="3"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="58" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="O14" s="73">
+      <c r="O14" s="59">
         <f>SUM('Despesas Gerais'!B18:M18)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="40"/>
+      <c r="P14" s="39"/>
     </row>
     <row r="15" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="18">
+      <c r="B15" s="5"/>
+      <c r="C15" s="17">
         <f>SUM(C3:C14)</f>
         <v>150</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <f>SUM(D3:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="22">
+      <c r="E15" s="7"/>
+      <c r="F15" s="21">
         <f>SUM(F3:F14)</f>
         <v>50</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="26" t="s">
+      <c r="G15" s="8"/>
+      <c r="H15" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="20">
         <f>'Gráfico Anual'!L9</f>
         <v>100</v>
       </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
     </row>
     <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="18">
+      <c r="B16" s="5"/>
+      <c r="C16" s="17">
         <f>AVERAGE(C3:C14)</f>
         <v>12.5</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="16">
         <f>AVERAGE(D3:D14)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="23">
+      <c r="E16" s="7"/>
+      <c r="F16" s="22">
         <f>AVERAGE(F3:F14)</f>
         <v>4.166666666666667</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
     </row>
     <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="16">
+      <c r="B17" s="5"/>
+      <c r="C17" s="15">
         <f>SUM(C3:C8)</f>
         <v>150</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="18">
         <f>SUM(D3:D8)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="24">
+      <c r="E17" s="8"/>
+      <c r="F17" s="23">
         <f>SUM(F3:F8)</f>
         <v>50</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
     </row>
     <row r="18" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="20">
+      <c r="B18" s="5"/>
+      <c r="C18" s="19">
         <f>SUM($C$9:$C$14)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <f>SUM($D$9:$D$14)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="25">
+      <c r="E18" s="8"/>
+      <c r="F18" s="24">
         <f>SUM($F$9:$F$14)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="40"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
     </row>
     <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="39"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
     </row>
     <row r="26" spans="1:16" ht="14.3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:16" ht="8.5500000000000007" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C98EDD8-B05E-4212-A645-DEE9F8878BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472D660E-05D4-4B09-A765-8574A3B9112C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Gráfico Anual" sheetId="13" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Ativos">'Saldo &amp; Mov.'!$B$9:$B$11</definedName>
+    <definedName name="Ativos">'Saldo &amp; Mov.'!$B$7:$B$9</definedName>
     <definedName name="Categorias">'Despesas Gerais'!$A$7:$A$18</definedName>
     <definedName name="Dash">'Gráfico Anual'!$A$1:$P$26</definedName>
     <definedName name="Despesas">'Despesas Gerais'!$A$7:$A$18</definedName>
@@ -30,7 +30,7 @@
     <definedName name="Perdas">'Receita Líquida'!$A$8:$A$12</definedName>
     <definedName name="Receita_Líquida">'Receita Líquida'!$A$3:$A$14</definedName>
     <definedName name="Receitas">'Receita Líquida'!$A$3:$A$7</definedName>
-    <definedName name="Transferir">'Saldo &amp; Mov.'!$B$9:$B$11</definedName>
+    <definedName name="Transferir">'Saldo &amp; Mov.'!$B$7:$B$9</definedName>
     <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="2" hidden="1">'Despesas Gerais'!$6:$6,'Despesas Gerais'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
   <si>
     <t>Mês</t>
   </si>
@@ -255,9 +255,6 @@
     <t>Receitas</t>
   </si>
   <si>
-    <t>Transferir</t>
-  </si>
-  <si>
     <t>Receita_Líquida</t>
   </si>
   <si>
@@ -274,6 +271,9 @@
   </si>
   <si>
     <t>Curso</t>
+  </si>
+  <si>
+    <t>SubTotal</t>
   </si>
 </sst>
 </file>
@@ -343,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,24 +371,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,7 +549,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -686,9 +668,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -700,29 +679,17 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -732,45 +699,50 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="8" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2123,7 +2095,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3988,7 +3960,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4555,7 +4527,7 @@
                   <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -4885,7 +4857,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -9323,222 +9295,219 @@
   <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="70" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="71" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" style="72" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" style="70" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="75" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="74" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="70" customWidth="1"/>
-    <col min="10" max="10" width="10" style="70" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="70"/>
+    <col min="1" max="1" width="11.42578125" style="68" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="66" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" style="67" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="68" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="71" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" style="70" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="68" customWidth="1"/>
+    <col min="10" max="10" width="10" style="68" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="68"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="45" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="83" t="s">
+      <c r="F2" s="78" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="48" t="s">
+      <c r="B3" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="81" t="str" cm="1">
-        <f t="array" ref="E3:E14">IF(C3="Despesas",Categorias,IF(C3="Receita Líquida",Receita_Líquida,""))</f>
+      <c r="C3" s="26">
+        <f>IF(B3="Despesas",HLOOKUP(B2,'Despesas Gerais'!B2:M20,19,FALSE),IF(B3="Receita Líquida",HLOOKUP(B2,'Receita Líquida'!B2:M16,15,FALSE),""))</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="77" t="str" cm="1">
+        <f t="array" ref="E3:E14">IF(B3="Despesas",Categorias,IF(B3="Receita Líquida",Receita_Líquida,""))</f>
         <v>Alimentação</v>
       </c>
-      <c r="F3" s="83" cm="1">
-        <f t="array" ref="F3:F14">IF(C3="Despesas",_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,'Despesas Gerais'!B2:M2=C2),IF(C3="Receita Líquida",_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,'Receita Líquida'!B2:M2=C2),""))</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="70"/>
+      <c r="F3" s="78" cm="1">
+        <f t="array" ref="F3:F14">IF(B3="Despesas",_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,'Despesas Gerais'!B2:M2=B2),IF(B3="Receita Líquida",_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,'Receita Líquida'!B2:M2=B2),""))</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="68"/>
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="27" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="26">
-        <f>IF(C3="Despesas",HLOOKUP(C2,'Despesas Gerais'!B2:M20,19,FALSE),IF(C3="Receita Líquida",HLOOKUP(C2,'Receita Líquida'!B2:M16,15,FALSE),""))</f>
-        <v>50</v>
-      </c>
-      <c r="E4" s="81" t="str">
+        <f>VLOOKUP(B2,'Gráfico Anual'!A3:I14,9,FALSE)</f>
+        <v>150</v>
+      </c>
+      <c r="E4" s="77" t="str">
         <v>Carro</v>
       </c>
-      <c r="F4" s="83">
-        <v>0</v>
-      </c>
-      <c r="H4" s="70"/>
+      <c r="F4" s="78">
+        <v>0</v>
+      </c>
+      <c r="H4" s="68"/>
     </row>
     <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="E5" s="81" t="str">
+      <c r="B5" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="26">
+        <f>'Gráfico Anual'!I15</f>
+        <v>150</v>
+      </c>
+      <c r="E5" s="77" t="str">
         <v>Condomínio</v>
       </c>
-      <c r="F5" s="83">
-        <v>0</v>
-      </c>
-      <c r="H5" s="70"/>
-    </row>
-    <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="26">
-        <f>VLOOKUP(C2,'Gráfico Anual'!A3:I14,9,FALSE)</f>
-        <v>100</v>
-      </c>
-      <c r="E6" s="81" t="str">
+      <c r="F5" s="78">
+        <v>0</v>
+      </c>
+      <c r="H5" s="68"/>
+    </row>
+    <row r="6" spans="1:8" ht="10.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="77" t="str">
         <v>Curso</v>
       </c>
-      <c r="F6" s="83">
-        <v>0</v>
-      </c>
-      <c r="H6" s="70"/>
+      <c r="F6" s="78">
+        <v>0</v>
+      </c>
+      <c r="H6" s="68"/>
     </row>
     <row r="7" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="26">
-        <f>'Gráfico Anual'!I15</f>
-        <v>100</v>
-      </c>
-      <c r="E7" s="81" t="str">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" cm="1">
+        <f t="array" aca="1" ref="C7" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B7,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B7,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B7,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <v>150</v>
+      </c>
+      <c r="E7" s="77" t="str">
         <v>Eletrônicos</v>
       </c>
-      <c r="F7" s="83">
-        <v>0</v>
-      </c>
-      <c r="H7" s="70"/>
+      <c r="F7" s="78">
+        <v>0</v>
+      </c>
+      <c r="H7" s="68"/>
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="81" t="str">
+      <c r="B8" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B8,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B8,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B8,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="77" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="F8" s="83">
-        <v>0</v>
-      </c>
-      <c r="H8" s="70"/>
+      <c r="F8" s="78">
+        <v>0</v>
+      </c>
+      <c r="H8" s="68"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B9,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
-        <v>75</v>
-      </c>
-      <c r="E9" s="81" t="str">
+        <v>0</v>
+      </c>
+      <c r="E9" s="77" t="str">
         <v>G. Residencial</v>
       </c>
-      <c r="F9" s="83">
-        <v>0</v>
-      </c>
-      <c r="H9" s="70"/>
+      <c r="F9" s="78">
+        <v>0</v>
+      </c>
+      <c r="H9" s="68"/>
     </row>
     <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="72"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="2" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B10,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="81" t="str">
+        <v>44</v>
+      </c>
+      <c r="C10" s="2">
+        <f ca="1">SUM(C7:C9)</f>
+        <v>150</v>
+      </c>
+      <c r="E10" s="77" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="F10" s="83">
-        <v>50</v>
-      </c>
-      <c r="H10" s="70"/>
+      <c r="F10" s="78">
+        <v>0</v>
+      </c>
+      <c r="H10" s="68"/>
     </row>
     <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="72"/>
+      <c r="A11" s="67"/>
       <c r="B11" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="2" cm="1">
-        <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B11,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
-        <v>25</v>
-      </c>
-      <c r="E11" s="81" t="str">
+        <v>45</v>
+      </c>
+      <c r="C11" s="26">
+        <f ca="1">ROUND(C4-C10,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="77" t="str">
         <v>Jogos/ Livros</v>
       </c>
-      <c r="F11" s="83">
-        <v>0</v>
-      </c>
-      <c r="H11" s="70"/>
+      <c r="F11" s="78">
+        <v>0</v>
+      </c>
+      <c r="H11" s="68"/>
     </row>
     <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="72"/>
-      <c r="B12" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="2">
-        <f ca="1">SUM(C9:C11)</f>
-        <v>100</v>
-      </c>
-      <c r="E12" s="81" t="str">
+      <c r="A12" s="67"/>
+      <c r="E12" s="77" t="str">
         <v>Rolê/ Entret.</v>
       </c>
-      <c r="F12" s="83">
-        <v>0</v>
-      </c>
-      <c r="H12" s="70"/>
+      <c r="F12" s="78">
+        <v>0</v>
+      </c>
+      <c r="H12" s="68"/>
     </row>
     <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="72"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="26">
-        <f ca="1">ROUND(C6-C12,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="81" t="str">
+        <v>65</v>
+      </c>
+      <c r="C13" s="2">
+        <f>SUBTOTAL(9,Tabela1[Valor])</f>
+        <v>150</v>
+      </c>
+      <c r="E13" s="77" t="str">
         <v>Roupas</v>
       </c>
-      <c r="F13" s="83">
-        <v>0</v>
-      </c>
-      <c r="H13" s="70"/>
+      <c r="F13" s="78">
+        <v>0</v>
+      </c>
+      <c r="H13" s="68"/>
     </row>
     <row r="14" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="72"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="E14" s="81" t="str">
+      <c r="A14" s="67"/>
+      <c r="E14" s="77" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="F14" s="82">
-        <v>0</v>
-      </c>
-      <c r="H14" s="70"/>
+      <c r="F14" s="79">
+        <v>0</v>
+      </c>
+      <c r="H14" s="68"/>
     </row>
     <row r="15" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="78"/>
-      <c r="B15" s="70"/>
-      <c r="H15" s="70"/>
+      <c r="A15" s="74"/>
+      <c r="B15" s="68"/>
+      <c r="H15" s="68"/>
     </row>
     <row r="16" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="80">
+      <c r="A16" s="76">
         <f>SUBTOTAL(2,Tabela1[Data])</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>32</v>
@@ -9585,47 +9554,27 @@
       <c r="H17" s="37"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="33">
-        <v>44927</v>
-      </c>
+      <c r="B18" s="33"/>
       <c r="C18" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Janeiro</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="36">
-        <v>50</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="36"/>
       <c r="H18" s="37"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="33">
-        <v>44927</v>
-      </c>
+      <c r="B19" s="33"/>
       <c r="C19" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>Janeiro</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="36">
-        <v>25</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="36"/>
       <c r="H19" s="37"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
@@ -9641,3206 +9590,3206 @@
       <c r="H20" s="37"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G23" s="73"/>
+      <c r="G23" s="69"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G25" s="73"/>
+      <c r="G25" s="69"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G26" s="73"/>
+      <c r="G26" s="69"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G27" s="73"/>
+      <c r="G27" s="69"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G28" s="73"/>
+      <c r="G28" s="69"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I38" s="70" t="s">
+      <c r="I38" s="68" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G137" s="73"/>
+      <c r="G137" s="69"/>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G139" s="73"/>
+      <c r="G139" s="69"/>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G140" s="73"/>
+      <c r="G140" s="69"/>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G141" s="73"/>
+      <c r="G141" s="69"/>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G142" s="73"/>
+      <c r="G142" s="69"/>
     </row>
     <row r="248" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C248" s="72" t="str">
+      <c r="C248" s="67" t="str">
         <f>IF(ISBLANK(B248),"",PROPER(TEXT(B248,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="249" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C249" s="72" t="str">
+      <c r="C249" s="67" t="str">
         <f>IF(ISBLANK(B249),"",PROPER(TEXT(B249,"MMMM")))</f>
         <v/>
       </c>
-      <c r="G249" s="76"/>
+      <c r="G249" s="72"/>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C258" s="72" t="str">
+      <c r="C258" s="67" t="str">
         <f>IF(ISBLANK(B258),"",PROPER(TEXT(B258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="D258" s="72" t="str">
+      <c r="D258" s="67" t="str">
         <f t="shared" ref="D258:G258" si="1">IF(ISBLANK(C258),"",PROPER(TEXT(C258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="E258" s="72" t="str">
+      <c r="E258" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F258" s="72" t="str">
+      <c r="F258" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G258" s="72" t="str">
+      <c r="G258" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C267" s="72" t="str">
+      <c r="C267" s="67" t="str">
         <f t="shared" ref="C267" si="2">IF(ISBLANK(B267),"",PROPER(TEXT(B267,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C268" s="72" t="str">
+      <c r="C268" s="67" t="str">
         <f t="shared" ref="C268:C282" si="3">IF(ISBLANK(B268),"",PROPER(TEXT(B268,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C269" s="72" t="str">
+      <c r="C269" s="67" t="str">
         <f t="shared" ref="C269:C279" si="4">IF(ISBLANK(B269),"",PROPER(TEXT(B269,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C270" s="72" t="str">
+      <c r="C270" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C271" s="72" t="str">
+      <c r="C271" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C272" s="72" t="str">
+      <c r="C272" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C273" s="72" t="str">
+      <c r="C273" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C274" s="72" t="str">
+      <c r="C274" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C275" s="72" t="str">
+      <c r="C275" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C276" s="72" t="str">
+      <c r="C276" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C277" s="72" t="str">
+      <c r="C277" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C278" s="72" t="str">
+      <c r="C278" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C279" s="72" t="str">
+      <c r="C279" s="67" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C280" s="72" t="str">
+      <c r="C280" s="67" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C281" s="72" t="str">
+      <c r="C281" s="67" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C282" s="72" t="str">
+      <c r="C282" s="67" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G282" s="73"/>
-      <c r="H282" s="77"/>
+      <c r="G282" s="69"/>
+      <c r="H282" s="73"/>
     </row>
     <row r="283" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B283" s="70"/>
-      <c r="C283" s="70"/>
-      <c r="D283" s="70"/>
-      <c r="E283" s="78"/>
-      <c r="F283" s="78"/>
-      <c r="G283" s="73"/>
-      <c r="H283" s="77"/>
+      <c r="B283" s="68"/>
+      <c r="C283" s="68"/>
+      <c r="D283" s="68"/>
+      <c r="E283" s="74"/>
+      <c r="F283" s="74"/>
+      <c r="G283" s="69"/>
+      <c r="H283" s="73"/>
     </row>
     <row r="284" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B284" s="70"/>
-      <c r="C284" s="70"/>
-      <c r="D284" s="70"/>
-      <c r="E284" s="78"/>
-      <c r="F284" s="78"/>
-      <c r="G284" s="73"/>
-      <c r="H284" s="77"/>
+      <c r="B284" s="68"/>
+      <c r="C284" s="68"/>
+      <c r="D284" s="68"/>
+      <c r="E284" s="74"/>
+      <c r="F284" s="74"/>
+      <c r="G284" s="69"/>
+      <c r="H284" s="73"/>
     </row>
     <row r="285" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B285" s="70"/>
-      <c r="C285" s="70"/>
-      <c r="D285" s="70"/>
-      <c r="E285" s="78"/>
-      <c r="F285" s="78"/>
-      <c r="G285" s="73"/>
-      <c r="H285" s="77"/>
+      <c r="B285" s="68"/>
+      <c r="C285" s="68"/>
+      <c r="D285" s="68"/>
+      <c r="E285" s="74"/>
+      <c r="F285" s="74"/>
+      <c r="G285" s="69"/>
+      <c r="H285" s="73"/>
     </row>
     <row r="286" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B286" s="70"/>
-      <c r="C286" s="79"/>
-      <c r="D286" s="79"/>
-      <c r="E286" s="78"/>
-      <c r="F286" s="78"/>
-      <c r="G286" s="73"/>
-      <c r="H286" s="77"/>
+      <c r="B286" s="68"/>
+      <c r="C286" s="75"/>
+      <c r="D286" s="75"/>
+      <c r="E286" s="74"/>
+      <c r="F286" s="74"/>
+      <c r="G286" s="69"/>
+      <c r="H286" s="73"/>
     </row>
     <row r="287" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B287" s="70"/>
-      <c r="C287" s="70"/>
-      <c r="D287" s="70"/>
-      <c r="G287" s="70"/>
+      <c r="B287" s="68"/>
+      <c r="C287" s="68"/>
+      <c r="D287" s="68"/>
+      <c r="G287" s="68"/>
     </row>
     <row r="288" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B288" s="70"/>
-      <c r="C288" s="70"/>
-      <c r="D288" s="70"/>
-      <c r="G288" s="70"/>
+      <c r="B288" s="68"/>
+      <c r="C288" s="68"/>
+      <c r="D288" s="68"/>
+      <c r="G288" s="68"/>
     </row>
     <row r="289" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B289" s="70"/>
-      <c r="C289" s="70"/>
-      <c r="D289" s="70"/>
-      <c r="G289" s="70"/>
+      <c r="B289" s="68"/>
+      <c r="C289" s="68"/>
+      <c r="D289" s="68"/>
+      <c r="G289" s="68"/>
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B290" s="70"/>
-      <c r="C290" s="70"/>
-      <c r="D290" s="70"/>
-      <c r="G290" s="70"/>
+      <c r="B290" s="68"/>
+      <c r="C290" s="68"/>
+      <c r="D290" s="68"/>
+      <c r="G290" s="68"/>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B291" s="70"/>
-      <c r="C291" s="70"/>
-      <c r="D291" s="70"/>
-      <c r="G291" s="70"/>
+      <c r="B291" s="68"/>
+      <c r="C291" s="68"/>
+      <c r="D291" s="68"/>
+      <c r="G291" s="68"/>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B292" s="70"/>
-      <c r="C292" s="70"/>
-      <c r="D292" s="70"/>
-      <c r="G292" s="70"/>
+      <c r="B292" s="68"/>
+      <c r="C292" s="68"/>
+      <c r="D292" s="68"/>
+      <c r="G292" s="68"/>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B293" s="70"/>
-      <c r="C293" s="70"/>
-      <c r="D293" s="70"/>
-      <c r="G293" s="70"/>
+      <c r="B293" s="68"/>
+      <c r="C293" s="68"/>
+      <c r="D293" s="68"/>
+      <c r="G293" s="68"/>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C294" s="72" t="str">
+      <c r="C294" s="67" t="str">
         <f t="shared" ref="C294:C352" si="5">IF(ISBLANK(B294),"",PROPER(TEXT(B294,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C295" s="72" t="str">
+      <c r="C295" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C296" s="72" t="str">
+      <c r="C296" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C297" s="72" t="str">
+      <c r="C297" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C298" s="72" t="str">
+      <c r="C298" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C299" s="72" t="str">
+      <c r="C299" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C300" s="72" t="str">
+      <c r="C300" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C301" s="72" t="str">
+      <c r="C301" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C302" s="72" t="str">
+      <c r="C302" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C303" s="72" t="str">
+      <c r="C303" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C304" s="72" t="str">
+      <c r="C304" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C305" s="72" t="str">
+      <c r="C305" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C306" s="72" t="str">
+      <c r="C306" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C307" s="72" t="str">
+      <c r="C307" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" s="72" t="str">
+      <c r="C308" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C309" s="72" t="str">
+      <c r="C309" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C310" s="72" t="str">
+      <c r="C310" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C311" s="72" t="str">
+      <c r="C311" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C312" s="72" t="str">
+      <c r="C312" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C313" s="72" t="str">
+      <c r="C313" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C314" s="72" t="str">
+      <c r="C314" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C315" s="72" t="str">
+      <c r="C315" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C316" s="72" t="str">
+      <c r="C316" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C317" s="72" t="str">
+      <c r="C317" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C318" s="72" t="str">
+      <c r="C318" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C319" s="72" t="str">
+      <c r="C319" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C320" s="72" t="str">
+      <c r="C320" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C321" s="72" t="str">
+      <c r="C321" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C322" s="72" t="str">
+      <c r="C322" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C323" s="72" t="str">
+      <c r="C323" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C324" s="72" t="str">
+      <c r="C324" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C325" s="72" t="str">
+      <c r="C325" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C326" s="72" t="str">
+      <c r="C326" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C327" s="72" t="str">
+      <c r="C327" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C328" s="72" t="str">
+      <c r="C328" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C329" s="72" t="str">
+      <c r="C329" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C330" s="72" t="str">
+      <c r="C330" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C331" s="72" t="str">
+      <c r="C331" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C332" s="72" t="str">
+      <c r="C332" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C333" s="72" t="str">
+      <c r="C333" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C334" s="72" t="str">
+      <c r="C334" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C335" s="72" t="str">
+      <c r="C335" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C336" s="72" t="str">
+      <c r="C336" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C337" s="72" t="str">
+      <c r="C337" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C338" s="72" t="str">
+      <c r="C338" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C339" s="72" t="str">
+      <c r="C339" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C340" s="72" t="str">
+      <c r="C340" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C341" s="72" t="str">
+      <c r="C341" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C342" s="72" t="str">
+      <c r="C342" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C343" s="72" t="str">
+      <c r="C343" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C344" s="72" t="str">
+      <c r="C344" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C345" s="72" t="str">
+      <c r="C345" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C346" s="72" t="str">
+      <c r="C346" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C347" s="72" t="str">
+      <c r="C347" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C348" s="72" t="str">
+      <c r="C348" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C349" s="72" t="str">
+      <c r="C349" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C350" s="72" t="str">
+      <c r="C350" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C351" s="72" t="str">
+      <c r="C351" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C352" s="72" t="str">
+      <c r="C352" s="67" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C353" s="72" t="str">
+      <c r="C353" s="67" t="str">
         <f t="shared" ref="C353:C416" si="6">IF(ISBLANK(B353),"",PROPER(TEXT(B353,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C354" s="72" t="str">
+      <c r="C354" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C355" s="72" t="str">
+      <c r="C355" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C356" s="72" t="str">
+      <c r="C356" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C357" s="72" t="str">
+      <c r="C357" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C358" s="72" t="str">
+      <c r="C358" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C359" s="72" t="str">
+      <c r="C359" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C360" s="72" t="str">
+      <c r="C360" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C361" s="72" t="str">
+      <c r="C361" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C362" s="72" t="str">
+      <c r="C362" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C363" s="72" t="str">
+      <c r="C363" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C364" s="72" t="str">
+      <c r="C364" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C365" s="72" t="str">
+      <c r="C365" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C366" s="72" t="str">
+      <c r="C366" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C367" s="72" t="str">
+      <c r="C367" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C368" s="72" t="str">
+      <c r="C368" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C369" s="72" t="str">
+      <c r="C369" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C370" s="72" t="str">
+      <c r="C370" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C371" s="72" t="str">
+      <c r="C371" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C372" s="72" t="str">
+      <c r="C372" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C373" s="72" t="str">
+      <c r="C373" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C374" s="72" t="str">
+      <c r="C374" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C375" s="72" t="str">
+      <c r="C375" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C376" s="72" t="str">
+      <c r="C376" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C377" s="72" t="str">
+      <c r="C377" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C378" s="72" t="str">
+      <c r="C378" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C379" s="72" t="str">
+      <c r="C379" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C380" s="72" t="str">
+      <c r="C380" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C381" s="72" t="str">
+      <c r="C381" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C382" s="72" t="str">
+      <c r="C382" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C383" s="72" t="str">
+      <c r="C383" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C384" s="72" t="str">
+      <c r="C384" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C385" s="72" t="str">
+      <c r="C385" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C386" s="72" t="str">
+      <c r="C386" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C387" s="72" t="str">
+      <c r="C387" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C388" s="72" t="str">
+      <c r="C388" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C389" s="72" t="str">
+      <c r="C389" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="72" t="str">
+      <c r="C390" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C391" s="72" t="str">
+      <c r="C391" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C392" s="72" t="str">
+      <c r="C392" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C393" s="72" t="str">
+      <c r="C393" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C394" s="72" t="str">
+      <c r="C394" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C395" s="72" t="str">
+      <c r="C395" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C396" s="72" t="str">
+      <c r="C396" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C397" s="72" t="str">
+      <c r="C397" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C398" s="72" t="str">
+      <c r="C398" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C399" s="72" t="str">
+      <c r="C399" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C400" s="72" t="str">
+      <c r="C400" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C401" s="72" t="str">
+      <c r="C401" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C402" s="72" t="str">
+      <c r="C402" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C403" s="72" t="str">
+      <c r="C403" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C404" s="72" t="str">
+      <c r="C404" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C405" s="72" t="str">
+      <c r="C405" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C406" s="72" t="str">
+      <c r="C406" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C407" s="72" t="str">
+      <c r="C407" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C408" s="72" t="str">
+      <c r="C408" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C409" s="72" t="str">
+      <c r="C409" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C410" s="72" t="str">
+      <c r="C410" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C411" s="72" t="str">
+      <c r="C411" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C412" s="72" t="str">
+      <c r="C412" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C413" s="72" t="str">
+      <c r="C413" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C414" s="72" t="str">
+      <c r="C414" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C415" s="72" t="str">
+      <c r="C415" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C416" s="72" t="str">
+      <c r="C416" s="67" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="72" t="str">
+      <c r="C417" s="67" t="str">
         <f t="shared" ref="C417:C480" si="7">IF(ISBLANK(B417),"",PROPER(TEXT(B417,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C418" s="72" t="str">
+      <c r="C418" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C419" s="72" t="str">
+      <c r="C419" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="72" t="str">
+      <c r="C420" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C421" s="72" t="str">
+      <c r="C421" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C422" s="72" t="str">
+      <c r="C422" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C423" s="72" t="str">
+      <c r="C423" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C424" s="72" t="str">
+      <c r="C424" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C425" s="72" t="str">
+      <c r="C425" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C426" s="72" t="str">
+      <c r="C426" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C427" s="72" t="str">
+      <c r="C427" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C428" s="72" t="str">
+      <c r="C428" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C429" s="72" t="str">
+      <c r="C429" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C430" s="72" t="str">
+      <c r="C430" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C431" s="72" t="str">
+      <c r="C431" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C432" s="72" t="str">
+      <c r="C432" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="72" t="str">
+      <c r="C433" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C434" s="72" t="str">
+      <c r="C434" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C435" s="72" t="str">
+      <c r="C435" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="72" t="str">
+      <c r="C436" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C437" s="72" t="str">
+      <c r="C437" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C438" s="72" t="str">
+      <c r="C438" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C439" s="72" t="str">
+      <c r="C439" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C440" s="72" t="str">
+      <c r="C440" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C441" s="72" t="str">
+      <c r="C441" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C442" s="72" t="str">
+      <c r="C442" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C443" s="72" t="str">
+      <c r="C443" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C444" s="72" t="str">
+      <c r="C444" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C445" s="72" t="str">
+      <c r="C445" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C446" s="72" t="str">
+      <c r="C446" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C447" s="72" t="str">
+      <c r="C447" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C448" s="72" t="str">
+      <c r="C448" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C449" s="72" t="str">
+      <c r="C449" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C450" s="72" t="str">
+      <c r="C450" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C451" s="72" t="str">
+      <c r="C451" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C452" s="72" t="str">
+      <c r="C452" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C453" s="72" t="str">
+      <c r="C453" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C454" s="72" t="str">
+      <c r="C454" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C455" s="72" t="str">
+      <c r="C455" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C456" s="72" t="str">
+      <c r="C456" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C457" s="72" t="str">
+      <c r="C457" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C458" s="72" t="str">
+      <c r="C458" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C459" s="72" t="str">
+      <c r="C459" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C460" s="72" t="str">
+      <c r="C460" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C461" s="72" t="str">
+      <c r="C461" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C462" s="72" t="str">
+      <c r="C462" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C463" s="72" t="str">
+      <c r="C463" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C464" s="72" t="str">
+      <c r="C464" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" s="72" t="str">
+      <c r="C465" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C466" s="72" t="str">
+      <c r="C466" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C467" s="72" t="str">
+      <c r="C467" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C468" s="72" t="str">
+      <c r="C468" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C469" s="72" t="str">
+      <c r="C469" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C470" s="72" t="str">
+      <c r="C470" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C471" s="72" t="str">
+      <c r="C471" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C472" s="72" t="str">
+      <c r="C472" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C473" s="72" t="str">
+      <c r="C473" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" s="72" t="str">
+      <c r="C474" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" s="72" t="str">
+      <c r="C475" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" s="72" t="str">
+      <c r="C476" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C477" s="72" t="str">
+      <c r="C477" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C478" s="72" t="str">
+      <c r="C478" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C479" s="72" t="str">
+      <c r="C479" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C480" s="72" t="str">
+      <c r="C480" s="67" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C481" s="72" t="str">
+      <c r="C481" s="67" t="str">
         <f t="shared" ref="C481:C544" si="8">IF(ISBLANK(B481),"",PROPER(TEXT(B481,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="482" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C482" s="72" t="str">
+      <c r="C482" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C483" s="72" t="str">
+      <c r="C483" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C484" s="72" t="str">
+      <c r="C484" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C485" s="72" t="str">
+      <c r="C485" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C486" s="72" t="str">
+      <c r="C486" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="72" t="str">
+      <c r="C487" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" s="72" t="str">
+      <c r="C488" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" s="72" t="str">
+      <c r="C489" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C490" s="72" t="str">
+      <c r="C490" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C491" s="72" t="str">
+      <c r="C491" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C492" s="72" t="str">
+      <c r="C492" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C493" s="72" t="str">
+      <c r="C493" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C494" s="72" t="str">
+      <c r="C494" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C495" s="72" t="str">
+      <c r="C495" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C496" s="72" t="str">
+      <c r="C496" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C497" s="72" t="str">
+      <c r="C497" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="72" t="str">
+      <c r="C498" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" s="72" t="str">
+      <c r="C499" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" s="72" t="str">
+      <c r="C500" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="72" t="str">
+      <c r="C501" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C502" s="72" t="str">
+      <c r="C502" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C503" s="72" t="str">
+      <c r="C503" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C504" s="72" t="str">
+      <c r="C504" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C505" s="72" t="str">
+      <c r="C505" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C506" s="72" t="str">
+      <c r="C506" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C507" s="72" t="str">
+      <c r="C507" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C508" s="72" t="str">
+      <c r="C508" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C509" s="72" t="str">
+      <c r="C509" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C510" s="72" t="str">
+      <c r="C510" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C511" s="72" t="str">
+      <c r="C511" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C512" s="72" t="str">
+      <c r="C512" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C513" s="72" t="str">
+      <c r="C513" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" s="72" t="str">
+      <c r="C514" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" s="72" t="str">
+      <c r="C515" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" s="72" t="str">
+      <c r="C516" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C517" s="72" t="str">
+      <c r="C517" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C518" s="72" t="str">
+      <c r="C518" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C519" s="72" t="str">
+      <c r="C519" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C520" s="72" t="str">
+      <c r="C520" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C521" s="72" t="str">
+      <c r="C521" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" s="72" t="str">
+      <c r="C522" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" s="72" t="str">
+      <c r="C523" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" s="72" t="str">
+      <c r="C524" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C525" s="72" t="str">
+      <c r="C525" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C526" s="72" t="str">
+      <c r="C526" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C527" s="72" t="str">
+      <c r="C527" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C528" s="72" t="str">
+      <c r="C528" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C529" s="72" t="str">
+      <c r="C529" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" s="72" t="str">
+      <c r="C530" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" s="72" t="str">
+      <c r="C531" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" s="72" t="str">
+      <c r="C532" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C533" s="72" t="str">
+      <c r="C533" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C534" s="72" t="str">
+      <c r="C534" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C535" s="72" t="str">
+      <c r="C535" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C536" s="72" t="str">
+      <c r="C536" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C537" s="72" t="str">
+      <c r="C537" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C538" s="72" t="str">
+      <c r="C538" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C539" s="72" t="str">
+      <c r="C539" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C540" s="72" t="str">
+      <c r="C540" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C541" s="72" t="str">
+      <c r="C541" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C542" s="72" t="str">
+      <c r="C542" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C543" s="72" t="str">
+      <c r="C543" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C544" s="72" t="str">
+      <c r="C544" s="67" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C545" s="72" t="str">
+      <c r="C545" s="67" t="str">
         <f t="shared" ref="C545:C608" si="9">IF(ISBLANK(B545),"",PROPER(TEXT(B545,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="546" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C546" s="72" t="str">
+      <c r="C546" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C547" s="72" t="str">
+      <c r="C547" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C548" s="72" t="str">
+      <c r="C548" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C549" s="72" t="str">
+      <c r="C549" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C550" s="72" t="str">
+      <c r="C550" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C551" s="72" t="str">
+      <c r="C551" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C552" s="72" t="str">
+      <c r="C552" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C553" s="72" t="str">
+      <c r="C553" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C554" s="72" t="str">
+      <c r="C554" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C555" s="72" t="str">
+      <c r="C555" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C556" s="72" t="str">
+      <c r="C556" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C557" s="72" t="str">
+      <c r="C557" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C558" s="72" t="str">
+      <c r="C558" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C559" s="72" t="str">
+      <c r="C559" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C560" s="72" t="str">
+      <c r="C560" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C561" s="72" t="str">
+      <c r="C561" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C562" s="72" t="str">
+      <c r="C562" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C563" s="72" t="str">
+      <c r="C563" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C564" s="72" t="str">
+      <c r="C564" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C565" s="72" t="str">
+      <c r="C565" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C566" s="72" t="str">
+      <c r="C566" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C567" s="72" t="str">
+      <c r="C567" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C568" s="72" t="str">
+      <c r="C568" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C569" s="72" t="str">
+      <c r="C569" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C570" s="72" t="str">
+      <c r="C570" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C571" s="72" t="str">
+      <c r="C571" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C572" s="72" t="str">
+      <c r="C572" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C573" s="72" t="str">
+      <c r="C573" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C574" s="72" t="str">
+      <c r="C574" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C575" s="72" t="str">
+      <c r="C575" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C576" s="72" t="str">
+      <c r="C576" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C577" s="72" t="str">
+      <c r="C577" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C578" s="72" t="str">
+      <c r="C578" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C579" s="72" t="str">
+      <c r="C579" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C580" s="72" t="str">
+      <c r="C580" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C581" s="72" t="str">
+      <c r="C581" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C582" s="72" t="str">
+      <c r="C582" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C583" s="72" t="str">
+      <c r="C583" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C584" s="72" t="str">
+      <c r="C584" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C585" s="72" t="str">
+      <c r="C585" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C586" s="72" t="str">
+      <c r="C586" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C587" s="72" t="str">
+      <c r="C587" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C588" s="72" t="str">
+      <c r="C588" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C589" s="72" t="str">
+      <c r="C589" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C590" s="72" t="str">
+      <c r="C590" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C591" s="72" t="str">
+      <c r="C591" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C592" s="72" t="str">
+      <c r="C592" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C593" s="72" t="str">
+      <c r="C593" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C594" s="72" t="str">
+      <c r="C594" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C595" s="72" t="str">
+      <c r="C595" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C596" s="72" t="str">
+      <c r="C596" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C597" s="72" t="str">
+      <c r="C597" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C598" s="72" t="str">
+      <c r="C598" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C599" s="72" t="str">
+      <c r="C599" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C600" s="72" t="str">
+      <c r="C600" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C601" s="72" t="str">
+      <c r="C601" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C602" s="72" t="str">
+      <c r="C602" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C603" s="72" t="str">
+      <c r="C603" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C604" s="72" t="str">
+      <c r="C604" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C605" s="72" t="str">
+      <c r="C605" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C606" s="72" t="str">
+      <c r="C606" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C607" s="72" t="str">
+      <c r="C607" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C608" s="72" t="str">
+      <c r="C608" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C609" s="72" t="str">
+      <c r="C609" s="67" t="str">
         <f t="shared" ref="C609:C672" si="10">IF(ISBLANK(B609),"",PROPER(TEXT(B609,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="610" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C610" s="72" t="str">
+      <c r="C610" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C611" s="72" t="str">
+      <c r="C611" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C612" s="72" t="str">
+      <c r="C612" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C613" s="72" t="str">
+      <c r="C613" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C614" s="72" t="str">
+      <c r="C614" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C615" s="72" t="str">
+      <c r="C615" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C616" s="72" t="str">
+      <c r="C616" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C617" s="72" t="str">
+      <c r="C617" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C618" s="72" t="str">
+      <c r="C618" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C619" s="72" t="str">
+      <c r="C619" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C620" s="72" t="str">
+      <c r="C620" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C621" s="72" t="str">
+      <c r="C621" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C622" s="72" t="str">
+      <c r="C622" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C623" s="72" t="str">
+      <c r="C623" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C624" s="72" t="str">
+      <c r="C624" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C625" s="72" t="str">
+      <c r="C625" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C626" s="72" t="str">
+      <c r="C626" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C627" s="72" t="str">
+      <c r="C627" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C628" s="72" t="str">
+      <c r="C628" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C629" s="72" t="str">
+      <c r="C629" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C630" s="72" t="str">
+      <c r="C630" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C631" s="72" t="str">
+      <c r="C631" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C632" s="72" t="str">
+      <c r="C632" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C633" s="72" t="str">
+      <c r="C633" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C634" s="72" t="str">
+      <c r="C634" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C635" s="72" t="str">
+      <c r="C635" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C636" s="72" t="str">
+      <c r="C636" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C637" s="72" t="str">
+      <c r="C637" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C638" s="72" t="str">
+      <c r="C638" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C639" s="72" t="str">
+      <c r="C639" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C640" s="72" t="str">
+      <c r="C640" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C641" s="72" t="str">
+      <c r="C641" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C642" s="72" t="str">
+      <c r="C642" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C643" s="72" t="str">
+      <c r="C643" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C644" s="72" t="str">
+      <c r="C644" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C645" s="72" t="str">
+      <c r="C645" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C646" s="72" t="str">
+      <c r="C646" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C647" s="72" t="str">
+      <c r="C647" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C648" s="72" t="str">
+      <c r="C648" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C649" s="72" t="str">
+      <c r="C649" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C650" s="72" t="str">
+      <c r="C650" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C651" s="72" t="str">
+      <c r="C651" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C652" s="72" t="str">
+      <c r="C652" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C653" s="72" t="str">
+      <c r="C653" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C654" s="72" t="str">
+      <c r="C654" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C655" s="72" t="str">
+      <c r="C655" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C656" s="72" t="str">
+      <c r="C656" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C657" s="72" t="str">
+      <c r="C657" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C658" s="72" t="str">
+      <c r="C658" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C659" s="72" t="str">
+      <c r="C659" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C660" s="72" t="str">
+      <c r="C660" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C661" s="72" t="str">
+      <c r="C661" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C662" s="72" t="str">
+      <c r="C662" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C663" s="72" t="str">
+      <c r="C663" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C664" s="72" t="str">
+      <c r="C664" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C665" s="72" t="str">
+      <c r="C665" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C666" s="72" t="str">
+      <c r="C666" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C667" s="72" t="str">
+      <c r="C667" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C668" s="72" t="str">
+      <c r="C668" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C669" s="72" t="str">
+      <c r="C669" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C670" s="72" t="str">
+      <c r="C670" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C671" s="72" t="str">
+      <c r="C671" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C672" s="72" t="str">
+      <c r="C672" s="67" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C673" s="72" t="str">
+      <c r="C673" s="67" t="str">
         <f t="shared" ref="C673:C736" si="11">IF(ISBLANK(B673),"",PROPER(TEXT(B673,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="674" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C674" s="72" t="str">
+      <c r="C674" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C675" s="72" t="str">
+      <c r="C675" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C676" s="72" t="str">
+      <c r="C676" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C677" s="72" t="str">
+      <c r="C677" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C678" s="72" t="str">
+      <c r="C678" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C679" s="72" t="str">
+      <c r="C679" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C680" s="72" t="str">
+      <c r="C680" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C681" s="72" t="str">
+      <c r="C681" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C682" s="72" t="str">
+      <c r="C682" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C683" s="72" t="str">
+      <c r="C683" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C684" s="72" t="str">
+      <c r="C684" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C685" s="72" t="str">
+      <c r="C685" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="686" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C686" s="72" t="str">
+      <c r="C686" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="687" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C687" s="72" t="str">
+      <c r="C687" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="688" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C688" s="72" t="str">
+      <c r="C688" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="689" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C689" s="72" t="str">
+      <c r="C689" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="690" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C690" s="72" t="str">
+      <c r="C690" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="691" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C691" s="72" t="str">
+      <c r="C691" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="692" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C692" s="72" t="str">
+      <c r="C692" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="693" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C693" s="72" t="str">
+      <c r="C693" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="694" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C694" s="72" t="str">
+      <c r="C694" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="695" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C695" s="72" t="str">
+      <c r="C695" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="696" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C696" s="72" t="str">
+      <c r="C696" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="697" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C697" s="72" t="str">
+      <c r="C697" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="698" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C698" s="72" t="str">
+      <c r="C698" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="699" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C699" s="72" t="str">
+      <c r="C699" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="700" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C700" s="72" t="str">
+      <c r="C700" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="701" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C701" s="72" t="str">
+      <c r="C701" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="702" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C702" s="72" t="str">
+      <c r="C702" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="703" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C703" s="72" t="str">
+      <c r="C703" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="704" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C704" s="72" t="str">
+      <c r="C704" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="705" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C705" s="72" t="str">
+      <c r="C705" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="706" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C706" s="72" t="str">
+      <c r="C706" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="707" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C707" s="72" t="str">
+      <c r="C707" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="708" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C708" s="72" t="str">
+      <c r="C708" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="709" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C709" s="72" t="str">
+      <c r="C709" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="710" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C710" s="72" t="str">
+      <c r="C710" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="711" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C711" s="72" t="str">
+      <c r="C711" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="712" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C712" s="72" t="str">
+      <c r="C712" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="713" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C713" s="72" t="str">
+      <c r="C713" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="714" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C714" s="72" t="str">
+      <c r="C714" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="715" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C715" s="72" t="str">
+      <c r="C715" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="716" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C716" s="72" t="str">
+      <c r="C716" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="717" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C717" s="72" t="str">
+      <c r="C717" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="718" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C718" s="72" t="str">
+      <c r="C718" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="719" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C719" s="72" t="str">
+      <c r="C719" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="720" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C720" s="72" t="str">
+      <c r="C720" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="721" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C721" s="72" t="str">
+      <c r="C721" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="722" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C722" s="72" t="str">
+      <c r="C722" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="723" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C723" s="72" t="str">
+      <c r="C723" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="724" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C724" s="72" t="str">
+      <c r="C724" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="725" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C725" s="72" t="str">
+      <c r="C725" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="726" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C726" s="72" t="str">
+      <c r="C726" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="727" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C727" s="72" t="str">
+      <c r="C727" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="728" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C728" s="72" t="str">
+      <c r="C728" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="729" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C729" s="72" t="str">
+      <c r="C729" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="730" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C730" s="72" t="str">
+      <c r="C730" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="731" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C731" s="72" t="str">
+      <c r="C731" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="732" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C732" s="72" t="str">
+      <c r="C732" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="733" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C733" s="72" t="str">
+      <c r="C733" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="734" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C734" s="72" t="str">
+      <c r="C734" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="735" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C735" s="72" t="str">
+      <c r="C735" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="736" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C736" s="72" t="str">
+      <c r="C736" s="67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="737" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C737" s="72" t="str">
+      <c r="C737" s="67" t="str">
         <f t="shared" ref="C737:C785" si="12">IF(ISBLANK(B737),"",PROPER(TEXT(B737,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="738" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C738" s="72" t="str">
+      <c r="C738" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="739" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C739" s="72" t="str">
+      <c r="C739" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="740" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C740" s="72" t="str">
+      <c r="C740" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="741" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C741" s="72" t="str">
+      <c r="C741" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="742" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C742" s="72" t="str">
+      <c r="C742" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="743" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C743" s="72" t="str">
+      <c r="C743" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="744" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C744" s="72" t="str">
+      <c r="C744" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="745" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C745" s="72" t="str">
+      <c r="C745" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="746" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C746" s="72" t="str">
+      <c r="C746" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="747" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C747" s="72" t="str">
+      <c r="C747" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="748" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C748" s="72" t="str">
+      <c r="C748" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="749" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C749" s="72" t="str">
+      <c r="C749" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="750" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C750" s="72" t="str">
+      <c r="C750" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="751" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C751" s="72" t="str">
+      <c r="C751" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="752" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C752" s="72" t="str">
+      <c r="C752" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="753" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C753" s="72" t="str">
+      <c r="C753" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="754" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C754" s="72" t="str">
+      <c r="C754" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="755" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C755" s="72" t="str">
+      <c r="C755" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="756" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C756" s="72" t="str">
+      <c r="C756" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="757" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C757" s="72" t="str">
+      <c r="C757" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="758" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C758" s="72" t="str">
+      <c r="C758" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="759" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C759" s="72" t="str">
+      <c r="C759" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="760" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C760" s="72" t="str">
+      <c r="C760" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="761" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C761" s="72" t="str">
+      <c r="C761" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="762" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C762" s="72" t="str">
+      <c r="C762" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="763" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C763" s="72" t="str">
+      <c r="C763" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="764" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C764" s="72" t="str">
+      <c r="C764" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="765" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C765" s="72" t="str">
+      <c r="C765" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="766" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C766" s="72" t="str">
+      <c r="C766" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="767" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C767" s="72" t="str">
+      <c r="C767" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="768" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C768" s="72" t="str">
+      <c r="C768" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="769" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C769" s="72" t="str">
+      <c r="C769" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="770" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C770" s="72" t="str">
+      <c r="C770" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="771" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C771" s="72" t="str">
+      <c r="C771" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="772" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C772" s="72" t="str">
+      <c r="C772" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="773" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C773" s="72" t="str">
+      <c r="C773" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="774" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C774" s="72" t="str">
+      <c r="C774" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="775" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C775" s="72" t="str">
+      <c r="C775" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="776" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C776" s="72" t="str">
+      <c r="C776" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="777" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C777" s="72" t="str">
+      <c r="C777" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="778" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C778" s="72" t="str">
+      <c r="C778" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="779" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C779" s="72" t="str">
+      <c r="C779" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="780" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C780" s="72" t="str">
+      <c r="C780" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="781" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C781" s="72" t="str">
+      <c r="C781" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="782" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C782" s="72" t="str">
+      <c r="C782" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="783" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C783" s="72" t="str">
+      <c r="C783" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="784" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C784" s="72" t="str">
+      <c r="C784" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C785" s="72" t="str">
+      <c r="C785" s="67" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="C13">
+  <conditionalFormatting sqref="C11">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -12849,7 +12798,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
       <formula1>"Despesas, Receita Líquida"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17:E257" xr:uid="{E4F2BDDC-1223-4DFF-8087-7B85DF038B73}">
@@ -12875,7 +12824,7 @@
           <x14:formula1>
             <xm:f>'Receita Líquida'!$B$2:$M$2</xm:f>
           </x14:formula1>
-          <xm:sqref>C2</xm:sqref>
+          <xm:sqref>B2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12899,57 +12848,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="str">
+      <c r="B2" s="48" t="str">
         <f>PROPER(TEXT("01/01","MMMM"))</f>
         <v>Janeiro</v>
       </c>
-      <c r="C2" s="49" t="str">
+      <c r="C2" s="48" t="str">
         <f>PROPER(TEXT("01/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="D2" s="49" t="str">
+      <c r="D2" s="48" t="str">
         <f>PROPER(TEXT("01/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="E2" s="49" t="str">
+      <c r="E2" s="48" t="str">
         <f>PROPER(TEXT("01/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="F2" s="49" t="str">
+      <c r="F2" s="48" t="str">
         <f>PROPER(TEXT("01/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="G2" s="49" t="str">
+      <c r="G2" s="48" t="str">
         <f>PROPER(TEXT("01/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="H2" s="49" t="str">
+      <c r="H2" s="48" t="str">
         <f>PROPER(TEXT("01/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="I2" s="49" t="str">
+      <c r="I2" s="48" t="str">
         <f>PROPER(TEXT("01/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="J2" s="49" t="str">
+      <c r="J2" s="48" t="str">
         <f>PROPER(TEXT("01/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="K2" s="49" t="str">
+      <c r="K2" s="48" t="str">
         <f>PROPER(TEXT("01/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="L2" s="49" t="str">
+      <c r="L2" s="48" t="str">
         <f>PROPER(TEXT("01/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="M2" s="49" t="str">
+      <c r="M2" s="48" t="str">
         <f>PROPER(TEXT("01/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="47" t="s">
         <v>26</v>
       </c>
       <c r="B3" s="2">
@@ -13002,7 +12951,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="47" t="s">
         <v>36</v>
       </c>
       <c r="B4" s="2">
@@ -13055,7 +13004,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="47" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="2">
@@ -13108,7 +13057,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="47" t="s">
         <v>49</v>
       </c>
       <c r="B6" s="2">
@@ -13161,7 +13110,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="47" t="s">
         <v>46</v>
       </c>
       <c r="B7" s="2">
@@ -13214,7 +13163,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="47" t="s">
         <v>37</v>
       </c>
       <c r="B8" s="2">
@@ -13267,7 +13216,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="47" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="2">
@@ -13320,7 +13269,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="47" t="s">
         <v>57</v>
       </c>
       <c r="B10" s="2">
@@ -13373,7 +13322,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="47" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="2">
@@ -13426,7 +13375,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="47" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="2">
@@ -13479,7 +13428,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="47" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="2">
@@ -13532,7 +13481,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="47" t="s">
         <v>53</v>
       </c>
       <c r="B14" s="2">
@@ -13706,68 +13655,68 @@
   <dimension ref="A2:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="53" customWidth="1"/>
-    <col min="2" max="4" width="17.7109375" style="53" customWidth="1"/>
-    <col min="5" max="10" width="17.85546875" style="53" customWidth="1"/>
-    <col min="11" max="13" width="17.7109375" style="53" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="53" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="53"/>
+    <col min="1" max="1" width="15.7109375" style="52" customWidth="1"/>
+    <col min="2" max="4" width="17.7109375" style="52" customWidth="1"/>
+    <col min="5" max="10" width="17.85546875" style="52" customWidth="1"/>
+    <col min="11" max="13" width="17.7109375" style="52" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="52"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="50" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="49" t="s">
+    <row r="2" spans="1:13" s="49" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="52"/>
+      <c r="B2" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="49" t="str">
+      <c r="C2" s="48" t="str">
         <f>PROPER(TEXT("1/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
-      <c r="D2" s="49" t="str">
+      <c r="D2" s="48" t="str">
         <f>PROPER(TEXT("1/03","MMMM"))</f>
         <v>Março</v>
       </c>
-      <c r="E2" s="49" t="str">
+      <c r="E2" s="48" t="str">
         <f>PROPER(TEXT("1/04","MMMM"))</f>
         <v>Abril</v>
       </c>
-      <c r="F2" s="49" t="str">
+      <c r="F2" s="48" t="str">
         <f>PROPER(TEXT("1/05","MMMM"))</f>
         <v>Maio</v>
       </c>
-      <c r="G2" s="49" t="str">
+      <c r="G2" s="48" t="str">
         <f>PROPER(TEXT("1/06","MMMM"))</f>
         <v>Junho</v>
       </c>
-      <c r="H2" s="49" t="str">
+      <c r="H2" s="48" t="str">
         <f>PROPER(TEXT("1/07","MMMM"))</f>
         <v>Julho</v>
       </c>
-      <c r="I2" s="49" t="str">
+      <c r="I2" s="48" t="str">
         <f>PROPER(TEXT("1/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
-      <c r="J2" s="49" t="str">
+      <c r="J2" s="48" t="str">
         <f>PROPER(TEXT("1/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
-      <c r="K2" s="49" t="str">
+      <c r="K2" s="48" t="str">
         <f>PROPER(TEXT("1/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
-      <c r="L2" s="49" t="str">
+      <c r="L2" s="48" t="str">
         <f>PROPER(TEXT("1/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
-      <c r="M2" s="49" t="str">
+      <c r="M2" s="48" t="str">
         <f>PROPER(TEXT("1/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="51" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+    <row r="3" spans="1:13" s="50" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="60" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="2">
@@ -13820,56 +13769,56 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="52">
+      <c r="B4" s="51">
         <f>B3-(SUM(B7:B18))</f>
-        <v>100</v>
-      </c>
-      <c r="C4" s="52">
+        <v>150</v>
+      </c>
+      <c r="C4" s="51">
         <f t="shared" ref="C4:L4" si="0">C3-(SUM(C7:C18))+B4</f>
-        <v>100</v>
-      </c>
-      <c r="D4" s="52">
+        <v>150</v>
+      </c>
+      <c r="D4" s="51">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="E4" s="52">
+        <v>150</v>
+      </c>
+      <c r="E4" s="51">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F4" s="52">
+        <v>150</v>
+      </c>
+      <c r="F4" s="51">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="G4" s="52">
+        <v>150</v>
+      </c>
+      <c r="G4" s="51">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="H4" s="52">
+        <v>150</v>
+      </c>
+      <c r="H4" s="51">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I4" s="52">
+        <v>150</v>
+      </c>
+      <c r="I4" s="51">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="J4" s="52">
+        <v>150</v>
+      </c>
+      <c r="J4" s="51">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="K4" s="52">
+        <v>150</v>
+      </c>
+      <c r="K4" s="51">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="L4" s="52">
+        <v>150</v>
+      </c>
+      <c r="L4" s="51">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="M4" s="52">
+        <v>150</v>
+      </c>
+      <c r="M4" s="51">
         <f>M3-SUM(M7:M18)+L4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -13888,48 +13837,48 @@
       <c r="M5" s="46"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="69" t="s">
+      <c r="F6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="J6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="69" t="s">
+      <c r="K6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="69" t="s">
+      <c r="L6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="69" t="s">
+      <c r="M6" s="62" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="2">
@@ -13982,8 +13931,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="66" t="s">
-        <v>63</v>
+      <c r="A8" s="27" t="s">
+        <v>62</v>
       </c>
       <c r="B8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
@@ -14035,7 +13984,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="27" t="s">
         <v>56</v>
       </c>
       <c r="B9" s="2">
@@ -14088,8 +14037,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="66" t="s">
-        <v>65</v>
+      <c r="A10" s="27" t="s">
+        <v>64</v>
       </c>
       <c r="B10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
@@ -14141,7 +14090,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="27" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="2">
@@ -14194,7 +14143,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="27" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="2">
@@ -14247,7 +14196,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="27" t="s">
         <v>54</v>
       </c>
       <c r="B13" s="2">
@@ -14300,12 +14249,12 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="66" t="s">
-        <v>64</v>
+      <c r="A14" s="27" t="s">
+        <v>63</v>
       </c>
       <c r="B14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
@@ -14353,8 +14302,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="66" t="s">
-        <v>61</v>
+      <c r="A15" s="27" t="s">
+        <v>60</v>
       </c>
       <c r="B15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
@@ -14406,8 +14355,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="66" t="s">
-        <v>62</v>
+      <c r="A16" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="B16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
@@ -14459,7 +14408,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="27" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="2">
@@ -14512,7 +14461,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="17.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="27" t="s">
         <v>34</v>
       </c>
       <c r="B18" s="2">
@@ -14565,72 +14514,72 @@
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="51"/>
-    </row>
-    <row r="20" spans="1:14" s="51" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="49" t="s">
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+    </row>
+    <row r="20" spans="1:14" s="50" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="54">
+      <c r="B20" s="53">
         <f t="shared" ref="B20:M20" si="1">SUM(B7:B18)</f>
-        <v>50</v>
-      </c>
-      <c r="C20" s="54">
+        <v>0</v>
+      </c>
+      <c r="C20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="54">
+      <c r="H20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="54">
+      <c r="I20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="54">
+      <c r="J20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="54">
+      <c r="K20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="54">
+      <c r="L20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="54">
+      <c r="M20" s="53">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="55"/>
+      <c r="N20" s="54"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:A17">
@@ -14672,21 +14621,21 @@
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="3" customWidth="1"/>
-    <col min="2" max="3" width="17.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="3" customWidth="1"/>
-    <col min="9" max="10" width="17.140625" style="3" customWidth="1"/>
-    <col min="11" max="13" width="9.140625" style="3"/>
-    <col min="14" max="14" width="7.140625" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="8.5703125" style="63" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" style="63" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" style="63" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="63" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="63" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="63" customWidth="1"/>
+    <col min="9" max="10" width="17.140625" style="63" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="63"/>
+    <col min="14" max="14" width="7.140625" style="63" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="63"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="45" t="s">
         <v>26</v>
@@ -14699,204 +14648,204 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="62">
+      <c r="C3" s="59">
         <f>SUM(C6:C17)</f>
         <v>150</v>
       </c>
-      <c r="I3" s="61" t="s">
+      <c r="I3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="62">
+      <c r="J3" s="59">
         <f>SUM(J6:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5" s="60" t="s">
+      <c r="I5" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="64" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="str" cm="1">
+      <c r="B6" s="63" t="str" cm="1">
         <f t="array" ref="B6:B17">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="C6" s="60" cm="1">
+      <c r="C6" s="64" cm="1">
         <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,Receita_Líquida='Gráfico Categorias'!C2))</f>
         <v>150</v>
       </c>
-      <c r="I6" s="3" t="str" cm="1">
+      <c r="I6" s="63" t="str" cm="1">
         <f t="array" ref="I6:I17">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="J6" s="60" cm="1">
+      <c r="J6" s="64" cm="1">
         <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,Categorias='Gráfico Categorias'!J2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="str">
+      <c r="B7" s="63" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="C7" s="60">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="str">
+      <c r="C7" s="64">
+        <v>0</v>
+      </c>
+      <c r="I7" s="63" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="J7" s="60">
+      <c r="J7" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="str">
+      <c r="B8" s="63" t="str">
         <v>Março</v>
       </c>
-      <c r="C8" s="60">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="str">
+      <c r="C8" s="64">
+        <v>0</v>
+      </c>
+      <c r="I8" s="63" t="str">
         <v>Março</v>
       </c>
-      <c r="J8" s="60">
+      <c r="J8" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="str">
+      <c r="B9" s="63" t="str">
         <v>Abril</v>
       </c>
-      <c r="C9" s="60">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="str">
+      <c r="C9" s="64">
+        <v>0</v>
+      </c>
+      <c r="I9" s="63" t="str">
         <v>Abril</v>
       </c>
-      <c r="J9" s="60">
+      <c r="J9" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="str">
+      <c r="B10" s="63" t="str">
         <v>Maio</v>
       </c>
-      <c r="C10" s="60">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="str">
+      <c r="C10" s="64">
+        <v>0</v>
+      </c>
+      <c r="I10" s="63" t="str">
         <v>Maio</v>
       </c>
-      <c r="J10" s="60">
+      <c r="J10" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="str">
+      <c r="B11" s="63" t="str">
         <v>Junho</v>
       </c>
-      <c r="C11" s="60">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3" t="str">
+      <c r="C11" s="64">
+        <v>0</v>
+      </c>
+      <c r="I11" s="63" t="str">
         <v>Junho</v>
       </c>
-      <c r="J11" s="60">
+      <c r="J11" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="str">
+      <c r="B12" s="63" t="str">
         <v>Julho</v>
       </c>
-      <c r="C12" s="60">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="str">
+      <c r="C12" s="64">
+        <v>0</v>
+      </c>
+      <c r="I12" s="63" t="str">
         <v>Julho</v>
       </c>
-      <c r="J12" s="60">
+      <c r="J12" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="str">
+      <c r="B13" s="63" t="str">
         <v>Agosto</v>
       </c>
-      <c r="C13" s="60">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="str">
+      <c r="C13" s="64">
+        <v>0</v>
+      </c>
+      <c r="I13" s="63" t="str">
         <v>Agosto</v>
       </c>
-      <c r="J13" s="60">
+      <c r="J13" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="3" t="str">
+      <c r="B14" s="63" t="str">
         <v>Setembro</v>
       </c>
-      <c r="C14" s="60">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="str">
+      <c r="C14" s="64">
+        <v>0</v>
+      </c>
+      <c r="I14" s="63" t="str">
         <v>Setembro</v>
       </c>
-      <c r="J14" s="60">
+      <c r="J14" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="str">
+      <c r="B15" s="63" t="str">
         <v>Outubro</v>
       </c>
-      <c r="C15" s="60">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="str">
+      <c r="C15" s="64">
+        <v>0</v>
+      </c>
+      <c r="I15" s="63" t="str">
         <v>Outubro</v>
       </c>
-      <c r="J15" s="60">
+      <c r="J15" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="str">
+      <c r="B16" s="63" t="str">
         <v>Novembro</v>
       </c>
-      <c r="C16" s="60">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3" t="str">
+      <c r="C16" s="64">
+        <v>0</v>
+      </c>
+      <c r="I16" s="63" t="str">
         <v>Novembro</v>
       </c>
-      <c r="J16" s="60">
+      <c r="J16" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="str">
+      <c r="B17" s="63" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="C17" s="60">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3" t="str">
+      <c r="C17" s="64">
+        <v>0</v>
+      </c>
+      <c r="I17" s="63" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="J17" s="60">
+      <c r="J17" s="64">
         <v>0</v>
       </c>
     </row>
@@ -14967,15 +14916,15 @@
         <v>42</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="85" t="s">
+      <c r="K2" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="86"/>
+      <c r="L2" s="82"/>
       <c r="M2" s="38"/>
-      <c r="N2" s="85" t="s">
+      <c r="N2" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="86"/>
+      <c r="O2" s="82"/>
       <c r="P2" s="39"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
@@ -14995,16 +14944,16 @@
       <c r="E3" s="7"/>
       <c r="F3" s="21">
         <f>SUM('Despesas Gerais'!B20:B20)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="15">
         <f>I3</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I3" s="18">
         <f>'Despesas Gerais'!B4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="41" t="s">
@@ -15051,7 +15000,7 @@
       </c>
       <c r="I4" s="18">
         <f>'Despesas Gerais'!C4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="41" t="s">
@@ -15097,7 +15046,7 @@
       </c>
       <c r="I5" s="18">
         <f>'Despesas Gerais'!D4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="41" t="s">
@@ -15143,7 +15092,7 @@
       </c>
       <c r="I6" s="18">
         <f>'Despesas Gerais'!E4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="41" t="s">
@@ -15151,7 +15100,7 @@
       </c>
       <c r="L6" s="16">
         <f>SUM('Despesas Gerais'!B7:B17,'Despesas Gerais'!C7:C17,'Despesas Gerais'!D7:D17,'Despesas Gerais'!E7:E17,'Despesas Gerais'!F7:F17,'Despesas Gerais'!G7:G17,'Despesas Gerais'!H7:H17,'Despesas Gerais'!I7:I17,'Despesas Gerais'!J7:J17,'Despesas Gerais'!K7:K17,'Despesas Gerais'!L7:L17,'Despesas Gerais'!M7:M17)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="43" t="str">
@@ -15189,7 +15138,7 @@
       </c>
       <c r="I7" s="18">
         <f>'Despesas Gerais'!F4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="41" t="s">
@@ -15235,7 +15184,7 @@
       </c>
       <c r="I8" s="18">
         <f>'Despesas Gerais'!G4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="41" t="s">
@@ -15243,7 +15192,7 @@
       </c>
       <c r="L8" s="16">
         <f>SUM(L6:L7)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="43" t="str">
@@ -15281,7 +15230,7 @@
       </c>
       <c r="I9" s="18">
         <f>'Despesas Gerais'!H4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="41" t="s">
@@ -15289,7 +15238,7 @@
       </c>
       <c r="L9" s="18">
         <f>'Despesas Gerais'!M4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="43" t="str">
@@ -15327,7 +15276,7 @@
       </c>
       <c r="I10" s="18">
         <f>'Despesas Gerais'!I4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="42" t="s">
@@ -15343,7 +15292,7 @@
       </c>
       <c r="O10" s="44">
         <f>SUM('Despesas Gerais'!B14:M14)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P10" s="39"/>
     </row>
@@ -15373,7 +15322,7 @@
       </c>
       <c r="I11" s="18">
         <f>'Despesas Gerais'!J4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -15414,13 +15363,13 @@
       </c>
       <c r="I12" s="18">
         <f>'Despesas Gerais'!K4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="39"/>
       <c r="L12" s="40"/>
       <c r="M12" s="40"/>
-      <c r="N12" s="57" t="str">
+      <c r="N12" s="55" t="str">
         <v>Rolê/ Entret.</v>
       </c>
       <c r="O12" s="44">
@@ -15455,13 +15404,13 @@
       </c>
       <c r="I13" s="18">
         <f>'Despesas Gerais'!L4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="39"/>
       <c r="L13" s="40"/>
       <c r="M13" s="40"/>
-      <c r="N13" s="57" t="str">
+      <c r="N13" s="55" t="str">
         <v>Roupas</v>
       </c>
       <c r="O13" s="44">
@@ -15496,16 +15445,16 @@
       </c>
       <c r="I14" s="18">
         <f>'Despesas Gerais'!M4</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="39"/>
       <c r="L14" s="39"/>
       <c r="M14" s="39"/>
-      <c r="N14" s="58" t="str">
+      <c r="N14" s="56" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="O14" s="59">
+      <c r="O14" s="57">
         <f>SUM('Despesas Gerais'!B18:M18)</f>
         <v>0</v>
       </c>
@@ -15527,7 +15476,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="21">
         <f>SUM(F3:F14)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="25" t="s">
@@ -15535,7 +15484,7 @@
       </c>
       <c r="I15" s="20">
         <f>'Gráfico Anual'!L9</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="39"/>
@@ -15561,7 +15510,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="22">
         <f>AVERAGE(F3:F14)</f>
-        <v>4.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="5"/>
@@ -15590,7 +15539,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="23">
         <f>SUM(F3:F8)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="7"/>

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472D660E-05D4-4B09-A765-8574A3B9112C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018F92AB-9A83-4FD0-AC3D-82304DCD8C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Gráfico Anual" sheetId="13" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Ativos">'Saldo &amp; Mov.'!$B$7:$B$9</definedName>
+    <definedName name="Ativos">'Saldo &amp; Mov.'!$B$9:$B$11</definedName>
     <definedName name="Categorias">'Despesas Gerais'!$A$7:$A$18</definedName>
     <definedName name="Dash">'Gráfico Anual'!$A$1:$P$26</definedName>
     <definedName name="Despesas">'Despesas Gerais'!$A$7:$A$18</definedName>
@@ -30,7 +30,7 @@
     <definedName name="Perdas">'Receita Líquida'!$A$8:$A$12</definedName>
     <definedName name="Receita_Líquida">'Receita Líquida'!$A$3:$A$14</definedName>
     <definedName name="Receitas">'Receita Líquida'!$A$3:$A$7</definedName>
-    <definedName name="Transferir">'Saldo &amp; Mov.'!$B$7:$B$9</definedName>
+    <definedName name="Transferir">'Saldo &amp; Mov.'!$B$9:$B$11</definedName>
     <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="2" hidden="1">'Despesas Gerais'!$6:$6,'Despesas Gerais'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
   <si>
     <t>Mês</t>
   </si>
@@ -273,7 +273,10 @@
     <t>Curso</t>
   </si>
   <si>
-    <t>SubTotal</t>
+    <t>Desp./ Receitas</t>
+  </si>
+  <si>
+    <t>Ativos</t>
   </si>
 </sst>
 </file>
@@ -545,11 +548,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -690,15 +694,6 @@
     <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -743,16 +738,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -8749,13 +8757,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>2</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28669</xdr:rowOff>
+      <xdr:rowOff>21124</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2254313</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>16934</xdr:rowOff>
+      <xdr:rowOff>9389</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9295,15 +9303,16 @@
   <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="68" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="66" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" style="67" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" style="68" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="71" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="70" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="68" customWidth="1"/>
-    <col min="10" max="10" width="10" style="68" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="68"/>
+    <col min="1" max="1" width="14.28515625" style="65" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="63" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="64" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="64" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="65" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="68" customWidth="1"/>
+    <col min="8" max="8" width="34.28515625" style="67" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="65" customWidth="1"/>
+    <col min="10" max="10" width="10" style="65" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="65"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -9314,198 +9323,204 @@
       <c r="C2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="75" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="62" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="26">
         <f>IF(B3="Despesas",HLOOKUP(B2,'Despesas Gerais'!B2:M20,19,FALSE),IF(B3="Receita Líquida",HLOOKUP(B2,'Receita Líquida'!B2:M16,15,FALSE),""))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="77" t="str" cm="1">
+      <c r="E3" s="74" t="str" cm="1">
         <f t="array" ref="E3:E14">IF(B3="Despesas",Categorias,IF(B3="Receita Líquida",Receita_Líquida,""))</f>
         <v>Alimentação</v>
       </c>
-      <c r="F3" s="78" cm="1">
+      <c r="F3" s="75" cm="1">
         <f t="array" ref="F3:F14">IF(B3="Despesas",_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,'Despesas Gerais'!B2:M2=B2),IF(B3="Receita Líquida",_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,'Receita Líquida'!B2:M2=B2),""))</f>
         <v>0</v>
       </c>
-      <c r="H3" s="68"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="83">
+        <f>HLOOKUP(B2,'Despesas Gerais'!B2:M20,19,FALSE)/HLOOKUP(B2,'Receita Líquida'!B2:M16,15,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="74" t="str">
+        <v>Carro</v>
+      </c>
+      <c r="F4" s="75">
+        <v>0</v>
+      </c>
+      <c r="H4" s="65"/>
+    </row>
+    <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C5" s="26">
         <f>VLOOKUP(B2,'Gráfico Anual'!A3:I14,9,FALSE)</f>
         <v>150</v>
       </c>
-      <c r="E4" s="77" t="str">
-        <v>Carro</v>
-      </c>
-      <c r="F4" s="78">
-        <v>0</v>
-      </c>
-      <c r="H4" s="68"/>
-    </row>
-    <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="27" t="s">
+      <c r="E5" s="74" t="str">
+        <v>Condomínio</v>
+      </c>
+      <c r="F5" s="75">
+        <v>0</v>
+      </c>
+      <c r="H5" s="65"/>
+    </row>
+    <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C6" s="26">
         <f>'Gráfico Anual'!I15</f>
         <v>150</v>
       </c>
-      <c r="E5" s="77" t="str">
-        <v>Condomínio</v>
-      </c>
-      <c r="F5" s="78">
-        <v>0</v>
-      </c>
-      <c r="H5" s="68"/>
-    </row>
-    <row r="6" spans="1:8" ht="10.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="77" t="str">
+      <c r="E6" s="74" t="str">
         <v>Curso</v>
       </c>
-      <c r="F6" s="78">
-        <v>0</v>
-      </c>
-      <c r="H6" s="68"/>
+      <c r="F6" s="75">
+        <v>0</v>
+      </c>
+      <c r="H6" s="65"/>
     </row>
     <row r="7" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="2" cm="1">
-        <f t="array" aca="1" ref="C7" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B7,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B7,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B7,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
-        <v>150</v>
-      </c>
-      <c r="E7" s="77" t="str">
+      <c r="E7" s="74" t="str">
         <v>Eletrônicos</v>
       </c>
-      <c r="F7" s="78">
-        <v>0</v>
-      </c>
-      <c r="H7" s="68"/>
+      <c r="F7" s="75">
+        <v>0</v>
+      </c>
+      <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B8,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B8,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B8,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="77" t="str">
+      <c r="B8" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="74" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="F8" s="78">
-        <v>0</v>
-      </c>
-      <c r="H8" s="68"/>
+      <c r="F8" s="75">
+        <v>0</v>
+      </c>
+      <c r="H8" s="65"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B9,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="77" t="str">
+        <v>150</v>
+      </c>
+      <c r="E9" s="74" t="str">
         <v>G. Residencial</v>
       </c>
-      <c r="F9" s="78">
-        <v>0</v>
-      </c>
-      <c r="H9" s="68"/>
+      <c r="F9" s="75">
+        <v>0</v>
+      </c>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="67"/>
+      <c r="A10" s="64"/>
       <c r="B10" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B10,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="74" t="str">
+        <v>Gasolina</v>
+      </c>
+      <c r="F10" s="75">
+        <v>0</v>
+      </c>
+      <c r="H10" s="65"/>
+    </row>
+    <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="64"/>
+      <c r="B11" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B11,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="74" t="str">
+        <v>Jogos/ Livros</v>
+      </c>
+      <c r="F11" s="75">
+        <v>0</v>
+      </c>
+      <c r="H11" s="65"/>
+    </row>
+    <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="64"/>
+      <c r="B12" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="2">
-        <f ca="1">SUM(C7:C9)</f>
+      <c r="C12" s="2">
+        <f ca="1">SUM(C9:C11)</f>
         <v>150</v>
       </c>
-      <c r="E10" s="77" t="str">
-        <v>Gasolina</v>
-      </c>
-      <c r="F10" s="78">
-        <v>0</v>
-      </c>
-      <c r="H10" s="68"/>
-    </row>
-    <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="67"/>
-      <c r="B11" s="27" t="s">
+      <c r="E12" s="74" t="str">
+        <v>Rolê/ Entret.</v>
+      </c>
+      <c r="F12" s="75">
+        <v>0</v>
+      </c>
+      <c r="H12" s="65"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="64"/>
+      <c r="B13" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="26">
-        <f ca="1">ROUND(C4-C10,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="77" t="str">
-        <v>Jogos/ Livros</v>
-      </c>
-      <c r="F11" s="78">
-        <v>0</v>
-      </c>
-      <c r="H11" s="68"/>
-    </row>
-    <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="67"/>
-      <c r="E12" s="77" t="str">
-        <v>Rolê/ Entret.</v>
-      </c>
-      <c r="F12" s="78">
-        <v>0</v>
-      </c>
-      <c r="H12" s="68"/>
-    </row>
-    <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="67"/>
-      <c r="B13" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="2">
-        <f>SUBTOTAL(9,Tabela1[Valor])</f>
-        <v>150</v>
-      </c>
-      <c r="E13" s="77" t="str">
+      <c r="C13" s="26">
+        <f ca="1">ROUND(C5-C12,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="74" t="str">
         <v>Roupas</v>
       </c>
-      <c r="F13" s="78">
-        <v>0</v>
-      </c>
-      <c r="H13" s="68"/>
+      <c r="F13" s="75">
+        <v>0</v>
+      </c>
+      <c r="H13" s="65"/>
     </row>
     <row r="14" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="67"/>
-      <c r="E14" s="77" t="str">
+      <c r="A14" s="64"/>
+      <c r="E14" s="74" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="F14" s="79">
-        <v>0</v>
-      </c>
-      <c r="H14" s="68"/>
+      <c r="F14" s="76">
+        <v>0</v>
+      </c>
+      <c r="H14" s="65"/>
     </row>
     <row r="15" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="74"/>
-      <c r="B15" s="68"/>
-      <c r="H15" s="68"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="65"/>
+      <c r="H15" s="65"/>
     </row>
     <row r="16" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="76">
+      <c r="A16" s="73">
         <f>SUBTOTAL(2,Tabela1[Data])</f>
         <v>1</v>
       </c>
@@ -9590,3214 +9605,3228 @@
       <c r="H20" s="37"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G23" s="69"/>
+      <c r="G23" s="66"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G25" s="69"/>
+      <c r="G25" s="66"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G26" s="69"/>
+      <c r="G26" s="66"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G27" s="69"/>
+      <c r="G27" s="66"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G28" s="69"/>
+      <c r="G28" s="66"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I38" s="68" t="s">
+      <c r="I38" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G137" s="69"/>
+      <c r="G137" s="66"/>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G139" s="69"/>
+      <c r="G139" s="66"/>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G140" s="69"/>
+      <c r="G140" s="66"/>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G141" s="69"/>
+      <c r="G141" s="66"/>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G142" s="69"/>
+      <c r="G142" s="66"/>
     </row>
     <row r="248" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C248" s="67" t="str">
+      <c r="C248" s="64" t="str">
         <f>IF(ISBLANK(B248),"",PROPER(TEXT(B248,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="249" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C249" s="67" t="str">
+      <c r="C249" s="64" t="str">
         <f>IF(ISBLANK(B249),"",PROPER(TEXT(B249,"MMMM")))</f>
         <v/>
       </c>
-      <c r="G249" s="72"/>
+      <c r="G249" s="69"/>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C258" s="67" t="str">
+      <c r="C258" s="64" t="str">
         <f>IF(ISBLANK(B258),"",PROPER(TEXT(B258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="D258" s="67" t="str">
+      <c r="D258" s="64" t="str">
         <f t="shared" ref="D258:G258" si="1">IF(ISBLANK(C258),"",PROPER(TEXT(C258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="E258" s="67" t="str">
+      <c r="E258" s="64" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F258" s="67" t="str">
+      <c r="F258" s="64" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G258" s="67" t="str">
+      <c r="G258" s="64" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C267" s="67" t="str">
+      <c r="C267" s="64" t="str">
         <f t="shared" ref="C267" si="2">IF(ISBLANK(B267),"",PROPER(TEXT(B267,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C268" s="67" t="str">
+      <c r="C268" s="64" t="str">
         <f t="shared" ref="C268:C282" si="3">IF(ISBLANK(B268),"",PROPER(TEXT(B268,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C269" s="67" t="str">
+      <c r="C269" s="64" t="str">
         <f t="shared" ref="C269:C279" si="4">IF(ISBLANK(B269),"",PROPER(TEXT(B269,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C270" s="67" t="str">
+      <c r="C270" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C271" s="67" t="str">
+      <c r="C271" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C272" s="67" t="str">
+      <c r="C272" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C273" s="67" t="str">
+      <c r="C273" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C274" s="67" t="str">
+      <c r="C274" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C275" s="67" t="str">
+      <c r="C275" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C276" s="67" t="str">
+      <c r="C276" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C277" s="67" t="str">
+      <c r="C277" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C278" s="67" t="str">
+      <c r="C278" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C279" s="67" t="str">
+      <c r="C279" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C280" s="67" t="str">
+      <c r="C280" s="64" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C281" s="67" t="str">
+      <c r="C281" s="64" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C282" s="67" t="str">
+      <c r="C282" s="64" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G282" s="69"/>
-      <c r="H282" s="73"/>
+      <c r="G282" s="66"/>
+      <c r="H282" s="70"/>
     </row>
     <row r="283" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B283" s="68"/>
-      <c r="C283" s="68"/>
-      <c r="D283" s="68"/>
-      <c r="E283" s="74"/>
-      <c r="F283" s="74"/>
-      <c r="G283" s="69"/>
-      <c r="H283" s="73"/>
+      <c r="B283" s="65"/>
+      <c r="C283" s="65"/>
+      <c r="D283" s="65"/>
+      <c r="E283" s="71"/>
+      <c r="F283" s="71"/>
+      <c r="G283" s="66"/>
+      <c r="H283" s="70"/>
     </row>
     <row r="284" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B284" s="68"/>
-      <c r="C284" s="68"/>
-      <c r="D284" s="68"/>
-      <c r="E284" s="74"/>
-      <c r="F284" s="74"/>
-      <c r="G284" s="69"/>
-      <c r="H284" s="73"/>
+      <c r="B284" s="65"/>
+      <c r="C284" s="65"/>
+      <c r="D284" s="65"/>
+      <c r="E284" s="71"/>
+      <c r="F284" s="71"/>
+      <c r="G284" s="66"/>
+      <c r="H284" s="70"/>
     </row>
     <row r="285" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B285" s="68"/>
-      <c r="C285" s="68"/>
-      <c r="D285" s="68"/>
-      <c r="E285" s="74"/>
-      <c r="F285" s="74"/>
-      <c r="G285" s="69"/>
-      <c r="H285" s="73"/>
+      <c r="B285" s="65"/>
+      <c r="C285" s="65"/>
+      <c r="D285" s="65"/>
+      <c r="E285" s="71"/>
+      <c r="F285" s="71"/>
+      <c r="G285" s="66"/>
+      <c r="H285" s="70"/>
     </row>
     <row r="286" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B286" s="68"/>
-      <c r="C286" s="75"/>
-      <c r="D286" s="75"/>
-      <c r="E286" s="74"/>
-      <c r="F286" s="74"/>
-      <c r="G286" s="69"/>
-      <c r="H286" s="73"/>
+      <c r="B286" s="65"/>
+      <c r="C286" s="72"/>
+      <c r="D286" s="72"/>
+      <c r="E286" s="71"/>
+      <c r="F286" s="71"/>
+      <c r="G286" s="66"/>
+      <c r="H286" s="70"/>
     </row>
     <row r="287" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B287" s="68"/>
-      <c r="C287" s="68"/>
-      <c r="D287" s="68"/>
-      <c r="G287" s="68"/>
+      <c r="B287" s="65"/>
+      <c r="C287" s="65"/>
+      <c r="D287" s="65"/>
+      <c r="G287" s="65"/>
     </row>
     <row r="288" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B288" s="68"/>
-      <c r="C288" s="68"/>
-      <c r="D288" s="68"/>
-      <c r="G288" s="68"/>
+      <c r="B288" s="65"/>
+      <c r="C288" s="65"/>
+      <c r="D288" s="65"/>
+      <c r="G288" s="65"/>
     </row>
     <row r="289" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B289" s="68"/>
-      <c r="C289" s="68"/>
-      <c r="D289" s="68"/>
-      <c r="G289" s="68"/>
+      <c r="B289" s="65"/>
+      <c r="C289" s="65"/>
+      <c r="D289" s="65"/>
+      <c r="G289" s="65"/>
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B290" s="68"/>
-      <c r="C290" s="68"/>
-      <c r="D290" s="68"/>
-      <c r="G290" s="68"/>
+      <c r="B290" s="65"/>
+      <c r="C290" s="65"/>
+      <c r="D290" s="65"/>
+      <c r="G290" s="65"/>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B291" s="68"/>
-      <c r="C291" s="68"/>
-      <c r="D291" s="68"/>
-      <c r="G291" s="68"/>
+      <c r="B291" s="65"/>
+      <c r="C291" s="65"/>
+      <c r="D291" s="65"/>
+      <c r="G291" s="65"/>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B292" s="68"/>
-      <c r="C292" s="68"/>
-      <c r="D292" s="68"/>
-      <c r="G292" s="68"/>
+      <c r="B292" s="65"/>
+      <c r="C292" s="65"/>
+      <c r="D292" s="65"/>
+      <c r="G292" s="65"/>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B293" s="68"/>
-      <c r="C293" s="68"/>
-      <c r="D293" s="68"/>
-      <c r="G293" s="68"/>
+      <c r="B293" s="65"/>
+      <c r="C293" s="65"/>
+      <c r="D293" s="65"/>
+      <c r="G293" s="65"/>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C294" s="67" t="str">
+      <c r="C294" s="64" t="str">
         <f t="shared" ref="C294:C352" si="5">IF(ISBLANK(B294),"",PROPER(TEXT(B294,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C295" s="67" t="str">
+      <c r="C295" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C296" s="67" t="str">
+      <c r="C296" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C297" s="67" t="str">
+      <c r="C297" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C298" s="67" t="str">
+      <c r="C298" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C299" s="67" t="str">
+      <c r="C299" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C300" s="67" t="str">
+      <c r="C300" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C301" s="67" t="str">
+      <c r="C301" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C302" s="67" t="str">
+      <c r="C302" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C303" s="67" t="str">
+      <c r="C303" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C304" s="67" t="str">
+      <c r="C304" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C305" s="67" t="str">
+      <c r="C305" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C306" s="67" t="str">
+      <c r="C306" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C307" s="67" t="str">
+      <c r="C307" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" s="67" t="str">
+      <c r="C308" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C309" s="67" t="str">
+      <c r="C309" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C310" s="67" t="str">
+      <c r="C310" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C311" s="67" t="str">
+      <c r="C311" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C312" s="67" t="str">
+      <c r="C312" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C313" s="67" t="str">
+      <c r="C313" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C314" s="67" t="str">
+      <c r="C314" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C315" s="67" t="str">
+      <c r="C315" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C316" s="67" t="str">
+      <c r="C316" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C317" s="67" t="str">
+      <c r="C317" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C318" s="67" t="str">
+      <c r="C318" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C319" s="67" t="str">
+      <c r="C319" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C320" s="67" t="str">
+      <c r="C320" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C321" s="67" t="str">
+      <c r="C321" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C322" s="67" t="str">
+      <c r="C322" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C323" s="67" t="str">
+      <c r="C323" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C324" s="67" t="str">
+      <c r="C324" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C325" s="67" t="str">
+      <c r="C325" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C326" s="67" t="str">
+      <c r="C326" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C327" s="67" t="str">
+      <c r="C327" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C328" s="67" t="str">
+      <c r="C328" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C329" s="67" t="str">
+      <c r="C329" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C330" s="67" t="str">
+      <c r="C330" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C331" s="67" t="str">
+      <c r="C331" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C332" s="67" t="str">
+      <c r="C332" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C333" s="67" t="str">
+      <c r="C333" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C334" s="67" t="str">
+      <c r="C334" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C335" s="67" t="str">
+      <c r="C335" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C336" s="67" t="str">
+      <c r="C336" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C337" s="67" t="str">
+      <c r="C337" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C338" s="67" t="str">
+      <c r="C338" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C339" s="67" t="str">
+      <c r="C339" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C340" s="67" t="str">
+      <c r="C340" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C341" s="67" t="str">
+      <c r="C341" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C342" s="67" t="str">
+      <c r="C342" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C343" s="67" t="str">
+      <c r="C343" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C344" s="67" t="str">
+      <c r="C344" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C345" s="67" t="str">
+      <c r="C345" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C346" s="67" t="str">
+      <c r="C346" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C347" s="67" t="str">
+      <c r="C347" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C348" s="67" t="str">
+      <c r="C348" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C349" s="67" t="str">
+      <c r="C349" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C350" s="67" t="str">
+      <c r="C350" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C351" s="67" t="str">
+      <c r="C351" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C352" s="67" t="str">
+      <c r="C352" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C353" s="67" t="str">
+      <c r="C353" s="64" t="str">
         <f t="shared" ref="C353:C416" si="6">IF(ISBLANK(B353),"",PROPER(TEXT(B353,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C354" s="67" t="str">
+      <c r="C354" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C355" s="67" t="str">
+      <c r="C355" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C356" s="67" t="str">
+      <c r="C356" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C357" s="67" t="str">
+      <c r="C357" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C358" s="67" t="str">
+      <c r="C358" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C359" s="67" t="str">
+      <c r="C359" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C360" s="67" t="str">
+      <c r="C360" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C361" s="67" t="str">
+      <c r="C361" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C362" s="67" t="str">
+      <c r="C362" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C363" s="67" t="str">
+      <c r="C363" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C364" s="67" t="str">
+      <c r="C364" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C365" s="67" t="str">
+      <c r="C365" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C366" s="67" t="str">
+      <c r="C366" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C367" s="67" t="str">
+      <c r="C367" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C368" s="67" t="str">
+      <c r="C368" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C369" s="67" t="str">
+      <c r="C369" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C370" s="67" t="str">
+      <c r="C370" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C371" s="67" t="str">
+      <c r="C371" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C372" s="67" t="str">
+      <c r="C372" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C373" s="67" t="str">
+      <c r="C373" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C374" s="67" t="str">
+      <c r="C374" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C375" s="67" t="str">
+      <c r="C375" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C376" s="67" t="str">
+      <c r="C376" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C377" s="67" t="str">
+      <c r="C377" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C378" s="67" t="str">
+      <c r="C378" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C379" s="67" t="str">
+      <c r="C379" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C380" s="67" t="str">
+      <c r="C380" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C381" s="67" t="str">
+      <c r="C381" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C382" s="67" t="str">
+      <c r="C382" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C383" s="67" t="str">
+      <c r="C383" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C384" s="67" t="str">
+      <c r="C384" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C385" s="67" t="str">
+      <c r="C385" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C386" s="67" t="str">
+      <c r="C386" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C387" s="67" t="str">
+      <c r="C387" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C388" s="67" t="str">
+      <c r="C388" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C389" s="67" t="str">
+      <c r="C389" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="67" t="str">
+      <c r="C390" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C391" s="67" t="str">
+      <c r="C391" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C392" s="67" t="str">
+      <c r="C392" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C393" s="67" t="str">
+      <c r="C393" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C394" s="67" t="str">
+      <c r="C394" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C395" s="67" t="str">
+      <c r="C395" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C396" s="67" t="str">
+      <c r="C396" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C397" s="67" t="str">
+      <c r="C397" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C398" s="67" t="str">
+      <c r="C398" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C399" s="67" t="str">
+      <c r="C399" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C400" s="67" t="str">
+      <c r="C400" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C401" s="67" t="str">
+      <c r="C401" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C402" s="67" t="str">
+      <c r="C402" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C403" s="67" t="str">
+      <c r="C403" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C404" s="67" t="str">
+      <c r="C404" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C405" s="67" t="str">
+      <c r="C405" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C406" s="67" t="str">
+      <c r="C406" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C407" s="67" t="str">
+      <c r="C407" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C408" s="67" t="str">
+      <c r="C408" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C409" s="67" t="str">
+      <c r="C409" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C410" s="67" t="str">
+      <c r="C410" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C411" s="67" t="str">
+      <c r="C411" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C412" s="67" t="str">
+      <c r="C412" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C413" s="67" t="str">
+      <c r="C413" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C414" s="67" t="str">
+      <c r="C414" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C415" s="67" t="str">
+      <c r="C415" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C416" s="67" t="str">
+      <c r="C416" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="67" t="str">
+      <c r="C417" s="64" t="str">
         <f t="shared" ref="C417:C480" si="7">IF(ISBLANK(B417),"",PROPER(TEXT(B417,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C418" s="67" t="str">
+      <c r="C418" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C419" s="67" t="str">
+      <c r="C419" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="67" t="str">
+      <c r="C420" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C421" s="67" t="str">
+      <c r="C421" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C422" s="67" t="str">
+      <c r="C422" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C423" s="67" t="str">
+      <c r="C423" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C424" s="67" t="str">
+      <c r="C424" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C425" s="67" t="str">
+      <c r="C425" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C426" s="67" t="str">
+      <c r="C426" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C427" s="67" t="str">
+      <c r="C427" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C428" s="67" t="str">
+      <c r="C428" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C429" s="67" t="str">
+      <c r="C429" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C430" s="67" t="str">
+      <c r="C430" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C431" s="67" t="str">
+      <c r="C431" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C432" s="67" t="str">
+      <c r="C432" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="67" t="str">
+      <c r="C433" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C434" s="67" t="str">
+      <c r="C434" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C435" s="67" t="str">
+      <c r="C435" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="67" t="str">
+      <c r="C436" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C437" s="67" t="str">
+      <c r="C437" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C438" s="67" t="str">
+      <c r="C438" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C439" s="67" t="str">
+      <c r="C439" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C440" s="67" t="str">
+      <c r="C440" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C441" s="67" t="str">
+      <c r="C441" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C442" s="67" t="str">
+      <c r="C442" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C443" s="67" t="str">
+      <c r="C443" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C444" s="67" t="str">
+      <c r="C444" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C445" s="67" t="str">
+      <c r="C445" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C446" s="67" t="str">
+      <c r="C446" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C447" s="67" t="str">
+      <c r="C447" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C448" s="67" t="str">
+      <c r="C448" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C449" s="67" t="str">
+      <c r="C449" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C450" s="67" t="str">
+      <c r="C450" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C451" s="67" t="str">
+      <c r="C451" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C452" s="67" t="str">
+      <c r="C452" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C453" s="67" t="str">
+      <c r="C453" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C454" s="67" t="str">
+      <c r="C454" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C455" s="67" t="str">
+      <c r="C455" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C456" s="67" t="str">
+      <c r="C456" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C457" s="67" t="str">
+      <c r="C457" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C458" s="67" t="str">
+      <c r="C458" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C459" s="67" t="str">
+      <c r="C459" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C460" s="67" t="str">
+      <c r="C460" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C461" s="67" t="str">
+      <c r="C461" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C462" s="67" t="str">
+      <c r="C462" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C463" s="67" t="str">
+      <c r="C463" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C464" s="67" t="str">
+      <c r="C464" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" s="67" t="str">
+      <c r="C465" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C466" s="67" t="str">
+      <c r="C466" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C467" s="67" t="str">
+      <c r="C467" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C468" s="67" t="str">
+      <c r="C468" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C469" s="67" t="str">
+      <c r="C469" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C470" s="67" t="str">
+      <c r="C470" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C471" s="67" t="str">
+      <c r="C471" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C472" s="67" t="str">
+      <c r="C472" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C473" s="67" t="str">
+      <c r="C473" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" s="67" t="str">
+      <c r="C474" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" s="67" t="str">
+      <c r="C475" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" s="67" t="str">
+      <c r="C476" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C477" s="67" t="str">
+      <c r="C477" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C478" s="67" t="str">
+      <c r="C478" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C479" s="67" t="str">
+      <c r="C479" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C480" s="67" t="str">
+      <c r="C480" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C481" s="67" t="str">
+      <c r="C481" s="64" t="str">
         <f t="shared" ref="C481:C544" si="8">IF(ISBLANK(B481),"",PROPER(TEXT(B481,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="482" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C482" s="67" t="str">
+      <c r="C482" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C483" s="67" t="str">
+      <c r="C483" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C484" s="67" t="str">
+      <c r="C484" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C485" s="67" t="str">
+      <c r="C485" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C486" s="67" t="str">
+      <c r="C486" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="67" t="str">
+      <c r="C487" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" s="67" t="str">
+      <c r="C488" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" s="67" t="str">
+      <c r="C489" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C490" s="67" t="str">
+      <c r="C490" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C491" s="67" t="str">
+      <c r="C491" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C492" s="67" t="str">
+      <c r="C492" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C493" s="67" t="str">
+      <c r="C493" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C494" s="67" t="str">
+      <c r="C494" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C495" s="67" t="str">
+      <c r="C495" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C496" s="67" t="str">
+      <c r="C496" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C497" s="67" t="str">
+      <c r="C497" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="67" t="str">
+      <c r="C498" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" s="67" t="str">
+      <c r="C499" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" s="67" t="str">
+      <c r="C500" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="67" t="str">
+      <c r="C501" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C502" s="67" t="str">
+      <c r="C502" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C503" s="67" t="str">
+      <c r="C503" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C504" s="67" t="str">
+      <c r="C504" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C505" s="67" t="str">
+      <c r="C505" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C506" s="67" t="str">
+      <c r="C506" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C507" s="67" t="str">
+      <c r="C507" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C508" s="67" t="str">
+      <c r="C508" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C509" s="67" t="str">
+      <c r="C509" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C510" s="67" t="str">
+      <c r="C510" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C511" s="67" t="str">
+      <c r="C511" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C512" s="67" t="str">
+      <c r="C512" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C513" s="67" t="str">
+      <c r="C513" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" s="67" t="str">
+      <c r="C514" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" s="67" t="str">
+      <c r="C515" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" s="67" t="str">
+      <c r="C516" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C517" s="67" t="str">
+      <c r="C517" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C518" s="67" t="str">
+      <c r="C518" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C519" s="67" t="str">
+      <c r="C519" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C520" s="67" t="str">
+      <c r="C520" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C521" s="67" t="str">
+      <c r="C521" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" s="67" t="str">
+      <c r="C522" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" s="67" t="str">
+      <c r="C523" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" s="67" t="str">
+      <c r="C524" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C525" s="67" t="str">
+      <c r="C525" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C526" s="67" t="str">
+      <c r="C526" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C527" s="67" t="str">
+      <c r="C527" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C528" s="67" t="str">
+      <c r="C528" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C529" s="67" t="str">
+      <c r="C529" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" s="67" t="str">
+      <c r="C530" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" s="67" t="str">
+      <c r="C531" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" s="67" t="str">
+      <c r="C532" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C533" s="67" t="str">
+      <c r="C533" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C534" s="67" t="str">
+      <c r="C534" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C535" s="67" t="str">
+      <c r="C535" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C536" s="67" t="str">
+      <c r="C536" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C537" s="67" t="str">
+      <c r="C537" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C538" s="67" t="str">
+      <c r="C538" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C539" s="67" t="str">
+      <c r="C539" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C540" s="67" t="str">
+      <c r="C540" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C541" s="67" t="str">
+      <c r="C541" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C542" s="67" t="str">
+      <c r="C542" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C543" s="67" t="str">
+      <c r="C543" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C544" s="67" t="str">
+      <c r="C544" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C545" s="67" t="str">
+      <c r="C545" s="64" t="str">
         <f t="shared" ref="C545:C608" si="9">IF(ISBLANK(B545),"",PROPER(TEXT(B545,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="546" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C546" s="67" t="str">
+      <c r="C546" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C547" s="67" t="str">
+      <c r="C547" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C548" s="67" t="str">
+      <c r="C548" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C549" s="67" t="str">
+      <c r="C549" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C550" s="67" t="str">
+      <c r="C550" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C551" s="67" t="str">
+      <c r="C551" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C552" s="67" t="str">
+      <c r="C552" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C553" s="67" t="str">
+      <c r="C553" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C554" s="67" t="str">
+      <c r="C554" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C555" s="67" t="str">
+      <c r="C555" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C556" s="67" t="str">
+      <c r="C556" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C557" s="67" t="str">
+      <c r="C557" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C558" s="67" t="str">
+      <c r="C558" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C559" s="67" t="str">
+      <c r="C559" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C560" s="67" t="str">
+      <c r="C560" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C561" s="67" t="str">
+      <c r="C561" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C562" s="67" t="str">
+      <c r="C562" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C563" s="67" t="str">
+      <c r="C563" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C564" s="67" t="str">
+      <c r="C564" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C565" s="67" t="str">
+      <c r="C565" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C566" s="67" t="str">
+      <c r="C566" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C567" s="67" t="str">
+      <c r="C567" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C568" s="67" t="str">
+      <c r="C568" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C569" s="67" t="str">
+      <c r="C569" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C570" s="67" t="str">
+      <c r="C570" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C571" s="67" t="str">
+      <c r="C571" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C572" s="67" t="str">
+      <c r="C572" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C573" s="67" t="str">
+      <c r="C573" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C574" s="67" t="str">
+      <c r="C574" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C575" s="67" t="str">
+      <c r="C575" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C576" s="67" t="str">
+      <c r="C576" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C577" s="67" t="str">
+      <c r="C577" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C578" s="67" t="str">
+      <c r="C578" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C579" s="67" t="str">
+      <c r="C579" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C580" s="67" t="str">
+      <c r="C580" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C581" s="67" t="str">
+      <c r="C581" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C582" s="67" t="str">
+      <c r="C582" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C583" s="67" t="str">
+      <c r="C583" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C584" s="67" t="str">
+      <c r="C584" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C585" s="67" t="str">
+      <c r="C585" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C586" s="67" t="str">
+      <c r="C586" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C587" s="67" t="str">
+      <c r="C587" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C588" s="67" t="str">
+      <c r="C588" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C589" s="67" t="str">
+      <c r="C589" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C590" s="67" t="str">
+      <c r="C590" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C591" s="67" t="str">
+      <c r="C591" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C592" s="67" t="str">
+      <c r="C592" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C593" s="67" t="str">
+      <c r="C593" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C594" s="67" t="str">
+      <c r="C594" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C595" s="67" t="str">
+      <c r="C595" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C596" s="67" t="str">
+      <c r="C596" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C597" s="67" t="str">
+      <c r="C597" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C598" s="67" t="str">
+      <c r="C598" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C599" s="67" t="str">
+      <c r="C599" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C600" s="67" t="str">
+      <c r="C600" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C601" s="67" t="str">
+      <c r="C601" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C602" s="67" t="str">
+      <c r="C602" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C603" s="67" t="str">
+      <c r="C603" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C604" s="67" t="str">
+      <c r="C604" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C605" s="67" t="str">
+      <c r="C605" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C606" s="67" t="str">
+      <c r="C606" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C607" s="67" t="str">
+      <c r="C607" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C608" s="67" t="str">
+      <c r="C608" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C609" s="67" t="str">
+      <c r="C609" s="64" t="str">
         <f t="shared" ref="C609:C672" si="10">IF(ISBLANK(B609),"",PROPER(TEXT(B609,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="610" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C610" s="67" t="str">
+      <c r="C610" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C611" s="67" t="str">
+      <c r="C611" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C612" s="67" t="str">
+      <c r="C612" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C613" s="67" t="str">
+      <c r="C613" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C614" s="67" t="str">
+      <c r="C614" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C615" s="67" t="str">
+      <c r="C615" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C616" s="67" t="str">
+      <c r="C616" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C617" s="67" t="str">
+      <c r="C617" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C618" s="67" t="str">
+      <c r="C618" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C619" s="67" t="str">
+      <c r="C619" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C620" s="67" t="str">
+      <c r="C620" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C621" s="67" t="str">
+      <c r="C621" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C622" s="67" t="str">
+      <c r="C622" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C623" s="67" t="str">
+      <c r="C623" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C624" s="67" t="str">
+      <c r="C624" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C625" s="67" t="str">
+      <c r="C625" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C626" s="67" t="str">
+      <c r="C626" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C627" s="67" t="str">
+      <c r="C627" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C628" s="67" t="str">
+      <c r="C628" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C629" s="67" t="str">
+      <c r="C629" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C630" s="67" t="str">
+      <c r="C630" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C631" s="67" t="str">
+      <c r="C631" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C632" s="67" t="str">
+      <c r="C632" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C633" s="67" t="str">
+      <c r="C633" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C634" s="67" t="str">
+      <c r="C634" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C635" s="67" t="str">
+      <c r="C635" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C636" s="67" t="str">
+      <c r="C636" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C637" s="67" t="str">
+      <c r="C637" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C638" s="67" t="str">
+      <c r="C638" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C639" s="67" t="str">
+      <c r="C639" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C640" s="67" t="str">
+      <c r="C640" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C641" s="67" t="str">
+      <c r="C641" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C642" s="67" t="str">
+      <c r="C642" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C643" s="67" t="str">
+      <c r="C643" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C644" s="67" t="str">
+      <c r="C644" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C645" s="67" t="str">
+      <c r="C645" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C646" s="67" t="str">
+      <c r="C646" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C647" s="67" t="str">
+      <c r="C647" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C648" s="67" t="str">
+      <c r="C648" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C649" s="67" t="str">
+      <c r="C649" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C650" s="67" t="str">
+      <c r="C650" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C651" s="67" t="str">
+      <c r="C651" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C652" s="67" t="str">
+      <c r="C652" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C653" s="67" t="str">
+      <c r="C653" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C654" s="67" t="str">
+      <c r="C654" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C655" s="67" t="str">
+      <c r="C655" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C656" s="67" t="str">
+      <c r="C656" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C657" s="67" t="str">
+      <c r="C657" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C658" s="67" t="str">
+      <c r="C658" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C659" s="67" t="str">
+      <c r="C659" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C660" s="67" t="str">
+      <c r="C660" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C661" s="67" t="str">
+      <c r="C661" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C662" s="67" t="str">
+      <c r="C662" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C663" s="67" t="str">
+      <c r="C663" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C664" s="67" t="str">
+      <c r="C664" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C665" s="67" t="str">
+      <c r="C665" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C666" s="67" t="str">
+      <c r="C666" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C667" s="67" t="str">
+      <c r="C667" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C668" s="67" t="str">
+      <c r="C668" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C669" s="67" t="str">
+      <c r="C669" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C670" s="67" t="str">
+      <c r="C670" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C671" s="67" t="str">
+      <c r="C671" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C672" s="67" t="str">
+      <c r="C672" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C673" s="67" t="str">
+      <c r="C673" s="64" t="str">
         <f t="shared" ref="C673:C736" si="11">IF(ISBLANK(B673),"",PROPER(TEXT(B673,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="674" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C674" s="67" t="str">
+      <c r="C674" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C675" s="67" t="str">
+      <c r="C675" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C676" s="67" t="str">
+      <c r="C676" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C677" s="67" t="str">
+      <c r="C677" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C678" s="67" t="str">
+      <c r="C678" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C679" s="67" t="str">
+      <c r="C679" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C680" s="67" t="str">
+      <c r="C680" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C681" s="67" t="str">
+      <c r="C681" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C682" s="67" t="str">
+      <c r="C682" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C683" s="67" t="str">
+      <c r="C683" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C684" s="67" t="str">
+      <c r="C684" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C685" s="67" t="str">
+      <c r="C685" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="686" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C686" s="67" t="str">
+      <c r="C686" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="687" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C687" s="67" t="str">
+      <c r="C687" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="688" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C688" s="67" t="str">
+      <c r="C688" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="689" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C689" s="67" t="str">
+      <c r="C689" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="690" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C690" s="67" t="str">
+      <c r="C690" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="691" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C691" s="67" t="str">
+      <c r="C691" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="692" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C692" s="67" t="str">
+      <c r="C692" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="693" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C693" s="67" t="str">
+      <c r="C693" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="694" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C694" s="67" t="str">
+      <c r="C694" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="695" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C695" s="67" t="str">
+      <c r="C695" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="696" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C696" s="67" t="str">
+      <c r="C696" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="697" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C697" s="67" t="str">
+      <c r="C697" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="698" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C698" s="67" t="str">
+      <c r="C698" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="699" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C699" s="67" t="str">
+      <c r="C699" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="700" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C700" s="67" t="str">
+      <c r="C700" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="701" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C701" s="67" t="str">
+      <c r="C701" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="702" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C702" s="67" t="str">
+      <c r="C702" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="703" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C703" s="67" t="str">
+      <c r="C703" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="704" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C704" s="67" t="str">
+      <c r="C704" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="705" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C705" s="67" t="str">
+      <c r="C705" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="706" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C706" s="67" t="str">
+      <c r="C706" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="707" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C707" s="67" t="str">
+      <c r="C707" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="708" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C708" s="67" t="str">
+      <c r="C708" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="709" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C709" s="67" t="str">
+      <c r="C709" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="710" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C710" s="67" t="str">
+      <c r="C710" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="711" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C711" s="67" t="str">
+      <c r="C711" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="712" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C712" s="67" t="str">
+      <c r="C712" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="713" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C713" s="67" t="str">
+      <c r="C713" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="714" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C714" s="67" t="str">
+      <c r="C714" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="715" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C715" s="67" t="str">
+      <c r="C715" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="716" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C716" s="67" t="str">
+      <c r="C716" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="717" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C717" s="67" t="str">
+      <c r="C717" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="718" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C718" s="67" t="str">
+      <c r="C718" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="719" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C719" s="67" t="str">
+      <c r="C719" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="720" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C720" s="67" t="str">
+      <c r="C720" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="721" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C721" s="67" t="str">
+      <c r="C721" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="722" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C722" s="67" t="str">
+      <c r="C722" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="723" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C723" s="67" t="str">
+      <c r="C723" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="724" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C724" s="67" t="str">
+      <c r="C724" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="725" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C725" s="67" t="str">
+      <c r="C725" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="726" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C726" s="67" t="str">
+      <c r="C726" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="727" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C727" s="67" t="str">
+      <c r="C727" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="728" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C728" s="67" t="str">
+      <c r="C728" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="729" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C729" s="67" t="str">
+      <c r="C729" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="730" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C730" s="67" t="str">
+      <c r="C730" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="731" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C731" s="67" t="str">
+      <c r="C731" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="732" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C732" s="67" t="str">
+      <c r="C732" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="733" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C733" s="67" t="str">
+      <c r="C733" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="734" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C734" s="67" t="str">
+      <c r="C734" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="735" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C735" s="67" t="str">
+      <c r="C735" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="736" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C736" s="67" t="str">
+      <c r="C736" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="737" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C737" s="67" t="str">
+      <c r="C737" s="64" t="str">
         <f t="shared" ref="C737:C785" si="12">IF(ISBLANK(B737),"",PROPER(TEXT(B737,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="738" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C738" s="67" t="str">
+      <c r="C738" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="739" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C739" s="67" t="str">
+      <c r="C739" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="740" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C740" s="67" t="str">
+      <c r="C740" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="741" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C741" s="67" t="str">
+      <c r="C741" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="742" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C742" s="67" t="str">
+      <c r="C742" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="743" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C743" s="67" t="str">
+      <c r="C743" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="744" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C744" s="67" t="str">
+      <c r="C744" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="745" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C745" s="67" t="str">
+      <c r="C745" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="746" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C746" s="67" t="str">
+      <c r="C746" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="747" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C747" s="67" t="str">
+      <c r="C747" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="748" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C748" s="67" t="str">
+      <c r="C748" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="749" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C749" s="67" t="str">
+      <c r="C749" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="750" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C750" s="67" t="str">
+      <c r="C750" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="751" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C751" s="67" t="str">
+      <c r="C751" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="752" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C752" s="67" t="str">
+      <c r="C752" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="753" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C753" s="67" t="str">
+      <c r="C753" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="754" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C754" s="67" t="str">
+      <c r="C754" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="755" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C755" s="67" t="str">
+      <c r="C755" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="756" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C756" s="67" t="str">
+      <c r="C756" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="757" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C757" s="67" t="str">
+      <c r="C757" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="758" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C758" s="67" t="str">
+      <c r="C758" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="759" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C759" s="67" t="str">
+      <c r="C759" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="760" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C760" s="67" t="str">
+      <c r="C760" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="761" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C761" s="67" t="str">
+      <c r="C761" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="762" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C762" s="67" t="str">
+      <c r="C762" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="763" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C763" s="67" t="str">
+      <c r="C763" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="764" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C764" s="67" t="str">
+      <c r="C764" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="765" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C765" s="67" t="str">
+      <c r="C765" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="766" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C766" s="67" t="str">
+      <c r="C766" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="767" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C767" s="67" t="str">
+      <c r="C767" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="768" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C768" s="67" t="str">
+      <c r="C768" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="769" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C769" s="67" t="str">
+      <c r="C769" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="770" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C770" s="67" t="str">
+      <c r="C770" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="771" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C771" s="67" t="str">
+      <c r="C771" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="772" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C772" s="67" t="str">
+      <c r="C772" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="773" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C773" s="67" t="str">
+      <c r="C773" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="774" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C774" s="67" t="str">
+      <c r="C774" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="775" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C775" s="67" t="str">
+      <c r="C775" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="776" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C776" s="67" t="str">
+      <c r="C776" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="777" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C777" s="67" t="str">
+      <c r="C777" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="778" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C778" s="67" t="str">
+      <c r="C778" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="779" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C779" s="67" t="str">
+      <c r="C779" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="780" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C780" s="67" t="str">
+      <c r="C780" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="781" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C781" s="67" t="str">
+      <c r="C781" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="782" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C782" s="67" t="str">
+      <c r="C782" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="783" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C783" s="67" t="str">
+      <c r="C783" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="784" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C784" s="67" t="str">
+      <c r="C784" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C785" s="67" t="str">
+      <c r="C785" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="C11">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="C13">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="4">
+  <conditionalFormatting sqref="C4">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color theme="5"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{22E165F5-9619-4A9C-98F2-C7CF786D9B02}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
       <formula1>"Despesas, Receita Líquida"</formula1>
     </dataValidation>
@@ -12818,8 +12847,28 @@
     <tablePart r:id="rId3"/>
   </tableParts>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{22E165F5-9619-4A9C-98F2-C7CF786D9B02}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:borderColor theme="5"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C4</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9270E47-B020-4CBF-A3A9-E523B28C14E7}">
           <x14:formula1>
             <xm:f>'Receita Líquida'!$B$2:$M$2</xm:f>
@@ -12897,7 +12946,7 @@
         <v>Dezembro</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="47" t="s">
         <v>26</v>
       </c>
@@ -12950,7 +12999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="47" t="s">
         <v>36</v>
       </c>
@@ -13003,7 +13052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="47" t="s">
         <v>50</v>
       </c>
@@ -13056,7 +13105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>49</v>
       </c>
@@ -13109,7 +13158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="47" t="s">
         <v>46</v>
       </c>
@@ -13162,7 +13211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>37</v>
       </c>
@@ -13215,7 +13264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="47" t="s">
         <v>48</v>
       </c>
@@ -13268,7 +13317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>57</v>
       </c>
@@ -13321,7 +13370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
         <v>51</v>
       </c>
@@ -13374,7 +13423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
         <v>41</v>
       </c>
@@ -13427,7 +13476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
         <v>52</v>
       </c>
@@ -13480,7 +13529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
         <v>53</v>
       </c>
@@ -13652,19 +13701,18 @@
   <sheetPr codeName="Planilha3">
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A2:N20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="52" customWidth="1"/>
-    <col min="2" max="4" width="17.7109375" style="52" customWidth="1"/>
-    <col min="5" max="10" width="17.85546875" style="52" customWidth="1"/>
-    <col min="11" max="13" width="17.7109375" style="52" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" style="52" customWidth="1"/>
+    <col min="2" max="13" width="15" style="52" customWidth="1"/>
     <col min="14" max="14" width="10.5703125" style="52" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.42578125" style="52" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="10.5703125" style="52" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.140625" style="52"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:13" s="49" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="52"/>
       <c r="B2" s="48" t="s">
@@ -13715,8 +13763,8 @@
         <v>Dezembro</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="50" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="60" t="s">
+    <row r="3" spans="1:13" s="50" customFormat="1" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="2">
@@ -13768,8 +13816,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="60" t="s">
+    <row r="4" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="78" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="51">
@@ -13836,48 +13884,48 @@
       <c r="L5" s="46"/>
       <c r="M5" s="46"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="61" t="s">
+    <row r="6" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="62" t="s">
+      <c r="I6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="62" t="s">
+      <c r="J6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="62" t="s">
+      <c r="K6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="62" t="s">
+      <c r="L6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="62" t="s">
+      <c r="M6" s="80" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
         <v>21</v>
       </c>
@@ -13930,7 +13978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>62</v>
       </c>
@@ -13983,7 +14031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>56</v>
       </c>
@@ -14036,7 +14084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>64</v>
       </c>
@@ -14089,7 +14137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>55</v>
       </c>
@@ -14142,7 +14190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>20</v>
       </c>
@@ -14195,7 +14243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>54</v>
       </c>
@@ -14248,7 +14296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
         <v>63</v>
       </c>
@@ -14301,7 +14349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>60</v>
       </c>
@@ -14354,7 +14402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
         <v>61</v>
       </c>
@@ -14407,7 +14455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>11</v>
       </c>
@@ -14460,7 +14508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
         <v>34</v>
       </c>
@@ -14527,7 +14575,7 @@
       <c r="L19" s="50"/>
       <c r="M19" s="50"/>
     </row>
-    <row r="20" spans="1:14" s="50" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" s="50" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="48" t="s">
         <v>2</v>
       </c>
@@ -14621,16 +14669,16 @@
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="63" customWidth="1"/>
-    <col min="2" max="3" width="17.140625" style="63" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="63" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="63" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="63" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="63" customWidth="1"/>
-    <col min="9" max="10" width="17.140625" style="63" customWidth="1"/>
-    <col min="11" max="13" width="9.140625" style="63"/>
-    <col min="14" max="14" width="7.140625" style="63" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="63"/>
+    <col min="1" max="1" width="8.5703125" style="60" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" style="60" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" style="60" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="60" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="60" customWidth="1"/>
+    <col min="9" max="10" width="17.140625" style="60" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="60"/>
+    <col min="14" max="14" width="7.140625" style="60" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="60"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
@@ -14664,188 +14712,188 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="63" t="s">
+      <c r="B5" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5" s="64" t="s">
+      <c r="I5" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="61" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="63" t="str" cm="1">
+      <c r="B6" s="60" t="str" cm="1">
         <f t="array" ref="B6:B17">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="C6" s="64" cm="1">
+      <c r="C6" s="61" cm="1">
         <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,Receita_Líquida='Gráfico Categorias'!C2))</f>
         <v>150</v>
       </c>
-      <c r="I6" s="63" t="str" cm="1">
+      <c r="I6" s="60" t="str" cm="1">
         <f t="array" ref="I6:I17">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="J6" s="64" cm="1">
+      <c r="J6" s="61" cm="1">
         <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,Categorias='Gráfico Categorias'!J2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="63" t="str">
+      <c r="B7" s="60" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="C7" s="64">
-        <v>0</v>
-      </c>
-      <c r="I7" s="63" t="str">
+      <c r="C7" s="61">
+        <v>0</v>
+      </c>
+      <c r="I7" s="60" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="63" t="str">
+      <c r="B8" s="60" t="str">
         <v>Março</v>
       </c>
-      <c r="C8" s="64">
-        <v>0</v>
-      </c>
-      <c r="I8" s="63" t="str">
+      <c r="C8" s="61">
+        <v>0</v>
+      </c>
+      <c r="I8" s="60" t="str">
         <v>Março</v>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="63" t="str">
+      <c r="B9" s="60" t="str">
         <v>Abril</v>
       </c>
-      <c r="C9" s="64">
-        <v>0</v>
-      </c>
-      <c r="I9" s="63" t="str">
+      <c r="C9" s="61">
+        <v>0</v>
+      </c>
+      <c r="I9" s="60" t="str">
         <v>Abril</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="63" t="str">
+      <c r="B10" s="60" t="str">
         <v>Maio</v>
       </c>
-      <c r="C10" s="64">
-        <v>0</v>
-      </c>
-      <c r="I10" s="63" t="str">
+      <c r="C10" s="61">
+        <v>0</v>
+      </c>
+      <c r="I10" s="60" t="str">
         <v>Maio</v>
       </c>
-      <c r="J10" s="64">
+      <c r="J10" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="63" t="str">
+      <c r="B11" s="60" t="str">
         <v>Junho</v>
       </c>
-      <c r="C11" s="64">
-        <v>0</v>
-      </c>
-      <c r="I11" s="63" t="str">
+      <c r="C11" s="61">
+        <v>0</v>
+      </c>
+      <c r="I11" s="60" t="str">
         <v>Junho</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="63" t="str">
+      <c r="B12" s="60" t="str">
         <v>Julho</v>
       </c>
-      <c r="C12" s="64">
-        <v>0</v>
-      </c>
-      <c r="I12" s="63" t="str">
+      <c r="C12" s="61">
+        <v>0</v>
+      </c>
+      <c r="I12" s="60" t="str">
         <v>Julho</v>
       </c>
-      <c r="J12" s="64">
+      <c r="J12" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="63" t="str">
+      <c r="B13" s="60" t="str">
         <v>Agosto</v>
       </c>
-      <c r="C13" s="64">
-        <v>0</v>
-      </c>
-      <c r="I13" s="63" t="str">
+      <c r="C13" s="61">
+        <v>0</v>
+      </c>
+      <c r="I13" s="60" t="str">
         <v>Agosto</v>
       </c>
-      <c r="J13" s="64">
+      <c r="J13" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="63" t="str">
+      <c r="B14" s="60" t="str">
         <v>Setembro</v>
       </c>
-      <c r="C14" s="64">
-        <v>0</v>
-      </c>
-      <c r="I14" s="63" t="str">
+      <c r="C14" s="61">
+        <v>0</v>
+      </c>
+      <c r="I14" s="60" t="str">
         <v>Setembro</v>
       </c>
-      <c r="J14" s="64">
+      <c r="J14" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="63" t="str">
+      <c r="B15" s="60" t="str">
         <v>Outubro</v>
       </c>
-      <c r="C15" s="64">
-        <v>0</v>
-      </c>
-      <c r="I15" s="63" t="str">
+      <c r="C15" s="61">
+        <v>0</v>
+      </c>
+      <c r="I15" s="60" t="str">
         <v>Outubro</v>
       </c>
-      <c r="J15" s="64">
+      <c r="J15" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="63" t="str">
+      <c r="B16" s="60" t="str">
         <v>Novembro</v>
       </c>
-      <c r="C16" s="64">
-        <v>0</v>
-      </c>
-      <c r="I16" s="63" t="str">
+      <c r="C16" s="61">
+        <v>0</v>
+      </c>
+      <c r="I16" s="60" t="str">
         <v>Novembro</v>
       </c>
-      <c r="J16" s="64">
+      <c r="J16" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="63" t="str">
+      <c r="B17" s="60" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="C17" s="64">
-        <v>0</v>
-      </c>
-      <c r="I17" s="63" t="str">
+      <c r="C17" s="61">
+        <v>0</v>
+      </c>
+      <c r="I17" s="60" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="J17" s="64">
+      <c r="J17" s="61">
         <v>0</v>
       </c>
     </row>

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018F92AB-9A83-4FD0-AC3D-82304DCD8C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970FDD21-6B05-4FD2-ADCC-1A788F393972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo &amp; Mov." sheetId="12" r:id="rId1"/>
@@ -747,14 +747,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4044,7 +4044,9 @@
           <c:spPr>
             <a:ln w="34925" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4168,6 +4170,129 @@
         <c:axId val="590393455"/>
         <c:axId val="586649311"/>
       </c:lineChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Saldo Real</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="dash"/>
+            <c:size val="20"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="75000"/>
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000">
+                    <a:alpha val="50000"/>
+                  </a:srgbClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Gráfico Anual'!$I$3:$I$14</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>150</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4E5A-4226-BC63-E6F9D6BC3399}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="590393455"/>
+        <c:axId val="586649311"/>
+      </c:scatterChart>
       <c:catAx>
         <c:axId val="590393455"/>
         <c:scaling>
@@ -8875,15 +9000,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>6338</xdr:colOff>
+      <xdr:colOff>6334</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>27160</xdr:colOff>
+      <xdr:colOff>27156</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>80770</xdr:rowOff>
+      <xdr:rowOff>101851</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9352,7 +9477,7 @@
       <c r="B4" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="83">
+      <c r="C4" s="81">
         <f>HLOOKUP(B2,'Despesas Gerais'!B2:M20,19,FALSE)/HLOOKUP(B2,'Receita Líquida'!B2:M16,15,FALSE)</f>
         <v>0</v>
       </c>
@@ -12804,14 +12929,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="C13">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C4">
     <cfRule type="dataBar" priority="1">
       <dataBar>
@@ -12824,6 +12941,14 @@
           <x14:id>{22E165F5-9619-4A9C-98F2-C7CF786D9B02}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="notEqual">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -14964,15 +15089,15 @@
         <v>42</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="81" t="s">
+      <c r="K2" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="82"/>
+      <c r="L2" s="83"/>
       <c r="M2" s="38"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="82"/>
+      <c r="O2" s="83"/>
       <c r="P2" s="39"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -1,37 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970FDD21-6B05-4FD2-ADCC-1A788F393972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBED0C9-7F04-40EF-8929-A1A6744B0AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Saldo &amp; Mov." sheetId="12" r:id="rId1"/>
-    <sheet name="Receita Líquida" sheetId="8" r:id="rId2"/>
-    <sheet name="Despesas Gerais" sheetId="1" r:id="rId3"/>
-    <sheet name="Gráfico Categorias" sheetId="14" r:id="rId4"/>
-    <sheet name="Gráfico Anual" sheetId="13" r:id="rId5"/>
+    <sheet name="Validação de Dados" sheetId="15" r:id="rId1"/>
+    <sheet name="Saldo &amp; Mov." sheetId="12" r:id="rId2"/>
+    <sheet name="Receita Líquida" sheetId="8" state="hidden" r:id="rId3"/>
+    <sheet name="Despesas Gerais" sheetId="1" state="hidden" r:id="rId4"/>
+    <sheet name="Gráfico Categorias" sheetId="14" r:id="rId5"/>
+    <sheet name="Gráfico Anual" sheetId="13" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="Ativos">'Saldo &amp; Mov.'!$B$9:$B$11</definedName>
-    <definedName name="Categorias">'Despesas Gerais'!$A$7:$A$18</definedName>
+    <definedName name="Ativos">'Validação de Dados'!$B$5:$B$7</definedName>
     <definedName name="Dash">'Gráfico Anual'!$A$1:$P$26</definedName>
-    <definedName name="Despesas">'Despesas Gerais'!$A$7:$A$18</definedName>
-    <definedName name="Investimentos">'Receita Líquida'!$A$13:$A$14</definedName>
-    <definedName name="Item">'Despesas Gerais'!$A$7:$A$18</definedName>
-    <definedName name="Meses">'Receita Líquida'!$B$2:$M$2</definedName>
-    <definedName name="Perdas">'Receita Líquida'!$A$8:$A$12</definedName>
-    <definedName name="Receita_Líquida">'Receita Líquida'!$A$3:$A$14</definedName>
-    <definedName name="Receitas">'Receita Líquida'!$A$3:$A$7</definedName>
-    <definedName name="Transferir">'Saldo &amp; Mov.'!$B$9:$B$11</definedName>
-    <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="2" hidden="1">'Despesas Gerais'!$6:$6,'Despesas Gerais'!#REF!</definedName>
+    <definedName name="Despesas">'Validação de Dados'!$D$5:$D$16</definedName>
+    <definedName name="Investimentos">'Validação de Dados'!$F$5:$F$6</definedName>
+    <definedName name="Meses">'Validação de Dados'!$P$5:$P$16</definedName>
+    <definedName name="Perdas">'Validação de Dados'!$H$5:$H$9</definedName>
+    <definedName name="Receita_Líquida">'Validação de Dados'!$N$5:$N$16</definedName>
+    <definedName name="Receitas">'Validação de Dados'!$J$5:$J$9</definedName>
+    <definedName name="Transferir">'Validação de Dados'!$L$5:$L$7</definedName>
+    <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="3" hidden="1">'Despesas Gerais'!$6:$6,'Despesas Gerais'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -76,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="82">
   <si>
     <t>Mês</t>
   </si>
@@ -278,6 +277,51 @@
   <si>
     <t>Ativos</t>
   </si>
+  <si>
+    <t>Meses</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>Perdas</t>
+  </si>
+  <si>
+    <t>Transferir</t>
+  </si>
+  <si>
+    <t>*Faça alterações nos valores em azul como preferir, porém para adicionar ou remover valores será necessário alterar a planilha onde for preciso.</t>
+  </si>
 </sst>
 </file>
 
@@ -346,7 +390,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -374,6 +418,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,7 +609,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -750,6 +806,8 @@
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -9081,8 +9139,8 @@
       <xdr:rowOff>16384</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>578549</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1391</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>87585</xdr:rowOff>
     </xdr:to>
@@ -9421,6 +9479,259 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319F5F8E-9A60-4A91-9240-674E3E5733FC}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="B2:P16"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="3.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="3.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15" x14ac:dyDescent="0.3">
+      <c r="B4" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="82" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="82" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="83" t="str" cm="1">
+        <f t="array" ref="L5:L7">Ativos</f>
+        <v>Banco 1</v>
+      </c>
+      <c r="N5" s="83" t="str" cm="1">
+        <f t="array" ref="N5:N9">Receitas</f>
+        <v>Salário</v>
+      </c>
+      <c r="P5" s="83" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" s="82" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="83" t="str">
+        <v>Banco 2</v>
+      </c>
+      <c r="N6" s="83" t="str">
+        <v>Vendas</v>
+      </c>
+      <c r="P6" s="83" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="82" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="82" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="83" t="str">
+        <v>Carteira</v>
+      </c>
+      <c r="N7" s="83" t="str">
+        <v>Aluguel</v>
+      </c>
+      <c r="P7" s="83" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D8" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="82" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="83" t="str">
+        <v>Rendimentos</v>
+      </c>
+      <c r="P8" s="83" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D9" s="82" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="82" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" s="83" t="str">
+        <v>Receitas Outros</v>
+      </c>
+      <c r="P9" s="83" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D10" s="82" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" s="83" t="str" cm="1">
+        <f t="array" ref="N10:N14">Perdas</f>
+        <v>Inss</v>
+      </c>
+      <c r="P10" s="83" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D11" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="83" t="str">
+        <v>T. Transporte</v>
+      </c>
+      <c r="P11" s="83" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D12" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12" s="83" t="str">
+        <v>Taxa</v>
+      </c>
+      <c r="P12" s="83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D13" s="82" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13" s="83" t="str">
+        <v>Imposto de Renda</v>
+      </c>
+      <c r="P13" s="83" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D14" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" s="83" t="str">
+        <v>Perdas Outros</v>
+      </c>
+      <c r="P14" s="83" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D15" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15" s="83" t="str" cm="1">
+        <f t="array" ref="N15:N16">Investimentos</f>
+        <v>CDI</v>
+      </c>
+      <c r="P15" s="83" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D16" s="82" t="s">
+        <v>34</v>
+      </c>
+      <c r="N16" s="83" t="str">
+        <v>Tesouro Direto</v>
+      </c>
+      <c r="P16" s="83" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0180935C-8656-4D81-89AE-9797F0D184CE}">
   <sheetPr codeName="Planilha1">
     <tabColor theme="0"/>
@@ -9464,7 +9775,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="74" t="str" cm="1">
-        <f t="array" ref="E3:E14">IF(B3="Despesas",Categorias,IF(B3="Receita Líquida",Receita_Líquida,""))</f>
+        <f t="array" ref="E3:E14">IF(B3="Despesas",Despesas,IF(B3="Receita Líquida",Receita_Líquida,""))</f>
         <v>Alimentação</v>
       </c>
       <c r="F3" s="75" cm="1">
@@ -9546,8 +9857,9 @@
       <c r="H8" s="65"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="27" t="s">
-        <v>30</v>
+      <c r="B9" s="27" t="str" cm="1">
+        <f t="array" ref="B9:B11">Ativos</f>
+        <v>Banco 1</v>
       </c>
       <c r="C9" s="2" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B9,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
@@ -9563,8 +9875,8 @@
     </row>
     <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="64"/>
-      <c r="B10" s="27" t="s">
-        <v>31</v>
+      <c r="B10" s="27" t="str">
+        <v>Banco 2</v>
       </c>
       <c r="C10" s="2" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B10,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
@@ -9580,8 +9892,8 @@
     </row>
     <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64"/>
-      <c r="B11" s="27" t="s">
-        <v>27</v>
+      <c r="B11" s="27" t="str">
+        <v>Carteira</v>
       </c>
       <c r="C11" s="2" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B11,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
@@ -9673,7 +9985,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="33">
-        <v>44927</v>
+        <v>45292</v>
       </c>
       <c r="C17" s="34" t="str">
         <f t="shared" ref="C17:C20" si="0">IF(ISBLANK(B17),"",PROPER(TEXT(B17,"MMMM")))</f>
@@ -12951,7 +13263,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
       <formula1>"Despesas, Receita Líquida"</formula1>
     </dataValidation>
@@ -12963,6 +13275,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F257" xr:uid="{0D51CC9B-6F94-4F85-BAFC-26C786BB30BC}">
       <formula1>Ativos</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{D9270E47-B020-4CBF-A3A9-E523B28C14E7}">
+      <formula1>Meses</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -12992,21 +13307,11 @@
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9270E47-B020-4CBF-A3A9-E523B28C14E7}">
-          <x14:formula1>
-            <xm:f>'Receita Líquida'!$B$2:$M$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
   </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2">
     <tabColor theme="0"/>
@@ -13022,58 +13327,48 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="str">
-        <f>PROPER(TEXT("01/01","MMMM"))</f>
+      <c r="B2" s="48" t="str" cm="1">
+        <f t="array" ref="B2:M2">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
       <c r="C2" s="48" t="str">
-        <f>PROPER(TEXT("01/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
       <c r="D2" s="48" t="str">
-        <f>PROPER(TEXT("01/03","MMMM"))</f>
         <v>Março</v>
       </c>
       <c r="E2" s="48" t="str">
-        <f>PROPER(TEXT("01/04","MMMM"))</f>
         <v>Abril</v>
       </c>
       <c r="F2" s="48" t="str">
-        <f>PROPER(TEXT("01/05","MMMM"))</f>
         <v>Maio</v>
       </c>
       <c r="G2" s="48" t="str">
-        <f>PROPER(TEXT("01/06","MMMM"))</f>
         <v>Junho</v>
       </c>
       <c r="H2" s="48" t="str">
-        <f>PROPER(TEXT("01/07","MMMM"))</f>
         <v>Julho</v>
       </c>
       <c r="I2" s="48" t="str">
-        <f>PROPER(TEXT("01/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
       <c r="J2" s="48" t="str">
-        <f>PROPER(TEXT("01/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
       <c r="K2" s="48" t="str">
-        <f>PROPER(TEXT("01/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
       <c r="L2" s="48" t="str">
-        <f>PROPER(TEXT("01/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
       <c r="M2" s="48" t="str">
-        <f>PROPER(TEXT("01/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
-        <v>26</v>
+      <c r="A3" s="47" t="str" cm="1">
+        <f t="array" ref="A3:A14">Receita_Líquida</f>
+        <v>Salário</v>
       </c>
       <c r="B3" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A3)</f>
@@ -13125,8 +13420,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
-        <v>36</v>
+      <c r="A4" s="47" t="str">
+        <v>Vendas</v>
       </c>
       <c r="B4" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A4)</f>
@@ -13178,8 +13473,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
-        <v>50</v>
+      <c r="A5" s="47" t="str">
+        <v>Aluguel</v>
       </c>
       <c r="B5" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A5)</f>
@@ -13231,8 +13526,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
-        <v>49</v>
+      <c r="A6" s="47" t="str">
+        <v>Rendimentos</v>
       </c>
       <c r="B6" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A6)</f>
@@ -13284,8 +13579,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
-        <v>46</v>
+      <c r="A7" s="47" t="str">
+        <v>Receitas Outros</v>
       </c>
       <c r="B7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A7)</f>
@@ -13337,8 +13632,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
-        <v>37</v>
+      <c r="A8" s="47" t="str">
+        <v>Inss</v>
       </c>
       <c r="B8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A8)</f>
@@ -13390,8 +13685,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
-        <v>48</v>
+      <c r="A9" s="47" t="str">
+        <v>T. Transporte</v>
       </c>
       <c r="B9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A9)</f>
@@ -13443,8 +13738,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="s">
-        <v>57</v>
+      <c r="A10" s="47" t="str">
+        <v>Taxa</v>
       </c>
       <c r="B10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A10)</f>
@@ -13496,8 +13791,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
-        <v>51</v>
+      <c r="A11" s="47" t="str">
+        <v>Imposto de Renda</v>
       </c>
       <c r="B11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A11)</f>
@@ -13549,8 +13844,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="s">
-        <v>41</v>
+      <c r="A12" s="47" t="str">
+        <v>Perdas Outros</v>
       </c>
       <c r="B12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A12)</f>
@@ -13602,8 +13897,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="47" t="s">
-        <v>52</v>
+      <c r="A13" s="47" t="str">
+        <v>CDI</v>
       </c>
       <c r="B13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A13)</f>
@@ -13655,8 +13950,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
-        <v>53</v>
+      <c r="A14" s="47" t="str">
+        <v>Tesouro Direto</v>
       </c>
       <c r="B14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A14)</f>
@@ -13821,7 +14116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Planilha3">
     <tabColor theme="0"/>
@@ -13840,51 +14135,41 @@
     <row r="1" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:13" s="49" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="52"/>
-      <c r="B2" s="48" t="s">
-        <v>47</v>
+      <c r="B2" s="48" t="str" cm="1">
+        <f t="array" ref="B2:M2">TRANSPOSE(Meses)</f>
+        <v>Janeiro</v>
       </c>
       <c r="C2" s="48" t="str">
-        <f>PROPER(TEXT("1/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
       <c r="D2" s="48" t="str">
-        <f>PROPER(TEXT("1/03","MMMM"))</f>
         <v>Março</v>
       </c>
       <c r="E2" s="48" t="str">
-        <f>PROPER(TEXT("1/04","MMMM"))</f>
         <v>Abril</v>
       </c>
       <c r="F2" s="48" t="str">
-        <f>PROPER(TEXT("1/05","MMMM"))</f>
         <v>Maio</v>
       </c>
       <c r="G2" s="48" t="str">
-        <f>PROPER(TEXT("1/06","MMMM"))</f>
         <v>Junho</v>
       </c>
       <c r="H2" s="48" t="str">
-        <f>PROPER(TEXT("1/07","MMMM"))</f>
         <v>Julho</v>
       </c>
       <c r="I2" s="48" t="str">
-        <f>PROPER(TEXT("1/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
       <c r="J2" s="48" t="str">
-        <f>PROPER(TEXT("1/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
       <c r="K2" s="48" t="str">
-        <f>PROPER(TEXT("1/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
       <c r="L2" s="48" t="str">
-        <f>PROPER(TEXT("1/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
       <c r="M2" s="48" t="str">
-        <f>PROPER(TEXT("1/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
     </row>
@@ -14051,8 +14336,9 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
-        <v>21</v>
+      <c r="A7" s="27" t="str" cm="1">
+        <f t="array" ref="A7:A18">Despesas</f>
+        <v>Alimentação</v>
       </c>
       <c r="B7" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
@@ -14104,8 +14390,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
-        <v>62</v>
+      <c r="A8" s="27" t="str">
+        <v>Carro</v>
       </c>
       <c r="B8" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
@@ -14157,8 +14443,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
-        <v>56</v>
+      <c r="A9" s="27" t="str">
+        <v>Condomínio</v>
       </c>
       <c r="B9" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
@@ -14210,8 +14496,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
-        <v>64</v>
+      <c r="A10" s="27" t="str">
+        <v>Curso</v>
       </c>
       <c r="B10" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
@@ -14263,8 +14549,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
-        <v>55</v>
+      <c r="A11" s="27" t="str">
+        <v>Eletrônicos</v>
       </c>
       <c r="B11" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
@@ -14316,8 +14602,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
-        <v>20</v>
+      <c r="A12" s="27" t="str">
+        <v>Farm. e Saúde.</v>
       </c>
       <c r="B12" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
@@ -14369,8 +14655,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
-        <v>54</v>
+      <c r="A13" s="27" t="str">
+        <v>G. Residencial</v>
       </c>
       <c r="B13" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
@@ -14422,8 +14708,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="27" t="s">
-        <v>63</v>
+      <c r="A14" s="27" t="str">
+        <v>Gasolina</v>
       </c>
       <c r="B14" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
@@ -14475,8 +14761,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="27" t="s">
-        <v>60</v>
+      <c r="A15" s="27" t="str">
+        <v>Jogos/ Livros</v>
       </c>
       <c r="B15" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
@@ -14528,8 +14814,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
-        <v>61</v>
+      <c r="A16" s="27" t="str">
+        <v>Rolê/ Entret.</v>
       </c>
       <c r="B16" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
@@ -14581,8 +14867,8 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
-        <v>11</v>
+      <c r="A17" s="27" t="str">
+        <v>Roupas</v>
       </c>
       <c r="B17" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
@@ -14634,8 +14920,8 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="27" t="s">
-        <v>34</v>
+      <c r="A18" s="27" t="str">
+        <v>G. Gerais</v>
       </c>
       <c r="B18" s="2">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
@@ -14789,7 +15075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6BFD9AA-7466-45C1-AB6A-4AD451301F03}">
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
@@ -14852,7 +15138,7 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="60" t="str" cm="1">
-        <f t="array" ref="B6:B17">TRANSPOSE(Meses)</f>
+        <f t="array" ref="B6:B17">Meses</f>
         <v>Janeiro</v>
       </c>
       <c r="C6" s="61" cm="1">
@@ -14860,11 +15146,11 @@
         <v>150</v>
       </c>
       <c r="I6" s="60" t="str" cm="1">
-        <f t="array" ref="I6:I17">TRANSPOSE(Meses)</f>
+        <f t="array" ref="I6:I17">Meses</f>
         <v>Janeiro</v>
       </c>
       <c r="J6" s="61" cm="1">
-        <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,Categorias='Gráfico Categorias'!J2))</f>
+        <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,Despesas='Gráfico Categorias'!J2))</f>
         <v>0</v>
       </c>
     </row>
@@ -15036,7 +15322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD330F4-3FAE-447F-BF05-82EFBCBD7BD0}">
   <sheetPr codeName="Planilha6">
     <tabColor theme="1"/>
@@ -15089,20 +15375,20 @@
         <v>42</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="82" t="s">
+      <c r="K2" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="83"/>
+      <c r="L2" s="85"/>
       <c r="M2" s="38"/>
-      <c r="N2" s="82" t="s">
+      <c r="N2" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="83"/>
+      <c r="O2" s="85"/>
       <c r="P2" s="39"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="str">
-        <f>PROPER(TEXT("01/01","MMMM"))</f>
+      <c r="A3" s="6" t="str" cm="1">
+        <f t="array" ref="A3:A14">Meses</f>
         <v>Janeiro</v>
       </c>
       <c r="B3" s="5"/>
@@ -15138,7 +15424,7 @@
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="43" t="str" cm="1">
-        <f t="array" ref="N3:N14">Categorias</f>
+        <f t="array" ref="N3:N14">Despesas</f>
         <v>Alimentação</v>
       </c>
       <c r="O3" s="44">
@@ -15149,7 +15435,6 @@
     </row>
     <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="str">
-        <f>PROPER(TEXT("01/02","MMMM"))</f>
         <v>Fevereiro</v>
       </c>
       <c r="B4" s="5"/>
@@ -15195,7 +15480,6 @@
     </row>
     <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="str">
-        <f>PROPER(TEXT("01/03","MMMM"))</f>
         <v>Março</v>
       </c>
       <c r="B5" s="5"/>
@@ -15241,7 +15525,6 @@
     </row>
     <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="str">
-        <f>PROPER(TEXT("01/04","MMMM"))</f>
         <v>Abril</v>
       </c>
       <c r="B6" s="5"/>
@@ -15287,7 +15570,6 @@
     </row>
     <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="str">
-        <f>PROPER(TEXT("01/05","MMMM"))</f>
         <v>Maio</v>
       </c>
       <c r="B7" s="5"/>
@@ -15333,7 +15615,6 @@
     </row>
     <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="str">
-        <f>PROPER(TEXT("01/06","MMMM"))</f>
         <v>Junho</v>
       </c>
       <c r="B8" s="5"/>
@@ -15379,7 +15660,6 @@
     </row>
     <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="str">
-        <f>PROPER(TEXT("01/07","MMMM"))</f>
         <v>Julho</v>
       </c>
       <c r="B9" s="5"/>
@@ -15425,7 +15705,6 @@
     </row>
     <row r="10" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="str">
-        <f>PROPER(TEXT("01/08","MMMM"))</f>
         <v>Agosto</v>
       </c>
       <c r="B10" s="5"/>
@@ -15471,7 +15750,6 @@
     </row>
     <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="str">
-        <f>PROPER(TEXT("01/09","MMMM"))</f>
         <v>Setembro</v>
       </c>
       <c r="B11" s="5"/>
@@ -15512,7 +15790,6 @@
     </row>
     <row r="12" spans="1:16" ht="15.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="str">
-        <f>PROPER(TEXT("01/10","MMMM"))</f>
         <v>Outubro</v>
       </c>
       <c r="B12" s="5"/>
@@ -15553,7 +15830,6 @@
     </row>
     <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="str">
-        <f>PROPER(TEXT("01/11","MMMM"))</f>
         <v>Novembro</v>
       </c>
       <c r="B13" s="5"/>
@@ -15594,7 +15870,6 @@
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="str">
-        <f>PROPER(TEXT("01/12","MMMM"))</f>
         <v>Dezembro</v>
       </c>
       <c r="B14" s="5"/>

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBED0C9-7F04-40EF-8929-A1A6744B0AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A54C0F2-A0A5-48C0-82A4-474FECB34395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Validação de Dados" sheetId="15" r:id="rId1"/>
     <sheet name="Saldo &amp; Mov." sheetId="12" r:id="rId2"/>
-    <sheet name="Receita Líquida" sheetId="8" state="hidden" r:id="rId3"/>
-    <sheet name="Despesas Gerais" sheetId="1" state="hidden" r:id="rId4"/>
+    <sheet name="Receita Líquida" sheetId="8" r:id="rId3"/>
+    <sheet name="Despesas Gerais" sheetId="1" r:id="rId4"/>
     <sheet name="Gráfico Categorias" sheetId="14" r:id="rId5"/>
     <sheet name="Gráfico Anual" sheetId="13" r:id="rId6"/>
   </sheets>
@@ -390,7 +390,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -430,6 +430,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -609,7 +615,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -676,9 +682,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -728,26 +731,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -794,25 +787,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9511,218 +9512,218 @@
       </c>
     </row>
     <row r="4" spans="2:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="45" t="s">
+      <c r="J4" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="L4" s="45" t="s">
+      <c r="L4" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="N4" s="45" t="s">
+      <c r="N4" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="45" t="s">
+      <c r="P4" s="44" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="82" t="s">
+      <c r="D5" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="82" t="s">
+      <c r="F5" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="82" t="s">
+      <c r="H5" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="82" t="s">
+      <c r="J5" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="83" t="str" cm="1">
+      <c r="L5" s="75" t="str" cm="1">
         <f t="array" ref="L5:L7">Ativos</f>
         <v>Banco 1</v>
       </c>
-      <c r="N5" s="83" t="str" cm="1">
+      <c r="N5" s="75" t="str" cm="1">
         <f t="array" ref="N5:N9">Receitas</f>
         <v>Salário</v>
       </c>
-      <c r="P5" s="83" t="s">
+      <c r="P5" s="75" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="82" t="s">
+      <c r="B6" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="82" t="s">
+      <c r="H6" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="82" t="s">
+      <c r="J6" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="83" t="str">
+      <c r="L6" s="75" t="str">
         <v>Banco 2</v>
       </c>
-      <c r="N6" s="83" t="str">
+      <c r="N6" s="75" t="str">
         <v>Vendas</v>
       </c>
-      <c r="P6" s="83" t="s">
+      <c r="P6" s="75" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="82" t="s">
+      <c r="B7" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="82" t="s">
+      <c r="D7" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="82" t="s">
+      <c r="H7" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="82" t="s">
+      <c r="J7" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="83" t="str">
+      <c r="L7" s="75" t="str">
         <v>Carteira</v>
       </c>
-      <c r="N7" s="83" t="str">
+      <c r="N7" s="75" t="str">
         <v>Aluguel</v>
       </c>
-      <c r="P7" s="83" t="s">
+      <c r="P7" s="75" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D8" s="82" t="s">
+      <c r="D8" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="82" t="s">
+      <c r="H8" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="82" t="s">
+      <c r="J8" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="N8" s="83" t="str">
+      <c r="N8" s="75" t="str">
         <v>Rendimentos</v>
       </c>
-      <c r="P8" s="83" t="s">
+      <c r="P8" s="75" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D9" s="82" t="s">
+      <c r="D9" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="82" t="s">
+      <c r="H9" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="82" t="s">
+      <c r="J9" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="N9" s="83" t="str">
+      <c r="N9" s="75" t="str">
         <v>Receitas Outros</v>
       </c>
-      <c r="P9" s="83" t="s">
+      <c r="P9" s="75" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D10" s="82" t="s">
+      <c r="D10" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="N10" s="83" t="str" cm="1">
+      <c r="N10" s="75" t="str" cm="1">
         <f t="array" ref="N10:N14">Perdas</f>
         <v>Inss</v>
       </c>
-      <c r="P10" s="83" t="s">
+      <c r="P10" s="75" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D11" s="82" t="s">
+      <c r="D11" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="N11" s="83" t="str">
+      <c r="N11" s="75" t="str">
         <v>T. Transporte</v>
       </c>
-      <c r="P11" s="83" t="s">
+      <c r="P11" s="75" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D12" s="82" t="s">
+      <c r="D12" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="N12" s="83" t="str">
+      <c r="N12" s="75" t="str">
         <v>Taxa</v>
       </c>
-      <c r="P12" s="83" t="s">
+      <c r="P12" s="75" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D13" s="82" t="s">
+      <c r="D13" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="N13" s="83" t="str">
+      <c r="N13" s="75" t="str">
         <v>Imposto de Renda</v>
       </c>
-      <c r="P13" s="83" t="s">
+      <c r="P13" s="75" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D14" s="82" t="s">
+      <c r="D14" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="N14" s="83" t="str">
+      <c r="N14" s="75" t="str">
         <v>Perdas Outros</v>
       </c>
-      <c r="P14" s="83" t="s">
+      <c r="P14" s="75" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D15" s="82" t="s">
+      <c r="D15" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="83" t="str" cm="1">
+      <c r="N15" s="75" t="str" cm="1">
         <f t="array" ref="N15:N16">Investimentos</f>
         <v>CDI</v>
       </c>
-      <c r="P15" s="83" t="s">
+      <c r="P15" s="75" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D16" s="82" t="s">
+      <c r="D16" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="83" t="str">
+      <c r="N16" s="75" t="str">
         <v>Tesouro Direto</v>
       </c>
-      <c r="P16" s="83" t="s">
+      <c r="P16" s="75" t="s">
         <v>78</v>
       </c>
     </row>
@@ -9739,66 +9740,66 @@
   <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="65" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="63" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="64" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="64" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" style="65" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="68" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="67" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="65" customWidth="1"/>
-    <col min="10" max="10" width="10" style="65" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="65"/>
+    <col min="1" max="1" width="14.28515625" style="60" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="58" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="59" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="59" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="60" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="63" customWidth="1"/>
+    <col min="8" max="8" width="34.28515625" style="62" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="60" customWidth="1"/>
+    <col min="10" max="10" width="10" style="60" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="60"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="70" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="26">
         <f>IF(B3="Despesas",HLOOKUP(B2,'Despesas Gerais'!B2:M20,19,FALSE),IF(B3="Receita Líquida",HLOOKUP(B2,'Receita Líquida'!B2:M16,15,FALSE),""))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="74" t="str" cm="1">
+      <c r="E3" s="69" t="str" cm="1">
         <f t="array" ref="E3:E14">IF(B3="Despesas",Despesas,IF(B3="Receita Líquida",Receita_Líquida,""))</f>
         <v>Alimentação</v>
       </c>
-      <c r="F3" s="75" cm="1">
+      <c r="F3" s="70" cm="1">
         <f t="array" ref="F3:F14">IF(B3="Despesas",_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,'Despesas Gerais'!B2:M2=B2),IF(B3="Receita Líquida",_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,'Receita Líquida'!B2:M2=B2),""))</f>
         <v>0</v>
       </c>
-      <c r="H3" s="65"/>
+      <c r="H3" s="60"/>
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="73">
         <f>HLOOKUP(B2,'Despesas Gerais'!B2:M20,19,FALSE)/HLOOKUP(B2,'Receita Líquida'!B2:M16,15,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="74" t="str">
+      <c r="E4" s="69" t="str">
         <v>Carro</v>
       </c>
-      <c r="F4" s="75">
-        <v>0</v>
-      </c>
-      <c r="H4" s="65"/>
+      <c r="F4" s="70">
+        <v>0</v>
+      </c>
+      <c r="H4" s="60"/>
     </row>
     <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="27" t="s">
@@ -9808,13 +9809,13 @@
         <f>VLOOKUP(B2,'Gráfico Anual'!A3:I14,9,FALSE)</f>
         <v>150</v>
       </c>
-      <c r="E5" s="74" t="str">
+      <c r="E5" s="69" t="str">
         <v>Condomínio</v>
       </c>
-      <c r="F5" s="75">
-        <v>0</v>
-      </c>
-      <c r="H5" s="65"/>
+      <c r="F5" s="70">
+        <v>0</v>
+      </c>
+      <c r="H5" s="60"/>
     </row>
     <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="27" t="s">
@@ -9824,37 +9825,37 @@
         <f>'Gráfico Anual'!I15</f>
         <v>150</v>
       </c>
-      <c r="E6" s="74" t="str">
+      <c r="E6" s="69" t="str">
         <v>Curso</v>
       </c>
-      <c r="F6" s="75">
-        <v>0</v>
-      </c>
-      <c r="H6" s="65"/>
+      <c r="F6" s="70">
+        <v>0</v>
+      </c>
+      <c r="H6" s="60"/>
     </row>
     <row r="7" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="74" t="str">
+      <c r="E7" s="69" t="str">
         <v>Eletrônicos</v>
       </c>
-      <c r="F7" s="75">
-        <v>0</v>
-      </c>
-      <c r="H7" s="65"/>
+      <c r="F7" s="70">
+        <v>0</v>
+      </c>
+      <c r="H7" s="60"/>
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="74" t="str">
+      <c r="E8" s="69" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="F8" s="75">
-        <v>0</v>
-      </c>
-      <c r="H8" s="65"/>
+      <c r="F8" s="70">
+        <v>0</v>
+      </c>
+      <c r="H8" s="60"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="str" cm="1">
@@ -9865,16 +9866,16 @@
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B9,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>150</v>
       </c>
-      <c r="E9" s="74" t="str">
+      <c r="E9" s="69" t="str">
         <v>G. Residencial</v>
       </c>
-      <c r="F9" s="75">
-        <v>0</v>
-      </c>
-      <c r="H9" s="65"/>
+      <c r="F9" s="70">
+        <v>0</v>
+      </c>
+      <c r="H9" s="60"/>
     </row>
     <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="64"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="27" t="str">
         <v>Banco 2</v>
       </c>
@@ -9882,16 +9883,16 @@
         <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B10,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="74" t="str">
+      <c r="E10" s="69" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="F10" s="75">
-        <v>0</v>
-      </c>
-      <c r="H10" s="65"/>
+      <c r="F10" s="70">
+        <v>0</v>
+      </c>
+      <c r="H10" s="60"/>
     </row>
     <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
+      <c r="A11" s="59"/>
       <c r="B11" s="27" t="str">
         <v>Carteira</v>
       </c>
@@ -9899,16 +9900,16 @@
         <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B11,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="74" t="str">
+      <c r="E11" s="69" t="str">
         <v>Jogos/ Livros</v>
       </c>
-      <c r="F11" s="75">
-        <v>0</v>
-      </c>
-      <c r="H11" s="65"/>
+      <c r="F11" s="70">
+        <v>0</v>
+      </c>
+      <c r="H11" s="60"/>
     </row>
     <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="64"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="27" t="s">
         <v>44</v>
       </c>
@@ -9916,16 +9917,16 @@
         <f ca="1">SUM(C9:C11)</f>
         <v>150</v>
       </c>
-      <c r="E12" s="74" t="str">
+      <c r="E12" s="69" t="str">
         <v>Rolê/ Entret.</v>
       </c>
-      <c r="F12" s="75">
-        <v>0</v>
-      </c>
-      <c r="H12" s="65"/>
+      <c r="F12" s="70">
+        <v>0</v>
+      </c>
+      <c r="H12" s="60"/>
     </row>
     <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64"/>
+      <c r="A13" s="59"/>
       <c r="B13" s="27" t="s">
         <v>45</v>
       </c>
@@ -9933,3308 +9934,3308 @@
         <f ca="1">ROUND(C5-C12,2)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="74" t="str">
+      <c r="E13" s="69" t="str">
         <v>Roupas</v>
       </c>
-      <c r="F13" s="75">
-        <v>0</v>
-      </c>
-      <c r="H13" s="65"/>
+      <c r="F13" s="70">
+        <v>0</v>
+      </c>
+      <c r="H13" s="60"/>
     </row>
     <row r="14" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="64"/>
-      <c r="E14" s="74" t="str">
+      <c r="A14" s="59"/>
+      <c r="E14" s="69" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="F14" s="76">
-        <v>0</v>
-      </c>
-      <c r="H14" s="65"/>
+      <c r="F14" s="71">
+        <v>0</v>
+      </c>
+      <c r="H14" s="60"/>
     </row>
     <row r="15" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="71"/>
-      <c r="B15" s="65"/>
-      <c r="H15" s="65"/>
+      <c r="A15" s="66"/>
+      <c r="B15" s="60"/>
+      <c r="H15" s="60"/>
     </row>
     <row r="16" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="73">
+      <c r="A16" s="68">
         <f>SUBTOTAL(2,Tabela1[Data])</f>
         <v>1</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="30" t="s">
+      <c r="C16" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="33">
+      <c r="B17" s="32">
         <v>45292</v>
       </c>
-      <c r="C17" s="34" t="str">
+      <c r="C17" s="33" t="str">
         <f t="shared" ref="C17:C20" si="0">IF(ISBLANK(B17),"",PROPER(TEXT(B17,"MMMM")))</f>
         <v>Janeiro</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="35">
         <v>150</v>
       </c>
-      <c r="H17" s="37"/>
+      <c r="H17" s="36"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="33"/>
-      <c r="C18" s="34" t="str">
+      <c r="B18" s="32"/>
+      <c r="C18" s="33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="33"/>
-      <c r="C19" s="34" t="str">
+      <c r="B19" s="32"/>
+      <c r="C19" s="33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="36"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="33"/>
-      <c r="C20" s="34" t="str">
+      <c r="B20" s="32"/>
+      <c r="C20" s="33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G23" s="66"/>
+      <c r="G23" s="61"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G25" s="66"/>
+      <c r="G25" s="61"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G26" s="66"/>
+      <c r="G26" s="61"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G27" s="66"/>
+      <c r="G27" s="61"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G28" s="66"/>
+      <c r="G28" s="61"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I38" s="65" t="s">
+      <c r="I38" s="60" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G137" s="66"/>
+      <c r="G137" s="61"/>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G139" s="66"/>
+      <c r="G139" s="61"/>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G140" s="66"/>
+      <c r="G140" s="61"/>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G141" s="66"/>
+      <c r="G141" s="61"/>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G142" s="66"/>
+      <c r="G142" s="61"/>
     </row>
     <row r="248" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C248" s="64" t="str">
+      <c r="C248" s="59" t="str">
         <f>IF(ISBLANK(B248),"",PROPER(TEXT(B248,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="249" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C249" s="64" t="str">
+      <c r="C249" s="59" t="str">
         <f>IF(ISBLANK(B249),"",PROPER(TEXT(B249,"MMMM")))</f>
         <v/>
       </c>
-      <c r="G249" s="69"/>
+      <c r="G249" s="64"/>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C258" s="64" t="str">
+      <c r="C258" s="59" t="str">
         <f>IF(ISBLANK(B258),"",PROPER(TEXT(B258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="D258" s="64" t="str">
+      <c r="D258" s="59" t="str">
         <f t="shared" ref="D258:G258" si="1">IF(ISBLANK(C258),"",PROPER(TEXT(C258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="E258" s="64" t="str">
+      <c r="E258" s="59" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F258" s="64" t="str">
+      <c r="F258" s="59" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G258" s="64" t="str">
+      <c r="G258" s="59" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C267" s="64" t="str">
+      <c r="C267" s="59" t="str">
         <f t="shared" ref="C267" si="2">IF(ISBLANK(B267),"",PROPER(TEXT(B267,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C268" s="64" t="str">
+      <c r="C268" s="59" t="str">
         <f t="shared" ref="C268:C282" si="3">IF(ISBLANK(B268),"",PROPER(TEXT(B268,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C269" s="64" t="str">
+      <c r="C269" s="59" t="str">
         <f t="shared" ref="C269:C279" si="4">IF(ISBLANK(B269),"",PROPER(TEXT(B269,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C270" s="64" t="str">
+      <c r="C270" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C271" s="64" t="str">
+      <c r="C271" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C272" s="64" t="str">
+      <c r="C272" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C273" s="64" t="str">
+      <c r="C273" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C274" s="64" t="str">
+      <c r="C274" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C275" s="64" t="str">
+      <c r="C275" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C276" s="64" t="str">
+      <c r="C276" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C277" s="64" t="str">
+      <c r="C277" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C278" s="64" t="str">
+      <c r="C278" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C279" s="64" t="str">
+      <c r="C279" s="59" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C280" s="64" t="str">
+      <c r="C280" s="59" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C281" s="64" t="str">
+      <c r="C281" s="59" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C282" s="64" t="str">
+      <c r="C282" s="59" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G282" s="66"/>
-      <c r="H282" s="70"/>
+      <c r="G282" s="61"/>
+      <c r="H282" s="65"/>
     </row>
     <row r="283" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B283" s="65"/>
-      <c r="C283" s="65"/>
-      <c r="D283" s="65"/>
-      <c r="E283" s="71"/>
-      <c r="F283" s="71"/>
-      <c r="G283" s="66"/>
-      <c r="H283" s="70"/>
+      <c r="B283" s="60"/>
+      <c r="C283" s="60"/>
+      <c r="D283" s="60"/>
+      <c r="E283" s="66"/>
+      <c r="F283" s="66"/>
+      <c r="G283" s="61"/>
+      <c r="H283" s="65"/>
     </row>
     <row r="284" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B284" s="65"/>
-      <c r="C284" s="65"/>
-      <c r="D284" s="65"/>
-      <c r="E284" s="71"/>
-      <c r="F284" s="71"/>
-      <c r="G284" s="66"/>
-      <c r="H284" s="70"/>
+      <c r="B284" s="60"/>
+      <c r="C284" s="60"/>
+      <c r="D284" s="60"/>
+      <c r="E284" s="66"/>
+      <c r="F284" s="66"/>
+      <c r="G284" s="61"/>
+      <c r="H284" s="65"/>
     </row>
     <row r="285" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B285" s="65"/>
-      <c r="C285" s="65"/>
-      <c r="D285" s="65"/>
-      <c r="E285" s="71"/>
-      <c r="F285" s="71"/>
-      <c r="G285" s="66"/>
-      <c r="H285" s="70"/>
+      <c r="B285" s="60"/>
+      <c r="C285" s="60"/>
+      <c r="D285" s="60"/>
+      <c r="E285" s="66"/>
+      <c r="F285" s="66"/>
+      <c r="G285" s="61"/>
+      <c r="H285" s="65"/>
     </row>
     <row r="286" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B286" s="65"/>
-      <c r="C286" s="72"/>
-      <c r="D286" s="72"/>
-      <c r="E286" s="71"/>
-      <c r="F286" s="71"/>
-      <c r="G286" s="66"/>
-      <c r="H286" s="70"/>
+      <c r="B286" s="60"/>
+      <c r="C286" s="67"/>
+      <c r="D286" s="67"/>
+      <c r="E286" s="66"/>
+      <c r="F286" s="66"/>
+      <c r="G286" s="61"/>
+      <c r="H286" s="65"/>
     </row>
     <row r="287" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B287" s="65"/>
-      <c r="C287" s="65"/>
-      <c r="D287" s="65"/>
-      <c r="G287" s="65"/>
+      <c r="B287" s="60"/>
+      <c r="C287" s="60"/>
+      <c r="D287" s="60"/>
+      <c r="G287" s="60"/>
     </row>
     <row r="288" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B288" s="65"/>
-      <c r="C288" s="65"/>
-      <c r="D288" s="65"/>
-      <c r="G288" s="65"/>
+      <c r="B288" s="60"/>
+      <c r="C288" s="60"/>
+      <c r="D288" s="60"/>
+      <c r="G288" s="60"/>
     </row>
     <row r="289" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B289" s="65"/>
-      <c r="C289" s="65"/>
-      <c r="D289" s="65"/>
-      <c r="G289" s="65"/>
+      <c r="B289" s="60"/>
+      <c r="C289" s="60"/>
+      <c r="D289" s="60"/>
+      <c r="G289" s="60"/>
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B290" s="65"/>
-      <c r="C290" s="65"/>
-      <c r="D290" s="65"/>
-      <c r="G290" s="65"/>
+      <c r="B290" s="60"/>
+      <c r="C290" s="60"/>
+      <c r="D290" s="60"/>
+      <c r="G290" s="60"/>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B291" s="65"/>
-      <c r="C291" s="65"/>
-      <c r="D291" s="65"/>
-      <c r="G291" s="65"/>
+      <c r="B291" s="60"/>
+      <c r="C291" s="60"/>
+      <c r="D291" s="60"/>
+      <c r="G291" s="60"/>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B292" s="65"/>
-      <c r="C292" s="65"/>
-      <c r="D292" s="65"/>
-      <c r="G292" s="65"/>
+      <c r="B292" s="60"/>
+      <c r="C292" s="60"/>
+      <c r="D292" s="60"/>
+      <c r="G292" s="60"/>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B293" s="65"/>
-      <c r="C293" s="65"/>
-      <c r="D293" s="65"/>
-      <c r="G293" s="65"/>
+      <c r="B293" s="60"/>
+      <c r="C293" s="60"/>
+      <c r="D293" s="60"/>
+      <c r="G293" s="60"/>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C294" s="64" t="str">
+      <c r="C294" s="59" t="str">
         <f t="shared" ref="C294:C352" si="5">IF(ISBLANK(B294),"",PROPER(TEXT(B294,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C295" s="64" t="str">
+      <c r="C295" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C296" s="64" t="str">
+      <c r="C296" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C297" s="64" t="str">
+      <c r="C297" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C298" s="64" t="str">
+      <c r="C298" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C299" s="64" t="str">
+      <c r="C299" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C300" s="64" t="str">
+      <c r="C300" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C301" s="64" t="str">
+      <c r="C301" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C302" s="64" t="str">
+      <c r="C302" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C303" s="64" t="str">
+      <c r="C303" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C304" s="64" t="str">
+      <c r="C304" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C305" s="64" t="str">
+      <c r="C305" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C306" s="64" t="str">
+      <c r="C306" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C307" s="64" t="str">
+      <c r="C307" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" s="64" t="str">
+      <c r="C308" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C309" s="64" t="str">
+      <c r="C309" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C310" s="64" t="str">
+      <c r="C310" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C311" s="64" t="str">
+      <c r="C311" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C312" s="64" t="str">
+      <c r="C312" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C313" s="64" t="str">
+      <c r="C313" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C314" s="64" t="str">
+      <c r="C314" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C315" s="64" t="str">
+      <c r="C315" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C316" s="64" t="str">
+      <c r="C316" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C317" s="64" t="str">
+      <c r="C317" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C318" s="64" t="str">
+      <c r="C318" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C319" s="64" t="str">
+      <c r="C319" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C320" s="64" t="str">
+      <c r="C320" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C321" s="64" t="str">
+      <c r="C321" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C322" s="64" t="str">
+      <c r="C322" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C323" s="64" t="str">
+      <c r="C323" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C324" s="64" t="str">
+      <c r="C324" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C325" s="64" t="str">
+      <c r="C325" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C326" s="64" t="str">
+      <c r="C326" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C327" s="64" t="str">
+      <c r="C327" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C328" s="64" t="str">
+      <c r="C328" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C329" s="64" t="str">
+      <c r="C329" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C330" s="64" t="str">
+      <c r="C330" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C331" s="64" t="str">
+      <c r="C331" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C332" s="64" t="str">
+      <c r="C332" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C333" s="64" t="str">
+      <c r="C333" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C334" s="64" t="str">
+      <c r="C334" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C335" s="64" t="str">
+      <c r="C335" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C336" s="64" t="str">
+      <c r="C336" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C337" s="64" t="str">
+      <c r="C337" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C338" s="64" t="str">
+      <c r="C338" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C339" s="64" t="str">
+      <c r="C339" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C340" s="64" t="str">
+      <c r="C340" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C341" s="64" t="str">
+      <c r="C341" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C342" s="64" t="str">
+      <c r="C342" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C343" s="64" t="str">
+      <c r="C343" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C344" s="64" t="str">
+      <c r="C344" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C345" s="64" t="str">
+      <c r="C345" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C346" s="64" t="str">
+      <c r="C346" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C347" s="64" t="str">
+      <c r="C347" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C348" s="64" t="str">
+      <c r="C348" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C349" s="64" t="str">
+      <c r="C349" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C350" s="64" t="str">
+      <c r="C350" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C351" s="64" t="str">
+      <c r="C351" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C352" s="64" t="str">
+      <c r="C352" s="59" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C353" s="64" t="str">
+      <c r="C353" s="59" t="str">
         <f t="shared" ref="C353:C416" si="6">IF(ISBLANK(B353),"",PROPER(TEXT(B353,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C354" s="64" t="str">
+      <c r="C354" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C355" s="64" t="str">
+      <c r="C355" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C356" s="64" t="str">
+      <c r="C356" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C357" s="64" t="str">
+      <c r="C357" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C358" s="64" t="str">
+      <c r="C358" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C359" s="64" t="str">
+      <c r="C359" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C360" s="64" t="str">
+      <c r="C360" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C361" s="64" t="str">
+      <c r="C361" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C362" s="64" t="str">
+      <c r="C362" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C363" s="64" t="str">
+      <c r="C363" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C364" s="64" t="str">
+      <c r="C364" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C365" s="64" t="str">
+      <c r="C365" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C366" s="64" t="str">
+      <c r="C366" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C367" s="64" t="str">
+      <c r="C367" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C368" s="64" t="str">
+      <c r="C368" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C369" s="64" t="str">
+      <c r="C369" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C370" s="64" t="str">
+      <c r="C370" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C371" s="64" t="str">
+      <c r="C371" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C372" s="64" t="str">
+      <c r="C372" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C373" s="64" t="str">
+      <c r="C373" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C374" s="64" t="str">
+      <c r="C374" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C375" s="64" t="str">
+      <c r="C375" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C376" s="64" t="str">
+      <c r="C376" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C377" s="64" t="str">
+      <c r="C377" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C378" s="64" t="str">
+      <c r="C378" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C379" s="64" t="str">
+      <c r="C379" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C380" s="64" t="str">
+      <c r="C380" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C381" s="64" t="str">
+      <c r="C381" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C382" s="64" t="str">
+      <c r="C382" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C383" s="64" t="str">
+      <c r="C383" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C384" s="64" t="str">
+      <c r="C384" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C385" s="64" t="str">
+      <c r="C385" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C386" s="64" t="str">
+      <c r="C386" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C387" s="64" t="str">
+      <c r="C387" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C388" s="64" t="str">
+      <c r="C388" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C389" s="64" t="str">
+      <c r="C389" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="64" t="str">
+      <c r="C390" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C391" s="64" t="str">
+      <c r="C391" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C392" s="64" t="str">
+      <c r="C392" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C393" s="64" t="str">
+      <c r="C393" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C394" s="64" t="str">
+      <c r="C394" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C395" s="64" t="str">
+      <c r="C395" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C396" s="64" t="str">
+      <c r="C396" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C397" s="64" t="str">
+      <c r="C397" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C398" s="64" t="str">
+      <c r="C398" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C399" s="64" t="str">
+      <c r="C399" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C400" s="64" t="str">
+      <c r="C400" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C401" s="64" t="str">
+      <c r="C401" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C402" s="64" t="str">
+      <c r="C402" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C403" s="64" t="str">
+      <c r="C403" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C404" s="64" t="str">
+      <c r="C404" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C405" s="64" t="str">
+      <c r="C405" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C406" s="64" t="str">
+      <c r="C406" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C407" s="64" t="str">
+      <c r="C407" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C408" s="64" t="str">
+      <c r="C408" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C409" s="64" t="str">
+      <c r="C409" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C410" s="64" t="str">
+      <c r="C410" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C411" s="64" t="str">
+      <c r="C411" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C412" s="64" t="str">
+      <c r="C412" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C413" s="64" t="str">
+      <c r="C413" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C414" s="64" t="str">
+      <c r="C414" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C415" s="64" t="str">
+      <c r="C415" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C416" s="64" t="str">
+      <c r="C416" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="64" t="str">
+      <c r="C417" s="59" t="str">
         <f t="shared" ref="C417:C480" si="7">IF(ISBLANK(B417),"",PROPER(TEXT(B417,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C418" s="64" t="str">
+      <c r="C418" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C419" s="64" t="str">
+      <c r="C419" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="64" t="str">
+      <c r="C420" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C421" s="64" t="str">
+      <c r="C421" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C422" s="64" t="str">
+      <c r="C422" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C423" s="64" t="str">
+      <c r="C423" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C424" s="64" t="str">
+      <c r="C424" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C425" s="64" t="str">
+      <c r="C425" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C426" s="64" t="str">
+      <c r="C426" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C427" s="64" t="str">
+      <c r="C427" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C428" s="64" t="str">
+      <c r="C428" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C429" s="64" t="str">
+      <c r="C429" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C430" s="64" t="str">
+      <c r="C430" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C431" s="64" t="str">
+      <c r="C431" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C432" s="64" t="str">
+      <c r="C432" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="64" t="str">
+      <c r="C433" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C434" s="64" t="str">
+      <c r="C434" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C435" s="64" t="str">
+      <c r="C435" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="64" t="str">
+      <c r="C436" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C437" s="64" t="str">
+      <c r="C437" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C438" s="64" t="str">
+      <c r="C438" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C439" s="64" t="str">
+      <c r="C439" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C440" s="64" t="str">
+      <c r="C440" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C441" s="64" t="str">
+      <c r="C441" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C442" s="64" t="str">
+      <c r="C442" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C443" s="64" t="str">
+      <c r="C443" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C444" s="64" t="str">
+      <c r="C444" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C445" s="64" t="str">
+      <c r="C445" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C446" s="64" t="str">
+      <c r="C446" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C447" s="64" t="str">
+      <c r="C447" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C448" s="64" t="str">
+      <c r="C448" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C449" s="64" t="str">
+      <c r="C449" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C450" s="64" t="str">
+      <c r="C450" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C451" s="64" t="str">
+      <c r="C451" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C452" s="64" t="str">
+      <c r="C452" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C453" s="64" t="str">
+      <c r="C453" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C454" s="64" t="str">
+      <c r="C454" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C455" s="64" t="str">
+      <c r="C455" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C456" s="64" t="str">
+      <c r="C456" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C457" s="64" t="str">
+      <c r="C457" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C458" s="64" t="str">
+      <c r="C458" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C459" s="64" t="str">
+      <c r="C459" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C460" s="64" t="str">
+      <c r="C460" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C461" s="64" t="str">
+      <c r="C461" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C462" s="64" t="str">
+      <c r="C462" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C463" s="64" t="str">
+      <c r="C463" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C464" s="64" t="str">
+      <c r="C464" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" s="64" t="str">
+      <c r="C465" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C466" s="64" t="str">
+      <c r="C466" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C467" s="64" t="str">
+      <c r="C467" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C468" s="64" t="str">
+      <c r="C468" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C469" s="64" t="str">
+      <c r="C469" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C470" s="64" t="str">
+      <c r="C470" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C471" s="64" t="str">
+      <c r="C471" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C472" s="64" t="str">
+      <c r="C472" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C473" s="64" t="str">
+      <c r="C473" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" s="64" t="str">
+      <c r="C474" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" s="64" t="str">
+      <c r="C475" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" s="64" t="str">
+      <c r="C476" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C477" s="64" t="str">
+      <c r="C477" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C478" s="64" t="str">
+      <c r="C478" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C479" s="64" t="str">
+      <c r="C479" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C480" s="64" t="str">
+      <c r="C480" s="59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C481" s="64" t="str">
+      <c r="C481" s="59" t="str">
         <f t="shared" ref="C481:C544" si="8">IF(ISBLANK(B481),"",PROPER(TEXT(B481,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="482" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C482" s="64" t="str">
+      <c r="C482" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C483" s="64" t="str">
+      <c r="C483" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C484" s="64" t="str">
+      <c r="C484" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C485" s="64" t="str">
+      <c r="C485" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C486" s="64" t="str">
+      <c r="C486" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="64" t="str">
+      <c r="C487" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" s="64" t="str">
+      <c r="C488" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" s="64" t="str">
+      <c r="C489" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C490" s="64" t="str">
+      <c r="C490" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C491" s="64" t="str">
+      <c r="C491" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C492" s="64" t="str">
+      <c r="C492" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C493" s="64" t="str">
+      <c r="C493" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C494" s="64" t="str">
+      <c r="C494" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C495" s="64" t="str">
+      <c r="C495" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C496" s="64" t="str">
+      <c r="C496" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C497" s="64" t="str">
+      <c r="C497" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="64" t="str">
+      <c r="C498" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" s="64" t="str">
+      <c r="C499" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" s="64" t="str">
+      <c r="C500" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="64" t="str">
+      <c r="C501" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C502" s="64" t="str">
+      <c r="C502" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C503" s="64" t="str">
+      <c r="C503" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C504" s="64" t="str">
+      <c r="C504" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C505" s="64" t="str">
+      <c r="C505" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C506" s="64" t="str">
+      <c r="C506" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C507" s="64" t="str">
+      <c r="C507" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C508" s="64" t="str">
+      <c r="C508" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C509" s="64" t="str">
+      <c r="C509" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C510" s="64" t="str">
+      <c r="C510" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C511" s="64" t="str">
+      <c r="C511" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C512" s="64" t="str">
+      <c r="C512" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C513" s="64" t="str">
+      <c r="C513" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" s="64" t="str">
+      <c r="C514" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" s="64" t="str">
+      <c r="C515" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" s="64" t="str">
+      <c r="C516" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C517" s="64" t="str">
+      <c r="C517" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C518" s="64" t="str">
+      <c r="C518" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C519" s="64" t="str">
+      <c r="C519" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C520" s="64" t="str">
+      <c r="C520" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C521" s="64" t="str">
+      <c r="C521" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" s="64" t="str">
+      <c r="C522" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" s="64" t="str">
+      <c r="C523" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" s="64" t="str">
+      <c r="C524" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C525" s="64" t="str">
+      <c r="C525" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C526" s="64" t="str">
+      <c r="C526" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C527" s="64" t="str">
+      <c r="C527" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C528" s="64" t="str">
+      <c r="C528" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C529" s="64" t="str">
+      <c r="C529" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" s="64" t="str">
+      <c r="C530" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" s="64" t="str">
+      <c r="C531" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" s="64" t="str">
+      <c r="C532" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C533" s="64" t="str">
+      <c r="C533" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C534" s="64" t="str">
+      <c r="C534" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C535" s="64" t="str">
+      <c r="C535" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C536" s="64" t="str">
+      <c r="C536" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C537" s="64" t="str">
+      <c r="C537" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C538" s="64" t="str">
+      <c r="C538" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C539" s="64" t="str">
+      <c r="C539" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C540" s="64" t="str">
+      <c r="C540" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C541" s="64" t="str">
+      <c r="C541" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C542" s="64" t="str">
+      <c r="C542" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C543" s="64" t="str">
+      <c r="C543" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C544" s="64" t="str">
+      <c r="C544" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C545" s="64" t="str">
+      <c r="C545" s="59" t="str">
         <f t="shared" ref="C545:C608" si="9">IF(ISBLANK(B545),"",PROPER(TEXT(B545,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="546" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C546" s="64" t="str">
+      <c r="C546" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C547" s="64" t="str">
+      <c r="C547" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C548" s="64" t="str">
+      <c r="C548" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C549" s="64" t="str">
+      <c r="C549" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C550" s="64" t="str">
+      <c r="C550" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C551" s="64" t="str">
+      <c r="C551" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C552" s="64" t="str">
+      <c r="C552" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C553" s="64" t="str">
+      <c r="C553" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C554" s="64" t="str">
+      <c r="C554" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C555" s="64" t="str">
+      <c r="C555" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C556" s="64" t="str">
+      <c r="C556" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C557" s="64" t="str">
+      <c r="C557" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C558" s="64" t="str">
+      <c r="C558" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C559" s="64" t="str">
+      <c r="C559" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C560" s="64" t="str">
+      <c r="C560" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C561" s="64" t="str">
+      <c r="C561" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C562" s="64" t="str">
+      <c r="C562" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C563" s="64" t="str">
+      <c r="C563" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C564" s="64" t="str">
+      <c r="C564" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C565" s="64" t="str">
+      <c r="C565" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C566" s="64" t="str">
+      <c r="C566" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C567" s="64" t="str">
+      <c r="C567" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C568" s="64" t="str">
+      <c r="C568" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C569" s="64" t="str">
+      <c r="C569" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C570" s="64" t="str">
+      <c r="C570" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C571" s="64" t="str">
+      <c r="C571" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C572" s="64" t="str">
+      <c r="C572" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C573" s="64" t="str">
+      <c r="C573" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C574" s="64" t="str">
+      <c r="C574" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C575" s="64" t="str">
+      <c r="C575" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C576" s="64" t="str">
+      <c r="C576" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C577" s="64" t="str">
+      <c r="C577" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C578" s="64" t="str">
+      <c r="C578" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C579" s="64" t="str">
+      <c r="C579" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C580" s="64" t="str">
+      <c r="C580" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C581" s="64" t="str">
+      <c r="C581" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C582" s="64" t="str">
+      <c r="C582" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C583" s="64" t="str">
+      <c r="C583" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C584" s="64" t="str">
+      <c r="C584" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C585" s="64" t="str">
+      <c r="C585" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C586" s="64" t="str">
+      <c r="C586" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C587" s="64" t="str">
+      <c r="C587" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C588" s="64" t="str">
+      <c r="C588" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C589" s="64" t="str">
+      <c r="C589" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C590" s="64" t="str">
+      <c r="C590" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C591" s="64" t="str">
+      <c r="C591" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C592" s="64" t="str">
+      <c r="C592" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C593" s="64" t="str">
+      <c r="C593" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C594" s="64" t="str">
+      <c r="C594" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C595" s="64" t="str">
+      <c r="C595" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C596" s="64" t="str">
+      <c r="C596" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C597" s="64" t="str">
+      <c r="C597" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C598" s="64" t="str">
+      <c r="C598" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C599" s="64" t="str">
+      <c r="C599" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C600" s="64" t="str">
+      <c r="C600" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C601" s="64" t="str">
+      <c r="C601" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C602" s="64" t="str">
+      <c r="C602" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C603" s="64" t="str">
+      <c r="C603" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C604" s="64" t="str">
+      <c r="C604" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C605" s="64" t="str">
+      <c r="C605" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C606" s="64" t="str">
+      <c r="C606" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C607" s="64" t="str">
+      <c r="C607" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C608" s="64" t="str">
+      <c r="C608" s="59" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C609" s="64" t="str">
+      <c r="C609" s="59" t="str">
         <f t="shared" ref="C609:C672" si="10">IF(ISBLANK(B609),"",PROPER(TEXT(B609,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="610" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C610" s="64" t="str">
+      <c r="C610" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C611" s="64" t="str">
+      <c r="C611" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C612" s="64" t="str">
+      <c r="C612" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C613" s="64" t="str">
+      <c r="C613" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C614" s="64" t="str">
+      <c r="C614" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C615" s="64" t="str">
+      <c r="C615" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C616" s="64" t="str">
+      <c r="C616" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C617" s="64" t="str">
+      <c r="C617" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C618" s="64" t="str">
+      <c r="C618" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C619" s="64" t="str">
+      <c r="C619" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C620" s="64" t="str">
+      <c r="C620" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C621" s="64" t="str">
+      <c r="C621" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C622" s="64" t="str">
+      <c r="C622" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C623" s="64" t="str">
+      <c r="C623" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C624" s="64" t="str">
+      <c r="C624" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C625" s="64" t="str">
+      <c r="C625" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C626" s="64" t="str">
+      <c r="C626" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C627" s="64" t="str">
+      <c r="C627" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C628" s="64" t="str">
+      <c r="C628" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C629" s="64" t="str">
+      <c r="C629" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C630" s="64" t="str">
+      <c r="C630" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C631" s="64" t="str">
+      <c r="C631" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C632" s="64" t="str">
+      <c r="C632" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C633" s="64" t="str">
+      <c r="C633" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C634" s="64" t="str">
+      <c r="C634" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C635" s="64" t="str">
+      <c r="C635" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C636" s="64" t="str">
+      <c r="C636" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C637" s="64" t="str">
+      <c r="C637" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C638" s="64" t="str">
+      <c r="C638" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C639" s="64" t="str">
+      <c r="C639" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C640" s="64" t="str">
+      <c r="C640" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C641" s="64" t="str">
+      <c r="C641" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C642" s="64" t="str">
+      <c r="C642" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C643" s="64" t="str">
+      <c r="C643" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C644" s="64" t="str">
+      <c r="C644" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C645" s="64" t="str">
+      <c r="C645" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C646" s="64" t="str">
+      <c r="C646" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C647" s="64" t="str">
+      <c r="C647" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C648" s="64" t="str">
+      <c r="C648" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C649" s="64" t="str">
+      <c r="C649" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C650" s="64" t="str">
+      <c r="C650" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C651" s="64" t="str">
+      <c r="C651" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C652" s="64" t="str">
+      <c r="C652" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C653" s="64" t="str">
+      <c r="C653" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C654" s="64" t="str">
+      <c r="C654" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C655" s="64" t="str">
+      <c r="C655" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C656" s="64" t="str">
+      <c r="C656" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C657" s="64" t="str">
+      <c r="C657" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C658" s="64" t="str">
+      <c r="C658" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C659" s="64" t="str">
+      <c r="C659" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C660" s="64" t="str">
+      <c r="C660" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C661" s="64" t="str">
+      <c r="C661" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C662" s="64" t="str">
+      <c r="C662" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C663" s="64" t="str">
+      <c r="C663" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C664" s="64" t="str">
+      <c r="C664" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C665" s="64" t="str">
+      <c r="C665" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C666" s="64" t="str">
+      <c r="C666" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C667" s="64" t="str">
+      <c r="C667" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C668" s="64" t="str">
+      <c r="C668" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C669" s="64" t="str">
+      <c r="C669" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C670" s="64" t="str">
+      <c r="C670" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C671" s="64" t="str">
+      <c r="C671" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C672" s="64" t="str">
+      <c r="C672" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C673" s="64" t="str">
+      <c r="C673" s="59" t="str">
         <f t="shared" ref="C673:C736" si="11">IF(ISBLANK(B673),"",PROPER(TEXT(B673,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="674" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C674" s="64" t="str">
+      <c r="C674" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C675" s="64" t="str">
+      <c r="C675" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C676" s="64" t="str">
+      <c r="C676" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C677" s="64" t="str">
+      <c r="C677" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C678" s="64" t="str">
+      <c r="C678" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C679" s="64" t="str">
+      <c r="C679" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C680" s="64" t="str">
+      <c r="C680" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C681" s="64" t="str">
+      <c r="C681" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C682" s="64" t="str">
+      <c r="C682" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C683" s="64" t="str">
+      <c r="C683" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C684" s="64" t="str">
+      <c r="C684" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C685" s="64" t="str">
+      <c r="C685" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="686" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C686" s="64" t="str">
+      <c r="C686" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="687" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C687" s="64" t="str">
+      <c r="C687" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="688" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C688" s="64" t="str">
+      <c r="C688" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="689" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C689" s="64" t="str">
+      <c r="C689" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="690" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C690" s="64" t="str">
+      <c r="C690" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="691" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C691" s="64" t="str">
+      <c r="C691" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="692" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C692" s="64" t="str">
+      <c r="C692" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="693" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C693" s="64" t="str">
+      <c r="C693" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="694" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C694" s="64" t="str">
+      <c r="C694" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="695" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C695" s="64" t="str">
+      <c r="C695" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="696" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C696" s="64" t="str">
+      <c r="C696" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="697" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C697" s="64" t="str">
+      <c r="C697" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="698" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C698" s="64" t="str">
+      <c r="C698" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="699" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C699" s="64" t="str">
+      <c r="C699" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="700" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C700" s="64" t="str">
+      <c r="C700" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="701" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C701" s="64" t="str">
+      <c r="C701" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="702" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C702" s="64" t="str">
+      <c r="C702" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="703" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C703" s="64" t="str">
+      <c r="C703" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="704" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C704" s="64" t="str">
+      <c r="C704" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="705" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C705" s="64" t="str">
+      <c r="C705" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="706" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C706" s="64" t="str">
+      <c r="C706" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="707" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C707" s="64" t="str">
+      <c r="C707" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="708" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C708" s="64" t="str">
+      <c r="C708" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="709" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C709" s="64" t="str">
+      <c r="C709" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="710" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C710" s="64" t="str">
+      <c r="C710" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="711" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C711" s="64" t="str">
+      <c r="C711" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="712" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C712" s="64" t="str">
+      <c r="C712" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="713" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C713" s="64" t="str">
+      <c r="C713" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="714" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C714" s="64" t="str">
+      <c r="C714" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="715" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C715" s="64" t="str">
+      <c r="C715" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="716" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C716" s="64" t="str">
+      <c r="C716" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="717" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C717" s="64" t="str">
+      <c r="C717" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="718" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C718" s="64" t="str">
+      <c r="C718" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="719" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C719" s="64" t="str">
+      <c r="C719" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="720" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C720" s="64" t="str">
+      <c r="C720" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="721" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C721" s="64" t="str">
+      <c r="C721" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="722" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C722" s="64" t="str">
+      <c r="C722" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="723" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C723" s="64" t="str">
+      <c r="C723" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="724" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C724" s="64" t="str">
+      <c r="C724" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="725" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C725" s="64" t="str">
+      <c r="C725" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="726" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C726" s="64" t="str">
+      <c r="C726" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="727" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C727" s="64" t="str">
+      <c r="C727" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="728" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C728" s="64" t="str">
+      <c r="C728" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="729" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C729" s="64" t="str">
+      <c r="C729" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="730" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C730" s="64" t="str">
+      <c r="C730" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="731" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C731" s="64" t="str">
+      <c r="C731" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="732" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C732" s="64" t="str">
+      <c r="C732" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="733" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C733" s="64" t="str">
+      <c r="C733" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="734" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C734" s="64" t="str">
+      <c r="C734" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="735" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C735" s="64" t="str">
+      <c r="C735" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="736" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C736" s="64" t="str">
+      <c r="C736" s="59" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="737" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C737" s="64" t="str">
+      <c r="C737" s="59" t="str">
         <f t="shared" ref="C737:C785" si="12">IF(ISBLANK(B737),"",PROPER(TEXT(B737,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="738" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C738" s="64" t="str">
+      <c r="C738" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="739" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C739" s="64" t="str">
+      <c r="C739" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="740" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C740" s="64" t="str">
+      <c r="C740" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="741" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C741" s="64" t="str">
+      <c r="C741" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="742" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C742" s="64" t="str">
+      <c r="C742" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="743" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C743" s="64" t="str">
+      <c r="C743" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="744" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C744" s="64" t="str">
+      <c r="C744" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="745" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C745" s="64" t="str">
+      <c r="C745" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="746" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C746" s="64" t="str">
+      <c r="C746" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="747" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C747" s="64" t="str">
+      <c r="C747" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="748" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C748" s="64" t="str">
+      <c r="C748" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="749" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C749" s="64" t="str">
+      <c r="C749" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="750" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C750" s="64" t="str">
+      <c r="C750" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="751" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C751" s="64" t="str">
+      <c r="C751" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="752" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C752" s="64" t="str">
+      <c r="C752" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="753" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C753" s="64" t="str">
+      <c r="C753" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="754" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C754" s="64" t="str">
+      <c r="C754" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="755" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C755" s="64" t="str">
+      <c r="C755" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="756" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C756" s="64" t="str">
+      <c r="C756" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="757" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C757" s="64" t="str">
+      <c r="C757" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="758" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C758" s="64" t="str">
+      <c r="C758" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="759" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C759" s="64" t="str">
+      <c r="C759" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="760" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C760" s="64" t="str">
+      <c r="C760" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="761" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C761" s="64" t="str">
+      <c r="C761" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="762" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C762" s="64" t="str">
+      <c r="C762" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="763" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C763" s="64" t="str">
+      <c r="C763" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="764" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C764" s="64" t="str">
+      <c r="C764" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="765" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C765" s="64" t="str">
+      <c r="C765" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="766" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C766" s="64" t="str">
+      <c r="C766" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="767" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C767" s="64" t="str">
+      <c r="C767" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="768" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C768" s="64" t="str">
+      <c r="C768" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="769" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C769" s="64" t="str">
+      <c r="C769" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="770" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C770" s="64" t="str">
+      <c r="C770" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="771" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C771" s="64" t="str">
+      <c r="C771" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="772" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C772" s="64" t="str">
+      <c r="C772" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="773" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C773" s="64" t="str">
+      <c r="C773" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="774" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C774" s="64" t="str">
+      <c r="C774" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="775" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C775" s="64" t="str">
+      <c r="C775" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="776" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C776" s="64" t="str">
+      <c r="C776" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="777" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C777" s="64" t="str">
+      <c r="C777" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="778" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C778" s="64" t="str">
+      <c r="C778" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="779" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C779" s="64" t="str">
+      <c r="C779" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="780" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C780" s="64" t="str">
+      <c r="C780" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="781" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C781" s="64" t="str">
+      <c r="C781" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="782" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C782" s="64" t="str">
+      <c r="C782" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="783" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C783" s="64" t="str">
+      <c r="C783" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="784" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C784" s="64" t="str">
+      <c r="C784" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C785" s="64" t="str">
+      <c r="C785" s="59" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
@@ -13327,683 +13328,683 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="str" cm="1">
+      <c r="B2" s="80" t="str" cm="1">
         <f t="array" ref="B2:M2">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="C2" s="48" t="str">
+      <c r="C2" s="80" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="D2" s="48" t="str">
+      <c r="D2" s="80" t="str">
         <v>Março</v>
       </c>
-      <c r="E2" s="48" t="str">
+      <c r="E2" s="80" t="str">
         <v>Abril</v>
       </c>
-      <c r="F2" s="48" t="str">
+      <c r="F2" s="80" t="str">
         <v>Maio</v>
       </c>
-      <c r="G2" s="48" t="str">
+      <c r="G2" s="80" t="str">
         <v>Junho</v>
       </c>
-      <c r="H2" s="48" t="str">
+      <c r="H2" s="80" t="str">
         <v>Julho</v>
       </c>
-      <c r="I2" s="48" t="str">
+      <c r="I2" s="80" t="str">
         <v>Agosto</v>
       </c>
-      <c r="J2" s="48" t="str">
+      <c r="J2" s="80" t="str">
         <v>Setembro</v>
       </c>
-      <c r="K2" s="48" t="str">
+      <c r="K2" s="80" t="str">
         <v>Outubro</v>
       </c>
-      <c r="L2" s="48" t="str">
+      <c r="L2" s="80" t="str">
         <v>Novembro</v>
       </c>
-      <c r="M2" s="48" t="str">
+      <c r="M2" s="80" t="str">
         <v>Dezembro</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="str" cm="1">
+    <row r="3" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="46" t="str" cm="1">
         <f t="array" ref="A3:A14">Receita_Líquida</f>
         <v>Salário</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A3)</f>
         <v>150</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="str">
+    <row r="4" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="46" t="str">
         <v>Vendas</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A4)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="str">
+    <row r="5" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="46" t="str">
         <v>Aluguel</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="str">
+    <row r="6" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="46" t="str">
         <v>Rendimentos</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A6)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="str">
+    <row r="7" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="46" t="str">
         <v>Receitas Outros</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A7)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="str">
+    <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="46" t="str">
         <v>Inss</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="str">
+    <row r="9" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="46" t="str">
         <v>T. Transporte</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="str">
+    <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="46" t="str">
         <v>Taxa</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="str">
+    <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="46" t="str">
         <v>Imposto de Renda</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="str">
+    <row r="12" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="46" t="str">
         <v>Perdas Outros</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="47" t="str">
+    <row r="13" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="46" t="str">
         <v>CDI</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="str">
+    <row r="14" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="46" t="str">
         <v>Tesouro Direto</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],B$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],C$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],D$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],E$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],F$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],G$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],H$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],I$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],J$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],K$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],L$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],M$2,Tabela1[Categoria],$A14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="81" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="2">
@@ -14056,7 +14057,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="18.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="47" t="str">
+      <c r="A18" s="46" t="str">
         <f>A10</f>
         <v>Taxa</v>
       </c>
@@ -14124,178 +14125,178 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" style="52" customWidth="1"/>
-    <col min="2" max="13" width="15" style="52" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="52" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="52" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.5703125" style="52" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="52"/>
+    <col min="1" max="1" width="17.85546875" style="49" customWidth="1"/>
+    <col min="2" max="13" width="15" style="49" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="49" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="49" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.5703125" style="49" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:13" s="49" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="52"/>
-      <c r="B2" s="48" t="str" cm="1">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:13" s="47" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="49"/>
+      <c r="B2" s="80" t="str" cm="1">
         <f t="array" ref="B2:M2">TRANSPOSE(Meses)</f>
         <v>Janeiro</v>
       </c>
-      <c r="C2" s="48" t="str">
+      <c r="C2" s="80" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="D2" s="48" t="str">
+      <c r="D2" s="80" t="str">
         <v>Março</v>
       </c>
-      <c r="E2" s="48" t="str">
+      <c r="E2" s="80" t="str">
         <v>Abril</v>
       </c>
-      <c r="F2" s="48" t="str">
+      <c r="F2" s="80" t="str">
         <v>Maio</v>
       </c>
-      <c r="G2" s="48" t="str">
+      <c r="G2" s="80" t="str">
         <v>Junho</v>
       </c>
-      <c r="H2" s="48" t="str">
+      <c r="H2" s="80" t="str">
         <v>Julho</v>
       </c>
-      <c r="I2" s="48" t="str">
+      <c r="I2" s="80" t="str">
         <v>Agosto</v>
       </c>
-      <c r="J2" s="48" t="str">
+      <c r="J2" s="80" t="str">
         <v>Setembro</v>
       </c>
-      <c r="K2" s="48" t="str">
+      <c r="K2" s="80" t="str">
         <v>Outubro</v>
       </c>
-      <c r="L2" s="48" t="str">
+      <c r="L2" s="80" t="str">
         <v>Novembro</v>
       </c>
-      <c r="M2" s="48" t="str">
+      <c r="M2" s="80" t="str">
         <v>Dezembro</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="50" customFormat="1" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="78" t="s">
+    <row r="3" spans="1:13" s="48" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="76">
         <f>'Receita Líquida'!B16</f>
         <v>150</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="76">
         <f>'Receita Líquida'!C16</f>
         <v>0</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="76">
         <f>'Receita Líquida'!D16</f>
         <v>0</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="76">
         <f>'Receita Líquida'!E16</f>
         <v>0</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="76">
         <f>'Receita Líquida'!F16</f>
         <v>0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="76">
         <f>'Receita Líquida'!G16</f>
         <v>0</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="76">
         <f>'Receita Líquida'!H16</f>
         <v>0</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="76">
         <f>'Receita Líquida'!I16</f>
         <v>0</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="76">
         <f>'Receita Líquida'!J16</f>
         <v>0</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="76">
         <f>'Receita Líquida'!K16</f>
         <v>0</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="76">
         <f>'Receita Líquida'!L16</f>
         <v>0</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="76">
         <f>'Receita Líquida'!M16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="78" t="s">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="51">
+      <c r="B4" s="77">
         <f>B3-(SUM(B7:B18))</f>
         <v>150</v>
       </c>
-      <c r="C4" s="51">
+      <c r="C4" s="77">
         <f t="shared" ref="C4:L4" si="0">C3-(SUM(C7:C18))+B4</f>
         <v>150</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="77">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="77">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="F4" s="51">
+      <c r="F4" s="77">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="G4" s="51">
+      <c r="G4" s="77">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="H4" s="51">
+      <c r="H4" s="77">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="77">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="J4" s="51">
+      <c r="J4" s="77">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="K4" s="51">
+      <c r="K4" s="77">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="L4" s="51">
+      <c r="L4" s="77">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="M4" s="51">
+      <c r="M4" s="77">
         <f>M3-SUM(M7:M18)+L4</f>
         <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-    </row>
-    <row r="6" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79" t="s">
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="80" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="80" t="s">
@@ -14335,710 +14336,710 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="str" cm="1">
         <f t="array" ref="A7:A18">Despesas</f>
         <v>Alimentação</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A7)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="str">
         <v>Carro</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="str">
         <v>Condomínio</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="str">
         <v>Curso</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="str">
         <v>Eletrônicos</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="str">
         <v>G. Residencial</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="str">
         <v>Jogos/ Livros</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="str">
         <v>Rolê/ Entret.</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A16)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="str">
         <v>Roupas</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A17)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!C$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!D$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!E$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!F$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!G$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!H$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!I$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!J$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!K$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!L$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!M$2,Tabela1[Categoria],'Despesas Gerais'!$A18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-    </row>
-    <row r="20" spans="1:14" s="50" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48" t="s">
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+    </row>
+    <row r="20" spans="1:14" s="48" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="53">
+      <c r="B20" s="50">
         <f t="shared" ref="B20:M20" si="1">SUM(B7:B18)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="53">
+      <c r="C20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="53">
+      <c r="H20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="53">
+      <c r="I20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="53">
+      <c r="J20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="53">
+      <c r="K20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="53">
+      <c r="L20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="53">
+      <c r="M20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="54"/>
+      <c r="N20" s="51"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:A17">
@@ -15052,15 +15053,6 @@
       <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
     </customSheetView>
   </customSheetViews>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="iconSet" priority="1">
-      <iconSet>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="200"/>
-        <cfvo type="num" val="350"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N4:XFD4">
     <cfRule type="iconSet" priority="14">
       <iconSet>
@@ -15080,231 +15072,231 @@
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="60" customWidth="1"/>
-    <col min="2" max="3" width="17.140625" style="60" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="60" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="60" customWidth="1"/>
-    <col min="9" max="10" width="17.140625" style="60" customWidth="1"/>
-    <col min="11" max="13" width="9.140625" style="60"/>
-    <col min="14" max="14" width="7.140625" style="60" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="60"/>
+    <col min="1" max="1" width="8.5703125" style="55" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" style="55" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" style="55" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="55" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="55" customWidth="1"/>
+    <col min="9" max="10" width="17.140625" style="55" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="55"/>
+    <col min="14" max="14" width="7.140625" style="55" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="55"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="44" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="59">
+      <c r="C3" s="79">
         <f>SUM(C6:C17)</f>
         <v>150</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="59">
+      <c r="J3" s="79">
         <f>SUM(J6:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="60" t="s">
+      <c r="B5" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5" s="61" t="s">
+      <c r="I5" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="56" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="60" t="str" cm="1">
+      <c r="B6" s="55" t="str" cm="1">
         <f t="array" ref="B6:B17">Meses</f>
         <v>Janeiro</v>
       </c>
-      <c r="C6" s="61" cm="1">
+      <c r="C6" s="56" cm="1">
         <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Receita Líquida'!B3:M14,Receita_Líquida='Gráfico Categorias'!C2))</f>
         <v>150</v>
       </c>
-      <c r="I6" s="60" t="str" cm="1">
+      <c r="I6" s="55" t="str" cm="1">
         <f t="array" ref="I6:I17">Meses</f>
         <v>Janeiro</v>
       </c>
-      <c r="J6" s="61" cm="1">
+      <c r="J6" s="56" cm="1">
         <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER('Despesas Gerais'!B7:M18,Despesas='Gráfico Categorias'!J2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="60" t="str">
+      <c r="B7" s="55" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="C7" s="61">
-        <v>0</v>
-      </c>
-      <c r="I7" s="60" t="str">
+      <c r="C7" s="56">
+        <v>0</v>
+      </c>
+      <c r="I7" s="55" t="str">
         <v>Fevereiro</v>
       </c>
-      <c r="J7" s="61">
+      <c r="J7" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="60" t="str">
+      <c r="B8" s="55" t="str">
         <v>Março</v>
       </c>
-      <c r="C8" s="61">
-        <v>0</v>
-      </c>
-      <c r="I8" s="60" t="str">
+      <c r="C8" s="56">
+        <v>0</v>
+      </c>
+      <c r="I8" s="55" t="str">
         <v>Março</v>
       </c>
-      <c r="J8" s="61">
+      <c r="J8" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="60" t="str">
+      <c r="B9" s="55" t="str">
         <v>Abril</v>
       </c>
-      <c r="C9" s="61">
-        <v>0</v>
-      </c>
-      <c r="I9" s="60" t="str">
+      <c r="C9" s="56">
+        <v>0</v>
+      </c>
+      <c r="I9" s="55" t="str">
         <v>Abril</v>
       </c>
-      <c r="J9" s="61">
+      <c r="J9" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="60" t="str">
+      <c r="B10" s="55" t="str">
         <v>Maio</v>
       </c>
-      <c r="C10" s="61">
-        <v>0</v>
-      </c>
-      <c r="I10" s="60" t="str">
+      <c r="C10" s="56">
+        <v>0</v>
+      </c>
+      <c r="I10" s="55" t="str">
         <v>Maio</v>
       </c>
-      <c r="J10" s="61">
+      <c r="J10" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="60" t="str">
+      <c r="B11" s="55" t="str">
         <v>Junho</v>
       </c>
-      <c r="C11" s="61">
-        <v>0</v>
-      </c>
-      <c r="I11" s="60" t="str">
+      <c r="C11" s="56">
+        <v>0</v>
+      </c>
+      <c r="I11" s="55" t="str">
         <v>Junho</v>
       </c>
-      <c r="J11" s="61">
+      <c r="J11" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="60" t="str">
+      <c r="B12" s="55" t="str">
         <v>Julho</v>
       </c>
-      <c r="C12" s="61">
-        <v>0</v>
-      </c>
-      <c r="I12" s="60" t="str">
+      <c r="C12" s="56">
+        <v>0</v>
+      </c>
+      <c r="I12" s="55" t="str">
         <v>Julho</v>
       </c>
-      <c r="J12" s="61">
+      <c r="J12" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="60" t="str">
+      <c r="B13" s="55" t="str">
         <v>Agosto</v>
       </c>
-      <c r="C13" s="61">
-        <v>0</v>
-      </c>
-      <c r="I13" s="60" t="str">
+      <c r="C13" s="56">
+        <v>0</v>
+      </c>
+      <c r="I13" s="55" t="str">
         <v>Agosto</v>
       </c>
-      <c r="J13" s="61">
+      <c r="J13" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="60" t="str">
+      <c r="B14" s="55" t="str">
         <v>Setembro</v>
       </c>
-      <c r="C14" s="61">
-        <v>0</v>
-      </c>
-      <c r="I14" s="60" t="str">
+      <c r="C14" s="56">
+        <v>0</v>
+      </c>
+      <c r="I14" s="55" t="str">
         <v>Setembro</v>
       </c>
-      <c r="J14" s="61">
+      <c r="J14" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="60" t="str">
+      <c r="B15" s="55" t="str">
         <v>Outubro</v>
       </c>
-      <c r="C15" s="61">
-        <v>0</v>
-      </c>
-      <c r="I15" s="60" t="str">
+      <c r="C15" s="56">
+        <v>0</v>
+      </c>
+      <c r="I15" s="55" t="str">
         <v>Outubro</v>
       </c>
-      <c r="J15" s="61">
+      <c r="J15" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="60" t="str">
+      <c r="B16" s="55" t="str">
         <v>Novembro</v>
       </c>
-      <c r="C16" s="61">
-        <v>0</v>
-      </c>
-      <c r="I16" s="60" t="str">
+      <c r="C16" s="56">
+        <v>0</v>
+      </c>
+      <c r="I16" s="55" t="str">
         <v>Novembro</v>
       </c>
-      <c r="J16" s="61">
+      <c r="J16" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="60" t="str">
+      <c r="B17" s="55" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="C17" s="61">
-        <v>0</v>
-      </c>
-      <c r="I17" s="60" t="str">
+      <c r="C17" s="56">
+        <v>0</v>
+      </c>
+      <c r="I17" s="55" t="str">
         <v>Dezembro</v>
       </c>
-      <c r="J17" s="61">
+      <c r="J17" s="56">
         <v>0</v>
       </c>
     </row>
@@ -15375,16 +15367,16 @@
         <v>42</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="84" t="s">
+      <c r="K2" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="85"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="84" t="s">
+      <c r="L2" s="83"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="85"/>
-      <c r="P2" s="39"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="str" cm="1">
@@ -15415,7 +15407,7 @@
         <v>150</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="40" t="s">
         <v>14</v>
       </c>
       <c r="L3" s="16">
@@ -15423,15 +15415,15 @@
         <v>150</v>
       </c>
       <c r="M3" s="7"/>
-      <c r="N3" s="43" t="str" cm="1">
+      <c r="N3" s="42" t="str" cm="1">
         <f t="array" ref="N3:N14">Despesas</f>
         <v>Alimentação</v>
       </c>
-      <c r="O3" s="44">
+      <c r="O3" s="43">
         <f>SUM('Despesas Gerais'!B7:M7)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="39"/>
+      <c r="P3" s="38"/>
     </row>
     <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="str">
@@ -15461,7 +15453,7 @@
         <v>150</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="41" t="s">
+      <c r="K4" s="40" t="s">
         <v>10</v>
       </c>
       <c r="L4" s="16">
@@ -15469,14 +15461,14 @@
         <v>0</v>
       </c>
       <c r="M4" s="7"/>
-      <c r="N4" s="43" t="str">
+      <c r="N4" s="42" t="str">
         <v>Carro</v>
       </c>
-      <c r="O4" s="44">
+      <c r="O4" s="43">
         <f>SUM('Despesas Gerais'!B8:M8)</f>
         <v>0</v>
       </c>
-      <c r="P4" s="39"/>
+      <c r="P4" s="38"/>
     </row>
     <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="str">
@@ -15506,7 +15498,7 @@
         <v>150</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="41" t="s">
+      <c r="K5" s="40" t="s">
         <v>16</v>
       </c>
       <c r="L5" s="16">
@@ -15514,14 +15506,14 @@
         <v>150</v>
       </c>
       <c r="M5" s="7"/>
-      <c r="N5" s="43" t="str">
+      <c r="N5" s="42" t="str">
         <v>Condomínio</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="43">
         <f>SUM('Despesas Gerais'!B9:M9)</f>
         <v>0</v>
       </c>
-      <c r="P5" s="39"/>
+      <c r="P5" s="38"/>
     </row>
     <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="str">
@@ -15551,7 +15543,7 @@
         <v>150</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="41" t="s">
+      <c r="K6" s="40" t="s">
         <v>23</v>
       </c>
       <c r="L6" s="16">
@@ -15559,14 +15551,14 @@
         <v>0</v>
       </c>
       <c r="M6" s="7"/>
-      <c r="N6" s="43" t="str">
+      <c r="N6" s="42" t="str">
         <v>Curso</v>
       </c>
-      <c r="O6" s="44">
+      <c r="O6" s="43">
         <f>SUM('Despesas Gerais'!B10:M10)</f>
         <v>0</v>
       </c>
-      <c r="P6" s="39"/>
+      <c r="P6" s="38"/>
     </row>
     <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="str">
@@ -15596,7 +15588,7 @@
         <v>150</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="40" t="s">
         <v>18</v>
       </c>
       <c r="L7" s="16">
@@ -15604,14 +15596,14 @@
         <v>0</v>
       </c>
       <c r="M7" s="7"/>
-      <c r="N7" s="43" t="str">
+      <c r="N7" s="42" t="str">
         <v>Eletrônicos</v>
       </c>
-      <c r="O7" s="44">
+      <c r="O7" s="43">
         <f>SUM('Despesas Gerais'!B11:M11)</f>
         <v>0</v>
       </c>
-      <c r="P7" s="39"/>
+      <c r="P7" s="38"/>
     </row>
     <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="str">
@@ -15641,7 +15633,7 @@
         <v>150</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="41" t="s">
+      <c r="K8" s="40" t="s">
         <v>22</v>
       </c>
       <c r="L8" s="16">
@@ -15649,14 +15641,14 @@
         <v>0</v>
       </c>
       <c r="M8" s="7"/>
-      <c r="N8" s="43" t="str">
+      <c r="N8" s="42" t="str">
         <v>Farm. e Saúde.</v>
       </c>
-      <c r="O8" s="44">
+      <c r="O8" s="43">
         <f>SUM('Despesas Gerais'!B12:M12)</f>
         <v>0</v>
       </c>
-      <c r="P8" s="39"/>
+      <c r="P8" s="38"/>
     </row>
     <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="str">
@@ -15686,7 +15678,7 @@
         <v>150</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="40" t="s">
         <v>12</v>
       </c>
       <c r="L9" s="18">
@@ -15694,14 +15686,14 @@
         <v>150</v>
       </c>
       <c r="M9" s="8"/>
-      <c r="N9" s="43" t="str">
+      <c r="N9" s="42" t="str">
         <v>G. Residencial</v>
       </c>
-      <c r="O9" s="44">
+      <c r="O9" s="43">
         <f>SUM('Despesas Gerais'!B13:M13)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="39"/>
+      <c r="P9" s="38"/>
     </row>
     <row r="10" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="str">
@@ -15731,7 +15723,7 @@
         <v>150</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="42" t="s">
+      <c r="K10" s="41" t="s">
         <v>9</v>
       </c>
       <c r="L10" s="20">
@@ -15739,14 +15731,14 @@
         <v>0</v>
       </c>
       <c r="M10" s="8"/>
-      <c r="N10" s="43" t="str">
+      <c r="N10" s="42" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="O10" s="44">
+      <c r="O10" s="43">
         <f>SUM('Despesas Gerais'!B14:M14)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="39"/>
+      <c r="P10" s="38"/>
     </row>
     <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="str">
@@ -15779,14 +15771,14 @@
       <c r="K11" s="3"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
-      <c r="N11" s="41" t="str">
+      <c r="N11" s="40" t="str">
         <v>Jogos/ Livros</v>
       </c>
-      <c r="O11" s="44">
+      <c r="O11" s="43">
         <f>SUM('Despesas Gerais'!B15:M15)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="39"/>
+      <c r="P11" s="38"/>
     </row>
     <row r="12" spans="1:16" ht="15.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="str">
@@ -15816,17 +15808,17 @@
         <v>150</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="55" t="str">
+      <c r="K12" s="38"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="52" t="str">
         <v>Rolê/ Entret.</v>
       </c>
-      <c r="O12" s="44">
+      <c r="O12" s="43">
         <f>SUM('Despesas Gerais'!B16:M16)</f>
         <v>0</v>
       </c>
-      <c r="P12" s="40"/>
+      <c r="P12" s="39"/>
     </row>
     <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="str">
@@ -15856,17 +15848,17 @@
         <v>150</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="55" t="str">
+      <c r="K13" s="38"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="52" t="str">
         <v>Roupas</v>
       </c>
-      <c r="O13" s="44">
+      <c r="O13" s="43">
         <f>SUM('Despesas Gerais'!B17:M17)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="40"/>
+      <c r="P13" s="39"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="str">
@@ -15896,17 +15888,17 @@
         <v>150</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="56" t="str">
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="53" t="str">
         <v>G. Gerais</v>
       </c>
-      <c r="O14" s="57">
+      <c r="O14" s="54">
         <f>SUM('Despesas Gerais'!B18:M18)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="39"/>
+      <c r="P14" s="38"/>
     </row>
     <row r="15" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
@@ -15935,12 +15927,12 @@
         <v>150</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
     </row>
     <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -15964,12 +15956,12 @@
       <c r="H16" s="5"/>
       <c r="I16" s="10"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
     </row>
     <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
@@ -15993,12 +15985,12 @@
       <c r="H17" s="7"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="39"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
     </row>
     <row r="18" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
@@ -16022,12 +16014,12 @@
       <c r="H18" s="5"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
     </row>
     <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
@@ -16040,48 +16032,48 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="39"/>
-      <c r="P19" s="39"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="39"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="39"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="39"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="39"/>
-      <c r="P21" s="39"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
     </row>
     <row r="26" spans="1:16" ht="14.3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:16" ht="8.5500000000000007" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A54C0F2-A0A5-48C0-82A4-474FECB34395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C269ED6-8162-483B-8B49-9C9F06CD655F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Validação de Dados" sheetId="15" r:id="rId1"/>
     <sheet name="Saldo &amp; Mov." sheetId="12" r:id="rId2"/>
-    <sheet name="Receita Líquida" sheetId="8" r:id="rId3"/>
-    <sheet name="Despesas Gerais" sheetId="1" r:id="rId4"/>
-    <sheet name="Gráfico Categorias" sheetId="14" r:id="rId5"/>
+    <sheet name="Receita Líquida" sheetId="8" state="hidden" r:id="rId3"/>
+    <sheet name="Despesas Gerais" sheetId="1" state="hidden" r:id="rId4"/>
+    <sheet name="Gráfico Categorias" sheetId="14" state="hidden" r:id="rId5"/>
     <sheet name="Gráfico Anual" sheetId="13" r:id="rId6"/>
   </sheets>
   <definedNames>
@@ -806,14 +806,14 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -14175,7 +14175,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" s="48" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="82" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="76">
@@ -14228,7 +14228,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="82" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="77">
@@ -15367,15 +15367,15 @@
         <v>42</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="82" t="s">
+      <c r="K2" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="83"/>
+      <c r="L2" s="84"/>
       <c r="M2" s="37"/>
-      <c r="N2" s="82" t="s">
+      <c r="N2" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="83"/>
+      <c r="O2" s="84"/>
       <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF3BD6B-CC85-4E6A-9921-31AE8957C48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECF5E8A-ACE0-4A34-BE3A-98D39D10FE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,12 @@
     <sheet name="Receita Líquida" sheetId="8" state="hidden" r:id="rId3"/>
     <sheet name="Despesas Gerais" sheetId="1" state="hidden" r:id="rId4"/>
     <sheet name="Gráfico Categorias" sheetId="14" state="hidden" r:id="rId5"/>
-    <sheet name="Gráfico Anual" sheetId="13" r:id="rId6"/>
+    <sheet name="Objetivos" sheetId="16" state="hidden" r:id="rId6"/>
+    <sheet name="Gráfico Anual" sheetId="13" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Contas">'Validação de Dados'!$B$5:$B$8</definedName>
     <definedName name="Dash">'Gráfico Anual'!$A$1:$P$26</definedName>
@@ -75,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="88">
   <si>
     <t>Mês</t>
   </si>
@@ -321,6 +325,24 @@
   </si>
   <si>
     <t>Conta</t>
+  </si>
+  <si>
+    <t>Iphone</t>
+  </si>
+  <si>
+    <t>Console PS5</t>
+  </si>
+  <si>
+    <t>*Faça alterações nos objetivos e em seus valores como preferir.</t>
+  </si>
+  <si>
+    <t>Objetivo</t>
+  </si>
+  <si>
+    <t>Progresso</t>
+  </si>
+  <si>
+    <t>Viagem</t>
   </si>
 </sst>
 </file>
@@ -615,7 +637,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -809,6 +831,13 @@
     <xf numFmtId="44" fontId="4" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -9173,6 +9202,40 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Data Validation"/>
+      <sheetName val="Balance &amp; Tracking"/>
+      <sheetName val="Net Salary"/>
+      <sheetName val="Expenses"/>
+      <sheetName val="Graphic Categories"/>
+      <sheetName val="Goals"/>
+      <sheetName val="Graphic Annual"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="12">
+          <cell r="C12">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{739BA625-5E32-4F47-8323-C47308DEF24A}" name="Tabela1" displayName="Tabela1" ref="B16:H20" insertRowShift="1" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="B16:H20" xr:uid="{739BA625-5E32-4F47-8323-C47308DEF24A}"/>
@@ -15321,6 +15384,233 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64D7343-0B79-46A5-8FCF-1D91A6E6BF30}">
+  <dimension ref="C2:I16"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="3.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
+    <col min="4" max="6" width="17.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="9" width="14.28515625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C2" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9" ht="15" x14ac:dyDescent="0.3">
+      <c r="D4" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="44" t="str">
+        <f>'Saldo &amp; Mov.'!B12</f>
+        <v>Poupança</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D5" s="74" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="85">
+        <v>4000</v>
+      </c>
+      <c r="F5" s="83">
+        <f t="shared" ref="F5:F16" ca="1" si="0">$I$5/E5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="85">
+        <f ca="1">'[1]Balance &amp; Tracking'!C12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D6" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="85">
+        <v>4500</v>
+      </c>
+      <c r="F6" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D7" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="85">
+        <v>30000</v>
+      </c>
+      <c r="F7" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D8" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="85">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D9" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="85">
+        <v>1</v>
+      </c>
+      <c r="F9" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D10" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="85">
+        <v>1</v>
+      </c>
+      <c r="F10" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D11" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="85">
+        <v>1</v>
+      </c>
+      <c r="F11" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D12" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="85">
+        <v>1</v>
+      </c>
+      <c r="F12" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D13" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="85">
+        <v>1</v>
+      </c>
+      <c r="F13" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D14" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="85">
+        <v>1</v>
+      </c>
+      <c r="F14" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D15" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="85">
+        <v>1</v>
+      </c>
+      <c r="F15" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D16" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="85">
+        <v>1</v>
+      </c>
+      <c r="F16" s="83">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F5:F16">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{05B70BAD-B629-4120-AE30-6272C3F126ED}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{05B70BAD-B629-4120-AE30-6272C3F126ED}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F5:F16</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD330F4-3FAE-447F-BF05-82EFBCBD7BD0}">
   <sheetPr codeName="Planilha6">
     <tabColor theme="1"/>
@@ -15373,15 +15663,15 @@
         <v>41</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="83" t="s">
+      <c r="K2" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="84"/>
+      <c r="L2" s="87"/>
       <c r="M2" s="37"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="84"/>
+      <c r="O2" s="87"/>
       <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C269ED6-8162-483B-8B49-9C9F06CD655F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF3BD6B-CC85-4E6A-9921-31AE8957C48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Gráfico Anual" sheetId="13" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="Ativos">'Validação de Dados'!$B$5:$B$7</definedName>
+    <definedName name="Contas">'Validação de Dados'!$B$5:$B$8</definedName>
     <definedName name="Dash">'Gráfico Anual'!$A$1:$P$26</definedName>
     <definedName name="Despesas">'Validação de Dados'!$D$5:$D$16</definedName>
     <definedName name="Investimentos">'Validação de Dados'!$F$5:$F$6</definedName>
@@ -29,7 +29,7 @@
     <definedName name="Perdas">'Validação de Dados'!$H$5:$H$9</definedName>
     <definedName name="Receita_Líquida">'Validação de Dados'!$N$5:$N$16</definedName>
     <definedName name="Receitas">'Validação de Dados'!$J$5:$J$9</definedName>
-    <definedName name="Transferir">'Validação de Dados'!$L$5:$L$7</definedName>
+    <definedName name="Transferir">'Validação de Dados'!$L$5:$L$8</definedName>
     <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="3" hidden="1">'Despesas Gerais'!$6:$6,'Despesas Gerais'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -191,9 +191,6 @@
     <t>Inss</t>
   </si>
   <si>
-    <t>Alocação</t>
-  </si>
-  <si>
     <t>Operação</t>
   </si>
   <si>
@@ -207,9 +204,6 @@
   </si>
   <si>
     <t>Sld. Anual</t>
-  </si>
-  <si>
-    <t>Sld. Real</t>
   </si>
   <si>
     <t>Diferença</t>
@@ -275,9 +269,6 @@
     <t>Desp./ Receitas</t>
   </si>
   <si>
-    <t>Ativos</t>
-  </si>
-  <si>
     <t>Meses</t>
   </si>
   <si>
@@ -321,6 +312,15 @@
   </si>
   <si>
     <t>*Faça alterações nos valores em azul como preferir, porém para adicionar ou remover valores será necessário alterar a planilha onde for preciso.</t>
+  </si>
+  <si>
+    <t>Contas</t>
+  </si>
+  <si>
+    <t>Poupança</t>
+  </si>
+  <si>
+    <t>Conta</t>
   </si>
 </sst>
 </file>
@@ -9186,7 +9186,7 @@
     </tableColumn>
     <tableColumn id="6" xr3:uid="{23818CCC-08C7-4066-9B86-98D831460C75}" name="Operação" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{78815540-1C3C-4370-A3E4-1C8E033CFC39}" name="Categoria" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{F153B94E-6C60-4C63-A86C-8519A94E1F13}" name="Alocação" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{F153B94E-6C60-4C63-A86C-8519A94E1F13}" name="Conta" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{EE54C9A2-2D53-4D6A-93DF-88B691A8C3D9}" name="Valor" dataDxfId="3" dataCellStyle="Moeda"/>
     <tableColumn id="5" xr3:uid="{28149A80-D409-4A63-B4C2-6EDA92C21F54}" name="Descrição" dataDxfId="2"/>
   </tableColumns>
@@ -9508,12 +9508,12 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="15" x14ac:dyDescent="0.3">
       <c r="B4" s="44" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>1</v>
@@ -9522,19 +9522,19 @@
         <v>3</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>16</v>
       </c>
       <c r="P4" s="44" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
@@ -9545,7 +9545,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="74" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H5" s="74" t="s">
         <v>37</v>
@@ -9554,7 +9554,7 @@
         <v>26</v>
       </c>
       <c r="L5" s="75" t="str" cm="1">
-        <f t="array" ref="L5:L7">Ativos</f>
+        <f t="array" ref="L5:L8">Contas</f>
         <v>Banco 1</v>
       </c>
       <c r="N5" s="75" t="str" cm="1">
@@ -9562,7 +9562,7 @@
         <v>Salário</v>
       </c>
       <c r="P5" s="75" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
@@ -9570,13 +9570,13 @@
         <v>31</v>
       </c>
       <c r="D6" s="74" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F6" s="74" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H6" s="74" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J6" s="74" t="s">
         <v>36</v>
@@ -9588,7 +9588,7 @@
         <v>Vendas</v>
       </c>
       <c r="P6" s="75" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
@@ -9596,13 +9596,13 @@
         <v>27</v>
       </c>
       <c r="D7" s="74" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H7" s="74" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J7" s="74" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L7" s="75" t="str">
         <v>Carteira</v>
@@ -9611,41 +9611,47 @@
         <v>Aluguel</v>
       </c>
       <c r="P7" s="75" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" s="74" t="s">
+        <v>80</v>
+      </c>
       <c r="D8" s="74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H8" s="74" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J8" s="74" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="L8" s="75" t="str">
+        <v>Poupança</v>
       </c>
       <c r="N8" s="75" t="str">
         <v>Rendimentos</v>
       </c>
       <c r="P8" s="75" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D9" s="74" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H9" s="74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="74" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N9" s="75" t="str">
         <v>Receitas Outros</v>
       </c>
       <c r="P9" s="75" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
@@ -9657,51 +9663,51 @@
         <v>Inss</v>
       </c>
       <c r="P10" s="75" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D11" s="74" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N11" s="75" t="str">
         <v>T. Transporte</v>
       </c>
       <c r="P11" s="75" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D12" s="74" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N12" s="75" t="str">
         <v>Taxa</v>
       </c>
       <c r="P12" s="75" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D13" s="74" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N13" s="75" t="str">
         <v>Imposto de Renda</v>
       </c>
       <c r="P13" s="75" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D14" s="74" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N14" s="75" t="str">
         <v>Perdas Outros</v>
       </c>
       <c r="P14" s="75" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
@@ -9713,7 +9719,7 @@
         <v>CDI</v>
       </c>
       <c r="P15" s="75" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
@@ -9724,7 +9730,7 @@
         <v>Tesouro Direto</v>
       </c>
       <c r="P16" s="75" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -9755,13 +9761,13 @@
     <row r="1" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="44" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="70" t="s">
         <v>25</v>
@@ -9787,7 +9793,7 @@
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="57" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C4" s="73">
         <f>HLOOKUP(B2,'Despesas Gerais'!B2:M20,19,FALSE)/HLOOKUP(B2,'Receita Líquida'!B2:M16,15,FALSE)</f>
@@ -9819,7 +9825,7 @@
     </row>
     <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="26">
         <f>'Gráfico Anual'!I15</f>
@@ -9844,7 +9850,7 @@
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="44" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C8" s="44" t="s">
         <v>2</v>
@@ -9859,11 +9865,11 @@
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="str" cm="1">
-        <f t="array" ref="B9:B11">Ativos</f>
+        <f t="array" ref="B9:B12">Contas</f>
         <v>Banco 1</v>
       </c>
       <c r="C9" s="2" cm="1">
-        <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B9,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B9,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Conta],B9,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Conta],B9,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B9,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>150</v>
       </c>
       <c r="E9" s="69" t="str">
@@ -9880,7 +9886,7 @@
         <v>Banco 2</v>
       </c>
       <c r="C10" s="2" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B10,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B10,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Conta],B10,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Conta],B10,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B10,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
       <c r="E10" s="69" t="str">
@@ -9897,7 +9903,7 @@
         <v>Carteira</v>
       </c>
       <c r="C11" s="2" cm="1">
-        <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Alocação],B11,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B11,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Conta],B11,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Conta],B11,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B11,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
       <c r="E11" s="69" t="str">
@@ -9910,12 +9916,12 @@
     </row>
     <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="59"/>
-      <c r="B12" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="2">
-        <f ca="1">SUM(C9:C11)</f>
-        <v>150</v>
+      <c r="B12" s="27" t="str">
+        <v>Poupança</v>
+      </c>
+      <c r="C12" s="2" cm="1">
+        <f t="array" aca="1" ref="C12" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Conta],B12,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Conta],B12,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B12,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
       </c>
       <c r="E12" s="69" t="str">
         <v>Rolê/ Entret.</v>
@@ -9928,10 +9934,10 @@
     <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="59"/>
       <c r="B13" s="27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" s="26">
-        <f ca="1">ROUND(C5-C12,2)</f>
+        <f ca="1">ROUND(C5-SUM(C9:C12),2)</f>
         <v>0</v>
       </c>
       <c r="E13" s="69" t="str">
@@ -9969,13 +9975,13 @@
         <v>0</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E16" s="30" t="s">
         <v>33</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G16" s="31" t="s">
         <v>25</v>
@@ -9993,7 +9999,7 @@
         <v>Janeiro</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E17" s="34" t="s">
         <v>26</v>
@@ -13275,7 +13281,7 @@
       <formula1>"Receitas, Perdas, Investimentos, Despesas, Transferir"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F257" xr:uid="{0D51CC9B-6F94-4F85-BAFC-26C786BB30BC}">
-      <formula1>Ativos</formula1>
+      <formula1>Contas</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{D9270E47-B020-4CBF-A3A9-E523B28C14E7}">
       <formula1>Meses</formula1>
@@ -15086,7 +15092,7 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="44" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>26</v>
@@ -15364,7 +15370,7 @@
         <v>17</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="83" t="s">

--- a/C. Financeiro.xlsx
+++ b/C. Financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECF5E8A-ACE0-4A34-BE3A-98D39D10FE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B277D6EC-F48E-43C3-B79F-DF5FB0FDB92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,9 +21,6 @@
     <sheet name="Objetivos" sheetId="16" state="hidden" r:id="rId6"/>
     <sheet name="Gráfico Anual" sheetId="13" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Contas">'Validação de Dados'!$B$5:$B$8</definedName>
     <definedName name="Dash">'Gráfico Anual'!$A$1:$P$26</definedName>
@@ -79,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="89">
   <si>
     <t>Mês</t>
   </si>
@@ -321,9 +318,6 @@
     <t>Contas</t>
   </si>
   <si>
-    <t>Poupança</t>
-  </si>
-  <si>
     <t>Conta</t>
   </si>
   <si>
@@ -343,6 +337,12 @@
   </si>
   <si>
     <t>Viagem</t>
+  </si>
+  <si>
+    <t>Transp./ Carro</t>
+  </si>
+  <si>
+    <t>Savings</t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1277,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Carro</c:v>
+                  <c:v>Transp./ Carro</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5018,7 +5018,7 @@
                   <c:v>Alimentação</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Carro</c:v>
+                  <c:v>Transp./ Carro</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Condomínio</c:v>
@@ -9202,40 +9202,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Data Validation"/>
-      <sheetName val="Balance &amp; Tracking"/>
-      <sheetName val="Net Salary"/>
-      <sheetName val="Expenses"/>
-      <sheetName val="Graphic Categories"/>
-      <sheetName val="Goals"/>
-      <sheetName val="Graphic Annual"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="12">
-          <cell r="C12">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{739BA625-5E32-4F47-8323-C47308DEF24A}" name="Tabela1" displayName="Tabela1" ref="B16:H20" insertRowShift="1" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="B16:H20" xr:uid="{739BA625-5E32-4F47-8323-C47308DEF24A}"/>
@@ -9633,7 +9599,7 @@
         <v>31</v>
       </c>
       <c r="D6" s="74" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F6" s="74" t="s">
         <v>51</v>
@@ -9679,7 +9645,7 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="74" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D8" s="74" t="s">
         <v>62</v>
@@ -9691,7 +9657,7 @@
         <v>47</v>
       </c>
       <c r="L8" s="75" t="str">
-        <v>Poupança</v>
+        <v>Savings</v>
       </c>
       <c r="N8" s="75" t="str">
         <v>Rendimentos</v>
@@ -9863,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="69" t="str">
-        <v>Carro</v>
+        <v>Transp./ Carro</v>
       </c>
       <c r="F4" s="70">
         <v>0</v>
@@ -9980,7 +9946,7 @@
     <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="59"/>
       <c r="B12" s="27" t="str">
-        <v>Poupança</v>
+        <v>Savings</v>
       </c>
       <c r="C12" s="2" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">SUM(SUMIFS(Tabela1[Valor],Tabela1[Operação],{"Receitas";"Transferir"},Tabela1[Conta],B12,Tabela1[Data],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Valor],Tabela1[Operação],"&lt;&gt;Receitas",Tabela1[Operação],"&lt;&gt;Transferir",Tabela1[Conta],B12,Tabela1[Data],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Valor],Tabela1[Categoria],B12,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
@@ -10044,7 +10010,7 @@
         <v>33</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G16" s="31" t="s">
         <v>25</v>
@@ -14461,7 +14427,7 @@
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="str">
-        <v>Carro</v>
+        <v>Transp./ Carro</v>
       </c>
       <c r="B8" s="76">
         <f>SUMIFS(Tabela1[Valor],Tabela1[Mês],'Despesas Gerais'!B$2,Tabela1[Categoria],'Despesas Gerais'!$A8)</f>
@@ -15398,30 +15364,30 @@
   <sheetData>
     <row r="2" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="3:9" ht="15" x14ac:dyDescent="0.3">
       <c r="D4" s="44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4" s="44" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I4" s="44" t="str">
         <f>'Saldo &amp; Mov.'!B12</f>
-        <v>Poupança</v>
+        <v>Savings</v>
       </c>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D5" s="74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" s="85">
         <v>4000</v>
@@ -15434,13 +15400,13 @@
         <v>2</v>
       </c>
       <c r="I5" s="85">
-        <f ca="1">'[1]Balance &amp; Tracking'!C12</f>
+        <f ca="1">'Saldo &amp; Mov.'!C12</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D6" s="74" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6" s="85">
         <v>4500</v>
@@ -15464,7 +15430,7 @@
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D8" s="74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" s="85">
         <v>5000</v>
@@ -15476,7 +15442,7 @@
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D9" s="74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9" s="85">
         <v>1</v>
@@ -15488,7 +15454,7 @@
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D10" s="74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" s="85">
         <v>1</v>
@@ -15500,7 +15466,7 @@
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D11" s="74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="85">
         <v>1</v>
@@ -15512,7 +15478,7 @@
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D12" s="74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E12" s="85">
         <v>1</v>
@@ -15524,7 +15490,7 @@
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D13" s="74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E13" s="85">
         <v>1</v>
@@ -15536,7 +15502,7 @@
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D14" s="74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E14" s="85">
         <v>1</v>
@@ -15548,7 +15514,7 @@
     </row>
     <row r="15" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D15" s="74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" s="85">
         <v>1</v>
@@ -15560,7 +15526,7 @@
     </row>
     <row r="16" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D16" s="74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" s="85">
         <v>1</v>
@@ -15758,7 +15724,7 @@
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="42" t="str">
-        <v>Carro</v>
+        <v>Transp./ Carro</v>
       </c>
       <c r="O4" s="43">
         <f>SUM('Despesas Gerais'!B8:M8)</f>
